--- a/tables/N-Retention/Local_perf_matrix_protection_True_vo_False_CUE_True.xlsx
+++ b/tables/N-Retention/Local_perf_matrix_protection_True_vo_False_CUE_True.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -668,10 +668,10 @@
         <v>0.01736455621136393</v>
       </c>
       <c r="K2" t="n">
-        <v>0.2301524983055982</v>
+        <v>0.2301739080636254</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2005144311570493</v>
+        <v>0.2039300344446321</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
@@ -680,16 +680,16 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>4.403789484409526</v>
+        <v>4.404174211659919</v>
       </c>
       <c r="P2" t="n">
-        <v>4.387741933770839</v>
+        <v>4.431424726619325</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9916975456645211</v>
+        <v>0.9919808004389647</v>
       </c>
       <c r="R2" t="n">
-        <v>0.005601014863628516</v>
+        <v>0.005504640840660609</v>
       </c>
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr"/>
@@ -699,38 +699,38 @@
       <c r="X2" t="inlineStr"/>
       <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="n">
-        <v>0.9877870276686941</v>
+        <v>0.9890124723429545</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.008014246293056812</v>
+        <v>0.007601547069301921</v>
       </c>
       <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="n">
-        <v>0.99960582372522</v>
+        <v>0.9996337786634818</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.0001306356269042455</v>
+        <v>0.0001259181153758649</v>
       </c>
       <c r="AE2" t="inlineStr"/>
       <c r="AF2" t="n">
-        <v>0.9968357670248976</v>
+        <v>0.9971302268093319</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.002373441876592581</v>
+        <v>0.00226031080822027</v>
       </c>
       <c r="AH2" t="inlineStr"/>
       <c r="AI2" t="n">
-        <v>0.9590935846471985</v>
+        <v>0.9580123109228823</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.008606264600397755</v>
+        <v>0.008719266839641967</v>
       </c>
       <c r="AK2" t="inlineStr"/>
       <c r="AL2" t="n">
-        <v>0.7284360952633007</v>
+        <v>0.7265464176595912</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.001568176501970735</v>
+        <v>0.001573623121912464</v>
       </c>
       <c r="AN2" t="inlineStr"/>
     </row>
@@ -772,28 +772,28 @@
         <v>0.02342462405894816</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1224260723227339</v>
+        <v>0.124492385839805</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1443557305067127</v>
+        <v>0.5467435544568545</v>
       </c>
       <c r="M3" t="n">
-        <v>0.9897543411726338</v>
+        <v>0.9968569791571076</v>
       </c>
       <c r="N3" t="n">
-        <v>0.9821889463017941</v>
+        <v>0.1623742095056984</v>
       </c>
       <c r="O3" t="n">
-        <v>4.313657841931784</v>
+        <v>4.381960123977297</v>
       </c>
       <c r="P3" t="n">
-        <v>4.319598409484735</v>
+        <v>4.403723974542996</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.9883875370341966</v>
+        <v>0.7784300444341792</v>
       </c>
       <c r="R3" t="n">
-        <v>0.006552875854434134</v>
+        <v>0.02862366263480937</v>
       </c>
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr"/>
@@ -803,38 +803,38 @@
       <c r="X3" t="inlineStr"/>
       <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="n">
-        <v>0.9930582026932395</v>
+        <v>0.9885271892509452</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.005353816799778761</v>
+        <v>0.006882757315669541</v>
       </c>
       <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="n">
-        <v>-1.057186228100415</v>
+        <v>0.9999999439123698</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.003512210996364627</v>
+        <v>5.799323555995009e-07</v>
       </c>
       <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="n">
-        <v>0.9704693266730474</v>
+        <v>-0.6015617472902204</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.008334578440308819</v>
+        <v>0.06137885848485977</v>
       </c>
       <c r="AH3" t="inlineStr"/>
       <c r="AI3" t="n">
-        <v>0.8589432233531175</v>
+        <v>0.9904344700806155</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.009108502631780752</v>
+        <v>0.002371944525827628</v>
       </c>
       <c r="AK3" t="inlineStr"/>
       <c r="AL3" t="n">
-        <v>0.3350202951919334</v>
+        <v>0.8136148218013135</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.003327219982485916</v>
+        <v>0.001761501457408945</v>
       </c>
       <c r="AN3" t="inlineStr"/>
     </row>
@@ -876,10 +876,10 @@
         <v>0.001786449637055907</v>
       </c>
       <c r="K4" t="n">
-        <v>0.4340590818808676</v>
+        <v>0.4194869142069372</v>
       </c>
       <c r="L4" t="n">
-        <v>0.21863588345492</v>
+        <v>0.2274528975208619</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -888,16 +888,16 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>4.446044591924739</v>
+        <v>4.305760231268049</v>
       </c>
       <c r="P4" t="n">
-        <v>4.429130038368242</v>
+        <v>4.56492048676401</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9507489386040096</v>
+        <v>0.9536205709027058</v>
       </c>
       <c r="R4" t="n">
-        <v>0.01451750106244968</v>
+        <v>0.01408791648970575</v>
       </c>
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr"/>
@@ -907,38 +907,38 @@
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="n">
-        <v>0.9740130219477819</v>
+        <v>0.9843416257727393</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.01419434936322385</v>
+        <v>0.01101820718575779</v>
       </c>
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="n">
-        <v>0.9975712974500769</v>
+        <v>0.9985297636860492</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.0006133313654390875</v>
+        <v>0.0004772012615603849</v>
       </c>
       <c r="AE4" t="inlineStr"/>
       <c r="AF4" t="n">
-        <v>0.3222472996386909</v>
+        <v>0.311370323060871</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.02679433766490785</v>
+        <v>0.0270084875804072</v>
       </c>
       <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="n">
-        <v>0.971564414084291</v>
+        <v>0.9653626049956626</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.006994616952202641</v>
+        <v>0.007719789469329707</v>
       </c>
       <c r="AK4" t="inlineStr"/>
       <c r="AL4" t="n">
-        <v>0.4180316614090916</v>
+        <v>0.3931409070958956</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.003865881334803379</v>
+        <v>0.003947687548622647</v>
       </c>
       <c r="AN4" t="inlineStr"/>
     </row>
@@ -980,10 +980,10 @@
         <v>0.03029424940398749</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1851828485504524</v>
+        <v>0.1836362461632683</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2252457456610067</v>
+        <v>0.2221861976845268</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -992,16 +992,16 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>4.338269228295625</v>
+        <v>4.304261075601077</v>
       </c>
       <c r="P5" t="n">
-        <v>4.405479554640058</v>
+        <v>4.346593380071933</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9972630521400654</v>
+        <v>0.9972858912559299</v>
       </c>
       <c r="R5" t="n">
-        <v>0.00309649941187663</v>
+        <v>0.003083552605982152</v>
       </c>
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr"/>
@@ -1011,38 +1011,38 @@
       <c r="X5" t="inlineStr"/>
       <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="n">
-        <v>0.9989910764468314</v>
+        <v>0.9990181939574279</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.00227508047168832</v>
+        <v>0.002244297794327201</v>
       </c>
       <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="n">
-        <v>0.9999990352512182</v>
+        <v>0.9999987889313026</v>
       </c>
       <c r="AD5" t="n">
-        <v>6.052882405823826e-06</v>
+        <v>6.781714563141499e-06</v>
       </c>
       <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="n">
-        <v>0.9965572727515445</v>
+        <v>0.9965148807649968</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.002727505204451293</v>
+        <v>0.002744246380188192</v>
       </c>
       <c r="AH5" t="inlineStr"/>
       <c r="AI5" t="n">
-        <v>0.9715276443903649</v>
+        <v>0.9718307972700237</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.005610287804748234</v>
+        <v>0.005580340751151209</v>
       </c>
       <c r="AK5" t="inlineStr"/>
       <c r="AL5" t="n">
-        <v>0.9698789927789249</v>
+        <v>0.9694536761885827</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.0008092037441299843</v>
+        <v>0.0008148968031710688</v>
       </c>
       <c r="AN5" t="inlineStr"/>
     </row>
@@ -1084,10 +1084,10 @@
         <v>0.01850467691463906</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1720532088902192</v>
+        <v>0.1696932217433799</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2046305371493884</v>
+        <v>0.2020650347272388</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -1096,16 +1096,16 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>4.423356086505447</v>
+        <v>4.366356260172854</v>
       </c>
       <c r="P6" t="n">
-        <v>4.470166621535695</v>
+        <v>4.383108526810537</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.9757577476676973</v>
+        <v>0.9760522040493178</v>
       </c>
       <c r="R6" t="n">
-        <v>0.009412323845029187</v>
+        <v>0.009354986220420594</v>
       </c>
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
@@ -1115,38 +1115,38 @@
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="n">
-        <v>0.9881764256161415</v>
+        <v>0.9891066982890679</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.006272167201850505</v>
+        <v>0.006020367455342996</v>
       </c>
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="n">
-        <v>0.9997048524641727</v>
+        <v>0.9997180682022697</v>
       </c>
       <c r="AD6" t="n">
-        <v>4.588506476126856e-05</v>
+        <v>4.484600886827642e-05</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="n">
-        <v>0.9855618992183912</v>
+        <v>0.986619283507586</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.004928315755080918</v>
+        <v>0.004744420515172544</v>
       </c>
       <c r="AH6" t="inlineStr"/>
       <c r="AI6" t="n">
-        <v>0.6716919430789701</v>
+        <v>0.671840363340845</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.01861468591590341</v>
+        <v>0.01861047781193009</v>
       </c>
       <c r="AK6" t="inlineStr"/>
       <c r="AL6" t="n">
-        <v>0.4070846361481061</v>
+        <v>0.4054523507627874</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.001814462583530041</v>
+        <v>0.001816958458445496</v>
       </c>
       <c r="AN6" t="inlineStr"/>
     </row>
@@ -1188,28 +1188,28 @@
         <v>0.01739226579276497</v>
       </c>
       <c r="K7" t="n">
-        <v>0.2350473166772497</v>
+        <v>0.2323659267012791</v>
       </c>
       <c r="L7" t="n">
-        <v>0.158126000802144</v>
+        <v>0.1610687702225475</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1757241201877778</v>
+        <v>0.1587787932855586</v>
       </c>
       <c r="N7" t="n">
-        <v>0.008117467833909556</v>
+        <v>0.006878207158920089</v>
       </c>
       <c r="O7" t="n">
-        <v>4.322490428799298</v>
+        <v>4.276212554625182</v>
       </c>
       <c r="P7" t="n">
-        <v>4.317907197835608</v>
+        <v>4.38118619031477</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.9890985833123707</v>
+        <v>0.9893248225914084</v>
       </c>
       <c r="R7" t="n">
-        <v>0.006343841824372395</v>
+        <v>0.006277669192354968</v>
       </c>
       <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr"/>
@@ -1219,38 +1219,38 @@
       <c r="X7" t="inlineStr"/>
       <c r="Y7" t="inlineStr"/>
       <c r="Z7" t="n">
-        <v>0.9932205143337886</v>
+        <v>0.9939651095162066</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.006247119434154367</v>
+        <v>0.005894081438597126</v>
       </c>
       <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="n">
-        <v>0.9997121677140152</v>
+        <v>0.9997300330494965</v>
       </c>
       <c r="AD7" t="n">
-        <v>7.319420657709548e-05</v>
+        <v>7.08862911845798e-05</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="n">
-        <v>0.9219444655056189</v>
+        <v>0.9217167669312067</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.01113774282576095</v>
+        <v>0.0111539761484437</v>
       </c>
       <c r="AH7" t="inlineStr"/>
       <c r="AI7" t="n">
-        <v>0.9915925021184728</v>
+        <v>0.991662508479943</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.002414553918835233</v>
+        <v>0.002404480322515972</v>
       </c>
       <c r="AK7" t="inlineStr"/>
       <c r="AL7" t="n">
-        <v>0.3219662347229402</v>
+        <v>0.3192533779469415</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.00434711518137466</v>
+        <v>0.004355803043823402</v>
       </c>
       <c r="AN7" t="inlineStr"/>
     </row>
@@ -1292,28 +1292,28 @@
         <v>0.02806021357785015</v>
       </c>
       <c r="K8" t="n">
-        <v>0.173449561258173</v>
+        <v>0.1752392312349113</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1378948490767878</v>
+        <v>0.1427032566889714</v>
       </c>
       <c r="M8" t="n">
-        <v>0.05876461911297892</v>
+        <v>0.05994424918033647</v>
       </c>
       <c r="N8" t="n">
-        <v>0.001175292382259578</v>
+        <v>0.00122791830761624</v>
       </c>
       <c r="O8" t="n">
-        <v>4.395443563473687</v>
+        <v>4.438028116501265</v>
       </c>
       <c r="P8" t="n">
-        <v>4.279221992550466</v>
+        <v>4.409960664257727</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.9929785322860606</v>
+        <v>0.9930140996926716</v>
       </c>
       <c r="R8" t="n">
-        <v>0.004514210701985874</v>
+        <v>0.004502762766933771</v>
       </c>
       <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr"/>
@@ -1323,38 +1323,38 @@
       <c r="X8" t="inlineStr"/>
       <c r="Y8" t="inlineStr"/>
       <c r="Z8" t="n">
-        <v>0.9935455522909657</v>
+        <v>0.9935263022055555</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.005360868777524634</v>
+        <v>0.005368857094716001</v>
       </c>
       <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="n">
-        <v>0.9999987299279742</v>
+        <v>0.9999989463154563</v>
       </c>
       <c r="AD8" t="n">
-        <v>7.39726662204793e-06</v>
+        <v>6.737711357325079e-06</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="n">
-        <v>0.9864475163044225</v>
+        <v>0.9865032877238399</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.00576458405686615</v>
+        <v>0.005752710569895703</v>
       </c>
       <c r="AH8" t="inlineStr"/>
       <c r="AI8" t="n">
-        <v>0.9815265639004034</v>
+        <v>0.9817669427896122</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.00575513897775114</v>
+        <v>0.005717573044706909</v>
       </c>
       <c r="AK8" t="inlineStr"/>
       <c r="AL8" t="n">
-        <v>0.9994913462402926</v>
+        <v>0.9994683180165039</v>
       </c>
       <c r="AM8" t="n">
-        <v>8.238542062220864e-05</v>
+        <v>8.42296907054606e-05</v>
       </c>
       <c r="AN8" t="inlineStr"/>
     </row>
@@ -1396,28 +1396,28 @@
         <v>0.03857825619785213</v>
       </c>
       <c r="K9" t="n">
-        <v>0.2202316867728543</v>
+        <v>0.2156188681478334</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1626519929985002</v>
+        <v>0.1621272609070696</v>
       </c>
       <c r="M9" t="n">
-        <v>0.08616608872153664</v>
+        <v>0.06820748780767028</v>
       </c>
       <c r="N9" t="n">
-        <v>0.002242299261693099</v>
+        <v>0.001519868857758173</v>
       </c>
       <c r="O9" t="n">
-        <v>4.324191261447337</v>
+        <v>4.239179655326522</v>
       </c>
       <c r="P9" t="n">
-        <v>4.382132646652396</v>
+        <v>4.366687770643157</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.9958465446596954</v>
+        <v>0.9958040343451084</v>
       </c>
       <c r="R9" t="n">
-        <v>0.003485510850828918</v>
+        <v>0.0035033024184256</v>
       </c>
       <c r="S9" t="inlineStr"/>
       <c r="T9" t="inlineStr"/>
@@ -1427,38 +1427,38 @@
       <c r="X9" t="inlineStr"/>
       <c r="Y9" t="inlineStr"/>
       <c r="Z9" t="n">
-        <v>0.9964352323375485</v>
+        <v>0.9964918560559823</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.004309531260129127</v>
+        <v>0.004275167381806169</v>
       </c>
       <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="n">
-        <v>0.999930531310085</v>
+        <v>0.9999320419929165</v>
       </c>
       <c r="AD9" t="n">
-        <v>4.77333974690444e-05</v>
+        <v>4.721153376297057e-05</v>
       </c>
       <c r="AE9" t="inlineStr"/>
       <c r="AF9" t="n">
-        <v>0.9989205827080606</v>
+        <v>0.9989656082412256</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.001329421532628643</v>
+        <v>0.001301399241021734</v>
       </c>
       <c r="AH9" t="inlineStr"/>
       <c r="AI9" t="n">
-        <v>0.9748263108981713</v>
+        <v>0.974169649104024</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.00598652965034819</v>
+        <v>0.006064107040849132</v>
       </c>
       <c r="AK9" t="inlineStr"/>
       <c r="AL9" t="n">
-        <v>0.9857575218362274</v>
+        <v>0.9853657126885048</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.0007175351046333081</v>
+        <v>0.0007273378036397736</v>
       </c>
       <c r="AN9" t="inlineStr"/>
     </row>
@@ -1500,10 +1500,10 @@
         <v>0.033842442806071</v>
       </c>
       <c r="K10" t="n">
-        <v>0.2213013737149055</v>
+        <v>0.2191421967246366</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1197998906553826</v>
+        <v>0.1215020180010192</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -1512,16 +1512,16 @@
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>4.165105484036478</v>
+        <v>4.127028746765415</v>
       </c>
       <c r="P10" t="n">
-        <v>4.176031072779166</v>
+        <v>4.237101998462907</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.9909219092086153</v>
+        <v>0.9909284875006725</v>
       </c>
       <c r="R10" t="n">
-        <v>0.006052399251497523</v>
+        <v>0.006050205967349086</v>
       </c>
       <c r="S10" t="inlineStr"/>
       <c r="T10" t="inlineStr"/>
@@ -1531,38 +1531,38 @@
       <c r="X10" t="inlineStr"/>
       <c r="Y10" t="inlineStr"/>
       <c r="Z10" t="n">
-        <v>0.9998163324264245</v>
+        <v>0.9998449482573343</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.001198746441237836</v>
+        <v>0.001101411007373375</v>
       </c>
       <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="n">
-        <v>0.999989597226922</v>
+        <v>0.9999906698741804</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.695867498259641e-05</v>
+        <v>2.553099440830865e-05</v>
       </c>
       <c r="AE10" t="inlineStr"/>
       <c r="AF10" t="n">
-        <v>0.9078234845867079</v>
+        <v>0.9076723466714517</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.01241420822163687</v>
+        <v>0.01242438157797776</v>
       </c>
       <c r="AH10" t="inlineStr"/>
       <c r="AI10" t="n">
-        <v>0.9699367398825989</v>
+        <v>0.9706490950086941</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.002743262540140196</v>
+        <v>0.002710566610002775</v>
       </c>
       <c r="AK10" t="inlineStr"/>
       <c r="AL10" t="n">
-        <v>0.7903687022792791</v>
+        <v>0.7896845766287504</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.002805644059097986</v>
+        <v>0.002810218399024359</v>
       </c>
       <c r="AN10" t="inlineStr"/>
     </row>
@@ -1604,28 +1604,28 @@
         <v>0.02959337905881725</v>
       </c>
       <c r="K11" t="n">
-        <v>0.4160005438509808</v>
+        <v>0.4197102286204545</v>
       </c>
       <c r="L11" t="n">
-        <v>0.3952990156899107</v>
+        <v>0.402966803682714</v>
       </c>
       <c r="M11" t="n">
-        <v>0.4270133081104466</v>
+        <v>0.4281229235600672</v>
       </c>
       <c r="N11" t="n">
-        <v>0.06071739107815802</v>
+        <v>0.06209006392208215</v>
       </c>
       <c r="O11" t="n">
-        <v>4.094730808965064</v>
+        <v>4.128911664621688</v>
       </c>
       <c r="P11" t="n">
-        <v>4.190169222774444</v>
+        <v>4.272547903661769</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.9669735224431055</v>
+        <v>0.9675545627636214</v>
       </c>
       <c r="R11" t="n">
-        <v>0.01351987512942956</v>
+        <v>0.0134004186862141</v>
       </c>
       <c r="S11" t="inlineStr"/>
       <c r="T11" t="inlineStr"/>
@@ -1635,38 +1635,38 @@
       <c r="X11" t="inlineStr"/>
       <c r="Y11" t="inlineStr"/>
       <c r="Z11" t="n">
-        <v>0.94739196092541</v>
+        <v>0.9483560559914668</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.02867719019766283</v>
+        <v>0.02841320602911025</v>
       </c>
       <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="n">
-        <v>0.9995249739488581</v>
+        <v>0.999448339562569</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.0001535166251810384</v>
+        <v>0.0001654369902432127</v>
       </c>
       <c r="AE11" t="inlineStr"/>
       <c r="AF11" t="n">
-        <v>0.9491067748952021</v>
+        <v>0.9492371302240199</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.003998976451845071</v>
+        <v>0.003993851780363602</v>
       </c>
       <c r="AH11" t="inlineStr"/>
       <c r="AI11" t="n">
-        <v>0.8898501183319623</v>
+        <v>0.889008956058545</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.003729452575193773</v>
+        <v>0.003743665520462066</v>
       </c>
       <c r="AK11" t="inlineStr"/>
       <c r="AL11" t="n">
-        <v>0.9605204781882409</v>
+        <v>0.9607381703639869</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.0008417430504330366</v>
+        <v>0.0008394191345589718</v>
       </c>
       <c r="AN11" t="inlineStr"/>
     </row>
@@ -1708,28 +1708,28 @@
         <v>0.0207241649964606</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1394923145397872</v>
+        <v>0.1394114541171846</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1424150949981774</v>
+        <v>0.1456400020742224</v>
       </c>
       <c r="M12" t="n">
-        <v>0.4918203559581628</v>
+        <v>0.4869384248926201</v>
       </c>
       <c r="N12" t="n">
-        <v>0.1160864569956714</v>
+        <v>0.1169457036489209</v>
       </c>
       <c r="O12" t="n">
-        <v>4.059116436759205</v>
+        <v>4.056914465248047</v>
       </c>
       <c r="P12" t="n">
-        <v>4.078377161765708</v>
+        <v>4.115659556183942</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.9139332381893335</v>
+        <v>0.9143948714120741</v>
       </c>
       <c r="R12" t="n">
-        <v>0.03192861205602593</v>
+        <v>0.03184286974895834</v>
       </c>
       <c r="S12" t="inlineStr"/>
       <c r="T12" t="inlineStr"/>
@@ -1739,38 +1739,38 @@
       <c r="X12" t="inlineStr"/>
       <c r="Y12" t="inlineStr"/>
       <c r="Z12" t="n">
-        <v>0.5174197620429032</v>
+        <v>0.5205635677201037</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.06866883336301499</v>
+        <v>0.06844479371617959</v>
       </c>
       <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="n">
-        <v>0.999994660173041</v>
+        <v>0.9999929548141608</v>
       </c>
       <c r="AD12" t="n">
-        <v>5.42668568349605e-06</v>
+        <v>6.233289569796155e-06</v>
       </c>
       <c r="AE12" t="inlineStr"/>
       <c r="AF12" t="n">
-        <v>0.9762531086058344</v>
+        <v>0.9726203898339607</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.005827025646998973</v>
+        <v>0.006256870649394961</v>
       </c>
       <c r="AH12" t="inlineStr"/>
       <c r="AI12" t="n">
-        <v>0.5826596001231025</v>
+        <v>0.5819442682575993</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.002806726544009784</v>
+        <v>0.002809130913850659</v>
       </c>
       <c r="AK12" t="inlineStr"/>
       <c r="AL12" t="n">
-        <v>0.9685708120600403</v>
+        <v>0.9699770643931866</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.0003586265362770994</v>
+        <v>0.0003505116192059149</v>
       </c>
       <c r="AN12" t="inlineStr"/>
     </row>
@@ -1812,28 +1812,28 @@
         <v>0.05578662037324268</v>
       </c>
       <c r="K13" t="n">
-        <v>0.317485623382867</v>
+        <v>0.3157071197613084</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2605005180594304</v>
+        <v>0.2737591165764205</v>
       </c>
       <c r="M13" t="n">
-        <v>0.5337230385096925</v>
+        <v>0.4966396332798105</v>
       </c>
       <c r="N13" t="n">
-        <v>0.1714056144001363</v>
+        <v>0.1586538260390421</v>
       </c>
       <c r="O13" t="n">
-        <v>4.316000860305166</v>
+        <v>4.293313089366361</v>
       </c>
       <c r="P13" t="n">
-        <v>4.289772975574372</v>
+        <v>4.508014430141713</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.9973740341620733</v>
+        <v>0.9974045832287407</v>
       </c>
       <c r="R13" t="n">
-        <v>0.002932494875767166</v>
+        <v>0.002915387445691861</v>
       </c>
       <c r="S13" t="inlineStr"/>
       <c r="T13" t="inlineStr"/>
@@ -1843,38 +1843,38 @@
       <c r="X13" t="inlineStr"/>
       <c r="Y13" t="inlineStr"/>
       <c r="Z13" t="n">
-        <v>0.6975491951148258</v>
+        <v>0.7039377802764828</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.004335988619713817</v>
+        <v>0.00428995026077389</v>
       </c>
       <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="n">
-        <v>0.9783801784084195</v>
+        <v>0.975272006763534</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.0001126048487493</v>
+        <v>0.0001204274458024907</v>
       </c>
       <c r="AE13" t="inlineStr"/>
       <c r="AF13" t="n">
-        <v>0.6376240757397842</v>
+        <v>0.6366309637231208</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.004304686420832178</v>
+        <v>0.004310581005071804</v>
       </c>
       <c r="AH13" t="inlineStr"/>
       <c r="AI13" t="n">
-        <v>0.9997272772732007</v>
+        <v>0.9997852021798026</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.0006671823395451944</v>
+        <v>0.0005921051132542276</v>
       </c>
       <c r="AK13" t="inlineStr"/>
       <c r="AL13" t="n">
-        <v>0.9494409985717678</v>
+        <v>0.9500345569009239</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.002282256857554797</v>
+        <v>0.002268820556246008</v>
       </c>
       <c r="AN13" t="inlineStr"/>
     </row>
@@ -1916,28 +1916,28 @@
         <v>0.008819171744597891</v>
       </c>
       <c r="K14" t="n">
-        <v>0.2018962647297078</v>
+        <v>0.2052549529133269</v>
       </c>
       <c r="L14" t="n">
-        <v>0.2788861520057203</v>
+        <v>0.2822786211880685</v>
       </c>
       <c r="M14" t="n">
-        <v>0.4617038705730728</v>
+        <v>0.4723981861215936</v>
       </c>
       <c r="N14" t="n">
-        <v>0.4578481557281109</v>
+        <v>0.4670622347935909</v>
       </c>
       <c r="O14" t="n">
-        <v>4.329492817556477</v>
+        <v>4.397072460739371</v>
       </c>
       <c r="P14" t="n">
-        <v>4.327561274514951</v>
+        <v>4.362720201158953</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.9680519686869524</v>
+        <v>0.9682303921522599</v>
       </c>
       <c r="R14" t="n">
-        <v>0.0106443028301856</v>
+        <v>0.0106145380464991</v>
       </c>
       <c r="S14" t="inlineStr"/>
       <c r="T14" t="inlineStr"/>
@@ -1947,38 +1947,38 @@
       <c r="X14" t="inlineStr"/>
       <c r="Y14" t="inlineStr"/>
       <c r="Z14" t="n">
-        <v>0.8782707787632107</v>
+        <v>0.8784566753782201</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.01734725828540315</v>
+        <v>0.01733400744605725</v>
       </c>
       <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="n">
-        <v>0.9614806109789695</v>
+        <v>0.961480610978983</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.0009625122855061531</v>
+        <v>0.0009625122855059849</v>
       </c>
       <c r="AE14" t="inlineStr"/>
       <c r="AF14" t="n">
-        <v>0.9779216936325157</v>
+        <v>0.9792004142146234</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.006421726131030819</v>
+        <v>0.006232987350904815</v>
       </c>
       <c r="AH14" t="inlineStr"/>
       <c r="AI14" t="n">
-        <v>0.5686606469080693</v>
+        <v>0.5692768850073551</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0.01484102111311291</v>
+        <v>0.01483041592324839</v>
       </c>
       <c r="AK14" t="inlineStr"/>
       <c r="AL14" t="n">
-        <v>0.1898848432785193</v>
+        <v>0.1901828886784394</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.00177697484546637</v>
+        <v>0.00177664793644892</v>
       </c>
       <c r="AN14" t="inlineStr"/>
     </row>
@@ -2020,10 +2020,10 @@
         <v>0.02024626170970604</v>
       </c>
       <c r="K15" t="n">
-        <v>0.1960420645582539</v>
+        <v>0.1874830231703039</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2792991729616273</v>
+        <v>0.2737265099064331</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -2032,16 +2032,16 @@
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>4.259694900513283</v>
+        <v>4.085204214067701</v>
       </c>
       <c r="P15" t="n">
-        <v>4.32659567731145</v>
+        <v>4.241274189635918</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.9712742952609386</v>
+        <v>0.9712445023950077</v>
       </c>
       <c r="R15" t="n">
-        <v>0.00895692582655825</v>
+        <v>0.008961569460840967</v>
       </c>
       <c r="S15" t="inlineStr"/>
       <c r="T15" t="inlineStr"/>
@@ -2051,38 +2051,38 @@
       <c r="X15" t="inlineStr"/>
       <c r="Y15" t="inlineStr"/>
       <c r="Z15" t="n">
-        <v>0.9147279795603812</v>
+        <v>0.9145422215504312</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.01437899295171563</v>
+        <v>0.0143946461521398</v>
       </c>
       <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="n">
-        <v>-0.3674310730420616</v>
+        <v>-0.3452385109333218</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.003059937882951814</v>
+        <v>0.003035005859951621</v>
       </c>
       <c r="AE15" t="inlineStr"/>
       <c r="AF15" t="n">
-        <v>0.9186147393804118</v>
+        <v>0.9185682072038268</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.010446154224258</v>
+        <v>0.01044914010173467</v>
       </c>
       <c r="AH15" t="inlineStr"/>
       <c r="AI15" t="n">
-        <v>0.6076061642336401</v>
+        <v>0.607386875813883</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.007010679705472117</v>
+        <v>0.007012638383216577</v>
       </c>
       <c r="AK15" t="inlineStr"/>
       <c r="AL15" t="n">
-        <v>0.9999998106277576</v>
+        <v>0.9999997189716415</v>
       </c>
       <c r="AM15" t="n">
-        <v>1.61033957194876e-06</v>
+        <v>1.961708065212662e-06</v>
       </c>
       <c r="AN15" t="inlineStr"/>
     </row>
@@ -2124,10 +2124,10 @@
         <v>0.01569855494294647</v>
       </c>
       <c r="K16" t="n">
-        <v>0.5421174973423735</v>
+        <v>0.5161649251798621</v>
       </c>
       <c r="L16" t="n">
-        <v>0.5485039621940153</v>
+        <v>0.5289014976348139</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2136,16 +2136,16 @@
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>4.551455588325581</v>
+        <v>4.346437810309332</v>
       </c>
       <c r="P16" t="n">
-        <v>4.64273504780356</v>
+        <v>4.497205496280733</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.9757252005830671</v>
+        <v>0.9761601107018996</v>
       </c>
       <c r="R16" t="n">
-        <v>0.009476330870915355</v>
+        <v>0.009391057682706113</v>
       </c>
       <c r="S16" t="inlineStr"/>
       <c r="T16" t="inlineStr"/>
@@ -2155,31 +2155,31 @@
       <c r="X16" t="inlineStr"/>
       <c r="Y16" t="inlineStr"/>
       <c r="Z16" t="n">
-        <v>0.9942128773895915</v>
+        <v>0.9940557304405625</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.005607840063656768</v>
+        <v>0.005683469384110759</v>
       </c>
       <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="n">
-        <v>0.9580074322594889</v>
+        <v>0.9590590977589639</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.004223567489552747</v>
+        <v>0.004170344451248162</v>
       </c>
       <c r="AE16" t="inlineStr"/>
       <c r="AF16" t="n">
-        <v>0.9102878943193156</v>
+        <v>0.9097484832765053</v>
       </c>
       <c r="AG16" t="n">
-        <v>0.003596372452124203</v>
+        <v>0.003607168184178011</v>
       </c>
       <c r="AH16" t="inlineStr"/>
       <c r="AI16" t="n">
-        <v>0.8407783477616961</v>
+        <v>0.8444101086152463</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0.01808083834779744</v>
+        <v>0.01787344174117467</v>
       </c>
       <c r="AK16" t="inlineStr"/>
       <c r="AL16" t="inlineStr"/>
@@ -2226,28 +2226,28 @@
         <v>0.07189096045701066</v>
       </c>
       <c r="K17" t="n">
-        <v>0.2229860026107122</v>
+        <v>0.2110178984664703</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2782793322317066</v>
+        <v>0.2661393181762588</v>
       </c>
       <c r="M17" t="n">
-        <v>0.1267340574176717</v>
+        <v>0.1004615843598543</v>
       </c>
       <c r="N17" t="n">
-        <v>0.01716491282511557</v>
+        <v>0.0116670810391132</v>
       </c>
       <c r="O17" t="n">
-        <v>4.075120312358837</v>
+        <v>3.870271546959827</v>
       </c>
       <c r="P17" t="n">
-        <v>4.199567679373841</v>
+        <v>4.034650652477939</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.9886226078737885</v>
+        <v>0.9886786676698157</v>
       </c>
       <c r="R17" t="n">
-        <v>0.004951290486326637</v>
+        <v>0.004939077182431664</v>
       </c>
       <c r="S17" t="inlineStr"/>
       <c r="T17" t="inlineStr"/>
@@ -2257,38 +2257,38 @@
       <c r="X17" t="inlineStr"/>
       <c r="Y17" t="inlineStr"/>
       <c r="Z17" t="n">
-        <v>0.9650339703585605</v>
+        <v>0.9651186790951685</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.009407093889937991</v>
+        <v>0.009395692162997312</v>
       </c>
       <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="n">
-        <v>0.7114706327952356</v>
+        <v>0.7228519706229354</v>
       </c>
       <c r="AD17" t="n">
-        <v>0.001661275128228624</v>
+        <v>0.001628180124491695</v>
       </c>
       <c r="AE17" t="inlineStr"/>
       <c r="AF17" t="n">
-        <v>0.9938126522025038</v>
+        <v>0.9938354554072996</v>
       </c>
       <c r="AG17" t="n">
-        <v>0.002127296308859686</v>
+        <v>0.002123372660783748</v>
       </c>
       <c r="AH17" t="inlineStr"/>
       <c r="AI17" t="n">
-        <v>0.00621810810764889</v>
+        <v>0.01664500356008591</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.005130142000070209</v>
+        <v>0.005103157957807506</v>
       </c>
       <c r="AK17" t="inlineStr"/>
       <c r="AL17" t="n">
-        <v>0.9948761454755666</v>
+        <v>0.9947468990030295</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.0006923802189485468</v>
+        <v>0.0007010582940017842</v>
       </c>
       <c r="AN17" t="inlineStr"/>
     </row>
@@ -2330,10 +2330,10 @@
         <v>0.03009288922194302</v>
       </c>
       <c r="K18" t="n">
-        <v>0.2393672981629223</v>
+        <v>0.2424607087442707</v>
       </c>
       <c r="L18" t="n">
-        <v>0.2619826533862505</v>
+        <v>0.2651836289186233</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -2342,16 +2342,16 @@
         <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>4.246963527162229</v>
+        <v>4.298420190621356</v>
       </c>
       <c r="P18" t="n">
-        <v>4.250728850929033</v>
+        <v>4.300141674142705</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.9826182446224555</v>
+        <v>0.9826304224726914</v>
       </c>
       <c r="R18" t="n">
-        <v>0.006818445911916567</v>
+        <v>0.006816056954067184</v>
       </c>
       <c r="S18" t="inlineStr"/>
       <c r="T18" t="inlineStr"/>
@@ -2361,38 +2361,38 @@
       <c r="X18" t="inlineStr"/>
       <c r="Y18" t="inlineStr"/>
       <c r="Z18" t="n">
-        <v>0.9152165076409337</v>
+        <v>0.9152792494398896</v>
       </c>
       <c r="AA18" t="n">
-        <v>0.0149529946725015</v>
+        <v>0.01494746086284035</v>
       </c>
       <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="n">
-        <v>0.9897499981441324</v>
+        <v>0.9890578547182047</v>
       </c>
       <c r="AD18" t="n">
-        <v>0.0002788496689964799</v>
+        <v>0.0002881107079800557</v>
       </c>
       <c r="AE18" t="inlineStr"/>
       <c r="AF18" t="n">
-        <v>0.9973251938557485</v>
+        <v>0.9973079279727923</v>
       </c>
       <c r="AG18" t="n">
-        <v>0.00155230677329529</v>
+        <v>0.001557308787083497</v>
       </c>
       <c r="AH18" t="inlineStr"/>
       <c r="AI18" t="n">
-        <v>0.9777183202870661</v>
+        <v>0.9777848320257698</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0.002511214460882848</v>
+        <v>0.002507463619992367</v>
       </c>
       <c r="AK18" t="inlineStr"/>
       <c r="AL18" t="n">
-        <v>0.995048314955018</v>
+        <v>0.9950045809964476</v>
       </c>
       <c r="AM18" t="n">
-        <v>0.0002652584926734241</v>
+        <v>0.0002664273171593902</v>
       </c>
       <c r="AN18" t="inlineStr"/>
     </row>
@@ -2434,10 +2434,10 @@
         <v>0.01254934055241822</v>
       </c>
       <c r="K19" t="n">
-        <v>0.1872651872905624</v>
+        <v>0.161033465819801</v>
       </c>
       <c r="L19" t="n">
-        <v>0.2369652039641418</v>
+        <v>0.2232994455997759</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -2446,16 +2446,16 @@
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>4.597747250805167</v>
+        <v>3.990866149206148</v>
       </c>
       <c r="P19" t="n">
-        <v>4.654580273629279</v>
+        <v>4.375458080650116</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.9868556896403132</v>
+        <v>0.9869099488292812</v>
       </c>
       <c r="R19" t="n">
-        <v>0.008077799172500922</v>
+        <v>0.008061109514708967</v>
       </c>
       <c r="S19" t="inlineStr"/>
       <c r="T19" t="inlineStr"/>
@@ -2465,38 +2465,38 @@
       <c r="X19" t="inlineStr"/>
       <c r="Y19" t="inlineStr"/>
       <c r="Z19" t="n">
-        <v>0.6242906599571725</v>
+        <v>0.6274750871000984</v>
       </c>
       <c r="AA19" t="n">
-        <v>0.009126666723345816</v>
+        <v>0.00908790663969649</v>
       </c>
       <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="n">
-        <v>-0.0167814312972463</v>
+        <v>0.003989528014871735</v>
       </c>
       <c r="AD19" t="n">
-        <v>0.003004144813477837</v>
+        <v>0.002973301930883142</v>
       </c>
       <c r="AE19" t="inlineStr"/>
       <c r="AF19" t="n">
-        <v>0.7304437190212312</v>
+        <v>0.7305638330194407</v>
       </c>
       <c r="AG19" t="n">
-        <v>0.01465393174481852</v>
+        <v>0.01465066649266402</v>
       </c>
       <c r="AH19" t="inlineStr"/>
       <c r="AI19" t="n">
-        <v>0.8560008921894704</v>
+        <v>0.8587258722118825</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0.004377967449063088</v>
+        <v>0.004336346172917609</v>
       </c>
       <c r="AK19" t="inlineStr"/>
       <c r="AL19" t="n">
-        <v>0.9966130663101296</v>
+        <v>0.9963810197870483</v>
       </c>
       <c r="AM19" t="n">
-        <v>0.0001701506686823837</v>
+        <v>0.0001758828188849516</v>
       </c>
       <c r="AN19" t="inlineStr"/>
     </row>
@@ -2538,10 +2538,10 @@
         <v>0.005481236733903614</v>
       </c>
       <c r="K20" t="n">
-        <v>0.2655681489740055</v>
+        <v>0.2706740016525256</v>
       </c>
       <c r="L20" t="n">
-        <v>0.2867527403576336</v>
+        <v>0.292740499899429</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -2550,16 +2550,16 @@
         <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>4.545581196261954</v>
+        <v>4.627752525577289</v>
       </c>
       <c r="P20" t="n">
-        <v>4.509499226600938</v>
+        <v>4.593240864814092</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.9734477743280838</v>
+        <v>0.9734668925685214</v>
       </c>
       <c r="R20" t="n">
-        <v>0.009566656290347928</v>
+        <v>0.009563211558973351</v>
       </c>
       <c r="S20" t="inlineStr"/>
       <c r="T20" t="inlineStr"/>
@@ -2569,38 +2569,38 @@
       <c r="X20" t="inlineStr"/>
       <c r="Y20" t="inlineStr"/>
       <c r="Z20" t="n">
-        <v>0.8684397880780379</v>
+        <v>0.8668274204847926</v>
       </c>
       <c r="AA20" t="n">
-        <v>0.01056648990541221</v>
+        <v>0.01063104279203551</v>
       </c>
       <c r="AB20" t="inlineStr"/>
       <c r="AC20" t="n">
-        <v>0.8345420782509959</v>
+        <v>0.8317276085052017</v>
       </c>
       <c r="AD20" t="n">
-        <v>0.002775572037550959</v>
+        <v>0.002799078990648457</v>
       </c>
       <c r="AE20" t="inlineStr"/>
       <c r="AF20" t="n">
-        <v>0.9329551879037299</v>
+        <v>0.9346148841799236</v>
       </c>
       <c r="AG20" t="n">
-        <v>0.006909354220955615</v>
+        <v>0.006823297667878534</v>
       </c>
       <c r="AH20" t="inlineStr"/>
       <c r="AI20" t="n">
-        <v>0.7849271182929354</v>
+        <v>0.7854085969175137</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0.01703042449634398</v>
+        <v>0.01701135100923516</v>
       </c>
       <c r="AK20" t="inlineStr"/>
       <c r="AL20" t="n">
-        <v>0.4684714032388693</v>
+        <v>0.4660248096489776</v>
       </c>
       <c r="AM20" t="n">
-        <v>0.0006895792595088596</v>
+        <v>0.0006911644829887301</v>
       </c>
       <c r="AN20" t="inlineStr"/>
     </row>
@@ -2642,10 +2642,10 @@
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>0.1248690725745343</v>
+        <v>0.1202941340488625</v>
       </c>
       <c r="L21" t="n">
-        <v>0.1391849686632676</v>
+        <v>0.137931315746043</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -2654,16 +2654,16 @@
         <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>4.25389152450637</v>
+        <v>4.107682434211664</v>
       </c>
       <c r="P21" t="n">
-        <v>4.340556887373432</v>
+        <v>4.121104552990844</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.8775282290456505</v>
+        <v>0.8678897471651907</v>
       </c>
       <c r="R21" t="n">
-        <v>0.02277501650379183</v>
+        <v>0.02365423805969597</v>
       </c>
       <c r="S21" t="inlineStr"/>
       <c r="T21" t="inlineStr"/>
@@ -2673,38 +2673,38 @@
       <c r="X21" t="inlineStr"/>
       <c r="Y21" t="inlineStr"/>
       <c r="Z21" t="n">
-        <v>0.9478622042758609</v>
+        <v>0.9532826462626094</v>
       </c>
       <c r="AA21" t="n">
-        <v>0.008969414976336925</v>
+        <v>0.008490375570638316</v>
       </c>
       <c r="AB21" t="inlineStr"/>
       <c r="AC21" t="n">
-        <v>0.9955326288839087</v>
+        <v>0.9946418745541423</v>
       </c>
       <c r="AD21" t="n">
-        <v>0.002206289391927377</v>
+        <v>0.002416255744214073</v>
       </c>
       <c r="AE21" t="inlineStr"/>
       <c r="AF21" t="n">
-        <v>-3.437834220437437</v>
+        <v>-3.873668893466444</v>
       </c>
       <c r="AG21" t="n">
-        <v>0.04614178076741202</v>
+        <v>0.04835449193264897</v>
       </c>
       <c r="AH21" t="inlineStr"/>
       <c r="AI21" t="n">
-        <v>-0.3038157083104938</v>
+        <v>-0.3120718465706824</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0.01945834246620811</v>
+        <v>0.01951985317088758</v>
       </c>
       <c r="AK21" t="inlineStr"/>
       <c r="AL21" t="n">
-        <v>0.534979457748169</v>
+        <v>0.5248689173044851</v>
       </c>
       <c r="AM21" t="n">
-        <v>0.0007055082714829284</v>
+        <v>0.0007131366589121639</v>
       </c>
       <c r="AN21" t="inlineStr"/>
     </row>
@@ -2746,28 +2746,28 @@
         <v>0.02704531936448205</v>
       </c>
       <c r="K22" t="n">
-        <v>0.3240298729858146</v>
+        <v>0.3065794238146419</v>
       </c>
       <c r="L22" t="n">
-        <v>0.3314291869976703</v>
+        <v>0.3244168349152868</v>
       </c>
       <c r="M22" t="n">
-        <v>0.1091911482058442</v>
+        <v>0.06973292105409901</v>
       </c>
       <c r="N22" t="n">
-        <v>0.01366964325302079</v>
+        <v>0.006708888379584744</v>
       </c>
       <c r="O22" t="n">
-        <v>4.357078932018656</v>
+        <v>4.136683456812678</v>
       </c>
       <c r="P22" t="n">
-        <v>4.394963120427309</v>
+        <v>4.309238602403099</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.9816626753228745</v>
+        <v>0.9817618757604332</v>
       </c>
       <c r="R22" t="n">
-        <v>0.006845322617272464</v>
+        <v>0.006826781748058291</v>
       </c>
       <c r="S22" t="inlineStr"/>
       <c r="T22" t="inlineStr"/>
@@ -2777,38 +2777,38 @@
       <c r="X22" t="inlineStr"/>
       <c r="Y22" t="inlineStr"/>
       <c r="Z22" t="n">
-        <v>0.8918894456980766</v>
+        <v>0.8932080844474241</v>
       </c>
       <c r="AA22" t="n">
-        <v>0.009693556876925547</v>
+        <v>0.00963425870672871</v>
       </c>
       <c r="AB22" t="inlineStr"/>
       <c r="AC22" t="n">
-        <v>0.9267542890796088</v>
+        <v>0.9299684077244298</v>
       </c>
       <c r="AD22" t="n">
-        <v>0.001500067792606447</v>
+        <v>0.001466786106645489</v>
       </c>
       <c r="AE22" t="inlineStr"/>
       <c r="AF22" t="n">
-        <v>0.3397965601083457</v>
+        <v>0.342147610241776</v>
       </c>
       <c r="AG22" t="n">
-        <v>0.01121489402900875</v>
+        <v>0.01119490754296669</v>
       </c>
       <c r="AH22" t="inlineStr"/>
       <c r="AI22" t="n">
-        <v>0.9591704253174529</v>
+        <v>0.9570543125470841</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0.002893303390394622</v>
+        <v>0.002967333280691571</v>
       </c>
       <c r="AK22" t="inlineStr"/>
       <c r="AL22" t="n">
-        <v>0.7800292630825818</v>
+        <v>0.7805096407797885</v>
       </c>
       <c r="AM22" t="n">
-        <v>0.001982903873953239</v>
+        <v>0.001980737532589987</v>
       </c>
       <c r="AN22" t="inlineStr"/>
     </row>
@@ -2850,28 +2850,28 @@
         <v>0.0237900385797033</v>
       </c>
       <c r="K23" t="n">
-        <v>0.3048705428481599</v>
+        <v>0.2861768349137373</v>
       </c>
       <c r="L23" t="n">
-        <v>0.2935530774311012</v>
+        <v>0.2868386291898513</v>
       </c>
       <c r="M23" t="n">
-        <v>0.3152505502435201</v>
+        <v>0.2727188989077666</v>
       </c>
       <c r="N23" t="n">
-        <v>0.06352952933681413</v>
+        <v>0.05101810190704075</v>
       </c>
       <c r="O23" t="n">
-        <v>4.105159995358824</v>
+        <v>3.86931123372123</v>
       </c>
       <c r="P23" t="n">
-        <v>4.199272499410497</v>
+        <v>4.120131318366412</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.9816251076836717</v>
+        <v>0.9817958679547105</v>
       </c>
       <c r="R23" t="n">
-        <v>0.0101484789530359</v>
+        <v>0.01010121331597034</v>
       </c>
       <c r="S23" t="inlineStr"/>
       <c r="T23" t="inlineStr"/>
@@ -2881,38 +2881,38 @@
       <c r="X23" t="inlineStr"/>
       <c r="Y23" t="inlineStr"/>
       <c r="Z23" t="n">
-        <v>0.8965587605009202</v>
+        <v>0.8975098456803112</v>
       </c>
       <c r="AA23" t="n">
-        <v>0.02254758660137853</v>
+        <v>0.02244369091883516</v>
       </c>
       <c r="AB23" t="inlineStr"/>
       <c r="AC23" t="n">
-        <v>-0.6646437366621973</v>
+        <v>-0.6143717911277069</v>
       </c>
       <c r="AD23" t="n">
-        <v>0.00123209896123262</v>
+        <v>0.001213351750524985</v>
       </c>
       <c r="AE23" t="inlineStr"/>
       <c r="AF23" t="n">
-        <v>0.9822638544461998</v>
+        <v>0.9825040312554321</v>
       </c>
       <c r="AG23" t="n">
-        <v>0.002243108519897421</v>
+        <v>0.002227869048413941</v>
       </c>
       <c r="AH23" t="inlineStr"/>
       <c r="AI23" t="n">
-        <v>0.9987683062283933</v>
+        <v>0.9977380271393108</v>
       </c>
       <c r="AJ23" t="n">
-        <v>5.697957859806335e-05</v>
+        <v>7.721675654540557e-05</v>
       </c>
       <c r="AK23" t="inlineStr"/>
       <c r="AL23" t="n">
-        <v>0.9994649398273711</v>
+        <v>0.9994607279162693</v>
       </c>
       <c r="AM23" t="n">
-        <v>0.000107765484802879</v>
+        <v>0.0001081888099806526</v>
       </c>
       <c r="AN23" t="inlineStr"/>
     </row>
@@ -2954,28 +2954,28 @@
         <v>0.01655830938827357</v>
       </c>
       <c r="K24" t="n">
-        <v>0.3751494643248936</v>
+        <v>0.3875416039382416</v>
       </c>
       <c r="L24" t="n">
-        <v>0.4426590129696031</v>
+        <v>0.4583294648523437</v>
       </c>
       <c r="M24" t="n">
-        <v>0.03124752332551595</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>0.000624950466510319</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>4.176595398310353</v>
+        <v>4.305819674281706</v>
       </c>
       <c r="P24" t="n">
-        <v>4.305323349664603</v>
+        <v>4.374016760011923</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.9930118173094774</v>
+        <v>0.9930288636682071</v>
       </c>
       <c r="R24" t="n">
-        <v>0.004964422872088706</v>
+        <v>0.004958364286698705</v>
       </c>
       <c r="S24" t="inlineStr"/>
       <c r="T24" t="inlineStr"/>
@@ -2985,31 +2985,31 @@
       <c r="X24" t="inlineStr"/>
       <c r="Y24" t="inlineStr"/>
       <c r="Z24" t="n">
-        <v>0.9998995506003121</v>
+        <v>0.9998817939976682</v>
       </c>
       <c r="AA24" t="n">
-        <v>0.0008042595763917024</v>
+        <v>0.0008724535878225165</v>
       </c>
       <c r="AB24" t="inlineStr"/>
       <c r="AC24" t="n">
-        <v>0.9569173207399312</v>
+        <v>0.955596081366228</v>
       </c>
       <c r="AD24" t="n">
-        <v>0.003277179620668566</v>
+        <v>0.003327051647853078</v>
       </c>
       <c r="AE24" t="inlineStr"/>
       <c r="AF24" t="n">
-        <v>0.843485870872697</v>
+        <v>0.8450195515293615</v>
       </c>
       <c r="AG24" t="n">
-        <v>0.009749564330861531</v>
+        <v>0.009701678784436861</v>
       </c>
       <c r="AH24" t="inlineStr"/>
       <c r="AI24" t="n">
-        <v>0.9921923613488225</v>
+        <v>0.9872147780043223</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0.0005969910010699388</v>
+        <v>0.0007639449575686116</v>
       </c>
       <c r="AK24" t="inlineStr"/>
       <c r="AL24" t="inlineStr"/>
@@ -3056,10 +3056,10 @@
         <v>0.05553965571423582</v>
       </c>
       <c r="K25" t="n">
-        <v>0.2172140991091026</v>
+        <v>0.215848059616466</v>
       </c>
       <c r="L25" t="n">
-        <v>0.2288600004876191</v>
+        <v>0.2284773528280685</v>
       </c>
       <c r="M25" t="n">
         <v>0</v>
@@ -3068,65 +3068,65 @@
         <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>4.335750152080124</v>
+        <v>4.310157944037903</v>
       </c>
       <c r="P25" t="n">
-        <v>4.343858134200834</v>
+        <v>4.340625818175276</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.9844606436067111</v>
+        <v>0.984507854515332</v>
       </c>
       <c r="R25" t="n">
-        <v>0.0206738044475156</v>
+        <v>0.02064237548974292</v>
       </c>
       <c r="S25" t="inlineStr"/>
       <c r="T25" t="n">
-        <v>-0.1784868489677363</v>
+        <v>-0.1747078635040595</v>
       </c>
       <c r="U25" t="n">
-        <v>0.03996827854756024</v>
+        <v>0.03990414511207344</v>
       </c>
       <c r="V25" t="inlineStr"/>
       <c r="W25" t="n">
-        <v>0.5414934749891305</v>
+        <v>0.5431757325751052</v>
       </c>
       <c r="X25" t="n">
-        <v>0.0008591893592865932</v>
+        <v>0.0008576117306741309</v>
       </c>
       <c r="Y25" t="inlineStr"/>
       <c r="Z25" t="n">
-        <v>0.8917081150836333</v>
+        <v>0.8914663041449947</v>
       </c>
       <c r="AA25" t="n">
-        <v>0.01134453944735743</v>
+        <v>0.01135719830938619</v>
       </c>
       <c r="AB25" t="inlineStr"/>
       <c r="AC25" t="n">
-        <v>0.6613851571956257</v>
+        <v>0.661272200372327</v>
       </c>
       <c r="AD25" t="n">
-        <v>0.002851680356677807</v>
+        <v>0.00285215595587576</v>
       </c>
       <c r="AE25" t="inlineStr"/>
       <c r="AF25" t="n">
-        <v>0.979112405224479</v>
+        <v>0.9797649579601903</v>
       </c>
       <c r="AG25" t="n">
-        <v>0.002367461527634041</v>
+        <v>0.002330186967735424</v>
       </c>
       <c r="AH25" t="inlineStr"/>
       <c r="AI25" t="n">
-        <v>0.9738778607727459</v>
+        <v>0.9702799629899451</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0.001009485155863295</v>
+        <v>0.001076763288601591</v>
       </c>
       <c r="AK25" t="inlineStr"/>
       <c r="AL25" t="n">
-        <v>-0.02189032935739443</v>
+        <v>-0.02132222006607809</v>
       </c>
       <c r="AM25" t="n">
-        <v>0.003347444676746949</v>
+        <v>0.003346514058875605</v>
       </c>
       <c r="AN25" t="inlineStr"/>
     </row>
@@ -3168,10 +3168,10 @@
         <v>0.05246774739927379</v>
       </c>
       <c r="K26" t="n">
-        <v>0.3294247814180385</v>
+        <v>0.3197948172394026</v>
       </c>
       <c r="L26" t="n">
-        <v>0.3152821057620078</v>
+        <v>0.307729191614642</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -3180,65 +3180,65 @@
         <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>4.343361074649197</v>
+        <v>4.224153844393832</v>
       </c>
       <c r="P26" t="n">
-        <v>4.388959776362458</v>
+        <v>4.29966176391435</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.9811299599040499</v>
+        <v>0.9813081611594732</v>
       </c>
       <c r="R26" t="n">
-        <v>0.02111415666511614</v>
+        <v>0.02101422326656706</v>
       </c>
       <c r="S26" t="inlineStr"/>
       <c r="T26" t="n">
-        <v>0.3125442851664189</v>
+        <v>0.3194873422489407</v>
       </c>
       <c r="U26" t="n">
-        <v>0.04071700359685655</v>
+        <v>0.04051086820879415</v>
       </c>
       <c r="V26" t="inlineStr"/>
       <c r="W26" t="n">
-        <v>-0.3346691692462636</v>
+        <v>-0.3167759222675097</v>
       </c>
       <c r="X26" t="n">
-        <v>0.0008098727164863159</v>
+        <v>0.0008044256175139636</v>
       </c>
       <c r="Y26" t="inlineStr"/>
       <c r="Z26" t="n">
-        <v>0.9478603516527522</v>
+        <v>0.9473966963069762</v>
       </c>
       <c r="AA26" t="n">
-        <v>0.01232782958756913</v>
+        <v>0.01238252129801991</v>
       </c>
       <c r="AB26" t="inlineStr"/>
       <c r="AC26" t="n">
-        <v>-0.255237910558362</v>
+        <v>-0.2443036383060944</v>
       </c>
       <c r="AD26" t="n">
-        <v>0.003841552743827162</v>
+        <v>0.003824784425081982</v>
       </c>
       <c r="AE26" t="inlineStr"/>
       <c r="AF26" t="n">
-        <v>0.9169856801721336</v>
+        <v>0.9173235934568205</v>
       </c>
       <c r="AG26" t="n">
-        <v>0.003856646938879104</v>
+        <v>0.003848789612945321</v>
       </c>
       <c r="AH26" t="inlineStr"/>
       <c r="AI26" t="n">
-        <v>0.9819167181042554</v>
+        <v>0.981903816046003</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0.001143927637383856</v>
+        <v>0.001144335649310885</v>
       </c>
       <c r="AK26" t="inlineStr"/>
       <c r="AL26" t="n">
-        <v>0.4708558234012146</v>
+        <v>0.4672117928240014</v>
       </c>
       <c r="AM26" t="n">
-        <v>0.00100799117736772</v>
+        <v>0.001011456063301109</v>
       </c>
       <c r="AN26" t="inlineStr"/>
     </row>
@@ -3280,10 +3280,10 @@
         <v>0.07321928484019485</v>
       </c>
       <c r="K27" t="n">
-        <v>0.2426473726089903</v>
+        <v>0.2439507965539418</v>
       </c>
       <c r="L27" t="n">
-        <v>0.307398751289812</v>
+        <v>0.3066785751360043</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
@@ -3292,65 +3292,65 @@
         <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>4.128901529664978</v>
+        <v>4.149671453558346</v>
       </c>
       <c r="P27" t="n">
-        <v>4.155660369250016</v>
+        <v>4.151144737685096</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.9964520342592126</v>
+        <v>0.9964585972545316</v>
       </c>
       <c r="R27" t="n">
-        <v>0.009667581563723408</v>
+        <v>0.009658635921927991</v>
       </c>
       <c r="S27" t="inlineStr"/>
       <c r="T27" t="n">
-        <v>0.9041170421987085</v>
+        <v>0.9043392085180965</v>
       </c>
       <c r="U27" t="n">
-        <v>0.01625518984846173</v>
+        <v>0.01623634682286491</v>
       </c>
       <c r="V27" t="inlineStr"/>
       <c r="W27" t="n">
-        <v>0.7055811351248327</v>
+        <v>0.7029069180802154</v>
       </c>
       <c r="X27" t="n">
-        <v>0.000608071719338092</v>
+        <v>0.0006108270453513888</v>
       </c>
       <c r="Y27" t="inlineStr"/>
       <c r="Z27" t="n">
-        <v>0.9250324382481839</v>
+        <v>0.9251622015904822</v>
       </c>
       <c r="AA27" t="n">
-        <v>0.01161037276988822</v>
+        <v>0.01160032006669633</v>
       </c>
       <c r="AB27" t="inlineStr"/>
       <c r="AC27" t="n">
-        <v>0.9445619526742078</v>
+        <v>0.9436921249261397</v>
       </c>
       <c r="AD27" t="n">
-        <v>0.0008609988449865865</v>
+        <v>0.00086772712896629</v>
       </c>
       <c r="AE27" t="inlineStr"/>
       <c r="AF27" t="n">
-        <v>0.8862508529185191</v>
+        <v>0.8860893034683536</v>
       </c>
       <c r="AG27" t="n">
-        <v>0.009421613264955164</v>
+        <v>0.009428301299323778</v>
       </c>
       <c r="AH27" t="inlineStr"/>
       <c r="AI27" t="n">
-        <v>0.577053472379077</v>
+        <v>0.5798331579529565</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0.003503710906979478</v>
+        <v>0.003492178397757696</v>
       </c>
       <c r="AK27" t="inlineStr"/>
       <c r="AL27" t="n">
-        <v>0.4436342281651862</v>
+        <v>0.4433156051319086</v>
       </c>
       <c r="AM27" t="n">
-        <v>0.004856746569558771</v>
+        <v>0.004858137066522915</v>
       </c>
       <c r="AN27" t="inlineStr"/>
     </row>
@@ -3392,10 +3392,10 @@
         <v>0.02087465183044777</v>
       </c>
       <c r="K28" t="n">
-        <v>0.4028027310904022</v>
+        <v>0.3989355859737008</v>
       </c>
       <c r="L28" t="n">
-        <v>0.3961947966711687</v>
+        <v>0.4105436055047945</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
@@ -3404,16 +3404,16 @@
         <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>4.152089315711887</v>
+        <v>4.114744150286834</v>
       </c>
       <c r="P28" t="n">
-        <v>4.168356615802401</v>
+        <v>4.293035030241906</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.9430652934537903</v>
+        <v>0.9447349339657186</v>
       </c>
       <c r="R28" t="n">
-        <v>0.02484804348618884</v>
+        <v>0.02448099142661578</v>
       </c>
       <c r="S28" t="inlineStr"/>
       <c r="T28" t="inlineStr"/>
@@ -3425,38 +3425,38 @@
       </c>
       <c r="Y28" t="inlineStr"/>
       <c r="Z28" t="n">
-        <v>0.6056223613892402</v>
+        <v>0.6190441638909063</v>
       </c>
       <c r="AA28" t="n">
-        <v>0.05145842651115428</v>
+        <v>0.05057520790415165</v>
       </c>
       <c r="AB28" t="inlineStr"/>
       <c r="AC28" t="n">
-        <v>0.824901189644429</v>
+        <v>0.8456801459753259</v>
       </c>
       <c r="AD28" t="n">
-        <v>0.005004706815542984</v>
+        <v>0.004698377899981765</v>
       </c>
       <c r="AE28" t="inlineStr"/>
       <c r="AF28" t="n">
-        <v>0.5030984466990862</v>
+        <v>0.499701315190371</v>
       </c>
       <c r="AG28" t="n">
-        <v>0.01178367169736644</v>
+        <v>0.01182388338144986</v>
       </c>
       <c r="AH28" t="inlineStr"/>
       <c r="AI28" t="n">
-        <v>0.4040942832093631</v>
+        <v>0.402242829316459</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0.01677450729418537</v>
+        <v>0.01680054592746786</v>
       </c>
       <c r="AK28" t="inlineStr"/>
       <c r="AL28" t="n">
-        <v>0.9889585099658688</v>
+        <v>0.989618598729249</v>
       </c>
       <c r="AM28" t="n">
-        <v>0.0003637788993912171</v>
+        <v>0.0003527375152339036</v>
       </c>
       <c r="AN28" t="inlineStr"/>
     </row>
@@ -3498,10 +3498,10 @@
         <v>0.03864752444133265</v>
       </c>
       <c r="K29" t="n">
-        <v>0.512131704883432</v>
+        <v>0.5337507387871602</v>
       </c>
       <c r="L29" t="n">
-        <v>0.3338013518955662</v>
+        <v>0.3454522295906396</v>
       </c>
       <c r="M29" t="n">
         <v>0</v>
@@ -3510,16 +3510,16 @@
         <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>4.093722495858296</v>
+        <v>4.255427909449321</v>
       </c>
       <c r="P29" t="n">
-        <v>4.104304029444438</v>
+        <v>4.201654647402672</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.9483658110096799</v>
+        <v>0.9510114840119204</v>
       </c>
       <c r="R29" t="n">
-        <v>0.01466346976076592</v>
+        <v>0.01428286099957423</v>
       </c>
       <c r="S29" t="inlineStr"/>
       <c r="T29" t="inlineStr"/>
@@ -3531,38 +3531,38 @@
       </c>
       <c r="Y29" t="inlineStr"/>
       <c r="Z29" t="n">
-        <v>0.77566206986804</v>
+        <v>0.7866406000590361</v>
       </c>
       <c r="AA29" t="n">
-        <v>0.03086476682239346</v>
+        <v>0.03010007215515761</v>
       </c>
       <c r="AB29" t="inlineStr"/>
       <c r="AC29" t="n">
-        <v>0.927213008331135</v>
+        <v>0.9290719133346621</v>
       </c>
       <c r="AD29" t="n">
-        <v>0.009344714343725158</v>
+        <v>0.009224615380400224</v>
       </c>
       <c r="AE29" t="inlineStr"/>
       <c r="AF29" t="n">
-        <v>0.5960492644107308</v>
+        <v>0.6458639343134771</v>
       </c>
       <c r="AG29" t="n">
-        <v>0.008983235887299929</v>
+        <v>0.008411117137283838</v>
       </c>
       <c r="AH29" t="inlineStr"/>
       <c r="AI29" t="n">
-        <v>0.9928714174282394</v>
+        <v>0.9914430584326879</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0.002193756948084203</v>
+        <v>0.002403511476839721</v>
       </c>
       <c r="AK29" t="inlineStr"/>
       <c r="AL29" t="n">
-        <v>0.9053142069579798</v>
+        <v>0.905411353343703</v>
       </c>
       <c r="AM29" t="n">
-        <v>0.001836423088512983</v>
+        <v>0.001835480773710733</v>
       </c>
       <c r="AN29" t="inlineStr"/>
     </row>
@@ -3604,28 +3604,28 @@
         <v>0.0191674492264043</v>
       </c>
       <c r="K30" t="n">
-        <v>0.4907901004864869</v>
+        <v>0.5332067105517685</v>
       </c>
       <c r="L30" t="n">
-        <v>0.3818235419564829</v>
+        <v>0.4026179048601815</v>
       </c>
       <c r="M30" t="n">
-        <v>0.0660599278862708</v>
+        <v>0.1192796228668859</v>
       </c>
       <c r="N30" t="n">
-        <v>0.001988933738196343</v>
+        <v>0.005593869083316108</v>
       </c>
       <c r="O30" t="n">
-        <v>4.182807504896132</v>
+        <v>4.521248121695771</v>
       </c>
       <c r="P30" t="n">
-        <v>4.106915250642329</v>
+        <v>4.311878627455808</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.972217069102389</v>
+        <v>0.9727187905116642</v>
       </c>
       <c r="R30" t="n">
-        <v>0.01373899350222488</v>
+        <v>0.01361437469228239</v>
       </c>
       <c r="S30" t="inlineStr"/>
       <c r="T30" t="inlineStr"/>
@@ -3637,38 +3637,38 @@
       </c>
       <c r="Y30" t="inlineStr"/>
       <c r="Z30" t="n">
-        <v>0.8641305704452698</v>
+        <v>0.865763072347475</v>
       </c>
       <c r="AA30" t="n">
-        <v>0.02510757832032075</v>
+        <v>0.02495628587987226</v>
       </c>
       <c r="AB30" t="inlineStr"/>
       <c r="AC30" t="n">
-        <v>0.9995548149156858</v>
+        <v>0.9996047218401607</v>
       </c>
       <c r="AD30" t="n">
-        <v>9.508296045548658e-05</v>
+        <v>8.959500586566284e-05</v>
       </c>
       <c r="AE30" t="inlineStr"/>
       <c r="AF30" t="n">
-        <v>-0.03978134878786221</v>
+        <v>0.01431393370887513</v>
       </c>
       <c r="AG30" t="n">
-        <v>0.0137899754022092</v>
+        <v>0.0134264682354188</v>
       </c>
       <c r="AH30" t="inlineStr"/>
       <c r="AI30" t="n">
-        <v>0.8350640220989454</v>
+        <v>0.8321512384245673</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0.008500254109100326</v>
+        <v>0.008574983234710037</v>
       </c>
       <c r="AK30" t="inlineStr"/>
       <c r="AL30" t="n">
-        <v>0.4750534414555697</v>
+        <v>0.4749689970584041</v>
       </c>
       <c r="AM30" t="n">
-        <v>0.001948582984839624</v>
+        <v>0.001948739705839091</v>
       </c>
       <c r="AN30" t="inlineStr"/>
     </row>
@@ -3710,10 +3710,10 @@
         <v>0.02030227596285282</v>
       </c>
       <c r="K31" t="n">
-        <v>0.5036033975236921</v>
+        <v>0.4902078464552742</v>
       </c>
       <c r="L31" t="n">
-        <v>0.4304956211490192</v>
+        <v>0.4306016586812278</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
@@ -3722,16 +3722,16 @@
         <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>4.35839592105136</v>
+        <v>4.249538389327932</v>
       </c>
       <c r="P31" t="n">
-        <v>4.404017411239503</v>
+        <v>4.410030188172075</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.9858232890223656</v>
+        <v>0.9859206503437857</v>
       </c>
       <c r="R31" t="n">
-        <v>0.007775787064515909</v>
+        <v>0.007749040197655582</v>
       </c>
       <c r="S31" t="inlineStr"/>
       <c r="T31" t="inlineStr"/>
@@ -3743,38 +3743,38 @@
       </c>
       <c r="Y31" t="inlineStr"/>
       <c r="Z31" t="n">
-        <v>0.9470191990119275</v>
+        <v>0.9485192219064569</v>
       </c>
       <c r="AA31" t="n">
-        <v>0.01229409179958901</v>
+        <v>0.01211880347787228</v>
       </c>
       <c r="AB31" t="inlineStr"/>
       <c r="AC31" t="n">
-        <v>0.9006410868993017</v>
+        <v>0.899301487818288</v>
       </c>
       <c r="AD31" t="n">
-        <v>0.007674051872437552</v>
+        <v>0.007725611082399673</v>
       </c>
       <c r="AE31" t="inlineStr"/>
       <c r="AF31" t="n">
-        <v>-0.009324264556901163</v>
+        <v>-0.03053000177468723</v>
       </c>
       <c r="AG31" t="n">
-        <v>0.009135035430233401</v>
+        <v>0.009230499413846684</v>
       </c>
       <c r="AH31" t="inlineStr"/>
       <c r="AI31" t="n">
-        <v>0.9719680862886577</v>
+        <v>0.9731950440372746</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0.002627218280954633</v>
+        <v>0.002569078251395795</v>
       </c>
       <c r="AK31" t="inlineStr"/>
       <c r="AL31" t="n">
-        <v>0.05750339939584348</v>
+        <v>0.04864669288554757</v>
       </c>
       <c r="AM31" t="n">
-        <v>0.004080462825917504</v>
+        <v>0.00409959019304732</v>
       </c>
       <c r="AN31" t="inlineStr"/>
     </row>
@@ -3816,10 +3816,10 @@
         <v>0.02773752553385222</v>
       </c>
       <c r="K32" t="n">
-        <v>0.4586807473470598</v>
+        <v>0.5003204670714311</v>
       </c>
       <c r="L32" t="n">
-        <v>0.3970710215831935</v>
+        <v>0.4277157292674033</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
@@ -3828,16 +3828,16 @@
         <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>4.175457408489923</v>
+        <v>4.53028971271256</v>
       </c>
       <c r="P32" t="n">
-        <v>4.108392129153427</v>
+        <v>4.425992246404511</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.9792069787698368</v>
+        <v>0.9797092855898777</v>
       </c>
       <c r="R32" t="n">
-        <v>0.01388521934223277</v>
+        <v>0.01371647812577785</v>
       </c>
       <c r="S32" t="inlineStr"/>
       <c r="T32" t="inlineStr"/>
@@ -3849,38 +3849,38 @@
       </c>
       <c r="Y32" t="inlineStr"/>
       <c r="Z32" t="n">
-        <v>0.8905977097054126</v>
+        <v>0.9019187053601531</v>
       </c>
       <c r="AA32" t="n">
-        <v>0.009433410599240778</v>
+        <v>0.008931998180194519</v>
       </c>
       <c r="AB32" t="inlineStr"/>
       <c r="AC32" t="n">
-        <v>0.2263478857507</v>
+        <v>0.227125782583355</v>
       </c>
       <c r="AD32" t="n">
-        <v>0.0174594429321092</v>
+        <v>0.01745066310661357</v>
       </c>
       <c r="AE32" t="inlineStr"/>
       <c r="AF32" t="n">
-        <v>-0.653267241492739</v>
+        <v>-0.5421892580542693</v>
       </c>
       <c r="AG32" t="n">
-        <v>0.01635172288448259</v>
+        <v>0.0157928614398565</v>
       </c>
       <c r="AH32" t="inlineStr"/>
       <c r="AI32" t="n">
-        <v>0.2378540265935969</v>
+        <v>0.2311239848234773</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0.01808881656459832</v>
+        <v>0.01816850662788654</v>
       </c>
       <c r="AK32" t="inlineStr"/>
       <c r="AL32" t="n">
-        <v>0.07916749393971889</v>
+        <v>0.07382372874138743</v>
       </c>
       <c r="AM32" t="n">
-        <v>0.004877591713439125</v>
+        <v>0.004891724033596115</v>
       </c>
       <c r="AN32" t="inlineStr"/>
     </row>
@@ -3920,10 +3920,10 @@
         <v>0.02495281852103528</v>
       </c>
       <c r="K33" t="n">
-        <v>0.2751054178962024</v>
+        <v>0.2851358817564152</v>
       </c>
       <c r="L33" t="n">
-        <v>0.3042294682802154</v>
+        <v>0.318877189205591</v>
       </c>
       <c r="M33" t="n">
         <v>0</v>
@@ -3932,16 +3932,16 @@
         <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>4.166252496298712</v>
+        <v>4.308512879316226</v>
       </c>
       <c r="P33" t="n">
-        <v>4.145865324787048</v>
+        <v>4.271057230087922</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.9657376324354282</v>
+        <v>0.9655580660003291</v>
       </c>
       <c r="R33" t="n">
-        <v>0.005872318287096084</v>
+        <v>0.005887686362091251</v>
       </c>
       <c r="S33" t="inlineStr"/>
       <c r="T33" t="inlineStr"/>
@@ -3951,38 +3951,38 @@
       <c r="X33" t="inlineStr"/>
       <c r="Y33" t="inlineStr"/>
       <c r="Z33" t="n">
-        <v>0.9331222512501116</v>
+        <v>0.9329657134926262</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.01045006212430854</v>
+        <v>0.01046228497280141</v>
       </c>
       <c r="AB33" t="inlineStr"/>
       <c r="AC33" t="n">
-        <v>0.09038453464474583</v>
+        <v>0.1136216779889698</v>
       </c>
       <c r="AD33" t="n">
-        <v>0.006120543298630392</v>
+        <v>0.006041859472656011</v>
       </c>
       <c r="AE33" t="inlineStr"/>
       <c r="AF33" t="n">
-        <v>0.8547215110296592</v>
+        <v>0.8419596117641139</v>
       </c>
       <c r="AG33" t="n">
-        <v>0.004546406562272</v>
+        <v>0.004741891982336572</v>
       </c>
       <c r="AH33" t="inlineStr"/>
       <c r="AI33" t="n">
-        <v>0.7996824906554103</v>
+        <v>0.8087275627461875</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0.002123692716123653</v>
+        <v>0.00207519263564663</v>
       </c>
       <c r="AK33" t="inlineStr"/>
       <c r="AL33" t="n">
-        <v>0.4108863354325747</v>
+        <v>0.41811019654445</v>
       </c>
       <c r="AM33" t="n">
-        <v>0.0007588664378608386</v>
+        <v>0.0007541993802418439</v>
       </c>
       <c r="AN33" t="inlineStr"/>
     </row>
@@ -4024,10 +4024,10 @@
         <v>0.008784365836720525</v>
       </c>
       <c r="K34" t="n">
-        <v>0.5165578838213738</v>
+        <v>0.5350531219152354</v>
       </c>
       <c r="L34" t="n">
-        <v>0.4269943795072076</v>
+        <v>0.4496288558276344</v>
       </c>
       <c r="M34" t="n">
         <v>0</v>
@@ -4036,16 +4036,16 @@
         <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>4.125711815458049</v>
+        <v>4.263995602912937</v>
       </c>
       <c r="P34" t="n">
-        <v>4.121567441380877</v>
+        <v>4.285493285403806</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.8963689749147581</v>
+        <v>0.8874123644329036</v>
       </c>
       <c r="R34" t="n">
-        <v>0.0224490005745028</v>
+        <v>0.02339900894059084</v>
       </c>
       <c r="S34" t="inlineStr"/>
       <c r="T34" t="inlineStr"/>
@@ -4057,38 +4057,38 @@
       </c>
       <c r="Y34" t="inlineStr"/>
       <c r="Z34" t="n">
-        <v>0.8317388427930651</v>
+        <v>0.8163313485894672</v>
       </c>
       <c r="AA34" t="n">
-        <v>0.04910475167357138</v>
+        <v>0.05130374898203999</v>
       </c>
       <c r="AB34" t="inlineStr"/>
       <c r="AC34" t="n">
-        <v>0.9928960382843387</v>
+        <v>0.9926351345987787</v>
       </c>
       <c r="AD34" t="n">
-        <v>0.001993769156175944</v>
+        <v>0.002030051118949896</v>
       </c>
       <c r="AE34" t="inlineStr"/>
       <c r="AF34" t="n">
-        <v>0.6228066868572515</v>
+        <v>0.6403832964109917</v>
       </c>
       <c r="AG34" t="n">
-        <v>0.004728081865882822</v>
+        <v>0.004616607184114195</v>
       </c>
       <c r="AH34" t="inlineStr"/>
       <c r="AI34" t="n">
-        <v>0.3320590188781217</v>
+        <v>0.3490818289130715</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0.009072112940066183</v>
+        <v>0.008955763179533109</v>
       </c>
       <c r="AK34" t="inlineStr"/>
       <c r="AL34" t="n">
-        <v>0.07709921955381505</v>
+        <v>0.06473814985066573</v>
       </c>
       <c r="AM34" t="n">
-        <v>0.000933899958844064</v>
+        <v>0.0009401333509796495</v>
       </c>
       <c r="AN34" t="inlineStr"/>
     </row>
@@ -4130,10 +4130,10 @@
         <v>0.033117285160876</v>
       </c>
       <c r="K35" t="n">
-        <v>0.3001566209783726</v>
+        <v>0.3019491379002337</v>
       </c>
       <c r="L35" t="n">
-        <v>0.2394048332047958</v>
+        <v>0.2475197568595714</v>
       </c>
       <c r="M35" t="n">
         <v>0</v>
@@ -4142,16 +4142,16 @@
         <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>4.027064102812506</v>
+        <v>4.049560543950747</v>
       </c>
       <c r="P35" t="n">
-        <v>4.028153152889339</v>
+        <v>4.155419298433618</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.9967864775322797</v>
+        <v>0.9968026665346971</v>
       </c>
       <c r="R35" t="n">
-        <v>0.005647349326062998</v>
+        <v>0.005633106328177837</v>
       </c>
       <c r="S35" t="inlineStr"/>
       <c r="T35" t="inlineStr"/>
@@ -4161,10 +4161,10 @@
       <c r="X35" t="inlineStr"/>
       <c r="Y35" t="inlineStr"/>
       <c r="Z35" t="n">
-        <v>0.9858831089629368</v>
+        <v>0.986026611126027</v>
       </c>
       <c r="AA35" t="n">
-        <v>0.006483566569065676</v>
+        <v>0.006450528757181458</v>
       </c>
       <c r="AB35" t="inlineStr"/>
       <c r="AC35" t="inlineStr"/>
@@ -4173,24 +4173,24 @@
       </c>
       <c r="AE35" t="inlineStr"/>
       <c r="AF35" t="n">
-        <v>0.6252750088810934</v>
+        <v>0.6263631436893655</v>
       </c>
       <c r="AG35" t="n">
-        <v>0.009141977069239587</v>
+        <v>0.009128694080652602</v>
       </c>
       <c r="AH35" t="inlineStr"/>
       <c r="AI35" t="n">
-        <v>0.7268881631822571</v>
+        <v>0.725976549783718</v>
       </c>
       <c r="AJ35" t="n">
-        <v>0.002111893589370387</v>
+        <v>0.002115415272365411</v>
       </c>
       <c r="AK35" t="inlineStr"/>
       <c r="AL35" t="n">
-        <v>0.5254577496450483</v>
+        <v>0.5278622431736911</v>
       </c>
       <c r="AM35" t="n">
-        <v>0.002338991560940443</v>
+        <v>0.002333058229972926</v>
       </c>
       <c r="AN35" t="inlineStr"/>
     </row>
@@ -4232,10 +4232,10 @@
         <v>0.02290841461070009</v>
       </c>
       <c r="K36" t="n">
-        <v>0.4200622561347667</v>
+        <v>0.4306133506575378</v>
       </c>
       <c r="L36" t="n">
-        <v>0.3842170973366046</v>
+        <v>0.3952277307226713</v>
       </c>
       <c r="M36" t="n">
         <v>0</v>
@@ -4244,16 +4244,16 @@
         <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>4.208803672383319</v>
+        <v>4.307865273041947</v>
       </c>
       <c r="P36" t="n">
-        <v>4.208370513294874</v>
+        <v>4.321519067505179</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.9835100219792995</v>
+        <v>0.9835354887150053</v>
       </c>
       <c r="R36" t="n">
-        <v>0.01163616115699152</v>
+        <v>0.01162717237780395</v>
       </c>
       <c r="S36" t="inlineStr"/>
       <c r="T36" t="inlineStr"/>
@@ -4265,38 +4265,38 @@
       </c>
       <c r="Y36" t="inlineStr"/>
       <c r="Z36" t="n">
-        <v>0.8079645586487443</v>
+        <v>0.8084317089137957</v>
       </c>
       <c r="AA36" t="n">
-        <v>0.01904943476840007</v>
+        <v>0.01902625059212809</v>
       </c>
       <c r="AB36" t="inlineStr"/>
       <c r="AC36" t="n">
-        <v>0.3717385458786803</v>
+        <v>0.3717595996132993</v>
       </c>
       <c r="AD36" t="n">
-        <v>0.008130975314783554</v>
+        <v>0.008130839074664459</v>
       </c>
       <c r="AE36" t="inlineStr"/>
       <c r="AF36" t="n">
-        <v>0.06868358318826084</v>
+        <v>0.06964126973225437</v>
       </c>
       <c r="AG36" t="n">
-        <v>0.01346426915943055</v>
+        <v>0.01345734462455408</v>
       </c>
       <c r="AH36" t="inlineStr"/>
       <c r="AI36" t="n">
-        <v>0.7293098918225451</v>
+        <v>0.728509641823178</v>
       </c>
       <c r="AJ36" t="n">
-        <v>0.006095125915584966</v>
+        <v>0.006104128876372306</v>
       </c>
       <c r="AK36" t="inlineStr"/>
       <c r="AL36" t="n">
-        <v>0.1648704835151593</v>
+        <v>0.1670701935279308</v>
       </c>
       <c r="AM36" t="n">
-        <v>0.004041209743356386</v>
+        <v>0.004035884011984705</v>
       </c>
       <c r="AN36" t="inlineStr"/>
     </row>
@@ -4338,10 +4338,10 @@
         <v>0.007462828179086988</v>
       </c>
       <c r="K37" t="n">
-        <v>0.1057540787127461</v>
+        <v>0.1032759135620988</v>
       </c>
       <c r="L37" t="n">
-        <v>0.1082833480351216</v>
+        <v>0.1052974555473489</v>
       </c>
       <c r="M37" t="n">
         <v>0</v>
@@ -4350,61 +4350,61 @@
         <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>4.325915956550759</v>
+        <v>4.230764125716685</v>
       </c>
       <c r="P37" t="n">
-        <v>4.363108308494082</v>
+        <v>4.263232513024087</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.9931768556422819</v>
+        <v>0.9931562102604981</v>
       </c>
       <c r="R37" t="n">
-        <v>0.005504033253222641</v>
+        <v>0.005512353980038237</v>
       </c>
       <c r="S37" t="inlineStr"/>
       <c r="T37" t="inlineStr"/>
       <c r="U37" t="inlineStr"/>
       <c r="V37" t="inlineStr"/>
       <c r="W37" t="n">
-        <v>0.02213131017157455</v>
+        <v>0.02232969103987603</v>
       </c>
       <c r="X37" t="n">
-        <v>0.0004230470303942787</v>
+        <v>0.0004230041163021422</v>
       </c>
       <c r="Y37" t="inlineStr"/>
       <c r="Z37" t="n">
-        <v>0.9983945672884703</v>
+        <v>0.9984068109743827</v>
       </c>
       <c r="AA37" t="n">
-        <v>0.001902329413126887</v>
+        <v>0.00189506155895734</v>
       </c>
       <c r="AB37" t="inlineStr"/>
       <c r="AC37" t="n">
-        <v>-0.5024126061334153</v>
+        <v>-0.5007957506550722</v>
       </c>
       <c r="AD37" t="n">
-        <v>0.007760830944242138</v>
+        <v>0.007756653822795167</v>
       </c>
       <c r="AE37" t="inlineStr"/>
       <c r="AF37" t="n">
-        <v>0.9123580339123846</v>
+        <v>0.9118017575571626</v>
       </c>
       <c r="AG37" t="n">
-        <v>0.009634021853115517</v>
+        <v>0.009664547763306183</v>
       </c>
       <c r="AH37" t="inlineStr"/>
       <c r="AI37" t="n">
-        <v>0.9405286457972025</v>
+        <v>0.940625407252214</v>
       </c>
       <c r="AJ37" t="n">
-        <v>0.002187919986795259</v>
+        <v>0.002186139360582258</v>
       </c>
       <c r="AK37" t="inlineStr"/>
       <c r="AL37" t="n">
-        <v>0.9999999828682329</v>
+        <v>0.9999996806026822</v>
       </c>
       <c r="AM37" t="n">
-        <v>1.288418123788941e-07</v>
+        <v>5.563157774895456e-07</v>
       </c>
       <c r="AN37" t="inlineStr"/>
     </row>
@@ -4446,10 +4446,10 @@
         <v>0.003185097564105027</v>
       </c>
       <c r="K38" t="n">
-        <v>0.1483762115382365</v>
+        <v>0.1416438943560188</v>
       </c>
       <c r="L38" t="n">
-        <v>0.1145173439330902</v>
+        <v>0.1094955221332978</v>
       </c>
       <c r="M38" t="n">
         <v>0</v>
@@ -4458,61 +4458,61 @@
         <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>4.296526671931293</v>
+        <v>4.113546643685265</v>
       </c>
       <c r="P38" t="n">
-        <v>4.354332778840533</v>
+        <v>4.195575058726416</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.9537566371124399</v>
+        <v>0.9538747494938609</v>
       </c>
       <c r="R38" t="n">
-        <v>0.01206632146546173</v>
+        <v>0.01205090202935683</v>
       </c>
       <c r="S38" t="inlineStr"/>
       <c r="T38" t="inlineStr"/>
       <c r="U38" t="inlineStr"/>
       <c r="V38" t="inlineStr"/>
       <c r="W38" t="n">
-        <v>0.1898619657267673</v>
+        <v>0.1856746702867531</v>
       </c>
       <c r="X38" t="n">
-        <v>0.001179768030053185</v>
+        <v>0.001182812986735585</v>
       </c>
       <c r="Y38" t="inlineStr"/>
       <c r="Z38" t="n">
-        <v>0.8110566128695375</v>
+        <v>0.8117400695136249</v>
       </c>
       <c r="AA38" t="n">
-        <v>0.02096509654714988</v>
+        <v>0.02092714413211252</v>
       </c>
       <c r="AB38" t="inlineStr"/>
       <c r="AC38" t="n">
-        <v>-0.3930104832538854</v>
+        <v>-0.3889791861968517</v>
       </c>
       <c r="AD38" t="n">
-        <v>0.01713062726933477</v>
+        <v>0.01710582175510812</v>
       </c>
       <c r="AE38" t="inlineStr"/>
       <c r="AF38" t="n">
-        <v>0.9655307968817377</v>
+        <v>0.9638846440510584</v>
       </c>
       <c r="AG38" t="n">
-        <v>0.004309627963402</v>
+        <v>0.004411335700999675</v>
       </c>
       <c r="AH38" t="inlineStr"/>
       <c r="AI38" t="n">
-        <v>-1.201048055958978</v>
+        <v>-1.16109724143762</v>
       </c>
       <c r="AJ38" t="n">
-        <v>0.004900831290951427</v>
+        <v>0.004856150575323175</v>
       </c>
       <c r="AK38" t="inlineStr"/>
       <c r="AL38" t="n">
-        <v>0.9999971243826041</v>
+        <v>0.9999973457512438</v>
       </c>
       <c r="AM38" t="n">
-        <v>6.796466770352051e-07</v>
+        <v>6.529628274818922e-07</v>
       </c>
       <c r="AN38" t="inlineStr"/>
     </row>
@@ -4554,10 +4554,10 @@
         <v>0.03277409385829239</v>
       </c>
       <c r="K39" t="n">
-        <v>0.1491847814540822</v>
+        <v>0.1514776863482813</v>
       </c>
       <c r="L39" t="n">
-        <v>0.1315190608579613</v>
+        <v>0.1340732886312007</v>
       </c>
       <c r="M39" t="n">
         <v>0</v>
@@ -4566,16 +4566,16 @@
         <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>4.198070974628081</v>
+        <v>4.258531293425802</v>
       </c>
       <c r="P39" t="n">
-        <v>4.189041007434728</v>
+        <v>4.266000771504852</v>
       </c>
       <c r="Q39" t="n">
-        <v>0.9829561396814041</v>
+        <v>0.9829587365995249</v>
       </c>
       <c r="R39" t="n">
-        <v>0.008738539804861039</v>
+        <v>0.008737874047912922</v>
       </c>
       <c r="S39" t="inlineStr"/>
       <c r="T39" t="inlineStr"/>
@@ -4585,38 +4585,38 @@
       <c r="X39" t="inlineStr"/>
       <c r="Y39" t="inlineStr"/>
       <c r="Z39" t="n">
-        <v>0.8831099684226863</v>
+        <v>0.8831627197684985</v>
       </c>
       <c r="AA39" t="n">
-        <v>0.01144300007671734</v>
+        <v>0.01144041772745747</v>
       </c>
       <c r="AB39" t="inlineStr"/>
       <c r="AC39" t="n">
-        <v>0.125328563772693</v>
+        <v>0.1261866791231349</v>
       </c>
       <c r="AD39" t="n">
-        <v>0.001391409866112907</v>
+        <v>0.001390727162238847</v>
       </c>
       <c r="AE39" t="inlineStr"/>
       <c r="AF39" t="n">
-        <v>-0.04780206648583341</v>
+        <v>-0.04784161916678453</v>
       </c>
       <c r="AG39" t="n">
-        <v>0.01466174213525816</v>
+        <v>0.0146620188601067</v>
       </c>
       <c r="AH39" t="inlineStr"/>
       <c r="AI39" t="n">
-        <v>0.7520587042010333</v>
+        <v>0.7521066762451492</v>
       </c>
       <c r="AJ39" t="n">
-        <v>0.005403376423162519</v>
+        <v>0.005402853671293663</v>
       </c>
       <c r="AK39" t="inlineStr"/>
       <c r="AL39" t="n">
-        <v>-0.1201814015724485</v>
+        <v>-0.1202639646824426</v>
       </c>
       <c r="AM39" t="n">
-        <v>0.002183794455355543</v>
+        <v>0.002183874932294108</v>
       </c>
       <c r="AN39" t="inlineStr"/>
     </row>
@@ -4658,28 +4658,28 @@
         <v>0.003165060709665684</v>
       </c>
       <c r="K40" t="n">
-        <v>0.3948410699014029</v>
+        <v>0.369449111753018</v>
       </c>
       <c r="L40" t="n">
-        <v>0.4256977808607552</v>
+        <v>0.415290884536345</v>
       </c>
       <c r="M40" t="n">
-        <v>0.4017580473656158</v>
+        <v>0.3648046244607287</v>
       </c>
       <c r="N40" t="n">
-        <v>0.0533861988192782</v>
+        <v>0.04937948541704858</v>
       </c>
       <c r="O40" t="n">
-        <v>4.568405641987668</v>
+        <v>4.291879477204492</v>
       </c>
       <c r="P40" t="n">
-        <v>4.623819116867184</v>
+        <v>4.517574852075538</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.9911350056668842</v>
+        <v>0.9911917152218972</v>
       </c>
       <c r="R40" t="n">
-        <v>0.005655607941841044</v>
+        <v>0.005637489397757618</v>
       </c>
       <c r="S40" t="inlineStr"/>
       <c r="T40" t="inlineStr"/>
@@ -4689,38 +4689,38 @@
       <c r="X40" t="inlineStr"/>
       <c r="Y40" t="inlineStr"/>
       <c r="Z40" t="n">
-        <v>0.965066105208628</v>
+        <v>0.9653269449780828</v>
       </c>
       <c r="AA40" t="n">
-        <v>0.01127937943389813</v>
+        <v>0.01123719084758885</v>
       </c>
       <c r="AB40" t="inlineStr"/>
       <c r="AC40" t="n">
-        <v>0.9255183098071693</v>
+        <v>0.9342934874359159</v>
       </c>
       <c r="AD40" t="n">
-        <v>0.0006208793219989737</v>
+        <v>0.0005831585441500598</v>
       </c>
       <c r="AE40" t="inlineStr"/>
       <c r="AF40" t="n">
-        <v>0.9816453468070969</v>
+        <v>0.9817570138481977</v>
       </c>
       <c r="AG40" t="n">
-        <v>0.003402956466670876</v>
+        <v>0.003392589128107481</v>
       </c>
       <c r="AH40" t="inlineStr"/>
       <c r="AI40" t="n">
-        <v>0.9976464426978378</v>
+        <v>0.9975745222153841</v>
       </c>
       <c r="AJ40" t="n">
-        <v>0.002178658093229707</v>
+        <v>0.002211695539662375</v>
       </c>
       <c r="AK40" t="inlineStr"/>
       <c r="AL40" t="n">
-        <v>0.9999999156747157</v>
+        <v>0.9999999504038204</v>
       </c>
       <c r="AM40" t="n">
-        <v>1.765633802868788e-07</v>
+        <v>1.354084727160346e-07</v>
       </c>
       <c r="AN40" t="inlineStr"/>
     </row>
@@ -4762,10 +4762,10 @@
         <v>0.01422966781757511</v>
       </c>
       <c r="K41" t="n">
-        <v>0.2672649319402196</v>
+        <v>0.2579668639842531</v>
       </c>
       <c r="L41" t="n">
-        <v>0.2888214873181956</v>
+        <v>0.2827780651877471</v>
       </c>
       <c r="M41" t="n">
         <v>0</v>
@@ -4774,16 +4774,16 @@
         <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>4.586833780976132</v>
+        <v>4.436658070637798</v>
       </c>
       <c r="P41" t="n">
-        <v>4.613047272542106</v>
+        <v>4.506800334756738</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.9934763221255247</v>
+        <v>0.993566285594778</v>
       </c>
       <c r="R41" t="n">
-        <v>0.006259811568311294</v>
+        <v>0.006216499390980136</v>
       </c>
       <c r="S41" t="inlineStr"/>
       <c r="T41" t="inlineStr"/>
@@ -4793,38 +4793,38 @@
       <c r="X41" t="inlineStr"/>
       <c r="Y41" t="inlineStr"/>
       <c r="Z41" t="n">
-        <v>0.8660037616156491</v>
+        <v>0.8657218270983299</v>
       </c>
       <c r="AA41" t="n">
-        <v>0.01065990969056796</v>
+        <v>0.01067111827864404</v>
       </c>
       <c r="AB41" t="inlineStr"/>
       <c r="AC41" t="n">
-        <v>0.6469566662027474</v>
+        <v>0.6406308080845335</v>
       </c>
       <c r="AD41" t="n">
-        <v>0.001481789030163979</v>
+        <v>0.001495005495576569</v>
       </c>
       <c r="AE41" t="inlineStr"/>
       <c r="AF41" t="n">
-        <v>0.9689663709594214</v>
+        <v>0.9709982371512711</v>
       </c>
       <c r="AG41" t="n">
-        <v>0.004723426298359978</v>
+        <v>0.004566180336330381</v>
       </c>
       <c r="AH41" t="inlineStr"/>
       <c r="AI41" t="n">
-        <v>0.9454319545699498</v>
+        <v>0.9468872634985886</v>
       </c>
       <c r="AJ41" t="n">
-        <v>0.007531125076749281</v>
+        <v>0.007430020300221683</v>
       </c>
       <c r="AK41" t="inlineStr"/>
       <c r="AL41" t="n">
-        <v>0.8995948146727818</v>
+        <v>0.9002450500253879</v>
       </c>
       <c r="AM41" t="n">
-        <v>0.001033552173409745</v>
+        <v>0.001030200036920166</v>
       </c>
       <c r="AN41" t="inlineStr"/>
     </row>
@@ -4866,28 +4866,28 @@
         <v>0.01067227249555984</v>
       </c>
       <c r="K42" t="n">
-        <v>0.3175477744289016</v>
+        <v>0.3170323710220794</v>
       </c>
       <c r="L42" t="n">
-        <v>0.4071822285233245</v>
+        <v>0.3993080830134812</v>
       </c>
       <c r="M42" t="n">
-        <v>0.002457234051949975</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>4.91446810389995e-05</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>4.524889107463629</v>
+        <v>4.517983722179811</v>
       </c>
       <c r="P42" t="n">
-        <v>4.592867768406266</v>
+        <v>4.483687791166234</v>
       </c>
       <c r="Q42" t="n">
-        <v>0.9578979316030761</v>
+        <v>0.9576255058915635</v>
       </c>
       <c r="R42" t="n">
-        <v>0.01358785986745841</v>
+        <v>0.01363174979733731</v>
       </c>
       <c r="S42" t="inlineStr"/>
       <c r="T42" t="inlineStr"/>
@@ -4897,31 +4897,31 @@
       <c r="X42" t="inlineStr"/>
       <c r="Y42" t="inlineStr"/>
       <c r="Z42" t="n">
-        <v>0.8262292976336916</v>
+        <v>0.8251301097521397</v>
       </c>
       <c r="AA42" t="n">
-        <v>0.02287602133705518</v>
+        <v>0.02294825850524475</v>
       </c>
       <c r="AB42" t="inlineStr"/>
       <c r="AC42" t="n">
-        <v>0.9790624781339082</v>
+        <v>0.9707053533915105</v>
       </c>
       <c r="AD42" t="n">
-        <v>0.0007733801798722115</v>
+        <v>0.0009147965762054967</v>
       </c>
       <c r="AE42" t="inlineStr"/>
       <c r="AF42" t="n">
-        <v>0.6850751806285293</v>
+        <v>0.6837167814146191</v>
       </c>
       <c r="AG42" t="n">
-        <v>0.01637836411863444</v>
+        <v>0.01641364939248493</v>
       </c>
       <c r="AH42" t="inlineStr"/>
       <c r="AI42" t="n">
-        <v>0.991737496504515</v>
+        <v>0.9912451388612975</v>
       </c>
       <c r="AJ42" t="n">
-        <v>0.002811009554955053</v>
+        <v>0.002893550889321847</v>
       </c>
       <c r="AK42" t="inlineStr"/>
       <c r="AL42" t="inlineStr"/>
@@ -4968,28 +4968,28 @@
         <v>0.0240059836138475</v>
       </c>
       <c r="K43" t="n">
-        <v>0.2502194438201192</v>
+        <v>0.2387871798140294</v>
       </c>
       <c r="L43" t="n">
-        <v>0.3403997695012065</v>
+        <v>0.3353014420366665</v>
       </c>
       <c r="M43" t="n">
-        <v>0.336300729448571</v>
+        <v>0.3126694229390591</v>
       </c>
       <c r="N43" t="n">
-        <v>0.04179838433328786</v>
+        <v>0.03893489566485876</v>
       </c>
       <c r="O43" t="n">
-        <v>4.103051778684014</v>
+        <v>3.927442132088704</v>
       </c>
       <c r="P43" t="n">
-        <v>4.257619558485245</v>
+        <v>4.243780671119279</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.9463075286860317</v>
+        <v>0.9475162360891128</v>
       </c>
       <c r="R43" t="n">
-        <v>0.01415819315629504</v>
+        <v>0.0139979237253551</v>
       </c>
       <c r="S43" t="inlineStr"/>
       <c r="T43" t="inlineStr"/>
@@ -4999,38 +4999,38 @@
       <c r="X43" t="inlineStr"/>
       <c r="Y43" t="inlineStr"/>
       <c r="Z43" t="n">
-        <v>0.9005905264681827</v>
+        <v>0.9038189645539311</v>
       </c>
       <c r="AA43" t="n">
-        <v>0.02711552444059147</v>
+        <v>0.02667158626857022</v>
       </c>
       <c r="AB43" t="inlineStr"/>
       <c r="AC43" t="n">
-        <v>0.7102653163238406</v>
+        <v>0.7161858144185551</v>
       </c>
       <c r="AD43" t="n">
-        <v>0.00254204704092744</v>
+        <v>0.002515940630695684</v>
       </c>
       <c r="AE43" t="inlineStr"/>
       <c r="AF43" t="n">
-        <v>0.743212269402922</v>
+        <v>0.7417346933952286</v>
       </c>
       <c r="AG43" t="n">
-        <v>0.01605893846026579</v>
+        <v>0.01610507436084752</v>
       </c>
       <c r="AH43" t="inlineStr"/>
       <c r="AI43" t="n">
-        <v>0.9252727092352633</v>
+        <v>0.9267067145085874</v>
       </c>
       <c r="AJ43" t="n">
-        <v>0.001532405738274116</v>
+        <v>0.001517631198841486</v>
       </c>
       <c r="AK43" t="inlineStr"/>
       <c r="AL43" t="n">
-        <v>0.9796918467916849</v>
+        <v>0.9791523323083495</v>
       </c>
       <c r="AM43" t="n">
-        <v>0.0005663272824955718</v>
+        <v>0.0005738006110159018</v>
       </c>
       <c r="AN43" t="inlineStr"/>
     </row>
@@ -5072,10 +5072,10 @@
         <v>0.02192364384915694</v>
       </c>
       <c r="K44" t="n">
-        <v>0.1778728783246155</v>
+        <v>0.1743546614482898</v>
       </c>
       <c r="L44" t="n">
-        <v>0.3789954072656637</v>
+        <v>0.3607161911403574</v>
       </c>
       <c r="M44" t="n">
         <v>0</v>
@@ -5084,16 +5084,16 @@
         <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>4.33244628845221</v>
+        <v>4.252007996567885</v>
       </c>
       <c r="P44" t="n">
-        <v>4.593102175455646</v>
+        <v>4.379876703707501</v>
       </c>
       <c r="Q44" t="n">
-        <v>0.9319435325001026</v>
+        <v>0.9322289901765384</v>
       </c>
       <c r="R44" t="n">
-        <v>0.008885591275339017</v>
+        <v>0.00886693672513535</v>
       </c>
       <c r="S44" t="inlineStr"/>
       <c r="T44" t="inlineStr"/>
@@ -5103,38 +5103,38 @@
       <c r="X44" t="inlineStr"/>
       <c r="Y44" t="inlineStr"/>
       <c r="Z44" t="n">
-        <v>0.9114145470133936</v>
+        <v>0.9118343741510551</v>
       </c>
       <c r="AA44" t="n">
-        <v>0.01334680746483308</v>
+        <v>0.01331514308618879</v>
       </c>
       <c r="AB44" t="inlineStr"/>
       <c r="AC44" t="n">
-        <v>0.7652805407589276</v>
+        <v>0.7629989410251768</v>
       </c>
       <c r="AD44" t="n">
-        <v>0.005373114137091154</v>
+        <v>0.005399165764861191</v>
       </c>
       <c r="AE44" t="inlineStr"/>
       <c r="AF44" t="n">
-        <v>0.9086325102962264</v>
+        <v>0.9073004518172708</v>
       </c>
       <c r="AG44" t="n">
-        <v>0.01057204818929559</v>
+        <v>0.01064883496157211</v>
       </c>
       <c r="AH44" t="inlineStr"/>
       <c r="AI44" t="n">
-        <v>0.8417278495763652</v>
+        <v>0.8476536494680851</v>
       </c>
       <c r="AJ44" t="n">
-        <v>0.008642656904038181</v>
+        <v>0.008479320456552345</v>
       </c>
       <c r="AK44" t="inlineStr"/>
       <c r="AL44" t="n">
-        <v>0.7108236323566857</v>
+        <v>0.6941211503297948</v>
       </c>
       <c r="AM44" t="n">
-        <v>0.001138997476144957</v>
+        <v>0.001171429311538728</v>
       </c>
       <c r="AN44" t="inlineStr"/>
     </row>
@@ -5176,10 +5176,10 @@
         <v>0.02487778863857871</v>
       </c>
       <c r="K45" t="n">
-        <v>0.399617491041528</v>
+        <v>0.3961005288343256</v>
       </c>
       <c r="L45" t="n">
-        <v>0.2473456145660608</v>
+        <v>0.2489886367685431</v>
       </c>
       <c r="M45" t="n">
         <v>0</v>
@@ -5188,16 +5188,16 @@
         <v>0</v>
       </c>
       <c r="O45" t="n">
-        <v>4.249422615389083</v>
+        <v>4.214350986480778</v>
       </c>
       <c r="P45" t="n">
-        <v>4.265286307023164</v>
+        <v>4.320122892021073</v>
       </c>
       <c r="Q45" t="n">
-        <v>0.9701726788793036</v>
+        <v>0.9702313440706339</v>
       </c>
       <c r="R45" t="n">
-        <v>0.008434652993005241</v>
+        <v>0.008426354157252566</v>
       </c>
       <c r="S45" t="inlineStr"/>
       <c r="T45" t="inlineStr"/>
@@ -5207,38 +5207,38 @@
       <c r="X45" t="inlineStr"/>
       <c r="Y45" t="inlineStr"/>
       <c r="Z45" t="n">
-        <v>0.9783730772119841</v>
+        <v>0.9784347599200411</v>
       </c>
       <c r="AA45" t="n">
-        <v>0.01257841089639273</v>
+        <v>0.01256046048187576</v>
       </c>
       <c r="AB45" t="inlineStr"/>
       <c r="AC45" t="n">
-        <v>0.926196659549218</v>
+        <v>0.9263908096369194</v>
       </c>
       <c r="AD45" t="n">
-        <v>0.007124896570581607</v>
+        <v>0.007115518876935951</v>
       </c>
       <c r="AE45" t="inlineStr"/>
       <c r="AF45" t="n">
-        <v>0.8721312616593169</v>
+        <v>0.8721738592106956</v>
       </c>
       <c r="AG45" t="n">
-        <v>0.008497664350863304</v>
+        <v>0.008496248798279732</v>
       </c>
       <c r="AH45" t="inlineStr"/>
       <c r="AI45" t="n">
-        <v>0.9199585364815599</v>
+        <v>0.9200557691923775</v>
       </c>
       <c r="AJ45" t="n">
-        <v>0.008609728169577925</v>
+        <v>0.008604497120791905</v>
       </c>
       <c r="AK45" t="inlineStr"/>
       <c r="AL45" t="n">
-        <v>0.9793279983915609</v>
+        <v>0.9793660680563808</v>
       </c>
       <c r="AM45" t="n">
-        <v>0.0006313201787742881</v>
+        <v>0.0006307385896372336</v>
       </c>
       <c r="AN45" t="inlineStr"/>
     </row>
@@ -5280,10 +5280,10 @@
         <v>0.04354702384994095</v>
       </c>
       <c r="K46" t="n">
-        <v>0.4729359869420497</v>
+        <v>0.4197523519087317</v>
       </c>
       <c r="L46" t="n">
-        <v>0.3613876143166579</v>
+        <v>0.3538478146508492</v>
       </c>
       <c r="M46" t="n">
         <v>0</v>
@@ -5292,16 +5292,16 @@
         <v>0</v>
       </c>
       <c r="O46" t="n">
-        <v>4.220017038479095</v>
+        <v>3.774562388265622</v>
       </c>
       <c r="P46" t="n">
-        <v>4.495836855358798</v>
+        <v>4.469631474021861</v>
       </c>
       <c r="Q46" t="n">
-        <v>0.9665267445317528</v>
+        <v>0.9691700565078264</v>
       </c>
       <c r="R46" t="n">
-        <v>0.008723186907028606</v>
+        <v>0.008371678975015451</v>
       </c>
       <c r="S46" t="inlineStr"/>
       <c r="T46" t="inlineStr"/>
@@ -5311,38 +5311,38 @@
       <c r="X46" t="inlineStr"/>
       <c r="Y46" t="inlineStr"/>
       <c r="Z46" t="n">
-        <v>0.9832186455653973</v>
+        <v>0.9852529476931888</v>
       </c>
       <c r="AA46" t="n">
-        <v>0.00998911376145646</v>
+        <v>0.009364100463556499</v>
       </c>
       <c r="AB46" t="inlineStr"/>
       <c r="AC46" t="n">
-        <v>0.9291294401075613</v>
+        <v>0.9337676750333243</v>
       </c>
       <c r="AD46" t="n">
-        <v>0.009881332818604354</v>
+        <v>0.009552512080250805</v>
       </c>
       <c r="AE46" t="inlineStr"/>
       <c r="AF46" t="n">
-        <v>0.9829081762135977</v>
+        <v>0.9846233103721167</v>
       </c>
       <c r="AG46" t="n">
-        <v>0.002140044233702968</v>
+        <v>0.00202983142116043</v>
       </c>
       <c r="AH46" t="inlineStr"/>
       <c r="AI46" t="n">
-        <v>0.8382040096312283</v>
+        <v>0.8483107869021425</v>
       </c>
       <c r="AJ46" t="n">
-        <v>0.01332019707833567</v>
+        <v>0.01289745800054248</v>
       </c>
       <c r="AK46" t="inlineStr"/>
       <c r="AL46" t="n">
-        <v>0.9860668030814878</v>
+        <v>0.9862790930877983</v>
       </c>
       <c r="AM46" t="n">
-        <v>0.001019498668720425</v>
+        <v>0.001011702176816321</v>
       </c>
       <c r="AN46" t="inlineStr"/>
     </row>
@@ -5384,10 +5384,10 @@
         <v>0.01548193654302897</v>
       </c>
       <c r="K47" t="n">
-        <v>0.251984504906933</v>
+        <v>0.2493695583752376</v>
       </c>
       <c r="L47" t="n">
-        <v>0.3439320392361471</v>
+        <v>0.334323690586066</v>
       </c>
       <c r="M47" t="n">
         <v>0</v>
@@ -5396,16 +5396,16 @@
         <v>0</v>
       </c>
       <c r="O47" t="n">
-        <v>4.262041686410713</v>
+        <v>4.220558446554917</v>
       </c>
       <c r="P47" t="n">
-        <v>4.414315573316022</v>
+        <v>4.34135409092813</v>
       </c>
       <c r="Q47" t="n">
-        <v>0.9419684170552493</v>
+        <v>0.9415799702410498</v>
       </c>
       <c r="R47" t="n">
-        <v>0.009052995132189677</v>
+        <v>0.009083243677576116</v>
       </c>
       <c r="S47" t="inlineStr"/>
       <c r="T47" t="inlineStr"/>
@@ -5415,38 +5415,38 @@
       <c r="X47" t="inlineStr"/>
       <c r="Y47" t="inlineStr"/>
       <c r="Z47" t="n">
-        <v>0.933883964156669</v>
+        <v>0.9337982099239828</v>
       </c>
       <c r="AA47" t="n">
-        <v>0.01416756260572894</v>
+        <v>0.01417674747859337</v>
       </c>
       <c r="AB47" t="inlineStr"/>
       <c r="AC47" t="n">
-        <v>0.810896173029635</v>
+        <v>0.812072719846809</v>
       </c>
       <c r="AD47" t="n">
-        <v>0.006794620159821748</v>
+        <v>0.006773450144281096</v>
       </c>
       <c r="AE47" t="inlineStr"/>
       <c r="AF47" t="n">
-        <v>0.8256260049952657</v>
+        <v>0.8225035807354626</v>
       </c>
       <c r="AG47" t="n">
-        <v>0.01245077240543421</v>
+        <v>0.01256175254053157</v>
       </c>
       <c r="AH47" t="inlineStr"/>
       <c r="AI47" t="n">
-        <v>0.9685601463200485</v>
+        <v>0.9685788529767632</v>
       </c>
       <c r="AJ47" t="n">
-        <v>0.002749805806420708</v>
+        <v>0.002748987619929098</v>
       </c>
       <c r="AK47" t="inlineStr"/>
       <c r="AL47" t="n">
-        <v>0.9140451364309301</v>
+        <v>0.9144623201650787</v>
       </c>
       <c r="AM47" t="n">
-        <v>0.000560129939208636</v>
+        <v>0.0005587689846373318</v>
       </c>
       <c r="AN47" t="inlineStr"/>
     </row>
@@ -5488,10 +5488,10 @@
         <v>0.04054047652094685</v>
       </c>
       <c r="K48" t="n">
-        <v>0.1259930651411941</v>
+        <v>0.109062118721277</v>
       </c>
       <c r="L48" t="n">
-        <v>0.4829909521356937</v>
+        <v>0.4819694991065029</v>
       </c>
       <c r="M48" t="n">
         <v>0</v>
@@ -5500,16 +5500,16 @@
         <v>0</v>
       </c>
       <c r="O48" t="n">
-        <v>4.090716553477905</v>
+        <v>3.575232101365941</v>
       </c>
       <c r="P48" t="n">
-        <v>4.395585492355544</v>
+        <v>4.350282899258956</v>
       </c>
       <c r="Q48" t="n">
-        <v>0.9812143299570286</v>
+        <v>0.9799807072945712</v>
       </c>
       <c r="R48" t="n">
-        <v>0.007067105085269524</v>
+        <v>0.007295458123566167</v>
       </c>
       <c r="S48" t="inlineStr"/>
       <c r="T48" t="inlineStr"/>
@@ -5519,38 +5519,38 @@
       <c r="X48" t="inlineStr"/>
       <c r="Y48" t="inlineStr"/>
       <c r="Z48" t="n">
-        <v>0.9699694946918054</v>
+        <v>0.9670514601319901</v>
       </c>
       <c r="AA48" t="n">
-        <v>0.01267145679418735</v>
+        <v>0.01327282333452833</v>
       </c>
       <c r="AB48" t="inlineStr"/>
       <c r="AC48" t="n">
-        <v>0.8497517749665638</v>
+        <v>0.8511299313845332</v>
       </c>
       <c r="AD48" t="n">
-        <v>0.006547809298516494</v>
+        <v>0.006517710128062508</v>
       </c>
       <c r="AE48" t="inlineStr"/>
       <c r="AF48" t="n">
-        <v>0.9883541968936689</v>
+        <v>0.9879783933259402</v>
       </c>
       <c r="AG48" t="n">
-        <v>0.006258134678794291</v>
+        <v>0.006358306232025789</v>
       </c>
       <c r="AH48" t="inlineStr"/>
       <c r="AI48" t="n">
-        <v>0.8959851579885433</v>
+        <v>0.8971030179730674</v>
       </c>
       <c r="AJ48" t="n">
-        <v>0.002665168722003858</v>
+        <v>0.002650808591286444</v>
       </c>
       <c r="AK48" t="inlineStr"/>
       <c r="AL48" t="n">
-        <v>0.9997852655776804</v>
+        <v>0.9997445041281109</v>
       </c>
       <c r="AM48" t="n">
-        <v>0.0001134617109012748</v>
+        <v>0.0001237628887575433</v>
       </c>
       <c r="AN48" t="inlineStr"/>
     </row>
@@ -5592,28 +5592,28 @@
         <v>0.02297528417150188</v>
       </c>
       <c r="K49" t="n">
-        <v>0.3889285704498146</v>
+        <v>0.3626999688036405</v>
       </c>
       <c r="L49" t="n">
-        <v>0.4678817553966931</v>
+        <v>0.4627744792868939</v>
       </c>
       <c r="M49" t="n">
-        <v>0.06202462859300606</v>
+        <v>0.005612064057232025</v>
       </c>
       <c r="N49" t="n">
-        <v>0.001427840131873355</v>
+        <v>0.0001122412811446405</v>
       </c>
       <c r="O49" t="n">
-        <v>4.312452942874997</v>
+        <v>4.039369874984286</v>
       </c>
       <c r="P49" t="n">
-        <v>4.422077437510787</v>
+        <v>4.387228406735362</v>
       </c>
       <c r="Q49" t="n">
-        <v>0.9254433319770694</v>
+        <v>0.9269361823572662</v>
       </c>
       <c r="R49" t="n">
-        <v>0.01294251042103262</v>
+        <v>0.01281228109283159</v>
       </c>
       <c r="S49" t="inlineStr"/>
       <c r="T49" t="inlineStr"/>
@@ -5623,38 +5623,38 @@
       <c r="X49" t="inlineStr"/>
       <c r="Y49" t="inlineStr"/>
       <c r="Z49" t="n">
-        <v>0.9243734515088515</v>
+        <v>0.9261847630939968</v>
       </c>
       <c r="AA49" t="n">
-        <v>0.01854983099802832</v>
+        <v>0.0183263436531129</v>
       </c>
       <c r="AB49" t="inlineStr"/>
       <c r="AC49" t="n">
-        <v>0.9397428539218764</v>
+        <v>0.939138751826249</v>
       </c>
       <c r="AD49" t="n">
-        <v>0.002354041704845355</v>
+        <v>0.002365812383843992</v>
       </c>
       <c r="AE49" t="inlineStr"/>
       <c r="AF49" t="n">
-        <v>0.4445491829023263</v>
+        <v>0.446330723848371</v>
       </c>
       <c r="AG49" t="n">
-        <v>0.01375934934230566</v>
+        <v>0.01373726590074302</v>
       </c>
       <c r="AH49" t="inlineStr"/>
       <c r="AI49" t="n">
-        <v>0.3849840209327556</v>
+        <v>0.4015159472934428</v>
       </c>
       <c r="AJ49" t="n">
-        <v>0.01723071586054955</v>
+        <v>0.01699755332717078</v>
       </c>
       <c r="AK49" t="inlineStr"/>
       <c r="AL49" t="n">
-        <v>0.8735203286545978</v>
+        <v>0.8732485910420119</v>
       </c>
       <c r="AM49" t="n">
-        <v>0.001299182126772656</v>
+        <v>0.001300577004016838</v>
       </c>
       <c r="AN49" t="inlineStr"/>
     </row>
@@ -5696,10 +5696,10 @@
         <v>0.02365077480082941</v>
       </c>
       <c r="K50" t="n">
-        <v>0.5222632463286973</v>
+        <v>0.509975097271933</v>
       </c>
       <c r="L50" t="n">
-        <v>0.558864380711351</v>
+        <v>0.5505848201746671</v>
       </c>
       <c r="M50" t="n">
         <v>0</v>
@@ -5708,16 +5708,16 @@
         <v>0</v>
       </c>
       <c r="O50" t="n">
-        <v>4.388186391172322</v>
+        <v>4.291212719785222</v>
       </c>
       <c r="P50" t="n">
-        <v>4.624207671445591</v>
+        <v>4.500481878863585</v>
       </c>
       <c r="Q50" t="n">
-        <v>0.9597193127310113</v>
+        <v>0.9643131386676767</v>
       </c>
       <c r="R50" t="n">
-        <v>0.01072704208676341</v>
+        <v>0.01009684583614506</v>
       </c>
       <c r="S50" t="inlineStr"/>
       <c r="T50" t="inlineStr"/>
@@ -5727,31 +5727,31 @@
       <c r="X50" t="inlineStr"/>
       <c r="Y50" t="inlineStr"/>
       <c r="Z50" t="n">
-        <v>0.9769797146358428</v>
+        <v>0.9847225923342044</v>
       </c>
       <c r="AA50" t="n">
-        <v>0.0127643494824429</v>
+        <v>0.01039843948697537</v>
       </c>
       <c r="AB50" t="inlineStr"/>
       <c r="AC50" t="n">
-        <v>0.9364263585488526</v>
+        <v>0.9360197628461002</v>
       </c>
       <c r="AD50" t="n">
-        <v>0.005372529332951925</v>
+        <v>0.005389682398801431</v>
       </c>
       <c r="AE50" t="inlineStr"/>
       <c r="AF50" t="n">
-        <v>0.949144313253234</v>
+        <v>0.9495182886766423</v>
       </c>
       <c r="AG50" t="n">
-        <v>0.002303998394603033</v>
+        <v>0.002295511352826723</v>
       </c>
       <c r="AH50" t="inlineStr"/>
       <c r="AI50" t="n">
-        <v>0.8187384805901008</v>
+        <v>0.8194325120806389</v>
       </c>
       <c r="AJ50" t="n">
-        <v>0.017086368483732</v>
+        <v>0.01705362614871232</v>
       </c>
       <c r="AK50" t="inlineStr"/>
       <c r="AL50" t="inlineStr"/>
@@ -5798,10 +5798,10 @@
         <v>0.05173441476315732</v>
       </c>
       <c r="K51" t="n">
-        <v>0.5242408860059533</v>
+        <v>0.4767246818589526</v>
       </c>
       <c r="L51" t="n">
-        <v>0.5518822913381483</v>
+        <v>0.5516625159727202</v>
       </c>
       <c r="M51" t="n">
         <v>0</v>
@@ -5810,16 +5810,16 @@
         <v>0</v>
       </c>
       <c r="O51" t="n">
-        <v>4.210145903626906</v>
+        <v>3.852084868275818</v>
       </c>
       <c r="P51" t="n">
-        <v>4.426453653178759</v>
+        <v>4.425021504494057</v>
       </c>
       <c r="Q51" t="n">
-        <v>0.9283579700480439</v>
+        <v>0.928518635689824</v>
       </c>
       <c r="R51" t="n">
-        <v>0.0107497320965611</v>
+        <v>0.01073767156444199</v>
       </c>
       <c r="S51" t="inlineStr"/>
       <c r="T51" t="inlineStr"/>
@@ -5829,38 +5829,38 @@
       <c r="X51" t="inlineStr"/>
       <c r="Y51" t="inlineStr"/>
       <c r="Z51" t="n">
-        <v>0.9301420016690471</v>
+        <v>0.9298020078864232</v>
       </c>
       <c r="AA51" t="n">
-        <v>0.01562595348684905</v>
+        <v>0.01566393252059432</v>
       </c>
       <c r="AB51" t="inlineStr"/>
       <c r="AC51" t="n">
-        <v>0.7951343353028146</v>
+        <v>0.7959709183259848</v>
       </c>
       <c r="AD51" t="n">
-        <v>0.01445228090470585</v>
+        <v>0.01442274227687904</v>
       </c>
       <c r="AE51" t="inlineStr"/>
       <c r="AF51" t="n">
-        <v>-0.8405882887785427</v>
+        <v>-0.8079856495807261</v>
       </c>
       <c r="AG51" t="n">
-        <v>0.003403411922600078</v>
+        <v>0.003373134653022638</v>
       </c>
       <c r="AH51" t="inlineStr"/>
       <c r="AI51" t="n">
-        <v>0.890539712934876</v>
+        <v>0.8918970998225999</v>
       </c>
       <c r="AJ51" t="n">
-        <v>0.01062239004004227</v>
+        <v>0.01055632191053338</v>
       </c>
       <c r="AK51" t="inlineStr"/>
       <c r="AL51" t="n">
-        <v>0.9952384828488746</v>
+        <v>0.9956288507792258</v>
       </c>
       <c r="AM51" t="n">
-        <v>0.0005713774057479274</v>
+        <v>0.0005474547176660709</v>
       </c>
       <c r="AN51" t="inlineStr"/>
     </row>
@@ -5902,10 +5902,10 @@
         <v>0.004631983561397277</v>
       </c>
       <c r="K52" t="n">
-        <v>0.1593376026831239</v>
+        <v>0.1577619308753721</v>
       </c>
       <c r="L52" t="n">
-        <v>0.2352477480477142</v>
+        <v>0.2332576237530504</v>
       </c>
       <c r="M52" t="n">
         <v>0</v>
@@ -5914,16 +5914,16 @@
         <v>0</v>
       </c>
       <c r="O52" t="n">
-        <v>4.33297137534801</v>
+        <v>4.292754697312242</v>
       </c>
       <c r="P52" t="n">
-        <v>4.404387304977933</v>
+        <v>4.285138203429157</v>
       </c>
       <c r="Q52" t="n">
-        <v>0.9431726924890186</v>
+        <v>0.9438578508547878</v>
       </c>
       <c r="R52" t="n">
-        <v>0.0115114970100075</v>
+        <v>0.01144189036378144</v>
       </c>
       <c r="S52" t="inlineStr"/>
       <c r="T52" t="inlineStr"/>
@@ -5933,38 +5933,38 @@
       <c r="X52" t="inlineStr"/>
       <c r="Y52" t="inlineStr"/>
       <c r="Z52" t="n">
-        <v>0.9212031885323204</v>
+        <v>0.9213683409175074</v>
       </c>
       <c r="AA52" t="n">
-        <v>0.01285434277218719</v>
+        <v>0.01284086482256702</v>
       </c>
       <c r="AB52" t="inlineStr"/>
       <c r="AC52" t="n">
-        <v>0.8500631302283324</v>
+        <v>0.8528322432347442</v>
       </c>
       <c r="AD52" t="n">
-        <v>0.002739222663720225</v>
+        <v>0.002713810080924104</v>
       </c>
       <c r="AE52" t="inlineStr"/>
       <c r="AF52" t="n">
-        <v>0.7596250133477815</v>
+        <v>0.7649466021748099</v>
       </c>
       <c r="AG52" t="n">
-        <v>0.01760536682327913</v>
+        <v>0.01740939618453367</v>
       </c>
       <c r="AH52" t="inlineStr"/>
       <c r="AI52" t="n">
-        <v>0.3414044449178425</v>
+        <v>0.3437539527154617</v>
       </c>
       <c r="AJ52" t="n">
-        <v>0.0133793609951092</v>
+        <v>0.01335547456094254</v>
       </c>
       <c r="AK52" t="inlineStr"/>
       <c r="AL52" t="n">
-        <v>0.05421815294112897</v>
+        <v>0.05764133052217757</v>
       </c>
       <c r="AM52" t="n">
-        <v>0.0009376068104866502</v>
+        <v>0.0009359084779877782</v>
       </c>
       <c r="AN52" t="inlineStr"/>
     </row>
@@ -6006,10 +6006,10 @@
         <v>0.00319007047444387</v>
       </c>
       <c r="K53" t="n">
-        <v>0.331297244801841</v>
+        <v>0.3306984100273074</v>
       </c>
       <c r="L53" t="n">
-        <v>0.2184691391702042</v>
+        <v>0.2222187220843617</v>
       </c>
       <c r="M53" t="n">
         <v>0</v>
@@ -6018,16 +6018,16 @@
         <v>0</v>
       </c>
       <c r="O53" t="n">
-        <v>4.395968424017083</v>
+        <v>4.388506524434447</v>
       </c>
       <c r="P53" t="n">
-        <v>4.340674242517582</v>
+        <v>4.433029285114089</v>
       </c>
       <c r="Q53" t="n">
-        <v>0.9878832504193947</v>
+        <v>0.987816836719875</v>
       </c>
       <c r="R53" t="n">
-        <v>0.004732668188865793</v>
+        <v>0.004745620692211202</v>
       </c>
       <c r="S53" t="inlineStr"/>
       <c r="T53" t="inlineStr"/>
@@ -6037,38 +6037,38 @@
       <c r="X53" t="inlineStr"/>
       <c r="Y53" t="inlineStr"/>
       <c r="Z53" t="n">
-        <v>0.9849241668188445</v>
+        <v>0.9846901797282983</v>
       </c>
       <c r="AA53" t="n">
-        <v>0.007115984680691062</v>
+        <v>0.007170994494039955</v>
       </c>
       <c r="AB53" t="inlineStr"/>
       <c r="AC53" t="n">
-        <v>0.9244877951192282</v>
+        <v>0.9248878354650139</v>
       </c>
       <c r="AD53" t="n">
-        <v>0.002820903767059357</v>
+        <v>0.002813421705909762</v>
       </c>
       <c r="AE53" t="inlineStr"/>
       <c r="AF53" t="n">
-        <v>0.9764946329923102</v>
+        <v>0.9762568144864854</v>
       </c>
       <c r="AG53" t="n">
-        <v>0.003785135465830205</v>
+        <v>0.003804235567470246</v>
       </c>
       <c r="AH53" t="inlineStr"/>
       <c r="AI53" t="n">
-        <v>0.9605361989413794</v>
+        <v>0.9608967543252724</v>
       </c>
       <c r="AJ53" t="n">
-        <v>0.005785122295770583</v>
+        <v>0.005758634183792521</v>
       </c>
       <c r="AK53" t="inlineStr"/>
       <c r="AL53" t="n">
-        <v>0.9892768664341907</v>
+        <v>0.987966082527848</v>
       </c>
       <c r="AM53" t="n">
-        <v>4.586025858959441e-05</v>
+        <v>4.858242130553261e-05</v>
       </c>
       <c r="AN53" t="inlineStr"/>
     </row>
@@ -6110,28 +6110,28 @@
         <v>0.02695043454293275</v>
       </c>
       <c r="K54" t="n">
-        <v>0.2292086573981105</v>
+        <v>0.2248167586008439</v>
       </c>
       <c r="L54" t="n">
-        <v>0.4501100283142642</v>
+        <v>0.430984506537004</v>
       </c>
       <c r="M54" t="n">
-        <v>0.1993821946127108</v>
+        <v>0.2193819190100099</v>
       </c>
       <c r="N54" t="n">
-        <v>0.0191043553073281</v>
+        <v>0.02193961981936665</v>
       </c>
       <c r="O54" t="n">
-        <v>4.248018727268365</v>
+        <v>4.171678408154621</v>
       </c>
       <c r="P54" t="n">
-        <v>4.487655277056779</v>
+        <v>4.31119189240106</v>
       </c>
       <c r="Q54" t="n">
-        <v>0.9081010607325116</v>
+        <v>0.9063984135132683</v>
       </c>
       <c r="R54" t="n">
-        <v>0.01100795291461318</v>
+        <v>0.01110945921302189</v>
       </c>
       <c r="S54" t="inlineStr"/>
       <c r="T54" t="inlineStr"/>
@@ -6141,38 +6141,38 @@
       <c r="X54" t="inlineStr"/>
       <c r="Y54" t="inlineStr"/>
       <c r="Z54" t="n">
-        <v>0.8599445198202169</v>
+        <v>0.8563096775048245</v>
       </c>
       <c r="AA54" t="n">
-        <v>0.01928150471039111</v>
+        <v>0.01953010729127638</v>
       </c>
       <c r="AB54" t="inlineStr"/>
       <c r="AC54" t="n">
-        <v>0.3871664054368201</v>
+        <v>0.3948439112216421</v>
       </c>
       <c r="AD54" t="n">
-        <v>0.004514536684989694</v>
+        <v>0.004486168770392495</v>
       </c>
       <c r="AE54" t="inlineStr"/>
       <c r="AF54" t="n">
-        <v>0.8128114308386378</v>
+        <v>0.8090572030202201</v>
       </c>
       <c r="AG54" t="n">
-        <v>0.01283087489923461</v>
+        <v>0.01295890327429462</v>
       </c>
       <c r="AH54" t="inlineStr"/>
       <c r="AI54" t="n">
-        <v>0.7070199599115917</v>
+        <v>0.7164313503698311</v>
       </c>
       <c r="AJ54" t="n">
-        <v>0.006935796742596438</v>
+        <v>0.006823488247889323</v>
       </c>
       <c r="AK54" t="inlineStr"/>
       <c r="AL54" t="n">
-        <v>0.8869768647522115</v>
+        <v>0.878289257520015</v>
       </c>
       <c r="AM54" t="n">
-        <v>0.0009904768247323305</v>
+        <v>0.001027839015685435</v>
       </c>
       <c r="AN54" t="inlineStr"/>
     </row>
@@ -6214,28 +6214,28 @@
         <v>0.00266683139341308</v>
       </c>
       <c r="K55" t="n">
-        <v>0.1960898588687952</v>
+        <v>0.2017005542879495</v>
       </c>
       <c r="L55" t="n">
-        <v>0.472682540584936</v>
+        <v>0.4728720831123575</v>
       </c>
       <c r="M55" t="n">
-        <v>0.3439875214830873</v>
+        <v>0.3569864257382174</v>
       </c>
       <c r="N55" t="n">
-        <v>0.05336320037404024</v>
+        <v>0.05480160995698746</v>
       </c>
       <c r="O55" t="n">
-        <v>4.345610810250299</v>
+        <v>4.462283023203961</v>
       </c>
       <c r="P55" t="n">
-        <v>4.383573746814005</v>
+        <v>4.394418543764465</v>
       </c>
       <c r="Q55" t="n">
-        <v>0.8349428325005872</v>
+        <v>0.8348241177272965</v>
       </c>
       <c r="R55" t="n">
-        <v>0.01638303805210277</v>
+        <v>0.01638892861442154</v>
       </c>
       <c r="S55" t="inlineStr"/>
       <c r="T55" t="inlineStr"/>
@@ -6245,38 +6245,38 @@
       <c r="X55" t="inlineStr"/>
       <c r="Y55" t="inlineStr"/>
       <c r="Z55" t="n">
-        <v>0.6591841252396344</v>
+        <v>0.6578275067183574</v>
       </c>
       <c r="AA55" t="n">
-        <v>0.02818029295087811</v>
+        <v>0.02823632311576517</v>
       </c>
       <c r="AB55" t="inlineStr"/>
       <c r="AC55" t="n">
-        <v>0.1139303143009986</v>
+        <v>0.1185532815212251</v>
       </c>
       <c r="AD55" t="n">
-        <v>0.004121504369544224</v>
+        <v>0.004110738570071028</v>
       </c>
       <c r="AE55" t="inlineStr"/>
       <c r="AF55" t="n">
-        <v>0.5097536896364123</v>
+        <v>0.5124703405610749</v>
       </c>
       <c r="AG55" t="n">
-        <v>0.02242819645260708</v>
+        <v>0.02236596832072579</v>
       </c>
       <c r="AH55" t="inlineStr"/>
       <c r="AI55" t="n">
-        <v>0.8642532752740708</v>
+        <v>0.8609315862355822</v>
       </c>
       <c r="AJ55" t="n">
-        <v>0.005262345109249862</v>
+        <v>0.005326340136285111</v>
       </c>
       <c r="AK55" t="inlineStr"/>
       <c r="AL55" t="n">
-        <v>0.9022158002209866</v>
+        <v>0.9008326717535063</v>
       </c>
       <c r="AM55" t="n">
-        <v>0.000433241101664379</v>
+        <v>0.0004362943760247326</v>
       </c>
       <c r="AN55" t="inlineStr"/>
     </row>
@@ -6318,10 +6318,10 @@
         <v>0.03893815066809572</v>
       </c>
       <c r="K56" t="n">
-        <v>0.2182594007781727</v>
+        <v>0.2039298221414741</v>
       </c>
       <c r="L56" t="n">
-        <v>0.335541790913484</v>
+        <v>0.3222654196083304</v>
       </c>
       <c r="M56" t="n">
         <v>0</v>
@@ -6330,16 +6330,16 @@
         <v>0</v>
       </c>
       <c r="O56" t="n">
-        <v>4.242619804626787</v>
+        <v>3.981252851815452</v>
       </c>
       <c r="P56" t="n">
-        <v>4.372697484806177</v>
+        <v>4.305313728523216</v>
       </c>
       <c r="Q56" t="n">
-        <v>0.8124689049990117</v>
+        <v>0.8140026743624541</v>
       </c>
       <c r="R56" t="n">
-        <v>0.01270606835282853</v>
+        <v>0.01265400181587147</v>
       </c>
       <c r="S56" t="inlineStr"/>
       <c r="T56" t="inlineStr"/>
@@ -6349,38 +6349,38 @@
       <c r="X56" t="inlineStr"/>
       <c r="Y56" t="inlineStr"/>
       <c r="Z56" t="n">
-        <v>0.6261173282359895</v>
+        <v>0.6320085494266621</v>
       </c>
       <c r="AA56" t="n">
-        <v>0.02134839635525885</v>
+        <v>0.02117953657030387</v>
       </c>
       <c r="AB56" t="inlineStr"/>
       <c r="AC56" t="n">
-        <v>-0.05774371905414344</v>
+        <v>-0.02810911562099561</v>
       </c>
       <c r="AD56" t="n">
-        <v>0.009013991418768817</v>
+        <v>0.00888682273930924</v>
       </c>
       <c r="AE56" t="inlineStr"/>
       <c r="AF56" t="n">
-        <v>0.6546224018602105</v>
+        <v>0.6507137560021403</v>
       </c>
       <c r="AG56" t="n">
-        <v>0.01553769722558264</v>
+        <v>0.0156253701047111</v>
       </c>
       <c r="AH56" t="inlineStr"/>
       <c r="AI56" t="n">
-        <v>0.8770267244106206</v>
+        <v>0.8767529975207164</v>
       </c>
       <c r="AJ56" t="n">
-        <v>0.005098441735980837</v>
+        <v>0.005104112906601275</v>
       </c>
       <c r="AK56" t="inlineStr"/>
       <c r="AL56" t="n">
-        <v>0.8753680333446563</v>
+        <v>0.8724483612498279</v>
       </c>
       <c r="AM56" t="n">
-        <v>0.001673515307912398</v>
+        <v>0.001693004009184952</v>
       </c>
       <c r="AN56" t="inlineStr"/>
     </row>
@@ -6422,10 +6422,10 @@
         <v>0.02444228773888892</v>
       </c>
       <c r="K57" t="n">
-        <v>0.3849234920957109</v>
+        <v>0.3806411666965068</v>
       </c>
       <c r="L57" t="n">
-        <v>0.4515835818708642</v>
+        <v>0.446908871038932</v>
       </c>
       <c r="M57" t="n">
         <v>0</v>
@@ -6434,16 +6434,16 @@
         <v>0</v>
       </c>
       <c r="O57" t="n">
-        <v>4.301673038976071</v>
+        <v>4.256768970266466</v>
       </c>
       <c r="P57" t="n">
-        <v>4.401172320762215</v>
+        <v>4.367295926384822</v>
       </c>
       <c r="Q57" t="n">
-        <v>0.8999657343795482</v>
+        <v>0.9003983522957966</v>
       </c>
       <c r="R57" t="n">
-        <v>0.009617639111789407</v>
+        <v>0.009596819889347217</v>
       </c>
       <c r="S57" t="inlineStr"/>
       <c r="T57" t="inlineStr"/>
@@ -6453,38 +6453,38 @@
       <c r="X57" t="inlineStr"/>
       <c r="Y57" t="inlineStr"/>
       <c r="Z57" t="n">
-        <v>0.7848222517245842</v>
+        <v>0.7858990746237033</v>
       </c>
       <c r="AA57" t="n">
-        <v>0.01755750577520807</v>
+        <v>0.01751351879881869</v>
       </c>
       <c r="AB57" t="inlineStr"/>
       <c r="AC57" t="n">
-        <v>0.6369852556544864</v>
+        <v>0.6377957646282724</v>
       </c>
       <c r="AD57" t="n">
-        <v>0.008686045664944197</v>
+        <v>0.008676343508065438</v>
       </c>
       <c r="AE57" t="inlineStr"/>
       <c r="AF57" t="n">
-        <v>0.7509875234641659</v>
+        <v>0.7497121235996479</v>
       </c>
       <c r="AG57" t="n">
-        <v>0.007660706695063084</v>
+        <v>0.007680300061801535</v>
       </c>
       <c r="AH57" t="inlineStr"/>
       <c r="AI57" t="n">
-        <v>0.9452285711474302</v>
+        <v>0.9469764606982166</v>
       </c>
       <c r="AJ57" t="n">
-        <v>0.004306806324629269</v>
+        <v>0.004237528805731705</v>
       </c>
       <c r="AK57" t="inlineStr"/>
       <c r="AL57" t="n">
-        <v>0.6904617340249063</v>
+        <v>0.6899976100324631</v>
       </c>
       <c r="AM57" t="n">
-        <v>0.00124358525943944</v>
+        <v>0.001244517230741319</v>
       </c>
       <c r="AN57" t="inlineStr"/>
     </row>
@@ -6526,28 +6526,28 @@
         <v>0.02625641629885448</v>
       </c>
       <c r="K58" t="n">
-        <v>0.236072290229756</v>
+        <v>0.2253496777622122</v>
       </c>
       <c r="L58" t="n">
-        <v>0.5370469372835893</v>
+        <v>0.5201446820919224</v>
       </c>
       <c r="M58" t="n">
-        <v>0.5904383591492577</v>
+        <v>0.5808150276325121</v>
       </c>
       <c r="N58" t="n">
-        <v>0.09168351538041103</v>
+        <v>0.08217763978476436</v>
       </c>
       <c r="O58" t="n">
-        <v>4.317748846014766</v>
+        <v>4.133633433248462</v>
       </c>
       <c r="P58" t="n">
-        <v>4.773144104337497</v>
+        <v>4.449633703818832</v>
       </c>
       <c r="Q58" t="n">
-        <v>0.9732716560895285</v>
+        <v>0.9701268943931739</v>
       </c>
       <c r="R58" t="n">
-        <v>0.006874740017672171</v>
+        <v>0.007267925063510743</v>
       </c>
       <c r="S58" t="inlineStr"/>
       <c r="T58" t="inlineStr"/>
@@ -6557,38 +6557,38 @@
       <c r="X58" t="inlineStr"/>
       <c r="Y58" t="inlineStr"/>
       <c r="Z58" t="n">
-        <v>0.9777192634816771</v>
+        <v>0.9771800191796252</v>
       </c>
       <c r="AA58" t="n">
-        <v>0.008660898167395894</v>
+        <v>0.00876507826600265</v>
       </c>
       <c r="AB58" t="inlineStr"/>
       <c r="AC58" t="n">
-        <v>0.9815960138177839</v>
+        <v>0.9882162910998799</v>
       </c>
       <c r="AD58" t="n">
-        <v>0.001248567364265326</v>
+        <v>0.0009990725629719082</v>
       </c>
       <c r="AE58" t="inlineStr"/>
       <c r="AF58" t="n">
-        <v>0.9655688145224028</v>
+        <v>0.9653976550517741</v>
       </c>
       <c r="AG58" t="n">
-        <v>0.007129679485082957</v>
+        <v>0.007147378546939418</v>
       </c>
       <c r="AH58" t="inlineStr"/>
       <c r="AI58" t="n">
-        <v>0.8355423504685772</v>
+        <v>0.7956008072432688</v>
       </c>
       <c r="AJ58" t="n">
-        <v>0.01040387842860651</v>
+        <v>0.01159865998899373</v>
       </c>
       <c r="AK58" t="inlineStr"/>
       <c r="AL58" t="n">
-        <v>0.9468117414118244</v>
+        <v>0.9461867952425701</v>
       </c>
       <c r="AM58" t="n">
-        <v>0.0008167974697372152</v>
+        <v>0.0008215820198064019</v>
       </c>
       <c r="AN58" t="inlineStr"/>
     </row>
@@ -6630,10 +6630,10 @@
         <v>0.02080322163891103</v>
       </c>
       <c r="K59" t="n">
-        <v>0.4698313368793378</v>
+        <v>0.4654669130886756</v>
       </c>
       <c r="L59" t="n">
-        <v>0.516075818012792</v>
+        <v>0.5135266407365338</v>
       </c>
       <c r="M59" t="n">
         <v>0</v>
@@ -6642,16 +6642,16 @@
         <v>0</v>
       </c>
       <c r="O59" t="n">
-        <v>4.228884151391346</v>
+        <v>4.192052202289072</v>
       </c>
       <c r="P59" t="n">
-        <v>4.398744795083564</v>
+        <v>4.383827840564227</v>
       </c>
       <c r="Q59" t="n">
-        <v>0.7983709160949124</v>
+        <v>0.8047445056530412</v>
       </c>
       <c r="R59" t="n">
-        <v>0.01922000481717597</v>
+        <v>0.01891378881081737</v>
       </c>
       <c r="S59" t="inlineStr"/>
       <c r="T59" t="inlineStr"/>
@@ -6661,38 +6661,38 @@
       <c r="X59" t="inlineStr"/>
       <c r="Y59" t="inlineStr"/>
       <c r="Z59" t="n">
-        <v>0.7634652650741987</v>
+        <v>0.781230944941273</v>
       </c>
       <c r="AA59" t="n">
-        <v>0.03048872505260014</v>
+        <v>0.02932140296772496</v>
       </c>
       <c r="AB59" t="inlineStr"/>
       <c r="AC59" t="n">
-        <v>0.4532647019856167</v>
+        <v>0.4412019164161227</v>
       </c>
       <c r="AD59" t="n">
-        <v>0.02285060587555387</v>
+        <v>0.02310131047756706</v>
       </c>
       <c r="AE59" t="inlineStr"/>
       <c r="AF59" t="n">
-        <v>0.1460292584628687</v>
+        <v>0.1387715782668283</v>
       </c>
       <c r="AG59" t="n">
-        <v>0.01072074809752247</v>
+        <v>0.01076620816955282</v>
       </c>
       <c r="AH59" t="inlineStr"/>
       <c r="AI59" t="n">
-        <v>-0.7811709725098634</v>
+        <v>-0.7744006991037902</v>
       </c>
       <c r="AJ59" t="n">
-        <v>0.01655467171269097</v>
+        <v>0.01652317940717141</v>
       </c>
       <c r="AK59" t="inlineStr"/>
       <c r="AL59" t="n">
-        <v>-0.5643374143447497</v>
+        <v>-0.5584973427889075</v>
       </c>
       <c r="AM59" t="n">
-        <v>0.002517694652433166</v>
+        <v>0.002512990659079899</v>
       </c>
       <c r="AN59" t="inlineStr"/>
     </row>
@@ -6734,10 +6734,10 @@
         <v>0.0151609171982884</v>
       </c>
       <c r="K60" t="n">
-        <v>0.3312705578089989</v>
+        <v>0.3195516907355711</v>
       </c>
       <c r="L60" t="n">
-        <v>0.2457567089453432</v>
+        <v>0.2337909910577463</v>
       </c>
       <c r="M60" t="n">
         <v>0</v>
@@ -6746,16 +6746,16 @@
         <v>0</v>
       </c>
       <c r="O60" t="n">
-        <v>4.180622353107697</v>
+        <v>4.041987989944264</v>
       </c>
       <c r="P60" t="n">
-        <v>4.305866015917143</v>
+        <v>4.211312034823191</v>
       </c>
       <c r="Q60" t="n">
-        <v>0.8851495450092283</v>
+        <v>0.8938767987070141</v>
       </c>
       <c r="R60" t="n">
-        <v>0.02107846123653512</v>
+        <v>0.02026178555644128</v>
       </c>
       <c r="S60" t="inlineStr"/>
       <c r="T60" t="inlineStr"/>
@@ -6765,38 +6765,38 @@
       <c r="X60" t="inlineStr"/>
       <c r="Y60" t="inlineStr"/>
       <c r="Z60" t="n">
-        <v>0.5811682826861864</v>
+        <v>0.6153863286901591</v>
       </c>
       <c r="AA60" t="n">
-        <v>0.0453404368628236</v>
+        <v>0.04344884916800898</v>
       </c>
       <c r="AB60" t="inlineStr"/>
       <c r="AC60" t="n">
-        <v>-1.440366373384316</v>
+        <v>-1.405634905383364</v>
       </c>
       <c r="AD60" t="n">
-        <v>0.008279440950596427</v>
+        <v>0.008220313021881646</v>
       </c>
       <c r="AE60" t="inlineStr"/>
       <c r="AF60" t="n">
-        <v>0.6256141297198461</v>
+        <v>0.618216638052747</v>
       </c>
       <c r="AG60" t="n">
-        <v>0.006747956299305848</v>
+        <v>0.006814296643099133</v>
       </c>
       <c r="AH60" t="inlineStr"/>
       <c r="AI60" t="n">
-        <v>-9.38569717272434</v>
+        <v>-9.226993784798434</v>
       </c>
       <c r="AJ60" t="n">
-        <v>0.007170565834450304</v>
+        <v>0.007115568369428657</v>
       </c>
       <c r="AK60" t="inlineStr"/>
       <c r="AL60" t="n">
-        <v>0.9333603701438665</v>
+        <v>0.9316574957294248</v>
       </c>
       <c r="AM60" t="n">
-        <v>0.0005013527011342862</v>
+        <v>0.0005077179470773505</v>
       </c>
       <c r="AN60" t="inlineStr"/>
     </row>
@@ -6838,28 +6838,28 @@
         <v>0.01715393264003622</v>
       </c>
       <c r="K61" t="n">
-        <v>0.426923729397007</v>
+        <v>0.3994271141921055</v>
       </c>
       <c r="L61" t="n">
-        <v>0.2749042002709686</v>
+        <v>0.2758743685540509</v>
       </c>
       <c r="M61" t="n">
-        <v>0.2742096152843958</v>
+        <v>0.2241048170806427</v>
       </c>
       <c r="N61" t="n">
-        <v>0.01288384861182056</v>
+        <v>0.0100484440660553</v>
       </c>
       <c r="O61" t="n">
-        <v>4.076109010387499</v>
+        <v>3.830195138216759</v>
       </c>
       <c r="P61" t="n">
-        <v>4.180191456894658</v>
+        <v>4.249491999162036</v>
       </c>
       <c r="Q61" t="n">
-        <v>0.982663540163657</v>
+        <v>0.9833546433779143</v>
       </c>
       <c r="R61" t="n">
-        <v>0.00938739643103601</v>
+        <v>0.00919838327800061</v>
       </c>
       <c r="S61" t="inlineStr"/>
       <c r="T61" t="inlineStr"/>
@@ -6871,38 +6871,38 @@
       </c>
       <c r="Y61" t="inlineStr"/>
       <c r="Z61" t="n">
-        <v>0.9697434905904845</v>
+        <v>0.9711176223695276</v>
       </c>
       <c r="AA61" t="n">
-        <v>0.01938589282528799</v>
+        <v>0.01894056224051919</v>
       </c>
       <c r="AB61" t="inlineStr"/>
       <c r="AC61" t="n">
-        <v>0.4188743624851395</v>
+        <v>0.4257842539181919</v>
       </c>
       <c r="AD61" t="n">
-        <v>0.004132368581743455</v>
+        <v>0.004107727087694948</v>
       </c>
       <c r="AE61" t="inlineStr"/>
       <c r="AF61" t="n">
-        <v>0.6557934590672045</v>
+        <v>0.6582824405837779</v>
       </c>
       <c r="AG61" t="n">
-        <v>0.005944365212651464</v>
+        <v>0.005922834159065873</v>
       </c>
       <c r="AH61" t="inlineStr"/>
       <c r="AI61" t="n">
-        <v>0.8789121307890901</v>
+        <v>0.879444629051122</v>
       </c>
       <c r="AJ61" t="n">
-        <v>0.002781546625804414</v>
+        <v>0.002775423796375348</v>
       </c>
       <c r="AK61" t="inlineStr"/>
       <c r="AL61" t="n">
-        <v>0.2160252003911443</v>
+        <v>0.2167420090563152</v>
       </c>
       <c r="AM61" t="n">
-        <v>0.002412019025966835</v>
+        <v>0.002410916087755386</v>
       </c>
       <c r="AN61" t="inlineStr"/>
     </row>
@@ -6944,28 +6944,28 @@
         <v>0.03097209188130944</v>
       </c>
       <c r="K62" t="n">
-        <v>0.4112539384720597</v>
+        <v>0.4202651317069659</v>
       </c>
       <c r="L62" t="n">
-        <v>0.2381636008172383</v>
+        <v>0.2430607655564238</v>
       </c>
       <c r="M62" t="n">
-        <v>0.6509186583845913</v>
+        <v>0.6584053066600373</v>
       </c>
       <c r="N62" t="n">
-        <v>0.09567389526276088</v>
+        <v>0.09948379243991619</v>
       </c>
       <c r="O62" t="n">
-        <v>4.099154174190237</v>
+        <v>4.183223779089313</v>
       </c>
       <c r="P62" t="n">
-        <v>4.114701153905362</v>
+        <v>4.199946415830034</v>
       </c>
       <c r="Q62" t="n">
-        <v>0.9886331342672907</v>
+        <v>0.988628183542563</v>
       </c>
       <c r="R62" t="n">
-        <v>0.007031340535438794</v>
+        <v>0.007032871583785351</v>
       </c>
       <c r="S62" t="inlineStr"/>
       <c r="T62" t="inlineStr"/>
@@ -6977,38 +6977,38 @@
       </c>
       <c r="Y62" t="inlineStr"/>
       <c r="Z62" t="n">
-        <v>0.9846196282999672</v>
+        <v>0.9847418735900173</v>
       </c>
       <c r="AA62" t="n">
-        <v>0.01293554542919782</v>
+        <v>0.01288403613543487</v>
       </c>
       <c r="AB62" t="inlineStr"/>
       <c r="AC62" t="n">
-        <v>0.1476283944103978</v>
+        <v>0.1329803532834265</v>
       </c>
       <c r="AD62" t="n">
-        <v>0.003073492949936121</v>
+        <v>0.003099789505766278</v>
       </c>
       <c r="AE62" t="inlineStr"/>
       <c r="AF62" t="n">
-        <v>0.654101167273435</v>
+        <v>0.6472639082518614</v>
       </c>
       <c r="AG62" t="n">
-        <v>0.007874402639714667</v>
+        <v>0.007951847064461887</v>
       </c>
       <c r="AH62" t="inlineStr"/>
       <c r="AI62" t="n">
-        <v>0.975753835090734</v>
+        <v>0.9755347963306147</v>
       </c>
       <c r="AJ62" t="n">
-        <v>0.002311677548757051</v>
+        <v>0.002322095867356102</v>
       </c>
       <c r="AK62" t="inlineStr"/>
       <c r="AL62" t="n">
-        <v>0.8468985698679354</v>
+        <v>0.8468315138627321</v>
       </c>
       <c r="AM62" t="n">
-        <v>0.001960224521771395</v>
+        <v>0.001960653748448378</v>
       </c>
       <c r="AN62" t="inlineStr"/>
     </row>
@@ -7050,28 +7050,28 @@
         <v>0.01715393264003622</v>
       </c>
       <c r="K63" t="n">
-        <v>0.426923729397007</v>
+        <v>0.4162364024212756</v>
       </c>
       <c r="L63" t="n">
-        <v>0.2918010720242444</v>
+        <v>0.2950028200308563</v>
       </c>
       <c r="M63" t="n">
-        <v>0.390220376698603</v>
+        <v>0.3706319695558645</v>
       </c>
       <c r="N63" t="n">
-        <v>0.04019655992455379</v>
+        <v>0.03725342766212937</v>
       </c>
       <c r="O63" t="n">
-        <v>4.076109010387499</v>
+        <v>3.980573946132115</v>
       </c>
       <c r="P63" t="n">
-        <v>4.185989311654055</v>
+        <v>4.250735467782023</v>
       </c>
       <c r="Q63" t="n">
-        <v>0.9891626304194601</v>
+        <v>0.9891906288030091</v>
       </c>
       <c r="R63" t="n">
-        <v>0.007614058739404095</v>
+        <v>0.007604216904528887</v>
       </c>
       <c r="S63" t="inlineStr"/>
       <c r="T63" t="inlineStr"/>
@@ -7083,38 +7083,38 @@
       </c>
       <c r="Y63" t="inlineStr"/>
       <c r="Z63" t="n">
-        <v>0.9775466008862093</v>
+        <v>0.9776089665062692</v>
       </c>
       <c r="AA63" t="n">
-        <v>0.01649988041601305</v>
+        <v>0.01647694979409975</v>
       </c>
       <c r="AB63" t="inlineStr"/>
       <c r="AC63" t="n">
-        <v>0.9127164861592083</v>
+        <v>0.9160632499711816</v>
       </c>
       <c r="AD63" t="n">
-        <v>0.001290062228365995</v>
+        <v>0.00126508767221641</v>
       </c>
       <c r="AE63" t="inlineStr"/>
       <c r="AF63" t="n">
-        <v>0.9910257720274804</v>
+        <v>0.9910776423350016</v>
       </c>
       <c r="AG63" t="n">
-        <v>0.001053569030706389</v>
+        <v>0.001050519846673862</v>
       </c>
       <c r="AH63" t="inlineStr"/>
       <c r="AI63" t="n">
-        <v>0.8563256633208179</v>
+        <v>0.8551898488181919</v>
       </c>
       <c r="AJ63" t="n">
-        <v>0.003380424309031353</v>
+        <v>0.003393759942068076</v>
       </c>
       <c r="AK63" t="inlineStr"/>
       <c r="AL63" t="n">
-        <v>0.1979738557464727</v>
+        <v>0.2009758563970437</v>
       </c>
       <c r="AM63" t="n">
-        <v>0.002068170063165227</v>
+        <v>0.002064295832510188</v>
       </c>
       <c r="AN63" t="inlineStr"/>
     </row>
@@ -7156,28 +7156,28 @@
         <v>0.03097209188130944</v>
       </c>
       <c r="K64" t="n">
-        <v>0.4112539384720597</v>
+        <v>0.3674688031115195</v>
       </c>
       <c r="L64" t="n">
-        <v>0.2804791129371551</v>
+        <v>0.283775465909908</v>
       </c>
       <c r="M64" t="n">
-        <v>0.4850881183406947</v>
+        <v>0.4249259745682613</v>
       </c>
       <c r="N64" t="n">
-        <v>0.03065144192987263</v>
+        <v>0.02787018075536547</v>
       </c>
       <c r="O64" t="n">
-        <v>4.099154174190237</v>
+        <v>3.69002349828743</v>
       </c>
       <c r="P64" t="n">
-        <v>4.146198257605834</v>
+        <v>4.235841271884143</v>
       </c>
       <c r="Q64" t="n">
-        <v>0.9826257123274095</v>
+        <v>0.982818436213785</v>
       </c>
       <c r="R64" t="n">
-        <v>0.00883149310559293</v>
+        <v>0.00878237494817892</v>
       </c>
       <c r="S64" t="inlineStr"/>
       <c r="T64" t="inlineStr"/>
@@ -7189,38 +7189,38 @@
       </c>
       <c r="Y64" t="inlineStr"/>
       <c r="Z64" t="n">
-        <v>0.9754748541214379</v>
+        <v>0.9758883437391677</v>
       </c>
       <c r="AA64" t="n">
-        <v>0.01653918560661178</v>
+        <v>0.01639916906370878</v>
       </c>
       <c r="AB64" t="inlineStr"/>
       <c r="AC64" t="n">
-        <v>0.6132105295900352</v>
+        <v>0.604926596602269</v>
       </c>
       <c r="AD64" t="n">
-        <v>0.003358680085228504</v>
+        <v>0.003394456242877987</v>
       </c>
       <c r="AE64" t="inlineStr"/>
       <c r="AF64" t="n">
-        <v>0.3692183940542438</v>
+        <v>0.3687177045870821</v>
       </c>
       <c r="AG64" t="n">
-        <v>0.00966445147563201</v>
+        <v>0.009668286344281799</v>
       </c>
       <c r="AH64" t="inlineStr"/>
       <c r="AI64" t="n">
-        <v>0.9643449862421124</v>
+        <v>0.9645042467835913</v>
       </c>
       <c r="AJ64" t="n">
-        <v>0.00272516866019648</v>
+        <v>0.00271907558201289</v>
       </c>
       <c r="AK64" t="inlineStr"/>
       <c r="AL64" t="n">
-        <v>0.8308833176848293</v>
+        <v>0.8307446980928745</v>
       </c>
       <c r="AM64" t="n">
-        <v>0.002324541184419457</v>
+        <v>0.002325493665698345</v>
       </c>
       <c r="AN64" t="inlineStr"/>
     </row>
@@ -7262,28 +7262,28 @@
         <v>0.01715393264003622</v>
       </c>
       <c r="K65" t="n">
-        <v>0.426923729397007</v>
+        <v>0.4085515562507576</v>
       </c>
       <c r="L65" t="n">
-        <v>0.3538355434311965</v>
+        <v>0.3571931464515894</v>
       </c>
       <c r="M65" t="n">
-        <v>0.3274694572172158</v>
+        <v>0.2952640069260904</v>
       </c>
       <c r="N65" t="n">
-        <v>0.02545230562270915</v>
+        <v>0.02279375794611013</v>
       </c>
       <c r="O65" t="n">
-        <v>4.076109010387499</v>
+        <v>3.911842650195023</v>
       </c>
       <c r="P65" t="n">
-        <v>4.204148146404209</v>
+        <v>4.269299797239945</v>
       </c>
       <c r="Q65" t="n">
-        <v>0.9784038976681202</v>
+        <v>0.9786330214974474</v>
       </c>
       <c r="R65" t="n">
-        <v>0.01058523428480051</v>
+        <v>0.01052893253618677</v>
       </c>
       <c r="S65" t="inlineStr"/>
       <c r="T65" t="inlineStr"/>
@@ -7295,38 +7295,38 @@
       </c>
       <c r="Y65" t="inlineStr"/>
       <c r="Z65" t="n">
-        <v>0.9638827940068988</v>
+        <v>0.9643330021219167</v>
       </c>
       <c r="AA65" t="n">
-        <v>0.0217266353889594</v>
+        <v>0.02159079734616568</v>
       </c>
       <c r="AB65" t="inlineStr"/>
       <c r="AC65" t="n">
-        <v>0.7078756114260717</v>
+        <v>0.708418474992106</v>
       </c>
       <c r="AD65" t="n">
-        <v>0.003659882228987109</v>
+        <v>0.003656480012851004</v>
       </c>
       <c r="AE65" t="inlineStr"/>
       <c r="AF65" t="n">
-        <v>0.6641055794333262</v>
+        <v>0.6645594641749599</v>
       </c>
       <c r="AG65" t="n">
-        <v>0.008157489527163428</v>
+        <v>0.008151976170232061</v>
       </c>
       <c r="AH65" t="inlineStr"/>
       <c r="AI65" t="n">
-        <v>0.9283749548872433</v>
+        <v>0.9275836698363027</v>
       </c>
       <c r="AJ65" t="n">
-        <v>0.002309059382670426</v>
+        <v>0.002321779133958501</v>
       </c>
       <c r="AK65" t="inlineStr"/>
       <c r="AL65" t="n">
-        <v>0.5533031589794646</v>
+        <v>0.553878522517901</v>
       </c>
       <c r="AM65" t="n">
-        <v>0.001909879069228864</v>
+        <v>0.001908648672284967</v>
       </c>
       <c r="AN65" t="inlineStr"/>
     </row>
@@ -7368,28 +7368,28 @@
         <v>0.03097209188130944</v>
       </c>
       <c r="K66" t="n">
-        <v>0.4112539384720597</v>
+        <v>0.396032261454521</v>
       </c>
       <c r="L66" t="n">
-        <v>0.283860292663243</v>
+        <v>0.2888494714669217</v>
       </c>
       <c r="M66" t="n">
-        <v>0.3854447750313322</v>
+        <v>0.3555530335959829</v>
       </c>
       <c r="N66" t="n">
-        <v>0.02352979932610891</v>
+        <v>0.02161924171252751</v>
       </c>
       <c r="O66" t="n">
-        <v>4.099154174190237</v>
+        <v>3.957047851229053</v>
       </c>
       <c r="P66" t="n">
-        <v>4.150325694989506</v>
+        <v>4.239953806950777</v>
       </c>
       <c r="Q66" t="n">
-        <v>0.9815862936701246</v>
+        <v>0.9815684785941791</v>
       </c>
       <c r="R66" t="n">
-        <v>0.009178340176621896</v>
+        <v>0.009182779079204487</v>
       </c>
       <c r="S66" t="inlineStr"/>
       <c r="T66" t="inlineStr"/>
@@ -7401,38 +7401,38 @@
       </c>
       <c r="Y66" t="inlineStr"/>
       <c r="Z66" t="n">
-        <v>0.9711314346518367</v>
+        <v>0.9711260071913864</v>
       </c>
       <c r="AA66" t="n">
-        <v>0.01788518457781264</v>
+        <v>0.0178868657588605</v>
       </c>
       <c r="AB66" t="inlineStr"/>
       <c r="AC66" t="n">
-        <v>0.7168248668956172</v>
+        <v>0.711939438793706</v>
       </c>
       <c r="AD66" t="n">
-        <v>0.003280365253998921</v>
+        <v>0.003308541204600216</v>
       </c>
       <c r="AE66" t="inlineStr"/>
       <c r="AF66" t="n">
-        <v>0.6793210522014159</v>
+        <v>0.678138720744636</v>
       </c>
       <c r="AG66" t="n">
-        <v>0.00865190880858277</v>
+        <v>0.008667843768580171</v>
       </c>
       <c r="AH66" t="inlineStr"/>
       <c r="AI66" t="n">
-        <v>0.9385653911460582</v>
+        <v>0.9391441282304176</v>
       </c>
       <c r="AJ66" t="n">
-        <v>0.003447228701007101</v>
+        <v>0.003430953185534736</v>
       </c>
       <c r="AK66" t="inlineStr"/>
       <c r="AL66" t="n">
-        <v>0.8437566980818991</v>
+        <v>0.843851155595404</v>
       </c>
       <c r="AM66" t="n">
-        <v>0.002188066114691374</v>
+        <v>0.002187404612634378</v>
       </c>
       <c r="AN66" t="inlineStr"/>
     </row>
@@ -7474,10 +7474,10 @@
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>0.4063693156807596</v>
+        <v>0.4199481453543742</v>
       </c>
       <c r="L67" t="n">
-        <v>0.386523569299521</v>
+        <v>0.394686558825489</v>
       </c>
       <c r="M67" t="n">
         <v>0</v>
@@ -7486,61 +7486,61 @@
         <v>0</v>
       </c>
       <c r="O67" t="n">
-        <v>4.262792264471607</v>
+        <v>4.39633004726497</v>
       </c>
       <c r="P67" t="n">
-        <v>4.256196747984716</v>
+        <v>4.347009068166593</v>
       </c>
       <c r="Q67" t="n">
-        <v>0.8515403673158879</v>
+        <v>0.8548504315926932</v>
       </c>
       <c r="R67" t="n">
-        <v>0.02786865831891872</v>
+        <v>0.02755622641967012</v>
       </c>
       <c r="S67" t="inlineStr"/>
       <c r="T67" t="inlineStr"/>
       <c r="U67" t="inlineStr"/>
       <c r="V67" t="inlineStr"/>
       <c r="W67" t="n">
-        <v>0.803228873091353</v>
+        <v>0.8037811043712753</v>
       </c>
       <c r="X67" t="n">
-        <v>0.0007710678204935105</v>
+        <v>0.000769985072862494</v>
       </c>
       <c r="Y67" t="inlineStr"/>
       <c r="Z67" t="n">
-        <v>0.5853134859255658</v>
+        <v>0.5957043416201471</v>
       </c>
       <c r="AA67" t="n">
-        <v>0.06635431442539884</v>
+        <v>0.06551771600311547</v>
       </c>
       <c r="AB67" t="inlineStr"/>
       <c r="AC67" t="n">
-        <v>0.7648105432557438</v>
+        <v>0.7655115095172615</v>
       </c>
       <c r="AD67" t="n">
-        <v>0.002656871673949614</v>
+        <v>0.0026529094063066</v>
       </c>
       <c r="AE67" t="inlineStr"/>
       <c r="AF67" t="n">
-        <v>0.6418808797399105</v>
+        <v>0.6425546340731398</v>
       </c>
       <c r="AG67" t="n">
-        <v>0.01312595139866041</v>
+        <v>0.01311359820442935</v>
       </c>
       <c r="AH67" t="inlineStr"/>
       <c r="AI67" t="n">
-        <v>0.8204549809041437</v>
+        <v>0.8046678127678512</v>
       </c>
       <c r="AJ67" t="n">
-        <v>0.008775271242555071</v>
+        <v>0.009152943365267199</v>
       </c>
       <c r="AK67" t="inlineStr"/>
       <c r="AL67" t="n">
-        <v>0.8376823447986796</v>
+        <v>0.8180785874530363</v>
       </c>
       <c r="AM67" t="n">
-        <v>0.000107522220541372</v>
+        <v>0.0001138301359081168</v>
       </c>
       <c r="AN67" t="inlineStr"/>
     </row>
@@ -7582,10 +7582,10 @@
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>0.4063693156807596</v>
+        <v>0.4285024175374733</v>
       </c>
       <c r="L68" t="n">
-        <v>0.3724625469544469</v>
+        <v>0.388941449636978</v>
       </c>
       <c r="M68" t="n">
         <v>0</v>
@@ -7594,61 +7594,61 @@
         <v>0</v>
       </c>
       <c r="O68" t="n">
-        <v>4.262792264471607</v>
+        <v>4.480409000587638</v>
       </c>
       <c r="P68" t="n">
-        <v>4.186812160696786</v>
+        <v>4.346260088719825</v>
       </c>
       <c r="Q68" t="n">
-        <v>0.7735303230095345</v>
+        <v>0.7773934706989506</v>
       </c>
       <c r="R68" t="n">
-        <v>0.03174585473238706</v>
+        <v>0.03147392775018776</v>
       </c>
       <c r="S68" t="inlineStr"/>
       <c r="T68" t="inlineStr"/>
       <c r="U68" t="inlineStr"/>
       <c r="V68" t="inlineStr"/>
       <c r="W68" t="n">
-        <v>0.4936858894571182</v>
+        <v>0.4874339541326738</v>
       </c>
       <c r="X68" t="n">
-        <v>0.001163656948896191</v>
+        <v>0.001170819288718882</v>
       </c>
       <c r="Y68" t="inlineStr"/>
       <c r="Z68" t="n">
-        <v>0.3834898187160696</v>
+        <v>0.3955674114516097</v>
       </c>
       <c r="AA68" t="n">
-        <v>0.0763781924067386</v>
+        <v>0.07562635783685882</v>
       </c>
       <c r="AB68" t="inlineStr"/>
       <c r="AC68" t="n">
-        <v>0.4776910530034699</v>
+        <v>0.4695557683823047</v>
       </c>
       <c r="AD68" t="n">
-        <v>0.003856992697303989</v>
+        <v>0.003886914158561062</v>
       </c>
       <c r="AE68" t="inlineStr"/>
       <c r="AF68" t="n">
-        <v>0.7569294278011915</v>
+        <v>0.7501049465974345</v>
       </c>
       <c r="AG68" t="n">
-        <v>0.007249996475473175</v>
+        <v>0.007351067887737261</v>
       </c>
       <c r="AH68" t="inlineStr"/>
       <c r="AI68" t="n">
-        <v>0.7174906644609348</v>
+        <v>0.6990500340897213</v>
       </c>
       <c r="AJ68" t="n">
-        <v>0.01198578660282077</v>
+        <v>0.01237078583991602</v>
       </c>
       <c r="AK68" t="inlineStr"/>
       <c r="AL68" t="n">
-        <v>0.2963416590449497</v>
+        <v>0.2480709441268785</v>
       </c>
       <c r="AM68" t="n">
-        <v>0.0007455214405924371</v>
+        <v>0.0007706685767893581</v>
       </c>
       <c r="AN68" t="inlineStr"/>
     </row>
@@ -7690,10 +7690,10 @@
         <v>0.04611530568392795</v>
       </c>
       <c r="K69" t="n">
-        <v>0.1547738540766385</v>
+        <v>0.1574541057329026</v>
       </c>
       <c r="L69" t="n">
-        <v>0.2025031954442694</v>
+        <v>0.2051976353952231</v>
       </c>
       <c r="M69" t="n">
         <v>0</v>
@@ -7702,16 +7702,16 @@
         <v>0</v>
       </c>
       <c r="O69" t="n">
-        <v>4.262919614482086</v>
+        <v>4.332138796392004</v>
       </c>
       <c r="P69" t="n">
-        <v>4.256992567054649</v>
+        <v>4.301408134638223</v>
       </c>
       <c r="Q69" t="n">
-        <v>0.9719546034895027</v>
+        <v>0.971964674427934</v>
       </c>
       <c r="R69" t="n">
-        <v>0.009815159215614109</v>
+        <v>0.009813396774144721</v>
       </c>
       <c r="S69" t="inlineStr"/>
       <c r="T69" t="inlineStr"/>
@@ -7721,38 +7721,38 @@
       <c r="X69" t="inlineStr"/>
       <c r="Y69" t="inlineStr"/>
       <c r="Z69" t="n">
-        <v>0.9656971587970086</v>
+        <v>0.9659052190880125</v>
       </c>
       <c r="AA69" t="n">
-        <v>0.01026071843651978</v>
+        <v>0.0102295534510854</v>
       </c>
       <c r="AB69" t="inlineStr"/>
       <c r="AC69" t="n">
-        <v>0.4366510386648796</v>
+        <v>0.4411317996927842</v>
       </c>
       <c r="AD69" t="n">
-        <v>0.004766440075608007</v>
+        <v>0.004747446593787831</v>
       </c>
       <c r="AE69" t="inlineStr"/>
       <c r="AF69" t="n">
-        <v>0.8488168599107225</v>
+        <v>0.8485263686173259</v>
       </c>
       <c r="AG69" t="n">
-        <v>0.01574511563283986</v>
+        <v>0.01576023512306844</v>
       </c>
       <c r="AH69" t="inlineStr"/>
       <c r="AI69" t="n">
-        <v>0.9050013298882867</v>
+        <v>0.9048103366427537</v>
       </c>
       <c r="AJ69" t="n">
-        <v>0.0093518373706827</v>
+        <v>0.009361233507072192</v>
       </c>
       <c r="AK69" t="inlineStr"/>
       <c r="AL69" t="n">
-        <v>0.5185568192149187</v>
+        <v>0.5187109619344599</v>
       </c>
       <c r="AM69" t="n">
-        <v>0.004280178712644847</v>
+        <v>0.004279493469577684</v>
       </c>
       <c r="AN69" t="inlineStr"/>
     </row>
@@ -7794,10 +7794,10 @@
         <v>0.03389921553245138</v>
       </c>
       <c r="K70" t="n">
-        <v>0.153202753067615</v>
+        <v>0.1548184556465437</v>
       </c>
       <c r="L70" t="n">
-        <v>0.2829461371138142</v>
+        <v>0.2818792756835835</v>
       </c>
       <c r="M70" t="n">
         <v>0</v>
@@ -7806,16 +7806,16 @@
         <v>0</v>
       </c>
       <c r="O70" t="n">
-        <v>4.3508196972905</v>
+        <v>4.393884558299479</v>
       </c>
       <c r="P70" t="n">
-        <v>4.368878097748527</v>
+        <v>4.357184331136191</v>
       </c>
       <c r="Q70" t="n">
-        <v>0.9633290487570927</v>
+        <v>0.9634331301343807</v>
       </c>
       <c r="R70" t="n">
-        <v>0.009397531928199023</v>
+        <v>0.009384186172923768</v>
       </c>
       <c r="S70" t="inlineStr"/>
       <c r="T70" t="inlineStr"/>
@@ -7825,38 +7825,38 @@
       <c r="X70" t="inlineStr"/>
       <c r="Y70" t="inlineStr"/>
       <c r="Z70" t="n">
-        <v>0.9213868276056124</v>
+        <v>0.9218597383630527</v>
       </c>
       <c r="AA70" t="n">
-        <v>0.01251949645226193</v>
+        <v>0.01248178308088512</v>
       </c>
       <c r="AB70" t="inlineStr"/>
       <c r="AC70" t="n">
-        <v>0.9263895488967253</v>
+        <v>0.9266093425400458</v>
       </c>
       <c r="AD70" t="n">
-        <v>0.003147169632922407</v>
+        <v>0.00314246754918454</v>
       </c>
       <c r="AE70" t="inlineStr"/>
       <c r="AF70" t="n">
-        <v>0.9390317879240819</v>
+        <v>0.9388867506727477</v>
       </c>
       <c r="AG70" t="n">
-        <v>0.01121200146802888</v>
+        <v>0.01122532965866805</v>
       </c>
       <c r="AH70" t="inlineStr"/>
       <c r="AI70" t="n">
-        <v>0.8157953710477228</v>
+        <v>0.8165577140446746</v>
       </c>
       <c r="AJ70" t="n">
-        <v>0.0120209432961576</v>
+        <v>0.0119960427732964</v>
       </c>
       <c r="AK70" t="inlineStr"/>
       <c r="AL70" t="n">
-        <v>0.7687066856381957</v>
+        <v>0.7678154532435362</v>
       </c>
       <c r="AM70" t="n">
-        <v>0.002171061708587313</v>
+        <v>0.002175240515435225</v>
       </c>
       <c r="AN70" t="inlineStr"/>
     </row>
@@ -7898,10 +7898,10 @@
         <v>0.02861063360823382</v>
       </c>
       <c r="K71" t="n">
-        <v>0.3261006684563419</v>
+        <v>0.3259372934798359</v>
       </c>
       <c r="L71" t="n">
-        <v>0.3501365129571249</v>
+        <v>0.3494710757904321</v>
       </c>
       <c r="M71" t="n">
         <v>0</v>
@@ -7910,16 +7910,16 @@
         <v>0</v>
       </c>
       <c r="O71" t="n">
-        <v>4.438072623193317</v>
+        <v>4.435983780461879</v>
       </c>
       <c r="P71" t="n">
-        <v>4.457128638647151</v>
+        <v>4.438832256269587</v>
       </c>
       <c r="Q71" t="n">
-        <v>0.96113050370307</v>
+        <v>0.9612297385743878</v>
       </c>
       <c r="R71" t="n">
-        <v>0.01076489141467018</v>
+        <v>0.01075114110392152</v>
       </c>
       <c r="S71" t="inlineStr"/>
       <c r="T71" t="inlineStr"/>
@@ -7929,38 +7929,38 @@
       <c r="X71" t="inlineStr"/>
       <c r="Y71" t="inlineStr"/>
       <c r="Z71" t="n">
-        <v>0.9440241040172793</v>
+        <v>0.9443524956060733</v>
       </c>
       <c r="AA71" t="n">
-        <v>0.01408089283325346</v>
+        <v>0.01403952816563101</v>
       </c>
       <c r="AB71" t="inlineStr"/>
       <c r="AC71" t="n">
-        <v>0.7402077587520717</v>
+        <v>0.740770136758883</v>
       </c>
       <c r="AD71" t="n">
-        <v>0.004514960273418815</v>
+        <v>0.004510070808753229</v>
       </c>
       <c r="AE71" t="inlineStr"/>
       <c r="AF71" t="n">
-        <v>0.9068047708338732</v>
+        <v>0.9068221337088034</v>
       </c>
       <c r="AG71" t="n">
-        <v>0.00973646566636684</v>
+        <v>0.009735558640804524</v>
       </c>
       <c r="AH71" t="inlineStr"/>
       <c r="AI71" t="n">
-        <v>0.842298489585999</v>
+        <v>0.8424493265837444</v>
       </c>
       <c r="AJ71" t="n">
-        <v>0.01627629593485416</v>
+        <v>0.01626851016622633</v>
       </c>
       <c r="AK71" t="inlineStr"/>
       <c r="AL71" t="n">
-        <v>0.931762927229049</v>
+        <v>0.9318214553838008</v>
       </c>
       <c r="AM71" t="n">
-        <v>0.001020516322647619</v>
+        <v>0.001020078571232061</v>
       </c>
       <c r="AN71" t="inlineStr"/>
     </row>
@@ -8002,10 +8002,10 @@
         <v>0.03450948851818413</v>
       </c>
       <c r="K72" t="n">
-        <v>0.3263018165925168</v>
+        <v>0.3247916833722452</v>
       </c>
       <c r="L72" t="n">
-        <v>0.4177627411276522</v>
+        <v>0.4124836133381382</v>
       </c>
       <c r="M72" t="n">
         <v>0</v>
@@ -8014,16 +8014,16 @@
         <v>0</v>
       </c>
       <c r="O72" t="n">
-        <v>4.547889869855799</v>
+        <v>4.528094939538367</v>
       </c>
       <c r="P72" t="n">
-        <v>4.560646051212577</v>
+        <v>4.500901129508024</v>
       </c>
       <c r="Q72" t="n">
-        <v>0.9564257444158158</v>
+        <v>0.9568065162032868</v>
       </c>
       <c r="R72" t="n">
-        <v>0.01192050933930236</v>
+        <v>0.01186831162414009</v>
       </c>
       <c r="S72" t="inlineStr"/>
       <c r="T72" t="inlineStr"/>
@@ -8033,38 +8033,38 @@
       <c r="X72" t="inlineStr"/>
       <c r="Y72" t="inlineStr"/>
       <c r="Z72" t="n">
-        <v>0.874132867017217</v>
+        <v>0.8752494535083658</v>
       </c>
       <c r="AA72" t="n">
-        <v>0.01481743398670033</v>
+        <v>0.01475156371906827</v>
       </c>
       <c r="AB72" t="inlineStr"/>
       <c r="AC72" t="n">
-        <v>0.7955435151964435</v>
+        <v>0.7983015200767887</v>
       </c>
       <c r="AD72" t="n">
-        <v>0.004980617926090328</v>
+        <v>0.004946910977776198</v>
       </c>
       <c r="AE72" t="inlineStr"/>
       <c r="AF72" t="n">
-        <v>0.9510609888060759</v>
+        <v>0.9507928490029101</v>
       </c>
       <c r="AG72" t="n">
-        <v>0.006932623072027246</v>
+        <v>0.006951589258913556</v>
       </c>
       <c r="AH72" t="inlineStr"/>
       <c r="AI72" t="n">
-        <v>0.8432330043974766</v>
+        <v>0.8448082008498964</v>
       </c>
       <c r="AJ72" t="n">
-        <v>0.02039542268726629</v>
+        <v>0.02029269727636362</v>
       </c>
       <c r="AK72" t="inlineStr"/>
       <c r="AL72" t="n">
-        <v>0.8992162206224754</v>
+        <v>0.8996920647228908</v>
       </c>
       <c r="AM72" t="n">
-        <v>0.001447508347125764</v>
+        <v>0.001444087145549991</v>
       </c>
       <c r="AN72" t="inlineStr"/>
     </row>
@@ -8106,10 +8106,10 @@
         <v>0.01985208116188355</v>
       </c>
       <c r="K73" t="n">
-        <v>0.07823057899988078</v>
+        <v>0.08004889403840529</v>
       </c>
       <c r="L73" t="n">
-        <v>0.07897309760181233</v>
+        <v>0.08114029233833665</v>
       </c>
       <c r="M73" t="n">
         <v>0</v>
@@ -8118,16 +8118,16 @@
         <v>0</v>
       </c>
       <c r="O73" t="n">
-        <v>4.248593316158351</v>
+        <v>4.341167164957967</v>
       </c>
       <c r="P73" t="n">
-        <v>4.219470583051419</v>
+        <v>4.328595964617172</v>
       </c>
       <c r="Q73" t="n">
-        <v>0.9939675031331556</v>
+        <v>0.99396379112802</v>
       </c>
       <c r="R73" t="n">
-        <v>0.005165361105751143</v>
+        <v>0.005166950074523005</v>
       </c>
       <c r="S73" t="inlineStr"/>
       <c r="T73" t="inlineStr"/>
@@ -8137,38 +8137,38 @@
       <c r="X73" t="inlineStr"/>
       <c r="Y73" t="inlineStr"/>
       <c r="Z73" t="n">
-        <v>0.9488204343271356</v>
+        <v>0.9488331545213385</v>
       </c>
       <c r="AA73" t="n">
-        <v>0.007767489263112943</v>
+        <v>0.007766523935344358</v>
       </c>
       <c r="AB73" t="inlineStr"/>
       <c r="AC73" t="n">
-        <v>0.6123178230645259</v>
+        <v>0.6127159826583171</v>
       </c>
       <c r="AD73" t="n">
-        <v>0.001244669200602377</v>
+        <v>0.001244029882727097</v>
       </c>
       <c r="AE73" t="inlineStr"/>
       <c r="AF73" t="n">
-        <v>0.9645209311436876</v>
+        <v>0.9644744443477057</v>
       </c>
       <c r="AG73" t="n">
-        <v>0.006319749855966329</v>
+        <v>0.00632388875759245</v>
       </c>
       <c r="AH73" t="inlineStr"/>
       <c r="AI73" t="n">
-        <v>0.8260423998221404</v>
+        <v>0.8257202694666327</v>
       </c>
       <c r="AJ73" t="n">
-        <v>0.005099602343430179</v>
+        <v>0.005104321817953664</v>
       </c>
       <c r="AK73" t="inlineStr"/>
       <c r="AL73" t="n">
-        <v>-0.07132944660011598</v>
+        <v>-0.07098117044569197</v>
       </c>
       <c r="AM73" t="n">
-        <v>0.002361462171923441</v>
+        <v>0.002361078299427955</v>
       </c>
       <c r="AN73" t="inlineStr"/>
     </row>
@@ -8210,10 +8210,10 @@
         <v>0.03595872786204279</v>
       </c>
       <c r="K74" t="n">
-        <v>0.08513405677699858</v>
+        <v>0.08447253447494207</v>
       </c>
       <c r="L74" t="n">
-        <v>0.1655967713737086</v>
+        <v>0.1625861978258027</v>
       </c>
       <c r="M74" t="n">
         <v>0</v>
@@ -8222,16 +8222,16 @@
         <v>0</v>
       </c>
       <c r="O74" t="n">
-        <v>4.431244325415121</v>
+        <v>4.398896285344729</v>
       </c>
       <c r="P74" t="n">
-        <v>4.456983297157393</v>
+        <v>4.385988673786605</v>
       </c>
       <c r="Q74" t="n">
-        <v>0.969869586258971</v>
+        <v>0.9699037090616688</v>
       </c>
       <c r="R74" t="n">
-        <v>0.008222765883419345</v>
+        <v>0.008218108408320513</v>
       </c>
       <c r="S74" t="inlineStr"/>
       <c r="T74" t="inlineStr"/>
@@ -8241,38 +8241,38 @@
       <c r="X74" t="inlineStr"/>
       <c r="Y74" t="inlineStr"/>
       <c r="Z74" t="n">
-        <v>0.8556890052537963</v>
+        <v>0.8562060823726922</v>
       </c>
       <c r="AA74" t="n">
-        <v>0.009075961238933802</v>
+        <v>0.009059686722696567</v>
       </c>
       <c r="AB74" t="inlineStr"/>
       <c r="AC74" t="n">
-        <v>0.8691785458679916</v>
+        <v>0.8695764770133199</v>
       </c>
       <c r="AD74" t="n">
-        <v>0.00120195145568272</v>
+        <v>0.00120012202260546</v>
       </c>
       <c r="AE74" t="inlineStr"/>
       <c r="AF74" t="n">
-        <v>0.8769933148793208</v>
+        <v>0.8768505607842143</v>
       </c>
       <c r="AG74" t="n">
-        <v>0.01381020120368064</v>
+        <v>0.01381821252077201</v>
       </c>
       <c r="AH74" t="inlineStr"/>
       <c r="AI74" t="n">
-        <v>0.854648284865415</v>
+        <v>0.8554129903949861</v>
       </c>
       <c r="AJ74" t="n">
-        <v>0.007708595777670088</v>
+        <v>0.007688291306134383</v>
       </c>
       <c r="AK74" t="inlineStr"/>
       <c r="AL74" t="n">
-        <v>0.7051922540487452</v>
+        <v>0.7046206439018037</v>
       </c>
       <c r="AM74" t="n">
-        <v>0.002026703729093992</v>
+        <v>0.002028667591004688</v>
       </c>
       <c r="AN74" t="inlineStr"/>
     </row>
@@ -8314,10 +8314,10 @@
         <v>0.05396179716059933</v>
       </c>
       <c r="K75" t="n">
-        <v>0.210319821056764</v>
+        <v>0.2074205046880389</v>
       </c>
       <c r="L75" t="n">
-        <v>0.2634236320263108</v>
+        <v>0.2623019147692786</v>
       </c>
       <c r="M75" t="n">
         <v>0</v>
@@ -8326,16 +8326,16 @@
         <v>0</v>
       </c>
       <c r="O75" t="n">
-        <v>4.252039103170227</v>
+        <v>4.197065933067138</v>
       </c>
       <c r="P75" t="n">
-        <v>4.299044240918827</v>
+        <v>4.282679100501563</v>
       </c>
       <c r="Q75" t="n">
-        <v>0.9696019120289238</v>
+        <v>0.9696018005531949</v>
       </c>
       <c r="R75" t="n">
-        <v>0.006885532135907475</v>
+        <v>0.006885544761191853</v>
       </c>
       <c r="S75" t="inlineStr"/>
       <c r="T75" t="inlineStr"/>
@@ -8345,38 +8345,38 @@
       <c r="X75" t="inlineStr"/>
       <c r="Y75" t="inlineStr"/>
       <c r="Z75" t="n">
-        <v>0.8981176638451563</v>
+        <v>0.897979515517643</v>
       </c>
       <c r="AA75" t="n">
-        <v>0.01140568167166028</v>
+        <v>0.0114134118736275</v>
       </c>
       <c r="AB75" t="inlineStr"/>
       <c r="AC75" t="n">
-        <v>0.8464564021054091</v>
+        <v>0.8477274891773257</v>
       </c>
       <c r="AD75" t="n">
-        <v>0.002364376622409393</v>
+        <v>0.002354569719791642</v>
       </c>
       <c r="AE75" t="inlineStr"/>
       <c r="AF75" t="n">
-        <v>0.9213426443923648</v>
+        <v>0.9214214556774813</v>
       </c>
       <c r="AG75" t="n">
-        <v>0.007360748371424778</v>
+        <v>0.007357059870722868</v>
       </c>
       <c r="AH75" t="inlineStr"/>
       <c r="AI75" t="n">
-        <v>0.8715144130483571</v>
+        <v>0.8717190818218886</v>
       </c>
       <c r="AJ75" t="n">
-        <v>0.006799276671228964</v>
+        <v>0.006793859121008478</v>
       </c>
       <c r="AK75" t="inlineStr"/>
       <c r="AL75" t="n">
-        <v>0.9745507186122653</v>
+        <v>0.9745856468645073</v>
       </c>
       <c r="AM75" t="n">
-        <v>0.0009808837473821448</v>
+        <v>0.0009802104018786931</v>
       </c>
       <c r="AN75" t="inlineStr"/>
     </row>
@@ -8418,10 +8418,10 @@
         <v>0.03136066852465918</v>
       </c>
       <c r="K76" t="n">
-        <v>0.01998426772365844</v>
+        <v>0.02053193249929068</v>
       </c>
       <c r="L76" t="n">
-        <v>0.02450671973733828</v>
+        <v>0.02513714530450089</v>
       </c>
       <c r="M76" t="n">
         <v>0</v>
@@ -8430,16 +8430,16 @@
         <v>0</v>
       </c>
       <c r="O76" t="n">
-        <v>4.249893838573551</v>
+        <v>4.359073637778749</v>
       </c>
       <c r="P76" t="n">
-        <v>4.216642743375473</v>
+        <v>4.318198996410679</v>
       </c>
       <c r="Q76" t="n">
-        <v>0.9931713125430652</v>
+        <v>0.9931707673983977</v>
       </c>
       <c r="R76" t="n">
-        <v>0.00518535938823845</v>
+        <v>0.005185566361732481</v>
       </c>
       <c r="S76" t="inlineStr"/>
       <c r="T76" t="inlineStr"/>
@@ -8449,38 +8449,38 @@
       <c r="X76" t="inlineStr"/>
       <c r="Y76" t="inlineStr"/>
       <c r="Z76" t="n">
-        <v>0.936759501947704</v>
+        <v>0.9367592566914024</v>
       </c>
       <c r="AA76" t="n">
-        <v>0.007154815427212805</v>
+        <v>0.007154829300932363</v>
       </c>
       <c r="AB76" t="inlineStr"/>
       <c r="AC76" t="n">
-        <v>0.8856602418124458</v>
+        <v>0.8857275813456496</v>
       </c>
       <c r="AD76" t="n">
-        <v>0.0009322754287423825</v>
+        <v>0.0009320008600393794</v>
       </c>
       <c r="AE76" t="inlineStr"/>
       <c r="AF76" t="n">
-        <v>0.9550059818571397</v>
+        <v>0.9550001365592991</v>
       </c>
       <c r="AG76" t="n">
-        <v>0.008954429769472617</v>
+        <v>0.008955011398001417</v>
       </c>
       <c r="AH76" t="inlineStr"/>
       <c r="AI76" t="n">
-        <v>0.9887315412705995</v>
+        <v>0.9887224243519334</v>
       </c>
       <c r="AJ76" t="n">
-        <v>0.0008921754451073907</v>
+        <v>0.0008925362862222803</v>
       </c>
       <c r="AK76" t="inlineStr"/>
       <c r="AL76" t="n">
-        <v>0.5683680759093384</v>
+        <v>0.5683726223519512</v>
       </c>
       <c r="AM76" t="n">
-        <v>0.001183828168347948</v>
+        <v>0.001183821933613324</v>
       </c>
       <c r="AN76" t="inlineStr"/>
     </row>
@@ -8522,10 +8522,10 @@
         <v>0.02805201336700053</v>
       </c>
       <c r="K77" t="n">
-        <v>0.03972700182767472</v>
+        <v>0.03782537579660925</v>
       </c>
       <c r="L77" t="n">
-        <v>0.08804516698121599</v>
+        <v>0.0810297545649466</v>
       </c>
       <c r="M77" t="n">
         <v>0</v>
@@ -8534,16 +8534,16 @@
         <v>0</v>
       </c>
       <c r="O77" t="n">
-        <v>4.469822402045478</v>
+        <v>4.268656568147811</v>
       </c>
       <c r="P77" t="n">
-        <v>4.55307111873607</v>
+        <v>4.245264030884003</v>
       </c>
       <c r="Q77" t="n">
-        <v>0.9705445854393938</v>
+        <v>0.9704404554184087</v>
       </c>
       <c r="R77" t="n">
-        <v>0.01029178288752789</v>
+        <v>0.010309958460805</v>
       </c>
       <c r="S77" t="inlineStr"/>
       <c r="T77" t="inlineStr"/>
@@ -8553,38 +8553,38 @@
       <c r="X77" t="inlineStr"/>
       <c r="Y77" t="inlineStr"/>
       <c r="Z77" t="n">
-        <v>0.5346676032385946</v>
+        <v>0.5341118493949091</v>
       </c>
       <c r="AA77" t="n">
-        <v>0.01242830609820438</v>
+        <v>0.01243572554487824</v>
       </c>
       <c r="AB77" t="inlineStr"/>
       <c r="AC77" t="n">
-        <v>-0.5717452542310675</v>
+        <v>-0.582295642587052</v>
       </c>
       <c r="AD77" t="n">
-        <v>0.001226016424303441</v>
+        <v>0.00123012437861722</v>
       </c>
       <c r="AE77" t="inlineStr"/>
       <c r="AF77" t="n">
-        <v>0.900418690646708</v>
+        <v>0.8994691169864605</v>
       </c>
       <c r="AG77" t="n">
-        <v>0.01367974076813794</v>
+        <v>0.01374480870856579</v>
       </c>
       <c r="AH77" t="inlineStr"/>
       <c r="AI77" t="n">
-        <v>0.1665199098083074</v>
+        <v>0.1670451556864152</v>
       </c>
       <c r="AJ77" t="n">
-        <v>0.01363367037938438</v>
+        <v>0.01362937384140957</v>
       </c>
       <c r="AK77" t="inlineStr"/>
       <c r="AL77" t="n">
-        <v>0.8781589789734061</v>
+        <v>0.8761432611718952</v>
       </c>
       <c r="AM77" t="n">
-        <v>0.0007910693898610829</v>
+        <v>0.0007975862080373175</v>
       </c>
       <c r="AN77" t="inlineStr"/>
     </row>
@@ -8626,10 +8626,10 @@
         <v>0.01052672116974796</v>
       </c>
       <c r="K78" t="n">
-        <v>0.02841134719532212</v>
+        <v>0.02723295651487582</v>
       </c>
       <c r="L78" t="n">
-        <v>0.08118741286254531</v>
+        <v>0.07672500489828572</v>
       </c>
       <c r="M78" t="n">
         <v>0</v>
@@ -8638,16 +8638,16 @@
         <v>0</v>
       </c>
       <c r="O78" t="n">
-        <v>4.592870244659815</v>
+        <v>4.413573948301897</v>
       </c>
       <c r="P78" t="n">
-        <v>4.641336080836021</v>
+        <v>4.378228133504346</v>
       </c>
       <c r="Q78" t="n">
-        <v>0.9793835072922771</v>
+        <v>0.9788302541138123</v>
       </c>
       <c r="R78" t="n">
-        <v>0.01042651816742387</v>
+        <v>0.0105654922158259</v>
       </c>
       <c r="S78" t="inlineStr"/>
       <c r="T78" t="inlineStr"/>
@@ -8657,38 +8657,38 @@
       <c r="X78" t="inlineStr"/>
       <c r="Y78" t="inlineStr"/>
       <c r="Z78" t="n">
-        <v>0.115391647462593</v>
+        <v>0.113949239312316</v>
       </c>
       <c r="AA78" t="n">
-        <v>0.0114018097590613</v>
+        <v>0.01141110164775913</v>
       </c>
       <c r="AB78" t="inlineStr"/>
       <c r="AC78" t="n">
-        <v>0.7309757485715342</v>
+        <v>0.7001184909678355</v>
       </c>
       <c r="AD78" t="n">
-        <v>0.0006066841172578765</v>
+        <v>0.0006405333600049204</v>
       </c>
       <c r="AE78" t="inlineStr"/>
       <c r="AF78" t="n">
-        <v>0.8390898097169524</v>
+        <v>0.8316565248884472</v>
       </c>
       <c r="AG78" t="n">
-        <v>0.01649631478944097</v>
+        <v>0.01687303880176016</v>
       </c>
       <c r="AH78" t="inlineStr"/>
       <c r="AI78" t="n">
-        <v>-0.2176747054823913</v>
+        <v>-0.2331874867252572</v>
       </c>
       <c r="AJ78" t="n">
-        <v>0.01162528458276387</v>
+        <v>0.01169910140580508</v>
       </c>
       <c r="AK78" t="inlineStr"/>
       <c r="AL78" t="n">
-        <v>-1.714044742363709</v>
+        <v>-1.732284807928274</v>
       </c>
       <c r="AM78" t="n">
-        <v>0.00243237143865109</v>
+        <v>0.002440531274866863</v>
       </c>
       <c r="AN78" t="inlineStr"/>
     </row>
@@ -8730,10 +8730,10 @@
         <v>3.234988232153624e-17</v>
       </c>
       <c r="K79" t="n">
-        <v>0.2899193890845111</v>
+        <v>0.2905655997701949</v>
       </c>
       <c r="L79" t="n">
-        <v>0.3127446858319459</v>
+        <v>0.3193146508064549</v>
       </c>
       <c r="M79" t="n">
         <v>0</v>
@@ -8742,58 +8742,58 @@
         <v>0</v>
       </c>
       <c r="O79" t="n">
-        <v>4.375531902801428</v>
+        <v>4.384688376048642</v>
       </c>
       <c r="P79" t="n">
-        <v>4.432576077918742</v>
+        <v>4.414698453051978</v>
       </c>
       <c r="Q79" t="n">
-        <v>0.9810108722602041</v>
+        <v>0.9815531322839578</v>
       </c>
       <c r="R79" t="n">
-        <v>0.0202704360161466</v>
+        <v>0.01997891499838656</v>
       </c>
       <c r="S79" t="inlineStr"/>
       <c r="T79" t="n">
-        <v>0.9170676741277637</v>
+        <v>0.9196623074491694</v>
       </c>
       <c r="U79" t="n">
-        <v>0.04473029024035887</v>
+        <v>0.04402501071364347</v>
       </c>
       <c r="V79" t="inlineStr"/>
       <c r="W79" t="n">
-        <v>0.3527071299709108</v>
+        <v>0.3516903794273151</v>
       </c>
       <c r="X79" t="n">
-        <v>0.002264327602742231</v>
+        <v>0.002266105277930717</v>
       </c>
       <c r="Y79" t="inlineStr"/>
       <c r="Z79" t="n">
-        <v>0.9942276521231063</v>
+        <v>0.9944839157949258</v>
       </c>
       <c r="AA79" t="n">
-        <v>0.005937655902928306</v>
+        <v>0.005804358405889685</v>
       </c>
       <c r="AB79" t="inlineStr"/>
       <c r="AC79" t="n">
-        <v>0.5708832177632863</v>
+        <v>0.5717723827826132</v>
       </c>
       <c r="AD79" t="n">
-        <v>0.004951052288711787</v>
+        <v>0.004945920136422913</v>
       </c>
       <c r="AE79" t="inlineStr"/>
       <c r="AF79" t="n">
-        <v>0.9911652911557122</v>
+        <v>0.9905129846447099</v>
       </c>
       <c r="AG79" t="n">
-        <v>0.003015716966370638</v>
+        <v>0.003125066478163995</v>
       </c>
       <c r="AH79" t="inlineStr"/>
       <c r="AI79" t="n">
-        <v>0.8676387263675818</v>
+        <v>0.8635593018077488</v>
       </c>
       <c r="AJ79" t="n">
-        <v>0.00972203502580646</v>
+        <v>0.009870716514327103</v>
       </c>
       <c r="AK79" t="inlineStr"/>
       <c r="AL79" t="inlineStr"/>
@@ -8838,10 +8838,10 @@
         <v>7.592549229303372e-17</v>
       </c>
       <c r="K80" t="n">
-        <v>0.1594873656769697</v>
+        <v>0.1624757209231998</v>
       </c>
       <c r="L80" t="n">
-        <v>0.2379926598142801</v>
+        <v>0.2461187518334399</v>
       </c>
       <c r="M80" t="n">
         <v>0</v>
@@ -8850,58 +8850,58 @@
         <v>0</v>
       </c>
       <c r="O80" t="n">
-        <v>4.443827784785064</v>
+        <v>4.522041228329741</v>
       </c>
       <c r="P80" t="n">
-        <v>4.462778301728683</v>
+        <v>4.467278865581495</v>
       </c>
       <c r="Q80" t="n">
-        <v>0.9950458050695046</v>
+        <v>0.9950344922844104</v>
       </c>
       <c r="R80" t="n">
-        <v>0.009728520625944322</v>
+        <v>0.009739621713846859</v>
       </c>
       <c r="S80" t="inlineStr"/>
       <c r="T80" t="n">
-        <v>0.9834578043093579</v>
+        <v>0.983543339462064</v>
       </c>
       <c r="U80" t="n">
-        <v>0.02042400759812824</v>
+        <v>0.02037113569480754</v>
       </c>
       <c r="V80" t="inlineStr"/>
       <c r="W80" t="n">
-        <v>0.7804146988233094</v>
+        <v>0.7897403724063593</v>
       </c>
       <c r="X80" t="n">
-        <v>0.001253471854430479</v>
+        <v>0.001226565936104548</v>
       </c>
       <c r="Y80" t="inlineStr"/>
       <c r="Z80" t="n">
-        <v>0.9987612981391422</v>
+        <v>0.998808074989621</v>
       </c>
       <c r="AA80" t="n">
-        <v>0.00225966372002814</v>
+        <v>0.002216587522656439</v>
       </c>
       <c r="AB80" t="inlineStr"/>
       <c r="AC80" t="n">
-        <v>0.8089427781448492</v>
+        <v>0.8188547743234074</v>
       </c>
       <c r="AD80" t="n">
-        <v>0.003636840723033805</v>
+        <v>0.00354124519466525</v>
       </c>
       <c r="AE80" t="inlineStr"/>
       <c r="AF80" t="n">
-        <v>0.9877841139018675</v>
+        <v>0.9865905088871375</v>
       </c>
       <c r="AG80" t="n">
-        <v>0.00586242248404211</v>
+        <v>0.006142155035295631</v>
       </c>
       <c r="AH80" t="inlineStr"/>
       <c r="AI80" t="n">
-        <v>0.9635739665804065</v>
+        <v>0.9619852004538377</v>
       </c>
       <c r="AJ80" t="n">
-        <v>0.006252755606507725</v>
+        <v>0.006387661091562089</v>
       </c>
       <c r="AK80" t="inlineStr"/>
       <c r="AL80" t="inlineStr"/>
@@ -8946,66 +8946,66 @@
         <v>9.901399624920571e-18</v>
       </c>
       <c r="K81" t="n">
-        <v>0.2816063271155299</v>
+        <v>0.2809117196549366</v>
       </c>
       <c r="L81" t="n">
-        <v>0.2485526988237288</v>
+        <v>0.2569309911902229</v>
       </c>
       <c r="M81" t="n">
-        <v>0.01069204248481415</v>
+        <v>0.01550715044127104</v>
       </c>
       <c r="N81" t="n">
-        <v>0.0002138408496962829</v>
+        <v>0.0003101430088254209</v>
       </c>
       <c r="O81" t="n">
-        <v>4.554087837697824</v>
+        <v>4.54352300571286</v>
       </c>
       <c r="P81" t="n">
-        <v>4.556580055481451</v>
+        <v>4.588441251671693</v>
       </c>
       <c r="Q81" t="n">
-        <v>0.9916205150185653</v>
+        <v>0.9917981954435768</v>
       </c>
       <c r="R81" t="n">
-        <v>0.01244013340701087</v>
+        <v>0.01230753508043567</v>
       </c>
       <c r="S81" t="inlineStr"/>
       <c r="T81" t="n">
-        <v>0.9754961001087589</v>
+        <v>0.9763480632363547</v>
       </c>
       <c r="U81" t="n">
-        <v>0.02345876100324216</v>
+        <v>0.02304734062916472</v>
       </c>
       <c r="V81" t="inlineStr"/>
       <c r="W81" t="inlineStr"/>
       <c r="X81" t="inlineStr"/>
       <c r="Y81" t="inlineStr"/>
       <c r="Z81" t="n">
-        <v>0.9810094110299991</v>
+        <v>0.9798612306265722</v>
       </c>
       <c r="AA81" t="n">
-        <v>0.009082288430173191</v>
+        <v>0.009352819157074034</v>
       </c>
       <c r="AB81" t="inlineStr"/>
       <c r="AC81" t="n">
-        <v>0.7553199052409635</v>
+        <v>0.7584794322591948</v>
       </c>
       <c r="AD81" t="n">
-        <v>0.003003684806147688</v>
+        <v>0.002984228668381514</v>
       </c>
       <c r="AE81" t="inlineStr"/>
       <c r="AF81" t="n">
-        <v>0.9655603672724828</v>
+        <v>0.9655625310468964</v>
       </c>
       <c r="AG81" t="n">
-        <v>0.005953770565975743</v>
+        <v>0.005953583531188377</v>
       </c>
       <c r="AH81" t="inlineStr"/>
       <c r="AI81" t="n">
-        <v>0.958984237369588</v>
+        <v>0.9598947322598147</v>
       </c>
       <c r="AJ81" t="n">
-        <v>0.009824136532952098</v>
+        <v>0.009714483254968766</v>
       </c>
       <c r="AK81" t="inlineStr"/>
       <c r="AL81" t="inlineStr"/>
@@ -9050,66 +9050,66 @@
         <v>1.336850539002381e-17</v>
       </c>
       <c r="K82" t="n">
-        <v>0.2406107375126686</v>
+        <v>0.2356503211145312</v>
       </c>
       <c r="L82" t="n">
-        <v>0.1471991443837643</v>
+        <v>0.148057751150015</v>
       </c>
       <c r="M82" t="n">
-        <v>0.2108993759064173</v>
+        <v>0.1919334392279288</v>
       </c>
       <c r="N82" t="n">
-        <v>0.01269152303177152</v>
+        <v>0.01023216588646753</v>
       </c>
       <c r="O82" t="n">
-        <v>4.554008665274212</v>
+        <v>4.465692697328193</v>
       </c>
       <c r="P82" t="n">
-        <v>4.541138553390528</v>
+        <v>4.595172440501289</v>
       </c>
       <c r="Q82" t="n">
-        <v>0.9708461230986132</v>
+        <v>0.9711553463945806</v>
       </c>
       <c r="R82" t="n">
-        <v>0.02303314389211881</v>
+        <v>0.02291066667270036</v>
       </c>
       <c r="S82" t="inlineStr"/>
       <c r="T82" t="n">
-        <v>0.9193585043037708</v>
+        <v>0.9203277336269829</v>
       </c>
       <c r="U82" t="n">
-        <v>0.04433586969603506</v>
+        <v>0.04406862808979577</v>
       </c>
       <c r="V82" t="inlineStr"/>
       <c r="W82" t="inlineStr"/>
       <c r="X82" t="inlineStr"/>
       <c r="Y82" t="inlineStr"/>
       <c r="Z82" t="n">
-        <v>0.9498716899984319</v>
+        <v>0.9500201927113195</v>
       </c>
       <c r="AA82" t="n">
-        <v>0.01499146867160424</v>
+        <v>0.01496924644805508</v>
       </c>
       <c r="AB82" t="inlineStr"/>
       <c r="AC82" t="n">
-        <v>0.2976538942532601</v>
+        <v>0.3195872818241132</v>
       </c>
       <c r="AD82" t="n">
-        <v>0.002459687041678957</v>
+        <v>0.002420975949937057</v>
       </c>
       <c r="AE82" t="inlineStr"/>
       <c r="AF82" t="n">
-        <v>0.7232193574315088</v>
+        <v>0.7238868540660283</v>
       </c>
       <c r="AG82" t="n">
-        <v>0.01892725500179791</v>
+        <v>0.01890441831567093</v>
       </c>
       <c r="AH82" t="inlineStr"/>
       <c r="AI82" t="n">
-        <v>0.9649248214328021</v>
+        <v>0.9659246342608525</v>
       </c>
       <c r="AJ82" t="n">
-        <v>0.00989565919449892</v>
+        <v>0.009753602390630785</v>
       </c>
       <c r="AK82" t="inlineStr"/>
       <c r="AL82" t="inlineStr"/>
@@ -9152,10 +9152,10 @@
         <v>0.002282733977536599</v>
       </c>
       <c r="K83" t="n">
-        <v>0.1872142165502269</v>
+        <v>0.1900383461359677</v>
       </c>
       <c r="L83" t="n">
-        <v>0.1772856146487613</v>
+        <v>0.1856317839407446</v>
       </c>
       <c r="M83" t="n">
         <v>0</v>
@@ -9164,54 +9164,54 @@
         <v>0</v>
       </c>
       <c r="O83" t="n">
-        <v>4.516876761044007</v>
+        <v>4.580927191812872</v>
       </c>
       <c r="P83" t="n">
-        <v>4.496978800745321</v>
+        <v>4.571235328818583</v>
       </c>
       <c r="Q83" t="n">
-        <v>0.9756557465620812</v>
+        <v>0.9757404407581288</v>
       </c>
       <c r="R83" t="n">
-        <v>0.0186801778776956</v>
+        <v>0.01864765519030246</v>
       </c>
       <c r="S83" t="inlineStr"/>
       <c r="T83" t="n">
-        <v>0.9246272290043949</v>
+        <v>0.9249197679761967</v>
       </c>
       <c r="U83" t="n">
-        <v>0.03558079340781971</v>
+        <v>0.03551167767854237</v>
       </c>
       <c r="V83" t="inlineStr"/>
       <c r="W83" t="inlineStr"/>
       <c r="X83" t="inlineStr"/>
       <c r="Y83" t="inlineStr"/>
       <c r="Z83" t="n">
-        <v>0.9588429002158336</v>
+        <v>0.9595537246507585</v>
       </c>
       <c r="AA83" t="n">
-        <v>0.009782693923165123</v>
+        <v>0.009697847508947198</v>
       </c>
       <c r="AB83" t="inlineStr"/>
       <c r="AC83" t="n">
-        <v>0.2706377311692613</v>
+        <v>0.2748498321819083</v>
       </c>
       <c r="AD83" t="n">
-        <v>0.009545153594210294</v>
+        <v>0.009517551833251826</v>
       </c>
       <c r="AE83" t="inlineStr"/>
       <c r="AF83" t="n">
-        <v>0.9194893463950172</v>
+        <v>0.9182823089316973</v>
       </c>
       <c r="AG83" t="n">
-        <v>0.01089227453347397</v>
+        <v>0.0109736207374806</v>
       </c>
       <c r="AH83" t="inlineStr"/>
       <c r="AI83" t="n">
-        <v>0.8753081213351324</v>
+        <v>0.87585213908829</v>
       </c>
       <c r="AJ83" t="n">
-        <v>0.01316433310645966</v>
+        <v>0.0131355844042773</v>
       </c>
       <c r="AK83" t="inlineStr"/>
       <c r="AL83" t="inlineStr"/>
@@ -9254,10 +9254,10 @@
         <v>0.001579598306755124</v>
       </c>
       <c r="K84" t="n">
-        <v>0.1659043674747134</v>
+        <v>0.1700871734410854</v>
       </c>
       <c r="L84" t="n">
-        <v>0.2246133380102152</v>
+        <v>0.230632505156051</v>
       </c>
       <c r="M84" t="n">
         <v>0</v>
@@ -9266,54 +9266,54 @@
         <v>0</v>
       </c>
       <c r="O84" t="n">
-        <v>4.44868884650036</v>
+        <v>4.554043371413063</v>
       </c>
       <c r="P84" t="n">
-        <v>4.427867387048924</v>
+        <v>4.502795030495846</v>
       </c>
       <c r="Q84" t="n">
-        <v>0.9931423054468013</v>
+        <v>0.9948887639565135</v>
       </c>
       <c r="R84" t="n">
-        <v>0.009724780627055927</v>
+        <v>0.008395638170334084</v>
       </c>
       <c r="S84" t="inlineStr"/>
       <c r="T84" t="n">
-        <v>0.9859308616308792</v>
+        <v>0.9920505547613314</v>
       </c>
       <c r="U84" t="n">
-        <v>0.01586415409375104</v>
+        <v>0.01192481307821156</v>
       </c>
       <c r="V84" t="inlineStr"/>
       <c r="W84" t="inlineStr"/>
       <c r="X84" t="inlineStr"/>
       <c r="Y84" t="inlineStr"/>
       <c r="Z84" t="n">
-        <v>0.9951750783690448</v>
+        <v>0.9949403542211152</v>
       </c>
       <c r="AA84" t="n">
-        <v>0.004738890957035947</v>
+        <v>0.00485279159118447</v>
       </c>
       <c r="AB84" t="inlineStr"/>
       <c r="AC84" t="n">
-        <v>0.2545535877646719</v>
+        <v>0.26012084473174</v>
       </c>
       <c r="AD84" t="n">
-        <v>0.007816830767515095</v>
+        <v>0.007787586637965768</v>
       </c>
       <c r="AE84" t="inlineStr"/>
       <c r="AF84" t="n">
-        <v>0.921557783877419</v>
+        <v>0.9283595202945578</v>
       </c>
       <c r="AG84" t="n">
-        <v>0.01154295585124645</v>
+        <v>0.01103116421793434</v>
       </c>
       <c r="AH84" t="inlineStr"/>
       <c r="AI84" t="n">
-        <v>0.9957730490350364</v>
+        <v>0.9958075410492805</v>
       </c>
       <c r="AJ84" t="n">
-        <v>0.002094193299831946</v>
+        <v>0.002085631465824958</v>
       </c>
       <c r="AK84" t="inlineStr"/>
       <c r="AL84" t="inlineStr"/>
@@ -9356,10 +9356,10 @@
         <v>0</v>
       </c>
       <c r="K85" t="n">
-        <v>0.2307899480131057</v>
+        <v>0.234087371719241</v>
       </c>
       <c r="L85" t="n">
-        <v>0.271167086757682</v>
+        <v>0.2801892349008259</v>
       </c>
       <c r="M85" t="n">
         <v>0</v>
@@ -9368,54 +9368,54 @@
         <v>0</v>
       </c>
       <c r="O85" t="n">
-        <v>4.429178952661008</v>
+        <v>4.488615918273156</v>
       </c>
       <c r="P85" t="n">
-        <v>4.43994582376336</v>
+        <v>4.486831162584882</v>
       </c>
       <c r="Q85" t="n">
-        <v>0.97985006746092</v>
+        <v>0.9818367647150974</v>
       </c>
       <c r="R85" t="n">
-        <v>0.01774038604421447</v>
+        <v>0.01684313277916491</v>
       </c>
       <c r="S85" t="inlineStr"/>
       <c r="T85" t="n">
-        <v>0.9456307928860657</v>
+        <v>0.9556639838304075</v>
       </c>
       <c r="U85" t="n">
-        <v>0.02993496664281876</v>
+        <v>0.02703215146365415</v>
       </c>
       <c r="V85" t="inlineStr"/>
       <c r="W85" t="inlineStr"/>
       <c r="X85" t="inlineStr"/>
       <c r="Y85" t="inlineStr"/>
       <c r="Z85" t="n">
-        <v>0.9958862822495433</v>
+        <v>0.9930839207702232</v>
       </c>
       <c r="AA85" t="n">
-        <v>0.004942661777912991</v>
+        <v>0.006408754386141705</v>
       </c>
       <c r="AB85" t="inlineStr"/>
       <c r="AC85" t="n">
-        <v>-0.1892640510990242</v>
+        <v>-0.17773506303766</v>
       </c>
       <c r="AD85" t="n">
-        <v>0.01704145130355583</v>
+        <v>0.01695864834316122</v>
       </c>
       <c r="AE85" t="inlineStr"/>
       <c r="AF85" t="n">
-        <v>0.6546605816140657</v>
+        <v>0.6562344056870232</v>
       </c>
       <c r="AG85" t="n">
-        <v>0.01898024103914263</v>
+        <v>0.01893694208448688</v>
       </c>
       <c r="AH85" t="inlineStr"/>
       <c r="AI85" t="n">
-        <v>0.9970373945599537</v>
+        <v>0.9994565910971632</v>
       </c>
       <c r="AJ85" t="n">
-        <v>0.00155362131675181</v>
+        <v>0.0006653829039369449</v>
       </c>
       <c r="AK85" t="inlineStr"/>
       <c r="AL85" t="inlineStr"/>
@@ -9458,10 +9458,10 @@
         <v>0.001282293415705915</v>
       </c>
       <c r="K86" t="n">
-        <v>0.1218510305567165</v>
+        <v>0.1246919775437176</v>
       </c>
       <c r="L86" t="n">
-        <v>0.1509599798149005</v>
+        <v>0.1551042893757214</v>
       </c>
       <c r="M86" t="n">
         <v>0</v>
@@ -9470,54 +9470,54 @@
         <v>0</v>
       </c>
       <c r="O86" t="n">
-        <v>4.469780948890098</v>
+        <v>4.567691173450372</v>
       </c>
       <c r="P86" t="n">
-        <v>4.396928523311477</v>
+        <v>4.512783918100642</v>
       </c>
       <c r="Q86" t="n">
-        <v>0.9908000537962977</v>
+        <v>0.9909039273174141</v>
       </c>
       <c r="R86" t="n">
-        <v>0.01143967245848712</v>
+        <v>0.01137490837087109</v>
       </c>
       <c r="S86" t="inlineStr"/>
       <c r="T86" t="n">
-        <v>0.9861205437420999</v>
+        <v>0.9863386789774761</v>
       </c>
       <c r="U86" t="n">
-        <v>0.01637592225660886</v>
+        <v>0.01624672726569851</v>
       </c>
       <c r="V86" t="inlineStr"/>
       <c r="W86" t="inlineStr"/>
       <c r="X86" t="inlineStr"/>
       <c r="Y86" t="inlineStr"/>
       <c r="Z86" t="n">
-        <v>0.9966267204910166</v>
+        <v>0.9964264413668207</v>
       </c>
       <c r="AA86" t="n">
-        <v>0.003378422419369597</v>
+        <v>0.003477268628531569</v>
       </c>
       <c r="AB86" t="inlineStr"/>
       <c r="AC86" t="n">
-        <v>-0.4067486938097016</v>
+        <v>-0.3971742526560873</v>
       </c>
       <c r="AD86" t="n">
-        <v>0.0177535630609126</v>
+        <v>0.01769304384414355</v>
       </c>
       <c r="AE86" t="inlineStr"/>
       <c r="AF86" t="n">
-        <v>0.9866654374177412</v>
+        <v>0.9870512751829403</v>
       </c>
       <c r="AG86" t="n">
-        <v>0.005903818132130146</v>
+        <v>0.005817777186068403</v>
       </c>
       <c r="AH86" t="inlineStr"/>
       <c r="AI86" t="n">
-        <v>0.9766126777232114</v>
+        <v>0.977272647402363</v>
       </c>
       <c r="AJ86" t="n">
-        <v>0.004970099807255247</v>
+        <v>0.004899472054219723</v>
       </c>
       <c r="AK86" t="inlineStr"/>
       <c r="AL86" t="inlineStr"/>
@@ -9560,10 +9560,10 @@
         <v>1.327388309752159e-16</v>
       </c>
       <c r="K87" t="n">
-        <v>0.1823831187847791</v>
+        <v>0.1836947289226107</v>
       </c>
       <c r="L87" t="n">
-        <v>0.2670271452040271</v>
+        <v>0.2688491759473688</v>
       </c>
       <c r="M87" t="n">
         <v>0</v>
@@ -9572,54 +9572,54 @@
         <v>0</v>
       </c>
       <c r="O87" t="n">
-        <v>4.595558295125066</v>
+        <v>4.672696706020264</v>
       </c>
       <c r="P87" t="n">
-        <v>4.487800855705391</v>
+        <v>4.6165916632368</v>
       </c>
       <c r="Q87" t="n">
-        <v>0.9475031978279539</v>
+        <v>0.9489770484239606</v>
       </c>
       <c r="R87" t="n">
-        <v>0.02568590546386842</v>
+        <v>0.02532277196970733</v>
       </c>
       <c r="S87" t="inlineStr"/>
       <c r="T87" t="n">
-        <v>0.8853546793967833</v>
+        <v>0.8878462413202373</v>
       </c>
       <c r="U87" t="n">
-        <v>0.04390341990442511</v>
+        <v>0.0434237275674613</v>
       </c>
       <c r="V87" t="inlineStr"/>
       <c r="W87" t="inlineStr"/>
       <c r="X87" t="inlineStr"/>
       <c r="Y87" t="inlineStr"/>
       <c r="Z87" t="n">
-        <v>0.8450548750315666</v>
+        <v>0.8462727822444029</v>
       </c>
       <c r="AA87" t="n">
-        <v>0.02200030273565433</v>
+        <v>0.02191366823242608</v>
       </c>
       <c r="AB87" t="inlineStr"/>
       <c r="AC87" t="n">
-        <v>0.6284450780807785</v>
+        <v>0.6242750973345792</v>
       </c>
       <c r="AD87" t="n">
-        <v>0.007144935787732817</v>
+        <v>0.00718491791843408</v>
       </c>
       <c r="AE87" t="inlineStr"/>
       <c r="AF87" t="n">
-        <v>0.3703530346765419</v>
+        <v>0.4004281704486305</v>
       </c>
       <c r="AG87" t="n">
-        <v>0.02803608462879711</v>
+        <v>0.02735831935623596</v>
       </c>
       <c r="AH87" t="inlineStr"/>
       <c r="AI87" t="n">
-        <v>0.9801541462578517</v>
+        <v>0.9840846440822304</v>
       </c>
       <c r="AJ87" t="n">
-        <v>0.007087520652902481</v>
+        <v>0.006346987190991339</v>
       </c>
       <c r="AK87" t="inlineStr"/>
       <c r="AL87" t="inlineStr"/>
@@ -9662,10 +9662,10 @@
         <v>1.912261794240524e-16</v>
       </c>
       <c r="K88" t="n">
-        <v>0.2319557577696864</v>
+        <v>0.2272428571521708</v>
       </c>
       <c r="L88" t="n">
-        <v>0.1673537791490217</v>
+        <v>0.1651873530295883</v>
       </c>
       <c r="M88" t="n">
         <v>0</v>
@@ -9674,54 +9674,54 @@
         <v>0</v>
       </c>
       <c r="O88" t="n">
-        <v>4.602089508487431</v>
+        <v>4.514091802725877</v>
       </c>
       <c r="P88" t="n">
-        <v>4.562635209319115</v>
+        <v>4.61723128323364</v>
       </c>
       <c r="Q88" t="n">
-        <v>0.9907163219083407</v>
+        <v>0.9913494165910501</v>
       </c>
       <c r="R88" t="n">
-        <v>0.01129665073895184</v>
+        <v>0.0109046659038848</v>
       </c>
       <c r="S88" t="inlineStr"/>
       <c r="T88" t="n">
-        <v>0.9725877759883423</v>
+        <v>0.9752431053517345</v>
       </c>
       <c r="U88" t="n">
-        <v>0.0208673574022487</v>
+        <v>0.01983094465978683</v>
       </c>
       <c r="V88" t="inlineStr"/>
       <c r="W88" t="inlineStr"/>
       <c r="X88" t="inlineStr"/>
       <c r="Y88" t="inlineStr"/>
       <c r="Z88" t="n">
-        <v>0.9839007403157826</v>
+        <v>0.9852437620085113</v>
       </c>
       <c r="AA88" t="n">
-        <v>0.007179042179345218</v>
+        <v>0.006873079662333934</v>
       </c>
       <c r="AB88" t="inlineStr"/>
       <c r="AC88" t="n">
-        <v>0.5443885338955541</v>
+        <v>0.5498833804488671</v>
       </c>
       <c r="AD88" t="n">
-        <v>0.004210473827401671</v>
+        <v>0.004185006855959471</v>
       </c>
       <c r="AE88" t="inlineStr"/>
       <c r="AF88" t="n">
-        <v>0.9649689841371578</v>
+        <v>0.9655160293539473</v>
       </c>
       <c r="AG88" t="n">
-        <v>0.00557873314337093</v>
+        <v>0.005535002930686352</v>
       </c>
       <c r="AH88" t="inlineStr"/>
       <c r="AI88" t="n">
-        <v>0.9507208307437536</v>
+        <v>0.948953489190605</v>
       </c>
       <c r="AJ88" t="n">
-        <v>0.01011118117170909</v>
+        <v>0.01029089706513912</v>
       </c>
       <c r="AK88" t="inlineStr"/>
       <c r="AL88" t="inlineStr"/>
@@ -9764,66 +9764,66 @@
         <v>0</v>
       </c>
       <c r="K89" t="n">
-        <v>0.3543155928022084</v>
+        <v>0.3475847711320364</v>
       </c>
       <c r="L89" t="n">
-        <v>0.3108689021183701</v>
+        <v>0.3219291007459254</v>
       </c>
       <c r="M89" t="n">
-        <v>0.08273603057695156</v>
+        <v>0.06172363439144923</v>
       </c>
       <c r="N89" t="n">
-        <v>0.002305409273078578</v>
+        <v>0.001234472687828985</v>
       </c>
       <c r="O89" t="n">
-        <v>4.568276553466714</v>
+        <v>4.486632846602943</v>
       </c>
       <c r="P89" t="n">
-        <v>4.619463225094313</v>
+        <v>4.608423456168605</v>
       </c>
       <c r="Q89" t="n">
-        <v>0.994872429256817</v>
+        <v>0.9957171218059206</v>
       </c>
       <c r="R89" t="n">
-        <v>0.008473967515035652</v>
+        <v>0.007744597041355554</v>
       </c>
       <c r="S89" t="inlineStr"/>
       <c r="T89" t="n">
-        <v>0.99053130003781</v>
+        <v>0.9942343058906028</v>
       </c>
       <c r="U89" t="n">
-        <v>0.01329804062030081</v>
+        <v>0.01037691541133552</v>
       </c>
       <c r="V89" t="inlineStr"/>
       <c r="W89" t="inlineStr"/>
       <c r="X89" t="inlineStr"/>
       <c r="Y89" t="inlineStr"/>
       <c r="Z89" t="n">
-        <v>0.9953622910040673</v>
+        <v>0.995288873412944</v>
       </c>
       <c r="AA89" t="n">
-        <v>0.005189795622368448</v>
+        <v>0.005230713041086837</v>
       </c>
       <c r="AB89" t="inlineStr"/>
       <c r="AC89" t="n">
-        <v>0.7766982200827384</v>
+        <v>0.7649954660437221</v>
       </c>
       <c r="AD89" t="n">
-        <v>0.00457953235582101</v>
+        <v>0.004698001596208661</v>
       </c>
       <c r="AE89" t="inlineStr"/>
       <c r="AF89" t="n">
-        <v>0.9842042906898373</v>
+        <v>0.9803471441415109</v>
       </c>
       <c r="AG89" t="n">
-        <v>0.003053523184427446</v>
+        <v>0.0034059987940385</v>
       </c>
       <c r="AH89" t="inlineStr"/>
       <c r="AI89" t="n">
-        <v>0.9396515917658165</v>
+        <v>0.9366535539697193</v>
       </c>
       <c r="AJ89" t="n">
-        <v>0.01117911641644476</v>
+        <v>0.01145343343760667</v>
       </c>
       <c r="AK89" t="inlineStr"/>
       <c r="AL89" t="inlineStr"/>
@@ -9866,66 +9866,66 @@
         <v>0.03004752976171331</v>
       </c>
       <c r="K90" t="n">
-        <v>0.5131582127201041</v>
+        <v>0.559419327333303</v>
       </c>
       <c r="L90" t="n">
-        <v>0.4251117419112213</v>
+        <v>0.5228129052136478</v>
       </c>
       <c r="M90" t="n">
-        <v>0.6632550948527474</v>
+        <v>0.6569645775186483</v>
       </c>
       <c r="N90" t="n">
-        <v>0.1250881464897366</v>
+        <v>0.125351088660468</v>
       </c>
       <c r="O90" t="n">
-        <v>4.174898420666395</v>
+        <v>4.527214580177771</v>
       </c>
       <c r="P90" t="n">
-        <v>3.504704320236897</v>
+        <v>4.271620727012309</v>
       </c>
       <c r="Q90" t="n">
-        <v>0.9885211649590315</v>
+        <v>0.9896098720581251</v>
       </c>
       <c r="R90" t="n">
-        <v>0.01416735234515507</v>
+        <v>0.0134787691528249</v>
       </c>
       <c r="S90" t="inlineStr"/>
       <c r="T90" t="n">
-        <v>0.978701265047257</v>
+        <v>0.9807444152220886</v>
       </c>
       <c r="U90" t="n">
-        <v>0.02363539101223452</v>
+        <v>0.02247316513712744</v>
       </c>
       <c r="V90" t="inlineStr"/>
       <c r="W90" t="inlineStr"/>
       <c r="X90" t="inlineStr"/>
       <c r="Y90" t="inlineStr"/>
       <c r="Z90" t="n">
-        <v>0.9865811403034008</v>
+        <v>0.9878716595717181</v>
       </c>
       <c r="AA90" t="n">
-        <v>0.01496452263748116</v>
+        <v>0.01422675166769076</v>
       </c>
       <c r="AB90" t="inlineStr"/>
       <c r="AC90" t="n">
-        <v>0.8363186057414039</v>
+        <v>0.8296037825163912</v>
       </c>
       <c r="AD90" t="n">
-        <v>0.004609422135545868</v>
+        <v>0.004703019724144339</v>
       </c>
       <c r="AE90" t="inlineStr"/>
       <c r="AF90" t="n">
-        <v>0.9951488866144714</v>
+        <v>0.9948889173041052</v>
       </c>
       <c r="AG90" t="n">
-        <v>0.0005305066683491195</v>
+        <v>0.0005445359893933593</v>
       </c>
       <c r="AH90" t="inlineStr"/>
       <c r="AI90" t="n">
-        <v>0.9809067275066478</v>
+        <v>0.9843216885672784</v>
       </c>
       <c r="AJ90" t="n">
-        <v>0.004529192933228267</v>
+        <v>0.004104216662021562</v>
       </c>
       <c r="AK90" t="inlineStr"/>
       <c r="AL90" t="inlineStr"/>

--- a/tables/N-Retention/Local_perf_matrix_protection_True_vo_False_CUE_True.xlsx
+++ b/tables/N-Retention/Local_perf_matrix_protection_True_vo_False_CUE_True.xlsx
@@ -653,25 +653,25 @@
         <v>70.85714285714286</v>
       </c>
       <c r="F2" t="n">
-        <v>0.432164952517398</v>
+        <v>0.4321649524844555</v>
       </c>
       <c r="G2" t="n">
         <v>0.04480286738351254</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2627803891781534</v>
+        <v>0.2627803892434106</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2428872347095719</v>
+        <v>0.2428872346838566</v>
       </c>
       <c r="J2" t="n">
-        <v>0.01736455621136393</v>
+        <v>0.01736455620476475</v>
       </c>
       <c r="K2" t="n">
-        <v>0.2301739080636254</v>
+        <v>0.1675305560867122</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2039300344446321</v>
+        <v>0.204846462719715</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
@@ -680,16 +680,16 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>4.404174211659919</v>
+        <v>4.38984251428735</v>
       </c>
       <c r="P2" t="n">
-        <v>4.431424726619325</v>
+        <v>4.431227414842789</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9919808004389647</v>
+        <v>0.9902211115362363</v>
       </c>
       <c r="R2" t="n">
-        <v>0.005504640840660609</v>
+        <v>0.006078665196490592</v>
       </c>
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr"/>
@@ -699,38 +699,38 @@
       <c r="X2" t="inlineStr"/>
       <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="n">
-        <v>0.9890124723429545</v>
+        <v>0.9873359517631325</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.007601547069301921</v>
+        <v>0.008160904136693703</v>
       </c>
       <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="n">
-        <v>0.9996337786634818</v>
+        <v>0.9996362892401145</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.0001259181153758649</v>
+        <v>0.0001254857665442994</v>
       </c>
       <c r="AE2" t="inlineStr"/>
       <c r="AF2" t="n">
-        <v>0.9971302268093319</v>
+        <v>0.9964802293392158</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.00226031080822027</v>
+        <v>0.002503234630236532</v>
       </c>
       <c r="AH2" t="inlineStr"/>
       <c r="AI2" t="n">
-        <v>0.9580123109228823</v>
+        <v>0.9467715915209353</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.008719266839641967</v>
+        <v>0.009817269718867559</v>
       </c>
       <c r="AK2" t="inlineStr"/>
       <c r="AL2" t="n">
-        <v>0.7265464176595912</v>
+        <v>0.6490235369003312</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.001573623121912464</v>
+        <v>0.001782780657027325</v>
       </c>
       <c r="AN2" t="inlineStr"/>
     </row>
@@ -757,43 +757,43 @@
         <v>82.71186440677965</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4230480283044928</v>
+        <v>0.4230480283479805</v>
       </c>
       <c r="G3" t="n">
         <v>0.03838147280770231</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3417824749441816</v>
+        <v>0.341782474747073</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1733633998846752</v>
+        <v>0.1733633999809309</v>
       </c>
       <c r="J3" t="n">
-        <v>0.02342462405894816</v>
+        <v>0.02342462411631339</v>
       </c>
       <c r="K3" t="n">
-        <v>0.124492385839805</v>
+        <v>0.07316695088643521</v>
       </c>
       <c r="L3" t="n">
-        <v>0.5467435544568545</v>
+        <v>0.5472992917928778</v>
       </c>
       <c r="M3" t="n">
-        <v>0.9968569791571076</v>
+        <v>0.9999533840445122</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1623742095056984</v>
+        <v>0.9914415362022148</v>
       </c>
       <c r="O3" t="n">
-        <v>4.381960123977297</v>
+        <v>4.382030300423189</v>
       </c>
       <c r="P3" t="n">
-        <v>4.403723974542996</v>
+        <v>4.415507514592171</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.7784300444341792</v>
+        <v>0.7781479672248282</v>
       </c>
       <c r="R3" t="n">
-        <v>0.02862366263480937</v>
+        <v>0.02864187700201053</v>
       </c>
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr"/>
@@ -803,38 +803,38 @@
       <c r="X3" t="inlineStr"/>
       <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="n">
-        <v>0.9885271892509452</v>
+        <v>0.9893553636581875</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.006882757315669541</v>
+        <v>0.006629685952884967</v>
       </c>
       <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="n">
-        <v>0.9999999439123698</v>
+        <v>-1.05718622810043</v>
       </c>
       <c r="AD3" t="n">
-        <v>5.799323555995009e-07</v>
+        <v>0.00351221099636464</v>
       </c>
       <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="n">
-        <v>-0.6015617472902204</v>
+        <v>-0.6016290106713973</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.06137885848485977</v>
+        <v>0.06138014733826209</v>
       </c>
       <c r="AH3" t="inlineStr"/>
       <c r="AI3" t="n">
-        <v>0.9904344700806155</v>
+        <v>0.9908184711382073</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.002371944525827628</v>
+        <v>0.00232384690119623</v>
       </c>
       <c r="AK3" t="inlineStr"/>
       <c r="AL3" t="n">
-        <v>0.8136148218013135</v>
+        <v>0.8057403106436466</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.001761501457408945</v>
+        <v>0.001798327004718359</v>
       </c>
       <c r="AN3" t="inlineStr"/>
     </row>
@@ -861,43 +861,43 @@
         <v>38.828125</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5026131523004256</v>
+        <v>0.5026131523545405</v>
       </c>
       <c r="G4" t="n">
         <v>0.08176040369199321</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1418117772088146</v>
+        <v>0.1418117771640022</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2720282171617107</v>
+        <v>0.2720282171735377</v>
       </c>
       <c r="J4" t="n">
-        <v>0.001786449637055907</v>
+        <v>0.00178644961592619</v>
       </c>
       <c r="K4" t="n">
-        <v>0.4194869142069372</v>
+        <v>0.3810454070602846</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2274528975208619</v>
+        <v>0.3190108794678196</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>0.0118276119752504</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>0.0002365522395050079</v>
       </c>
       <c r="O4" t="n">
-        <v>4.305760231268049</v>
+        <v>4.287181927873305</v>
       </c>
       <c r="P4" t="n">
-        <v>4.56492048676401</v>
+        <v>4.555836708814627</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9536205709027058</v>
+        <v>0.9510385469601577</v>
       </c>
       <c r="R4" t="n">
-        <v>0.01408791648970575</v>
+        <v>0.01447475489306316</v>
       </c>
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr"/>
@@ -907,38 +907,38 @@
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="n">
-        <v>0.9843416257727393</v>
+        <v>0.9796920079287218</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.01101820718575779</v>
+        <v>0.01254790127477844</v>
       </c>
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="n">
-        <v>0.9985297636860492</v>
+        <v>0.9970632265212911</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.0004772012615603849</v>
+        <v>0.0006744398687500662</v>
       </c>
       <c r="AE4" t="inlineStr"/>
       <c r="AF4" t="n">
-        <v>0.311370323060871</v>
+        <v>0.2731750947833502</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.0270084875804072</v>
+        <v>0.02774740019061813</v>
       </c>
       <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="n">
-        <v>0.9653626049956626</v>
+        <v>0.9815107898243549</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.007719789469329707</v>
+        <v>0.005640167803955353</v>
       </c>
       <c r="AK4" t="inlineStr"/>
       <c r="AL4" t="n">
-        <v>0.3931409070958956</v>
+        <v>0.2885419900256958</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.003947687548622647</v>
+        <v>0.004274383422843446</v>
       </c>
       <c r="AN4" t="inlineStr"/>
     </row>
@@ -965,25 +965,25 @@
         <v>67.8082191780822</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4142260612899763</v>
+        <v>0.414226061397911</v>
       </c>
       <c r="G5" t="n">
         <v>0.04681738015071348</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2912830177383198</v>
+        <v>0.2912830175544637</v>
       </c>
       <c r="I5" t="n">
-        <v>0.217379291417003</v>
+        <v>0.2173792914645093</v>
       </c>
       <c r="J5" t="n">
-        <v>0.03029424940398749</v>
+        <v>0.03029424943240262</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1836362461632683</v>
+        <v>0.1248471362609869</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2221861976845268</v>
+        <v>0.203789512373197</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -992,16 +992,16 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>4.304261075601077</v>
+        <v>4.305018894746432</v>
       </c>
       <c r="P5" t="n">
-        <v>4.346593380071933</v>
+        <v>4.340671858606973</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9972858912559299</v>
+        <v>0.9964952508841056</v>
       </c>
       <c r="R5" t="n">
-        <v>0.003083552605982152</v>
+        <v>0.003504017022525783</v>
       </c>
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr"/>
@@ -1011,38 +1011,38 @@
       <c r="X5" t="inlineStr"/>
       <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="n">
-        <v>0.9990181939574279</v>
+        <v>0.9983403694456905</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.002244297794327201</v>
+        <v>0.002917919748323837</v>
       </c>
       <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="n">
-        <v>0.9999987889313026</v>
+        <v>0.9999995410971284</v>
       </c>
       <c r="AD5" t="n">
-        <v>6.781714563141499e-06</v>
+        <v>4.174606114269828e-06</v>
       </c>
       <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="n">
-        <v>0.9965148807649968</v>
+        <v>0.9969587613896407</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.002744246380188192</v>
+        <v>0.002563536626686021</v>
       </c>
       <c r="AH5" t="inlineStr"/>
       <c r="AI5" t="n">
-        <v>0.9718307972700237</v>
+        <v>0.9623083899581459</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.005580340751151209</v>
+        <v>0.006454993154143594</v>
       </c>
       <c r="AK5" t="inlineStr"/>
       <c r="AL5" t="n">
-        <v>0.9694536761885827</v>
+        <v>0.974928361689114</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.0008148968031710688</v>
+        <v>0.0007382687679643921</v>
       </c>
       <c r="AN5" t="inlineStr"/>
     </row>
@@ -1069,43 +1069,43 @@
         <v>77.65625</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3890909284533883</v>
+        <v>0.3890909284112034</v>
       </c>
       <c r="G6" t="n">
         <v>0.0408802018459966</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3036991224550851</v>
+        <v>0.3036991225960292</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2478250703308909</v>
+        <v>0.2478250702399798</v>
       </c>
       <c r="J6" t="n">
-        <v>0.01850467691463906</v>
+        <v>0.01850467690679097</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1696932217433799</v>
+        <v>0.1116049959268887</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2020650347272388</v>
+        <v>0.1682081781759014</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>0.04725969848550204</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>0.001243171383549835</v>
       </c>
       <c r="O6" t="n">
-        <v>4.366356260172854</v>
+        <v>4.368984812169352</v>
       </c>
       <c r="P6" t="n">
-        <v>4.383108526810537</v>
+        <v>4.376139737626668</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.9760522040493178</v>
+        <v>0.9754490978244779</v>
       </c>
       <c r="R6" t="n">
-        <v>0.009354986220420594</v>
+        <v>0.009472052695978268</v>
       </c>
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
@@ -1115,38 +1115,38 @@
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="n">
-        <v>0.9891066982890679</v>
+        <v>0.9910076539222745</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.006020367455342996</v>
+        <v>0.005469904442380396</v>
       </c>
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="n">
-        <v>0.9997180682022697</v>
+        <v>0.9999798477986652</v>
       </c>
       <c r="AD6" t="n">
-        <v>4.484600886827642e-05</v>
+        <v>1.19898297088161e-05</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="n">
-        <v>0.986619283507586</v>
+        <v>0.9869783654277139</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.004744420515172544</v>
+        <v>0.004680327494058509</v>
       </c>
       <c r="AH6" t="inlineStr"/>
       <c r="AI6" t="n">
-        <v>0.671840363340845</v>
+        <v>0.6557983544845141</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.01861047781193009</v>
+        <v>0.01905993491428451</v>
       </c>
       <c r="AK6" t="inlineStr"/>
       <c r="AL6" t="n">
-        <v>0.4054523507627874</v>
+        <v>0.3542259254482721</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.001816958458445496</v>
+        <v>0.001893616236366474</v>
       </c>
       <c r="AN6" t="inlineStr"/>
     </row>
@@ -1173,43 +1173,43 @@
         <v>66.19718309859155</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4886958146778536</v>
+        <v>0.4886958146760266</v>
       </c>
       <c r="G7" t="n">
         <v>0.04795677136102667</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2566075839924613</v>
+        <v>0.2566075840123206</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1893475641758934</v>
+        <v>0.1893475641544703</v>
       </c>
       <c r="J7" t="n">
-        <v>0.01739226579276497</v>
+        <v>0.01739226579615577</v>
       </c>
       <c r="K7" t="n">
-        <v>0.2323659267012791</v>
+        <v>0.1710238365812231</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1610687702225475</v>
+        <v>0.165511751169688</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1587787932855586</v>
+        <v>0.2524138755881966</v>
       </c>
       <c r="N7" t="n">
-        <v>0.006878207158920089</v>
+        <v>0.01087935721985341</v>
       </c>
       <c r="O7" t="n">
-        <v>4.276212554625182</v>
+        <v>4.248631377567689</v>
       </c>
       <c r="P7" t="n">
-        <v>4.38118619031477</v>
+        <v>4.382458765177754</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.9893248225914084</v>
+        <v>0.9898286776399727</v>
       </c>
       <c r="R7" t="n">
-        <v>0.006277669192354968</v>
+        <v>0.006127729491581061</v>
       </c>
       <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr"/>
@@ -1219,38 +1219,38 @@
       <c r="X7" t="inlineStr"/>
       <c r="Y7" t="inlineStr"/>
       <c r="Z7" t="n">
-        <v>0.9939651095162066</v>
+        <v>0.9964112408788701</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.005894081438597126</v>
+        <v>0.004545206197845395</v>
       </c>
       <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="n">
-        <v>0.9997300330494965</v>
+        <v>0.9998294968624098</v>
       </c>
       <c r="AD7" t="n">
-        <v>7.08862911845798e-05</v>
+        <v>5.633433104999663e-05</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="n">
-        <v>0.9217167669312067</v>
+        <v>0.9166221059148588</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.0111539761484437</v>
+        <v>0.01151120519766844</v>
       </c>
       <c r="AH7" t="inlineStr"/>
       <c r="AI7" t="n">
-        <v>0.991662508479943</v>
+        <v>0.9981174901520277</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.002404480322515972</v>
+        <v>0.001142541945257163</v>
       </c>
       <c r="AK7" t="inlineStr"/>
       <c r="AL7" t="n">
-        <v>0.3192533779469415</v>
+        <v>0.255326306650788</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.004355803043823402</v>
+        <v>0.004555735405430645</v>
       </c>
       <c r="AN7" t="inlineStr"/>
     </row>
@@ -1277,43 +1277,43 @@
         <v>66.66666666666667</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3735503885622976</v>
+        <v>0.3735503886646729</v>
       </c>
       <c r="G8" t="n">
         <v>0.04761904761904761</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3017797553926043</v>
+        <v>0.3017797550644881</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2489905948482005</v>
+        <v>0.2489905949934041</v>
       </c>
       <c r="J8" t="n">
-        <v>0.02806021357785015</v>
+        <v>0.02806021365838738</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1752392312349113</v>
+        <v>0.1151420474620844</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1427032566889714</v>
+        <v>0.1535615276024868</v>
       </c>
       <c r="M8" t="n">
-        <v>0.05994424918033647</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>0.00122791830761624</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>4.438028116501265</v>
+        <v>4.414719551879695</v>
       </c>
       <c r="P8" t="n">
-        <v>4.409960664257727</v>
+        <v>4.414487795394955</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.9930140996926716</v>
+        <v>0.9947196745094726</v>
       </c>
       <c r="R8" t="n">
-        <v>0.004502762766933771</v>
+        <v>0.00391469761683358</v>
       </c>
       <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr"/>
@@ -1323,38 +1323,38 @@
       <c r="X8" t="inlineStr"/>
       <c r="Y8" t="inlineStr"/>
       <c r="Z8" t="n">
-        <v>0.9935263022055555</v>
+        <v>0.9957711048782146</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.005368857094716001</v>
+        <v>0.00433929415004317</v>
       </c>
       <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="n">
-        <v>0.9999989463154563</v>
+        <v>0.9999958295758243</v>
       </c>
       <c r="AD8" t="n">
-        <v>6.737711357325079e-06</v>
+        <v>1.340439483912673e-05</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="n">
-        <v>0.9865032877238399</v>
+        <v>0.9878517858502087</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.005752710569895703</v>
+        <v>0.005457763950972908</v>
       </c>
       <c r="AH8" t="inlineStr"/>
       <c r="AI8" t="n">
-        <v>0.9817669427896122</v>
+        <v>0.9872345485669369</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.005717573044706909</v>
+        <v>0.004784097956668194</v>
       </c>
       <c r="AK8" t="inlineStr"/>
       <c r="AL8" t="n">
-        <v>0.9994683180165039</v>
+        <v>0.9991286391697034</v>
       </c>
       <c r="AM8" t="n">
-        <v>8.42296907054606e-05</v>
+        <v>0.0001078296641126185</v>
       </c>
       <c r="AN8" t="inlineStr"/>
     </row>
@@ -1381,43 +1381,43 @@
         <v>69.85074626865672</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4184346509008527</v>
+        <v>0.4184346509642805</v>
       </c>
       <c r="G9" t="n">
         <v>0.0454483787817121</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2664295170187482</v>
+        <v>0.2664295168783421</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2311091971008347</v>
+        <v>0.2311091971723147</v>
       </c>
       <c r="J9" t="n">
-        <v>0.03857825619785213</v>
+        <v>0.03857825620335059</v>
       </c>
       <c r="K9" t="n">
-        <v>0.2156188681478334</v>
+        <v>0.1553258947904939</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1621272609070696</v>
+        <v>0.1660903677132669</v>
       </c>
       <c r="M9" t="n">
-        <v>0.06820748780767028</v>
+        <v>0.1074126153214888</v>
       </c>
       <c r="N9" t="n">
-        <v>0.001519868857758173</v>
+        <v>0.002148252306429776</v>
       </c>
       <c r="O9" t="n">
-        <v>4.239179655326522</v>
+        <v>4.219349096074717</v>
       </c>
       <c r="P9" t="n">
-        <v>4.366687770643157</v>
+        <v>4.365415875492378</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.9958040343451084</v>
+        <v>0.9953517561077069</v>
       </c>
       <c r="R9" t="n">
-        <v>0.0035033024184256</v>
+        <v>0.003687280020722479</v>
       </c>
       <c r="S9" t="inlineStr"/>
       <c r="T9" t="inlineStr"/>
@@ -1427,38 +1427,38 @@
       <c r="X9" t="inlineStr"/>
       <c r="Y9" t="inlineStr"/>
       <c r="Z9" t="n">
-        <v>0.9964918560559823</v>
+        <v>0.9984987390898317</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.004275167381806169</v>
+        <v>0.002796678276038676</v>
       </c>
       <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="n">
-        <v>0.9999320419929165</v>
+        <v>0.9999210169516304</v>
       </c>
       <c r="AD9" t="n">
-        <v>4.721153376297057e-05</v>
+        <v>5.089729925283484e-05</v>
       </c>
       <c r="AE9" t="inlineStr"/>
       <c r="AF9" t="n">
-        <v>0.9989656082412256</v>
+        <v>0.9988934094769101</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.001301399241021734</v>
+        <v>0.001346050941921027</v>
       </c>
       <c r="AH9" t="inlineStr"/>
       <c r="AI9" t="n">
-        <v>0.974169649104024</v>
+        <v>0.9627549900154824</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.006064107040849132</v>
+        <v>0.007281749812967667</v>
       </c>
       <c r="AK9" t="inlineStr"/>
       <c r="AL9" t="n">
-        <v>0.9853657126885048</v>
+        <v>0.9781659116465962</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.0007273378036397736</v>
+        <v>0.0008884191347973994</v>
       </c>
       <c r="AN9" t="inlineStr"/>
     </row>
@@ -1485,25 +1485,25 @@
         <v>52.61363636363636</v>
       </c>
       <c r="F10" t="n">
-        <v>0.5306916825504616</v>
+        <v>0.5306916826579526</v>
       </c>
       <c r="G10" t="n">
         <v>0.0603380301004491</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2597511503162143</v>
+        <v>0.2597511501438604</v>
       </c>
       <c r="I10" t="n">
-        <v>0.115376694226804</v>
+        <v>0.1153766942703101</v>
       </c>
       <c r="J10" t="n">
-        <v>0.033842442806071</v>
+        <v>0.03384244282742767</v>
       </c>
       <c r="K10" t="n">
-        <v>0.2191421967246366</v>
+        <v>0.160196857539937</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1215020180010192</v>
+        <v>0.1312015322400468</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -1512,16 +1512,16 @@
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>4.127028746765415</v>
+        <v>4.102673349198579</v>
       </c>
       <c r="P10" t="n">
-        <v>4.237101998462907</v>
+        <v>4.238137546540484</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.9909284875006725</v>
+        <v>0.9903058489416114</v>
       </c>
       <c r="R10" t="n">
-        <v>0.006050205967349086</v>
+        <v>0.006254393466079149</v>
       </c>
       <c r="S10" t="inlineStr"/>
       <c r="T10" t="inlineStr"/>
@@ -1531,38 +1531,38 @@
       <c r="X10" t="inlineStr"/>
       <c r="Y10" t="inlineStr"/>
       <c r="Z10" t="n">
-        <v>0.9998449482573343</v>
+        <v>0.9989145792364963</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.001101411007373375</v>
+        <v>0.002914138236121024</v>
       </c>
       <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="n">
-        <v>0.9999906698741804</v>
+        <v>0.9999640109979354</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.553099440830865e-05</v>
+        <v>5.014283474539781e-05</v>
       </c>
       <c r="AE10" t="inlineStr"/>
       <c r="AF10" t="n">
-        <v>0.9076723466714517</v>
+        <v>0.9028110459696396</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.01242438157797776</v>
+        <v>0.0127472744401768</v>
       </c>
       <c r="AH10" t="inlineStr"/>
       <c r="AI10" t="n">
-        <v>0.9706490950086941</v>
+        <v>0.989165365244886</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.002710566610002775</v>
+        <v>0.001646859214542769</v>
       </c>
       <c r="AK10" t="inlineStr"/>
       <c r="AL10" t="n">
-        <v>0.7896845766287504</v>
+        <v>0.7643400219194291</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.002810218399024359</v>
+        <v>0.002974729143800156</v>
       </c>
       <c r="AN10" t="inlineStr"/>
     </row>
@@ -1589,43 +1589,43 @@
         <v>61.69014084507042</v>
       </c>
       <c r="F11" t="n">
-        <v>0.6976459379986636</v>
+        <v>0.6976459379735106</v>
       </c>
       <c r="G11" t="n">
         <v>0.05146046241936653</v>
       </c>
       <c r="H11" t="n">
-        <v>0.128689928922737</v>
+        <v>0.1286899289623047</v>
       </c>
       <c r="I11" t="n">
-        <v>0.09261029160041566</v>
+        <v>0.09261029157801856</v>
       </c>
       <c r="J11" t="n">
-        <v>0.02959337905881725</v>
+        <v>0.02959337906679948</v>
       </c>
       <c r="K11" t="n">
-        <v>0.4197102286204545</v>
+        <v>0.3872233474870604</v>
       </c>
       <c r="L11" t="n">
-        <v>0.402966803682714</v>
+        <v>0.427689322118694</v>
       </c>
       <c r="M11" t="n">
-        <v>0.4281229235600672</v>
+        <v>0.5328776299899765</v>
       </c>
       <c r="N11" t="n">
-        <v>0.06209006392208215</v>
+        <v>0.0743359621221935</v>
       </c>
       <c r="O11" t="n">
-        <v>4.128911664621688</v>
+        <v>4.108821795020701</v>
       </c>
       <c r="P11" t="n">
-        <v>4.272547903661769</v>
+        <v>4.281542595509519</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.9675545627636214</v>
+        <v>0.9853632299444373</v>
       </c>
       <c r="R11" t="n">
-        <v>0.0134004186862141</v>
+        <v>0.009000449039319382</v>
       </c>
       <c r="S11" t="inlineStr"/>
       <c r="T11" t="inlineStr"/>
@@ -1635,38 +1635,38 @@
       <c r="X11" t="inlineStr"/>
       <c r="Y11" t="inlineStr"/>
       <c r="Z11" t="n">
-        <v>0.9483560559914668</v>
+        <v>0.9771945657710693</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.02841320602911025</v>
+        <v>0.01888120521885246</v>
       </c>
       <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="n">
-        <v>0.999448339562569</v>
+        <v>0.9999541143259071</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.0001654369902432127</v>
+        <v>4.771283902150711e-05</v>
       </c>
       <c r="AE11" t="inlineStr"/>
       <c r="AF11" t="n">
-        <v>0.9492371302240199</v>
+        <v>0.9605319294936677</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.003993851780363602</v>
+        <v>0.00352161445869084</v>
       </c>
       <c r="AH11" t="inlineStr"/>
       <c r="AI11" t="n">
-        <v>0.889008956058545</v>
+        <v>0.9318556929884206</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.003743665520462066</v>
+        <v>0.002933376853167626</v>
       </c>
       <c r="AK11" t="inlineStr"/>
       <c r="AL11" t="n">
-        <v>0.9607381703639869</v>
+        <v>0.9704780973321371</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.0008394191345589718</v>
+        <v>0.0007278900276445923</v>
       </c>
       <c r="AN11" t="inlineStr"/>
     </row>
@@ -1693,43 +1693,43 @@
         <v>1182.5</v>
       </c>
       <c r="F12" t="n">
-        <v>0.6580079528637066</v>
+        <v>0.658007952809377</v>
       </c>
       <c r="G12" t="n">
         <v>0.002684653847444545</v>
       </c>
       <c r="H12" t="n">
-        <v>0.3185832282923884</v>
+        <v>0.3185832283714021</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0.0207241649964606</v>
+        <v>0.02072416497177636</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1394114541171846</v>
+        <v>0.0922222144048621</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1456400020742224</v>
+        <v>0.4552213226489177</v>
       </c>
       <c r="M12" t="n">
-        <v>0.4869384248926201</v>
+        <v>0.4941407965351625</v>
       </c>
       <c r="N12" t="n">
-        <v>0.1169457036489209</v>
+        <v>0.2947726234867759</v>
       </c>
       <c r="O12" t="n">
-        <v>4.056914465248047</v>
+        <v>4.245803122192966</v>
       </c>
       <c r="P12" t="n">
-        <v>4.115659556183942</v>
+        <v>4.260691735883928</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.9143948714120741</v>
+        <v>0.9065269863107119</v>
       </c>
       <c r="R12" t="n">
-        <v>0.03184286974895834</v>
+        <v>0.03327403208020357</v>
       </c>
       <c r="S12" t="inlineStr"/>
       <c r="T12" t="inlineStr"/>
@@ -1739,38 +1739,38 @@
       <c r="X12" t="inlineStr"/>
       <c r="Y12" t="inlineStr"/>
       <c r="Z12" t="n">
-        <v>0.5205635677201037</v>
+        <v>0.7903388528889077</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.06844479371617959</v>
+        <v>0.04526201469403961</v>
       </c>
       <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="n">
-        <v>0.9999929548141608</v>
+        <v>0.9999783578756222</v>
       </c>
       <c r="AD12" t="n">
-        <v>6.233289569796155e-06</v>
+        <v>1.092498929846012e-05</v>
       </c>
       <c r="AE12" t="inlineStr"/>
       <c r="AF12" t="n">
-        <v>0.9726203898339607</v>
+        <v>-1.178999940093187</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.006256870649394961</v>
+        <v>0.05581772809701747</v>
       </c>
       <c r="AH12" t="inlineStr"/>
       <c r="AI12" t="n">
-        <v>0.5819442682575993</v>
+        <v>0.8702732850156538</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.002809130913850659</v>
+        <v>0.001564838779720206</v>
       </c>
       <c r="AK12" t="inlineStr"/>
       <c r="AL12" t="n">
-        <v>0.9699770643931866</v>
+        <v>0.9915024253371105</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.0003505116192059149</v>
+        <v>0.0001864761677393421</v>
       </c>
       <c r="AN12" t="inlineStr"/>
     </row>
@@ -1797,43 +1797,43 @@
         <v>37.30769230769231</v>
       </c>
       <c r="F13" t="n">
-        <v>0.3764292995365501</v>
+        <v>0.3764292995885038</v>
       </c>
       <c r="G13" t="n">
         <v>0.08509245622647683</v>
       </c>
       <c r="H13" t="n">
-        <v>0.20530781079537</v>
+        <v>0.2053078106416003</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2773838130683605</v>
+        <v>0.2773838131849478</v>
       </c>
       <c r="J13" t="n">
-        <v>0.05578662037324268</v>
+        <v>0.0557866203584713</v>
       </c>
       <c r="K13" t="n">
-        <v>0.3157071197613084</v>
+        <v>0.2602259461942728</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2737591165764205</v>
+        <v>0.242165068423074</v>
       </c>
       <c r="M13" t="n">
-        <v>0.4966396332798105</v>
+        <v>0.4640503052386877</v>
       </c>
       <c r="N13" t="n">
-        <v>0.1586538260390421</v>
+        <v>0.133723630070304</v>
       </c>
       <c r="O13" t="n">
-        <v>4.293313089366361</v>
+        <v>4.287383668443933</v>
       </c>
       <c r="P13" t="n">
-        <v>4.508014430141713</v>
+        <v>4.512263775673728</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.9974045832287407</v>
+        <v>0.9976180450350064</v>
       </c>
       <c r="R13" t="n">
-        <v>0.002915387445691861</v>
+        <v>0.002792926451685169</v>
       </c>
       <c r="S13" t="inlineStr"/>
       <c r="T13" t="inlineStr"/>
@@ -1843,38 +1843,38 @@
       <c r="X13" t="inlineStr"/>
       <c r="Y13" t="inlineStr"/>
       <c r="Z13" t="n">
-        <v>0.7039377802764828</v>
+        <v>0.7735658460953334</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.00428995026077389</v>
+        <v>0.003751731294573254</v>
       </c>
       <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="n">
-        <v>0.975272006763534</v>
+        <v>0.9841269663666189</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.0001204274458024907</v>
+        <v>9.64852678725433e-05</v>
       </c>
       <c r="AE13" t="inlineStr"/>
       <c r="AF13" t="n">
-        <v>0.6366309637231208</v>
+        <v>0.6157301426645949</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.004310581005071804</v>
+        <v>0.004432819120087571</v>
       </c>
       <c r="AH13" t="inlineStr"/>
       <c r="AI13" t="n">
-        <v>0.9997852021798026</v>
+        <v>0.9999101087088271</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.0005921051132542276</v>
+        <v>0.000383038728475612</v>
       </c>
       <c r="AK13" t="inlineStr"/>
       <c r="AL13" t="n">
-        <v>0.9500345569009239</v>
+        <v>0.95029427778076</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.002268820556246008</v>
+        <v>0.002262916191574632</v>
       </c>
       <c r="AN13" t="inlineStr"/>
     </row>
@@ -1901,43 +1901,43 @@
         <v>44</v>
       </c>
       <c r="F14" t="n">
-        <v>0.4685666630154797</v>
+        <v>0.4685666629631464</v>
       </c>
       <c r="G14" t="n">
         <v>0.07215007215007214</v>
       </c>
       <c r="H14" t="n">
-        <v>0.2791093997172449</v>
+        <v>0.2791093997308827</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1713546933726054</v>
+        <v>0.1713546934252931</v>
       </c>
       <c r="J14" t="n">
-        <v>0.008819171744597891</v>
+        <v>0.008819171730605837</v>
       </c>
       <c r="K14" t="n">
-        <v>0.2052549529133269</v>
+        <v>0.1437589046858702</v>
       </c>
       <c r="L14" t="n">
-        <v>0.2822786211880685</v>
+        <v>0.2262354282073267</v>
       </c>
       <c r="M14" t="n">
-        <v>0.4723981861215936</v>
+        <v>0.04364789509743716</v>
       </c>
       <c r="N14" t="n">
-        <v>0.4670622347935909</v>
+        <v>0.0783012438364307</v>
       </c>
       <c r="O14" t="n">
-        <v>4.397072460739371</v>
+        <v>4.390242826472774</v>
       </c>
       <c r="P14" t="n">
-        <v>4.362720201158953</v>
+        <v>4.350552692593566</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.9682303921522599</v>
+        <v>0.9651720385528869</v>
       </c>
       <c r="R14" t="n">
-        <v>0.0106145380464991</v>
+        <v>0.01111371353925304</v>
       </c>
       <c r="S14" t="inlineStr"/>
       <c r="T14" t="inlineStr"/>
@@ -1947,38 +1947,38 @@
       <c r="X14" t="inlineStr"/>
       <c r="Y14" t="inlineStr"/>
       <c r="Z14" t="n">
-        <v>0.8784566753782201</v>
+        <v>0.8708915047922428</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.01733400744605725</v>
+        <v>0.01786532135515786</v>
       </c>
       <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="n">
-        <v>0.961480610978983</v>
+        <v>0.958256154743988</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.0009625122855059849</v>
+        <v>0.001001988674030949</v>
       </c>
       <c r="AE14" t="inlineStr"/>
       <c r="AF14" t="n">
-        <v>0.9792004142146234</v>
+        <v>0.9614222793334045</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.006232987350904815</v>
+        <v>0.008488621795341465</v>
       </c>
       <c r="AH14" t="inlineStr"/>
       <c r="AI14" t="n">
-        <v>0.5692768850073551</v>
+        <v>0.5650571041065934</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0.01483041592324839</v>
+        <v>0.01490288546671894</v>
       </c>
       <c r="AK14" t="inlineStr"/>
       <c r="AL14" t="n">
-        <v>0.1901828886784394</v>
+        <v>0.1670204810922231</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.00177664793644892</v>
+        <v>0.001801876665714711</v>
       </c>
       <c r="AN14" t="inlineStr"/>
     </row>
@@ -2005,25 +2005,25 @@
         <v>37.66666666666666</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4676168791864762</v>
+        <v>0.467616879374457</v>
       </c>
       <c r="G15" t="n">
         <v>0.08428150021070376</v>
       </c>
       <c r="H15" t="n">
-        <v>0.2808036479653256</v>
+        <v>0.280803647842334</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1470517109277883</v>
+        <v>0.1470517108760386</v>
       </c>
       <c r="J15" t="n">
-        <v>0.02024626170970604</v>
+        <v>0.02024626169646662</v>
       </c>
       <c r="K15" t="n">
-        <v>0.1874830231703039</v>
+        <v>0.1307591005177591</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2737265099064331</v>
+        <v>0.2272711616521533</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -2032,16 +2032,16 @@
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>4.085204214067701</v>
+        <v>4.079261036110907</v>
       </c>
       <c r="P15" t="n">
-        <v>4.241274189635918</v>
+        <v>4.223223841031757</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.9712445023950077</v>
+        <v>0.9694304685738983</v>
       </c>
       <c r="R15" t="n">
-        <v>0.008961569460840967</v>
+        <v>0.009239915987418593</v>
       </c>
       <c r="S15" t="inlineStr"/>
       <c r="T15" t="inlineStr"/>
@@ -2051,38 +2051,38 @@
       <c r="X15" t="inlineStr"/>
       <c r="Y15" t="inlineStr"/>
       <c r="Z15" t="n">
-        <v>0.9145422215504312</v>
+        <v>0.9069081310186005</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.0143946461521398</v>
+        <v>0.01502384416913792</v>
       </c>
       <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="n">
-        <v>-0.3452385109333218</v>
+        <v>-0.2042450790744863</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.003035005859951621</v>
+        <v>0.002871556252226525</v>
       </c>
       <c r="AE15" t="inlineStr"/>
       <c r="AF15" t="n">
-        <v>0.9185682072038268</v>
+        <v>0.9165244550217656</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.01044914010173467</v>
+        <v>0.01057945228498054</v>
       </c>
       <c r="AH15" t="inlineStr"/>
       <c r="AI15" t="n">
-        <v>0.607386875813883</v>
+        <v>0.5805784843102495</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.007012638383216577</v>
+        <v>0.007248103627623186</v>
       </c>
       <c r="AK15" t="inlineStr"/>
       <c r="AL15" t="n">
-        <v>0.9999997189716415</v>
+        <v>0.9999990127455193</v>
       </c>
       <c r="AM15" t="n">
-        <v>1.961708065212662e-06</v>
+        <v>3.676832638433941e-06</v>
       </c>
       <c r="AN15" t="inlineStr"/>
     </row>
@@ -2109,25 +2109,25 @@
         <v>21.39130434782609</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3751087963773801</v>
+        <v>0.3751087964018581</v>
       </c>
       <c r="G16" t="n">
         <v>0.1484062459672215</v>
       </c>
       <c r="H16" t="n">
-        <v>0.06809149804835848</v>
+        <v>0.06809149804106746</v>
       </c>
       <c r="I16" t="n">
-        <v>0.3926949046640935</v>
+        <v>0.3926949046425352</v>
       </c>
       <c r="J16" t="n">
-        <v>0.01569855494294647</v>
+        <v>0.01569855494731771</v>
       </c>
       <c r="K16" t="n">
-        <v>0.5161649251798621</v>
+        <v>0.5129655543643412</v>
       </c>
       <c r="L16" t="n">
-        <v>0.5289014976348139</v>
+        <v>0.5570648930193127</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2136,16 +2136,16 @@
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>4.346437810309332</v>
+        <v>4.407580888704488</v>
       </c>
       <c r="P16" t="n">
-        <v>4.497205496280733</v>
+        <v>4.533248426339919</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.9761601107018996</v>
+        <v>0.9772531111522044</v>
       </c>
       <c r="R16" t="n">
-        <v>0.009391057682706113</v>
+        <v>0.009173253465776601</v>
       </c>
       <c r="S16" t="inlineStr"/>
       <c r="T16" t="inlineStr"/>
@@ -2155,31 +2155,31 @@
       <c r="X16" t="inlineStr"/>
       <c r="Y16" t="inlineStr"/>
       <c r="Z16" t="n">
-        <v>0.9940557304405625</v>
+        <v>0.9942457559178858</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.005683469384110759</v>
+        <v>0.005591887390113188</v>
       </c>
       <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="n">
-        <v>0.9590590977589639</v>
+        <v>0.9592775241567592</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.004170344451248162</v>
+        <v>0.00415920483919991</v>
       </c>
       <c r="AE16" t="inlineStr"/>
       <c r="AF16" t="n">
-        <v>0.9097484832765053</v>
+        <v>0.903678497459134</v>
       </c>
       <c r="AG16" t="n">
-        <v>0.003607168184178011</v>
+        <v>0.003726496878166753</v>
       </c>
       <c r="AH16" t="inlineStr"/>
       <c r="AI16" t="n">
-        <v>0.8444101086152463</v>
+        <v>0.8528218055756928</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0.01787344174117467</v>
+        <v>0.01738358060098302</v>
       </c>
       <c r="AK16" t="inlineStr"/>
       <c r="AL16" t="inlineStr"/>
@@ -2211,43 +2211,43 @@
         <v>51.25</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4780640258980272</v>
+        <v>0.478064025668827</v>
       </c>
       <c r="G17" t="n">
         <v>0.06194347657762291</v>
       </c>
       <c r="H17" t="n">
-        <v>0.2550441184335309</v>
+        <v>0.2550441188812936</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1330574186338084</v>
+        <v>0.1330574185135598</v>
       </c>
       <c r="J17" t="n">
-        <v>0.07189096045701066</v>
+        <v>0.07189096035869673</v>
       </c>
       <c r="K17" t="n">
-        <v>0.2110178984664703</v>
+        <v>0.1557936046085961</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2661393181762588</v>
+        <v>0.2186325185453777</v>
       </c>
       <c r="M17" t="n">
-        <v>0.1004615843598543</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>0.0116670810391132</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>3.870271546959827</v>
+        <v>3.843478583732289</v>
       </c>
       <c r="P17" t="n">
-        <v>4.034650652477939</v>
+        <v>4.003719165031207</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.9886786676698157</v>
+        <v>0.9887922887941479</v>
       </c>
       <c r="R17" t="n">
-        <v>0.004939077182431664</v>
+        <v>0.004914230343642085</v>
       </c>
       <c r="S17" t="inlineStr"/>
       <c r="T17" t="inlineStr"/>
@@ -2257,38 +2257,38 @@
       <c r="X17" t="inlineStr"/>
       <c r="Y17" t="inlineStr"/>
       <c r="Z17" t="n">
-        <v>0.9651186790951685</v>
+        <v>0.9645849319296694</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.009395692162997312</v>
+        <v>0.009467304770567786</v>
       </c>
       <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="n">
-        <v>0.7228519706229354</v>
+        <v>0.7759965842772603</v>
       </c>
       <c r="AD17" t="n">
-        <v>0.001628180124491695</v>
+        <v>0.001463773470828168</v>
       </c>
       <c r="AE17" t="inlineStr"/>
       <c r="AF17" t="n">
-        <v>0.9938354554072996</v>
+        <v>0.9936973707271253</v>
       </c>
       <c r="AG17" t="n">
-        <v>0.002123372660783748</v>
+        <v>0.002147022541762534</v>
       </c>
       <c r="AH17" t="inlineStr"/>
       <c r="AI17" t="n">
-        <v>0.01664500356008591</v>
+        <v>0.09993223714009614</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.005103157957807506</v>
+        <v>0.004882266102609818</v>
       </c>
       <c r="AK17" t="inlineStr"/>
       <c r="AL17" t="n">
-        <v>0.9947468990030295</v>
+        <v>0.9943397171283372</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.0007010582940017842</v>
+        <v>0.0007277216965418811</v>
       </c>
       <c r="AN17" t="inlineStr"/>
     </row>
@@ -2315,25 +2315,25 @@
         <v>31.46666666666667</v>
       </c>
       <c r="F18" t="n">
-        <v>0.4515185462382498</v>
+        <v>0.451518546451847</v>
       </c>
       <c r="G18" t="n">
         <v>0.1008878127522195</v>
       </c>
       <c r="H18" t="n">
-        <v>0.2508910324934933</v>
+        <v>0.2508910318037907</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1666097192940944</v>
+        <v>0.1666097196951048</v>
       </c>
       <c r="J18" t="n">
-        <v>0.03009288922194302</v>
+        <v>0.03009288929703804</v>
       </c>
       <c r="K18" t="n">
-        <v>0.2424607087442707</v>
+        <v>0.1816593812827441</v>
       </c>
       <c r="L18" t="n">
-        <v>0.2651836289186233</v>
+        <v>0.2297352108863215</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -2342,16 +2342,16 @@
         <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>4.298420190621356</v>
+        <v>4.289171463703494</v>
       </c>
       <c r="P18" t="n">
-        <v>4.300141674142705</v>
+        <v>4.290050057097835</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.9826304224726914</v>
+        <v>0.9831534514354511</v>
       </c>
       <c r="R18" t="n">
-        <v>0.006816056954067184</v>
+        <v>0.006712650750531434</v>
       </c>
       <c r="S18" t="inlineStr"/>
       <c r="T18" t="inlineStr"/>
@@ -2361,38 +2361,38 @@
       <c r="X18" t="inlineStr"/>
       <c r="Y18" t="inlineStr"/>
       <c r="Z18" t="n">
-        <v>0.9152792494398896</v>
+        <v>0.9176001397679907</v>
       </c>
       <c r="AA18" t="n">
-        <v>0.01494746086284035</v>
+        <v>0.01474129936032057</v>
       </c>
       <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="n">
-        <v>0.9890578547182047</v>
+        <v>0.9945932509422459</v>
       </c>
       <c r="AD18" t="n">
-        <v>0.0002881107079800557</v>
+        <v>0.0002025238934296109</v>
       </c>
       <c r="AE18" t="inlineStr"/>
       <c r="AF18" t="n">
-        <v>0.9973079279727923</v>
+        <v>0.9966815848087611</v>
       </c>
       <c r="AG18" t="n">
-        <v>0.001557308787083497</v>
+        <v>0.001729007014834954</v>
       </c>
       <c r="AH18" t="inlineStr"/>
       <c r="AI18" t="n">
-        <v>0.9777848320257698</v>
+        <v>0.9827759611838005</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0.002507463619992367</v>
+        <v>0.002207889531238888</v>
       </c>
       <c r="AK18" t="inlineStr"/>
       <c r="AL18" t="n">
-        <v>0.9950045809964476</v>
+        <v>0.9938608021566676</v>
       </c>
       <c r="AM18" t="n">
-        <v>0.0002664273171593902</v>
+        <v>0.0002953579109332178</v>
       </c>
       <c r="AN18" t="inlineStr"/>
     </row>
@@ -2419,25 +2419,25 @@
         <v>77.71428571428571</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2928786705374068</v>
+        <v>0.2928786705098768</v>
       </c>
       <c r="G19" t="n">
         <v>0.04084967320261438</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2980196009674419</v>
+        <v>0.2980196010147655</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3557027147401188</v>
+        <v>0.3557027147337084</v>
       </c>
       <c r="J19" t="n">
-        <v>0.01254934055241822</v>
+        <v>0.01254934053903507</v>
       </c>
       <c r="K19" t="n">
-        <v>0.161033465819801</v>
+        <v>0.107691775349662</v>
       </c>
       <c r="L19" t="n">
-        <v>0.2232994455997759</v>
+        <v>0.175768878345028</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -2446,16 +2446,16 @@
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>3.990866149206148</v>
+        <v>3.99750997059567</v>
       </c>
       <c r="P19" t="n">
-        <v>4.375458080650116</v>
+        <v>4.366276846972445</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.9869099488292812</v>
+        <v>0.9867131417466308</v>
       </c>
       <c r="R19" t="n">
-        <v>0.008061109514708967</v>
+        <v>0.00812148226279768</v>
       </c>
       <c r="S19" t="inlineStr"/>
       <c r="T19" t="inlineStr"/>
@@ -2465,38 +2465,38 @@
       <c r="X19" t="inlineStr"/>
       <c r="Y19" t="inlineStr"/>
       <c r="Z19" t="n">
-        <v>0.6274750871000984</v>
+        <v>0.6052939879003358</v>
       </c>
       <c r="AA19" t="n">
-        <v>0.00908790663969649</v>
+        <v>0.009354553561437724</v>
       </c>
       <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="n">
-        <v>0.003989528014871735</v>
+        <v>-0.07127706281254875</v>
       </c>
       <c r="AD19" t="n">
-        <v>0.002973301930883142</v>
+        <v>0.003083599479894748</v>
       </c>
       <c r="AE19" t="inlineStr"/>
       <c r="AF19" t="n">
-        <v>0.7305638330194407</v>
+        <v>0.730330564852065</v>
       </c>
       <c r="AG19" t="n">
-        <v>0.01465066649266402</v>
+        <v>0.014657007148279</v>
       </c>
       <c r="AH19" t="inlineStr"/>
       <c r="AI19" t="n">
-        <v>0.8587258722118825</v>
+        <v>0.8654478225841407</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0.004336346172917609</v>
+        <v>0.004231925295112624</v>
       </c>
       <c r="AK19" t="inlineStr"/>
       <c r="AL19" t="n">
-        <v>0.9963810197870483</v>
+        <v>0.9954301895032418</v>
       </c>
       <c r="AM19" t="n">
-        <v>0.0001758828188849516</v>
+        <v>0.0001976420763814884</v>
       </c>
       <c r="AN19" t="inlineStr"/>
     </row>
@@ -2523,25 +2523,25 @@
         <v>55.77777777777778</v>
       </c>
       <c r="F20" t="n">
-        <v>0.3719943274037391</v>
+        <v>0.3719943273800574</v>
       </c>
       <c r="G20" t="n">
         <v>0.05691519635742743</v>
       </c>
       <c r="H20" t="n">
-        <v>0.2459185029100323</v>
+        <v>0.2459185030013721</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3196907365948976</v>
+        <v>0.3196907365258876</v>
       </c>
       <c r="J20" t="n">
-        <v>0.005481236733903614</v>
+        <v>0.005481236735255395</v>
       </c>
       <c r="K20" t="n">
-        <v>0.2706740016525256</v>
+        <v>0.2057022057339838</v>
       </c>
       <c r="L20" t="n">
-        <v>0.292740499899429</v>
+        <v>0.2460155482071384</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -2550,16 +2550,16 @@
         <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>4.627752525577289</v>
+        <v>4.630732926731516</v>
       </c>
       <c r="P20" t="n">
-        <v>4.593240864814092</v>
+        <v>4.596123110829812</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.9734668925685214</v>
+        <v>0.9739197975232899</v>
       </c>
       <c r="R20" t="n">
-        <v>0.009563211558973351</v>
+        <v>0.009481240982862297</v>
       </c>
       <c r="S20" t="inlineStr"/>
       <c r="T20" t="inlineStr"/>
@@ -2569,38 +2569,38 @@
       <c r="X20" t="inlineStr"/>
       <c r="Y20" t="inlineStr"/>
       <c r="Z20" t="n">
-        <v>0.8668274204847926</v>
+        <v>0.8655988856614829</v>
       </c>
       <c r="AA20" t="n">
-        <v>0.01063104279203551</v>
+        <v>0.01067996660660704</v>
       </c>
       <c r="AB20" t="inlineStr"/>
       <c r="AC20" t="n">
-        <v>0.8317276085052017</v>
+        <v>0.8516988751596797</v>
       </c>
       <c r="AD20" t="n">
-        <v>0.002799078990648457</v>
+        <v>0.002627731236034267</v>
       </c>
       <c r="AE20" t="inlineStr"/>
       <c r="AF20" t="n">
-        <v>0.9346148841799236</v>
+        <v>0.9471838630083684</v>
       </c>
       <c r="AG20" t="n">
-        <v>0.006823297667878534</v>
+        <v>0.006132508891023972</v>
       </c>
       <c r="AH20" t="inlineStr"/>
       <c r="AI20" t="n">
-        <v>0.7854085969175137</v>
+        <v>0.7846625705889961</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0.01701135100923516</v>
+        <v>0.01704089531515587</v>
       </c>
       <c r="AK20" t="inlineStr"/>
       <c r="AL20" t="n">
-        <v>0.4660248096489776</v>
+        <v>0.437512436021801</v>
       </c>
       <c r="AM20" t="n">
-        <v>0.0006911644829887301</v>
+        <v>0.0007093773804379569</v>
       </c>
       <c r="AN20" t="inlineStr"/>
     </row>
@@ -2627,25 +2627,25 @@
         <v>17.60714285714286</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3926349948370401</v>
+        <v>0.3926349942752794</v>
       </c>
       <c r="G21" t="n">
         <v>0.1803020058598151</v>
       </c>
       <c r="H21" t="n">
-        <v>0.3377870452012128</v>
+        <v>0.3377870456849771</v>
       </c>
       <c r="I21" t="n">
-        <v>0.08927595410193191</v>
+        <v>0.08927595417992841</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>5.04831636563563e-18</v>
       </c>
       <c r="K21" t="n">
-        <v>0.1202941340488625</v>
+        <v>0.07261609984294198</v>
       </c>
       <c r="L21" t="n">
-        <v>0.137931315746043</v>
+        <v>0.1313628159483958</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -2654,16 +2654,16 @@
         <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>4.107682434211664</v>
+        <v>4.163497628306884</v>
       </c>
       <c r="P21" t="n">
-        <v>4.121104552990844</v>
+        <v>4.13089638658079</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.8678897471651907</v>
+        <v>0.8036222950424927</v>
       </c>
       <c r="R21" t="n">
-        <v>0.02365423805969597</v>
+        <v>0.02883943790158101</v>
       </c>
       <c r="S21" t="inlineStr"/>
       <c r="T21" t="inlineStr"/>
@@ -2673,38 +2673,38 @@
       <c r="X21" t="inlineStr"/>
       <c r="Y21" t="inlineStr"/>
       <c r="Z21" t="n">
-        <v>0.9532826462626094</v>
+        <v>0.9717485679318847</v>
       </c>
       <c r="AA21" t="n">
-        <v>0.008490375570638316</v>
+        <v>0.006602494021151395</v>
       </c>
       <c r="AB21" t="inlineStr"/>
       <c r="AC21" t="n">
-        <v>0.9946418745541423</v>
+        <v>0.9881406375564401</v>
       </c>
       <c r="AD21" t="n">
-        <v>0.002416255744214073</v>
+        <v>0.003594737083855108</v>
       </c>
       <c r="AE21" t="inlineStr"/>
       <c r="AF21" t="n">
-        <v>-3.873668893466444</v>
+        <v>-6.704116566711466</v>
       </c>
       <c r="AG21" t="n">
-        <v>0.04835449193264897</v>
+        <v>0.06079533245275909</v>
       </c>
       <c r="AH21" t="inlineStr"/>
       <c r="AI21" t="n">
-        <v>-0.3120718465706824</v>
+        <v>-0.3958334788459246</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0.01951985317088758</v>
+        <v>0.02013328042520356</v>
       </c>
       <c r="AK21" t="inlineStr"/>
       <c r="AL21" t="n">
-        <v>0.5248689173044851</v>
+        <v>0.4119749711134348</v>
       </c>
       <c r="AM21" t="n">
-        <v>0.0007131366589121639</v>
+        <v>0.0007933483931838523</v>
       </c>
       <c r="AN21" t="inlineStr"/>
     </row>
@@ -2731,43 +2731,43 @@
         <v>29.3125</v>
       </c>
       <c r="F22" t="n">
-        <v>0.4135808655857899</v>
+        <v>0.4135808655594087</v>
       </c>
       <c r="G22" t="n">
         <v>0.1083020272785731</v>
       </c>
       <c r="H22" t="n">
-        <v>0.2033297621759581</v>
+        <v>0.203329762176548</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2477420255951969</v>
+        <v>0.247742025507402</v>
       </c>
       <c r="J22" t="n">
-        <v>0.02704531936448205</v>
+        <v>0.02704531947806826</v>
       </c>
       <c r="K22" t="n">
-        <v>0.3065794238146419</v>
+        <v>0.2535748896970105</v>
       </c>
       <c r="L22" t="n">
-        <v>0.3244168349152868</v>
+        <v>0.2788840742338105</v>
       </c>
       <c r="M22" t="n">
-        <v>0.06973292105409901</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>0.006708888379584744</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>4.136683456812678</v>
+        <v>4.130086663000351</v>
       </c>
       <c r="P22" t="n">
-        <v>4.309238602403099</v>
+        <v>4.298037864574065</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.9817618757604332</v>
+        <v>0.9816645829256813</v>
       </c>
       <c r="R22" t="n">
-        <v>0.006826781748058291</v>
+        <v>0.006844966554480691</v>
       </c>
       <c r="S22" t="inlineStr"/>
       <c r="T22" t="inlineStr"/>
@@ -2777,38 +2777,38 @@
       <c r="X22" t="inlineStr"/>
       <c r="Y22" t="inlineStr"/>
       <c r="Z22" t="n">
-        <v>0.8932080844474241</v>
+        <v>0.894696765827208</v>
       </c>
       <c r="AA22" t="n">
-        <v>0.00963425870672871</v>
+        <v>0.009566872155521081</v>
       </c>
       <c r="AB22" t="inlineStr"/>
       <c r="AC22" t="n">
-        <v>0.9299684077244298</v>
+        <v>0.8808353626570743</v>
       </c>
       <c r="AD22" t="n">
-        <v>0.001466786106645489</v>
+        <v>0.001913345877976869</v>
       </c>
       <c r="AE22" t="inlineStr"/>
       <c r="AF22" t="n">
-        <v>0.342147610241776</v>
+        <v>0.3405662750325011</v>
       </c>
       <c r="AG22" t="n">
-        <v>0.01119490754296669</v>
+        <v>0.01120835455402986</v>
       </c>
       <c r="AH22" t="inlineStr"/>
       <c r="AI22" t="n">
-        <v>0.9570543125470841</v>
+        <v>0.9538585707465665</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0.002967333280691571</v>
+        <v>0.003075757331038508</v>
       </c>
       <c r="AK22" t="inlineStr"/>
       <c r="AL22" t="n">
-        <v>0.7805096407797885</v>
+        <v>0.7765328336879411</v>
       </c>
       <c r="AM22" t="n">
-        <v>0.001980737532589987</v>
+        <v>0.001998600861268104</v>
       </c>
       <c r="AN22" t="inlineStr"/>
     </row>
@@ -2835,43 +2835,43 @@
         <v>39.58333333333334</v>
       </c>
       <c r="F23" t="n">
-        <v>0.6238519511711706</v>
+        <v>0.6238519513177977</v>
       </c>
       <c r="G23" t="n">
         <v>0.08020050125313281</v>
       </c>
       <c r="H23" t="n">
-        <v>0.2028318968739128</v>
+        <v>0.2028318965921395</v>
       </c>
       <c r="I23" t="n">
-        <v>0.06932561212208042</v>
+        <v>0.06932561224073039</v>
       </c>
       <c r="J23" t="n">
-        <v>0.0237900385797033</v>
+        <v>0.02379003859619956</v>
       </c>
       <c r="K23" t="n">
-        <v>0.2861768349137373</v>
+        <v>0.2372061265604153</v>
       </c>
       <c r="L23" t="n">
-        <v>0.2868386291898513</v>
+        <v>0.2520378995393923</v>
       </c>
       <c r="M23" t="n">
-        <v>0.2727188989077666</v>
+        <v>0.3105906778138758</v>
       </c>
       <c r="N23" t="n">
-        <v>0.05101810190704075</v>
+        <v>0.05397796962199076</v>
       </c>
       <c r="O23" t="n">
-        <v>3.86931123372123</v>
+        <v>3.867552161569812</v>
       </c>
       <c r="P23" t="n">
-        <v>4.120131318366412</v>
+        <v>4.100434272486829</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.9817958679547105</v>
+        <v>0.9831954832527566</v>
       </c>
       <c r="R23" t="n">
-        <v>0.01010121331597034</v>
+        <v>0.009705134711564525</v>
       </c>
       <c r="S23" t="inlineStr"/>
       <c r="T23" t="inlineStr"/>
@@ -2881,38 +2881,38 @@
       <c r="X23" t="inlineStr"/>
       <c r="Y23" t="inlineStr"/>
       <c r="Z23" t="n">
-        <v>0.8975098456803112</v>
+        <v>0.9055208672743855</v>
       </c>
       <c r="AA23" t="n">
-        <v>0.02244369091883516</v>
+        <v>0.02154870397551074</v>
       </c>
       <c r="AB23" t="inlineStr"/>
       <c r="AC23" t="n">
-        <v>-0.6143717911277069</v>
+        <v>-0.5210567798314845</v>
       </c>
       <c r="AD23" t="n">
-        <v>0.001213351750524985</v>
+        <v>0.001177762314934617</v>
       </c>
       <c r="AE23" t="inlineStr"/>
       <c r="AF23" t="n">
-        <v>0.9825040312554321</v>
+        <v>0.9823119288334167</v>
       </c>
       <c r="AG23" t="n">
-        <v>0.002227869048413941</v>
+        <v>0.002240066437573727</v>
       </c>
       <c r="AH23" t="inlineStr"/>
       <c r="AI23" t="n">
-        <v>0.9977380271393108</v>
+        <v>0.9285600393147391</v>
       </c>
       <c r="AJ23" t="n">
-        <v>7.721675654540557e-05</v>
+        <v>0.000433948777350449</v>
       </c>
       <c r="AK23" t="inlineStr"/>
       <c r="AL23" t="n">
-        <v>0.9994607279162693</v>
+        <v>0.9996211644868392</v>
       </c>
       <c r="AM23" t="n">
-        <v>0.0001081888099806526</v>
+        <v>9.067837279190432e-05</v>
       </c>
       <c r="AN23" t="inlineStr"/>
     </row>
@@ -2939,25 +2939,25 @@
         <v>18.8</v>
       </c>
       <c r="F24" t="n">
-        <v>0.5366376492551596</v>
+        <v>0.5366376495537714</v>
       </c>
       <c r="G24" t="n">
         <v>0.1688618709895305</v>
       </c>
       <c r="H24" t="n">
-        <v>0.1622397270835717</v>
+        <v>0.1622397269217724</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1157024432834648</v>
+        <v>0.1157024431484001</v>
       </c>
       <c r="J24" t="n">
-        <v>0.01655830938827357</v>
+        <v>0.01655830938652574</v>
       </c>
       <c r="K24" t="n">
-        <v>0.3875416039382416</v>
+        <v>0.3446324318476313</v>
       </c>
       <c r="L24" t="n">
-        <v>0.4583294648523437</v>
+        <v>0.4517279862819904</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
@@ -2966,16 +2966,16 @@
         <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>4.305819674281706</v>
+        <v>4.315611646840071</v>
       </c>
       <c r="P24" t="n">
-        <v>4.374016760011923</v>
+        <v>4.364852064870672</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.9930288636682071</v>
+        <v>0.9931053841207508</v>
       </c>
       <c r="R24" t="n">
-        <v>0.004958364286698705</v>
+        <v>0.004931075828299149</v>
       </c>
       <c r="S24" t="inlineStr"/>
       <c r="T24" t="inlineStr"/>
@@ -2985,31 +2985,31 @@
       <c r="X24" t="inlineStr"/>
       <c r="Y24" t="inlineStr"/>
       <c r="Z24" t="n">
-        <v>0.9998817939976682</v>
+        <v>0.999844678512584</v>
       </c>
       <c r="AA24" t="n">
-        <v>0.0008724535878225165</v>
+        <v>0.001000088281498305</v>
       </c>
       <c r="AB24" t="inlineStr"/>
       <c r="AC24" t="n">
-        <v>0.955596081366228</v>
+        <v>0.9561997570489625</v>
       </c>
       <c r="AD24" t="n">
-        <v>0.003327051647853078</v>
+        <v>0.00330435845611347</v>
       </c>
       <c r="AE24" t="inlineStr"/>
       <c r="AF24" t="n">
-        <v>0.8450195515293615</v>
+        <v>0.849908364736977</v>
       </c>
       <c r="AG24" t="n">
-        <v>0.009701678784436861</v>
+        <v>0.009547434376895647</v>
       </c>
       <c r="AH24" t="inlineStr"/>
       <c r="AI24" t="n">
-        <v>0.9872147780043223</v>
+        <v>0.9497289807407813</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0.0007639449575686116</v>
+        <v>0.001514840040229435</v>
       </c>
       <c r="AK24" t="inlineStr"/>
       <c r="AL24" t="inlineStr"/>
@@ -3041,25 +3041,25 @@
         <v>68</v>
       </c>
       <c r="F25" t="n">
-        <v>0.3559522748638808</v>
+        <v>0.3559522750970078</v>
       </c>
       <c r="G25" t="n">
         <v>0.04668534080298786</v>
       </c>
       <c r="H25" t="n">
-        <v>0.2688668009066632</v>
+        <v>0.2688668010518658</v>
       </c>
       <c r="I25" t="n">
-        <v>0.2729559277122325</v>
+        <v>0.2729559273787527</v>
       </c>
       <c r="J25" t="n">
-        <v>0.05553965571423582</v>
+        <v>0.05553965566938588</v>
       </c>
       <c r="K25" t="n">
-        <v>0.215848059616466</v>
+        <v>0.1556201893189063</v>
       </c>
       <c r="L25" t="n">
-        <v>0.2284773528280685</v>
+        <v>0.1790082363919602</v>
       </c>
       <c r="M25" t="n">
         <v>0</v>
@@ -3068,65 +3068,65 @@
         <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>4.310157944037903</v>
+        <v>4.317303423812332</v>
       </c>
       <c r="P25" t="n">
-        <v>4.340625818175276</v>
+        <v>4.341410043232657</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.984507854515332</v>
+        <v>0.9852686721979196</v>
       </c>
       <c r="R25" t="n">
-        <v>0.02064237548974292</v>
+        <v>0.02012912223434183</v>
       </c>
       <c r="S25" t="inlineStr"/>
       <c r="T25" t="n">
-        <v>-0.1747078635040595</v>
+        <v>-0.1041191953581047</v>
       </c>
       <c r="U25" t="n">
-        <v>0.03990414511207344</v>
+        <v>0.03868664366379083</v>
       </c>
       <c r="V25" t="inlineStr"/>
       <c r="W25" t="n">
-        <v>0.5431757325751052</v>
+        <v>0.5617326875108888</v>
       </c>
       <c r="X25" t="n">
-        <v>0.0008576117306741309</v>
+        <v>0.0008400123475412664</v>
       </c>
       <c r="Y25" t="inlineStr"/>
       <c r="Z25" t="n">
-        <v>0.8914663041449947</v>
+        <v>0.8844143000396868</v>
       </c>
       <c r="AA25" t="n">
-        <v>0.01135719830938619</v>
+        <v>0.01172036040256918</v>
       </c>
       <c r="AB25" t="inlineStr"/>
       <c r="AC25" t="n">
-        <v>0.661272200372327</v>
+        <v>0.5141961807851072</v>
       </c>
       <c r="AD25" t="n">
-        <v>0.00285215595587576</v>
+        <v>0.003415688920036788</v>
       </c>
       <c r="AE25" t="inlineStr"/>
       <c r="AF25" t="n">
-        <v>0.9797649579601903</v>
+        <v>0.8961335738561573</v>
       </c>
       <c r="AG25" t="n">
-        <v>0.002330186967735424</v>
+        <v>0.005279299632849382</v>
       </c>
       <c r="AH25" t="inlineStr"/>
       <c r="AI25" t="n">
-        <v>0.9702799629899451</v>
+        <v>0.849319849722135</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0.001076763288601591</v>
+        <v>0.002424507765002992</v>
       </c>
       <c r="AK25" t="inlineStr"/>
       <c r="AL25" t="n">
-        <v>-0.02132222006607809</v>
+        <v>-0.01480890467144746</v>
       </c>
       <c r="AM25" t="n">
-        <v>0.003346514058875605</v>
+        <v>0.003335826041153304</v>
       </c>
       <c r="AN25" t="inlineStr"/>
     </row>
@@ -3153,25 +3153,25 @@
         <v>55</v>
       </c>
       <c r="F26" t="n">
-        <v>0.4002539035826087</v>
+        <v>0.4002539033355717</v>
       </c>
       <c r="G26" t="n">
         <v>0.05772005772005771</v>
       </c>
       <c r="H26" t="n">
-        <v>0.1994618786146296</v>
+        <v>0.199461878586617</v>
       </c>
       <c r="I26" t="n">
-        <v>0.2900964126834302</v>
+        <v>0.2900964128573777</v>
       </c>
       <c r="J26" t="n">
-        <v>0.05246774739927379</v>
+        <v>0.0524677475003759</v>
       </c>
       <c r="K26" t="n">
-        <v>0.3197948172394026</v>
+        <v>0.2658710797035032</v>
       </c>
       <c r="L26" t="n">
-        <v>0.307729191614642</v>
+        <v>0.267295589751696</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -3180,65 +3180,65 @@
         <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>4.224153844393832</v>
+        <v>4.209752341131509</v>
       </c>
       <c r="P26" t="n">
-        <v>4.29966176391435</v>
+        <v>4.288503334795399</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.9813081611594732</v>
+        <v>0.98209868352588</v>
       </c>
       <c r="R26" t="n">
-        <v>0.02101422326656706</v>
+        <v>0.0205650520661613</v>
       </c>
       <c r="S26" t="inlineStr"/>
       <c r="T26" t="n">
-        <v>0.3194873422489407</v>
+        <v>0.3492905135958023</v>
       </c>
       <c r="U26" t="n">
-        <v>0.04051086820879415</v>
+        <v>0.03961384665857288</v>
       </c>
       <c r="V26" t="inlineStr"/>
       <c r="W26" t="n">
-        <v>-0.3167759222675097</v>
+        <v>-0.3419665329242021</v>
       </c>
       <c r="X26" t="n">
-        <v>0.0008044256175139636</v>
+        <v>0.0008120837061757484</v>
       </c>
       <c r="Y26" t="inlineStr"/>
       <c r="Z26" t="n">
-        <v>0.9473966963069762</v>
+        <v>0.9478005965134833</v>
       </c>
       <c r="AA26" t="n">
-        <v>0.01238252129801991</v>
+        <v>0.01233489176985998</v>
       </c>
       <c r="AB26" t="inlineStr"/>
       <c r="AC26" t="n">
-        <v>-0.2443036383060944</v>
+        <v>-0.2480601128404065</v>
       </c>
       <c r="AD26" t="n">
-        <v>0.003824784425081982</v>
+        <v>0.003830553466249932</v>
       </c>
       <c r="AE26" t="inlineStr"/>
       <c r="AF26" t="n">
-        <v>0.9173235934568205</v>
+        <v>0.9185393677134852</v>
       </c>
       <c r="AG26" t="n">
-        <v>0.003848789612945321</v>
+        <v>0.003820386155343175</v>
       </c>
       <c r="AH26" t="inlineStr"/>
       <c r="AI26" t="n">
-        <v>0.981903816046003</v>
+        <v>0.9826956173426886</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0.001144335649310885</v>
+        <v>0.001119020349643972</v>
       </c>
       <c r="AK26" t="inlineStr"/>
       <c r="AL26" t="n">
-        <v>0.4672117928240014</v>
+        <v>0.4408496392470302</v>
       </c>
       <c r="AM26" t="n">
-        <v>0.001011456063301109</v>
+        <v>0.001036177184194751</v>
       </c>
       <c r="AN26" t="inlineStr"/>
     </row>
@@ -3265,25 +3265,25 @@
         <v>67</v>
       </c>
       <c r="F27" t="n">
-        <v>0.4605706049045288</v>
+        <v>0.4605706047574397</v>
       </c>
       <c r="G27" t="n">
         <v>0.04738213693437573</v>
       </c>
       <c r="H27" t="n">
-        <v>0.2439684145997375</v>
+        <v>0.2439684149537734</v>
       </c>
       <c r="I27" t="n">
-        <v>0.174859558721163</v>
+        <v>0.1748595584867289</v>
       </c>
       <c r="J27" t="n">
-        <v>0.07321928484019485</v>
+        <v>0.07321928486768225</v>
       </c>
       <c r="K27" t="n">
-        <v>0.2439507965539418</v>
+        <v>0.1853792209497878</v>
       </c>
       <c r="L27" t="n">
-        <v>0.3066785751360043</v>
+        <v>0.2583351741645584</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
@@ -3292,65 +3292,65 @@
         <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>4.149671453558346</v>
+        <v>4.135160058706046</v>
       </c>
       <c r="P27" t="n">
-        <v>4.151144737685096</v>
+        <v>4.129396968057459</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.9964585972545316</v>
+        <v>0.9964887188604876</v>
       </c>
       <c r="R27" t="n">
-        <v>0.009658635921927991</v>
+        <v>0.00961747216149119</v>
       </c>
       <c r="S27" t="inlineStr"/>
       <c r="T27" t="n">
-        <v>0.9043392085180965</v>
+        <v>0.9044653629726629</v>
       </c>
       <c r="U27" t="n">
-        <v>0.01623634682286491</v>
+        <v>0.0162256372981169</v>
       </c>
       <c r="V27" t="inlineStr"/>
       <c r="W27" t="n">
-        <v>0.7029069180802154</v>
+        <v>0.7479131096932732</v>
       </c>
       <c r="X27" t="n">
-        <v>0.0006108270453513888</v>
+        <v>0.0005626613953324784</v>
       </c>
       <c r="Y27" t="inlineStr"/>
       <c r="Z27" t="n">
-        <v>0.9251622015904822</v>
+        <v>0.929344340969139</v>
       </c>
       <c r="AA27" t="n">
-        <v>0.01160032006669633</v>
+        <v>0.01127153193964718</v>
       </c>
       <c r="AB27" t="inlineStr"/>
       <c r="AC27" t="n">
-        <v>0.9436921249261397</v>
+        <v>0.9618722636930784</v>
       </c>
       <c r="AD27" t="n">
-        <v>0.00086772712896629</v>
+        <v>0.0007140343701769467</v>
       </c>
       <c r="AE27" t="inlineStr"/>
       <c r="AF27" t="n">
-        <v>0.8860893034683536</v>
+        <v>0.8860631075603903</v>
       </c>
       <c r="AG27" t="n">
-        <v>0.009428301299323778</v>
+        <v>0.009429385375398469</v>
       </c>
       <c r="AH27" t="inlineStr"/>
       <c r="AI27" t="n">
-        <v>0.5798331579529565</v>
+        <v>0.5569803504220125</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0.003492178397757696</v>
+        <v>0.003585890514541132</v>
       </c>
       <c r="AK27" t="inlineStr"/>
       <c r="AL27" t="n">
-        <v>0.4433156051319086</v>
+        <v>0.4443088628636985</v>
       </c>
       <c r="AM27" t="n">
-        <v>0.004858137066522915</v>
+        <v>0.004853801102128594</v>
       </c>
       <c r="AN27" t="inlineStr"/>
     </row>
@@ -3377,25 +3377,25 @@
         <v>274.6</v>
       </c>
       <c r="F28" t="n">
-        <v>0.7158795401171276</v>
+        <v>0.7158795401305122</v>
       </c>
       <c r="G28" t="n">
         <v>0.01156082729280107</v>
       </c>
       <c r="H28" t="n">
-        <v>0.1423140067580003</v>
+        <v>0.1423140067686963</v>
       </c>
       <c r="I28" t="n">
-        <v>0.1093709740016232</v>
+        <v>0.1093709739889803</v>
       </c>
       <c r="J28" t="n">
-        <v>0.02087465183044777</v>
+        <v>0.02087465181901007</v>
       </c>
       <c r="K28" t="n">
-        <v>0.3989355859737008</v>
+        <v>0.3642355007425858</v>
       </c>
       <c r="L28" t="n">
-        <v>0.4105436055047945</v>
+        <v>0.4012499129564205</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
@@ -3404,16 +3404,16 @@
         <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>4.114744150286834</v>
+        <v>4.119195011468114</v>
       </c>
       <c r="P28" t="n">
-        <v>4.293035030241906</v>
+        <v>4.288479230654189</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.9447349339657186</v>
+        <v>0.9436085838523114</v>
       </c>
       <c r="R28" t="n">
-        <v>0.02448099142661578</v>
+        <v>0.0247292050518764</v>
       </c>
       <c r="S28" t="inlineStr"/>
       <c r="T28" t="inlineStr"/>
@@ -3425,38 +3425,38 @@
       </c>
       <c r="Y28" t="inlineStr"/>
       <c r="Z28" t="n">
-        <v>0.6190441638909063</v>
+        <v>0.6116326402296792</v>
       </c>
       <c r="AA28" t="n">
-        <v>0.05057520790415165</v>
+        <v>0.05106481025123934</v>
       </c>
       <c r="AB28" t="inlineStr"/>
       <c r="AC28" t="n">
-        <v>0.8456801459753259</v>
+        <v>0.8070347644237067</v>
       </c>
       <c r="AD28" t="n">
-        <v>0.004698377899981765</v>
+        <v>0.00525383684323853</v>
       </c>
       <c r="AE28" t="inlineStr"/>
       <c r="AF28" t="n">
-        <v>0.499701315190371</v>
+        <v>0.4792702637836035</v>
       </c>
       <c r="AG28" t="n">
-        <v>0.01182388338144986</v>
+        <v>0.01206289772425296</v>
       </c>
       <c r="AH28" t="inlineStr"/>
       <c r="AI28" t="n">
-        <v>0.402242829316459</v>
+        <v>0.3991449559341401</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0.01680054592746786</v>
+        <v>0.01684402403031332</v>
       </c>
       <c r="AK28" t="inlineStr"/>
       <c r="AL28" t="n">
-        <v>0.989618598729249</v>
+        <v>0.9902948864933674</v>
       </c>
       <c r="AM28" t="n">
-        <v>0.0003527375152339036</v>
+        <v>0.0003410546474975989</v>
       </c>
       <c r="AN28" t="inlineStr"/>
     </row>
@@ -3483,25 +3483,25 @@
         <v>15.1</v>
       </c>
       <c r="F29" t="n">
-        <v>0.5922072970736373</v>
+        <v>0.5922072966992186</v>
       </c>
       <c r="G29" t="n">
         <v>0.2102386208346473</v>
       </c>
       <c r="H29" t="n">
-        <v>0.01553978349820245</v>
+        <v>0.01553978410683548</v>
       </c>
       <c r="I29" t="n">
-        <v>0.1433667741521803</v>
+        <v>0.1433667739479109</v>
       </c>
       <c r="J29" t="n">
-        <v>0.03864752444133265</v>
+        <v>0.03864752441138786</v>
       </c>
       <c r="K29" t="n">
-        <v>0.5337507387871602</v>
+        <v>0.541363956397434</v>
       </c>
       <c r="L29" t="n">
-        <v>0.3454522295906396</v>
+        <v>0.5235586967604516</v>
       </c>
       <c r="M29" t="n">
         <v>0</v>
@@ -3510,16 +3510,16 @@
         <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>4.255427909449321</v>
+        <v>4.316787024057529</v>
       </c>
       <c r="P29" t="n">
-        <v>4.201654647402672</v>
+        <v>4.269495680096157</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.9510114840119204</v>
+        <v>0.9371892656395286</v>
       </c>
       <c r="R29" t="n">
-        <v>0.01428286099957423</v>
+        <v>0.01617279207781879</v>
       </c>
       <c r="S29" t="inlineStr"/>
       <c r="T29" t="inlineStr"/>
@@ -3531,38 +3531,38 @@
       </c>
       <c r="Y29" t="inlineStr"/>
       <c r="Z29" t="n">
-        <v>0.7866406000590361</v>
+        <v>0.7206565206622865</v>
       </c>
       <c r="AA29" t="n">
-        <v>0.03010007215515761</v>
+        <v>0.03444140935709698</v>
       </c>
       <c r="AB29" t="inlineStr"/>
       <c r="AC29" t="n">
-        <v>0.9290719133346621</v>
+        <v>0.9309243689582459</v>
       </c>
       <c r="AD29" t="n">
-        <v>0.009224615380400224</v>
+        <v>0.009103357019039344</v>
       </c>
       <c r="AE29" t="inlineStr"/>
       <c r="AF29" t="n">
-        <v>0.6458639343134771</v>
+        <v>0.6254273555169021</v>
       </c>
       <c r="AG29" t="n">
-        <v>0.008411117137283838</v>
+        <v>0.008650408706614061</v>
       </c>
       <c r="AH29" t="inlineStr"/>
       <c r="AI29" t="n">
-        <v>0.9914430584326879</v>
+        <v>0.9600792266793866</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0.002403511476839721</v>
+        <v>0.005191422666438352</v>
       </c>
       <c r="AK29" t="inlineStr"/>
       <c r="AL29" t="n">
-        <v>0.905411353343703</v>
+        <v>0.9347622362789099</v>
       </c>
       <c r="AM29" t="n">
-        <v>0.001835480773710733</v>
+        <v>0.001524333050086481</v>
       </c>
       <c r="AN29" t="inlineStr"/>
     </row>
@@ -3589,43 +3589,43 @@
         <v>45.4</v>
       </c>
       <c r="F30" t="n">
-        <v>0.6915723419858851</v>
+        <v>0.6915723419696138</v>
       </c>
       <c r="G30" t="n">
         <v>0.06992518005733864</v>
       </c>
       <c r="H30" t="n">
-        <v>0.07335276932576335</v>
+        <v>0.07335276911610503</v>
       </c>
       <c r="I30" t="n">
-        <v>0.1459822594046087</v>
+        <v>0.1459822596625786</v>
       </c>
       <c r="J30" t="n">
-        <v>0.0191674492264043</v>
+        <v>0.01916744919436398</v>
       </c>
       <c r="K30" t="n">
-        <v>0.5332067105517685</v>
+        <v>0.5214438824954322</v>
       </c>
       <c r="L30" t="n">
-        <v>0.4026179048601815</v>
+        <v>0.4586184056829536</v>
       </c>
       <c r="M30" t="n">
-        <v>0.1192796228668859</v>
+        <v>0.1788169123578601</v>
       </c>
       <c r="N30" t="n">
-        <v>0.005593869083316108</v>
+        <v>0.01092534838299661</v>
       </c>
       <c r="O30" t="n">
-        <v>4.521248121695771</v>
+        <v>4.530502495651595</v>
       </c>
       <c r="P30" t="n">
-        <v>4.311878627455808</v>
+        <v>4.321091965539605</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.9727187905116642</v>
+        <v>0.9724874892667829</v>
       </c>
       <c r="R30" t="n">
-        <v>0.01361437469228239</v>
+        <v>0.01367196699363085</v>
       </c>
       <c r="S30" t="inlineStr"/>
       <c r="T30" t="inlineStr"/>
@@ -3637,38 +3637,38 @@
       </c>
       <c r="Y30" t="inlineStr"/>
       <c r="Z30" t="n">
-        <v>0.865763072347475</v>
+        <v>0.8629858312321204</v>
       </c>
       <c r="AA30" t="n">
-        <v>0.02495628587987226</v>
+        <v>0.02521312577120071</v>
       </c>
       <c r="AB30" t="inlineStr"/>
       <c r="AC30" t="n">
-        <v>0.9996047218401607</v>
+        <v>0.9990788695314093</v>
       </c>
       <c r="AD30" t="n">
-        <v>8.959500586566284e-05</v>
+        <v>0.0001367706707235131</v>
       </c>
       <c r="AE30" t="inlineStr"/>
       <c r="AF30" t="n">
-        <v>0.01431393370887513</v>
+        <v>-0.01928708471193863</v>
       </c>
       <c r="AG30" t="n">
-        <v>0.0134264682354188</v>
+        <v>0.01365339776076719</v>
       </c>
       <c r="AH30" t="inlineStr"/>
       <c r="AI30" t="n">
-        <v>0.8321512384245673</v>
+        <v>0.8582092904992514</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0.008574983234710037</v>
+        <v>0.007881304323310762</v>
       </c>
       <c r="AK30" t="inlineStr"/>
       <c r="AL30" t="n">
-        <v>0.4749689970584041</v>
+        <v>0.4965562189636555</v>
       </c>
       <c r="AM30" t="n">
-        <v>0.001948739705839091</v>
+        <v>0.001908256925310108</v>
       </c>
       <c r="AN30" t="inlineStr"/>
     </row>
@@ -3695,25 +3695,25 @@
         <v>26.3</v>
       </c>
       <c r="F31" t="n">
-        <v>0.5100618132893889</v>
+        <v>0.510061813306836</v>
       </c>
       <c r="G31" t="n">
         <v>0.1207073450419458</v>
       </c>
       <c r="H31" t="n">
-        <v>0.08244690044211486</v>
+        <v>0.08244690045861332</v>
       </c>
       <c r="I31" t="n">
-        <v>0.2664816652636977</v>
+        <v>0.2664816652601923</v>
       </c>
       <c r="J31" t="n">
-        <v>0.02030227596285282</v>
+        <v>0.02030227593241257</v>
       </c>
       <c r="K31" t="n">
-        <v>0.4902078464552742</v>
+        <v>0.4761534586665042</v>
       </c>
       <c r="L31" t="n">
-        <v>0.4306016586812278</v>
+        <v>0.4435937749479988</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
@@ -3722,16 +3722,16 @@
         <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>4.249538389327932</v>
+        <v>4.256876131451557</v>
       </c>
       <c r="P31" t="n">
-        <v>4.410030188172075</v>
+        <v>4.406214783744725</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.9859206503437857</v>
+        <v>0.9861409780642537</v>
       </c>
       <c r="R31" t="n">
-        <v>0.007749040197655582</v>
+        <v>0.007688168757415434</v>
       </c>
       <c r="S31" t="inlineStr"/>
       <c r="T31" t="inlineStr"/>
@@ -3743,38 +3743,38 @@
       </c>
       <c r="Y31" t="inlineStr"/>
       <c r="Z31" t="n">
-        <v>0.9485192219064569</v>
+        <v>0.9497635023137877</v>
       </c>
       <c r="AA31" t="n">
-        <v>0.01211880347787228</v>
+        <v>0.01197145310566209</v>
       </c>
       <c r="AB31" t="inlineStr"/>
       <c r="AC31" t="n">
-        <v>0.899301487818288</v>
+        <v>0.9090348845965792</v>
       </c>
       <c r="AD31" t="n">
-        <v>0.007725611082399673</v>
+        <v>0.007342750171641711</v>
       </c>
       <c r="AE31" t="inlineStr"/>
       <c r="AF31" t="n">
-        <v>-0.03053000177468723</v>
+        <v>-0.07237371460497255</v>
       </c>
       <c r="AG31" t="n">
-        <v>0.009230499413846684</v>
+        <v>0.009416032778659647</v>
       </c>
       <c r="AH31" t="inlineStr"/>
       <c r="AI31" t="n">
-        <v>0.9731950440372746</v>
+        <v>0.9753948227631314</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0.002569078251395795</v>
+        <v>0.002461404730596016</v>
       </c>
       <c r="AK31" t="inlineStr"/>
       <c r="AL31" t="n">
-        <v>0.04864669288554757</v>
+        <v>0.03391823878889433</v>
       </c>
       <c r="AM31" t="n">
-        <v>0.00409959019304732</v>
+        <v>0.004131202385804385</v>
       </c>
       <c r="AN31" t="inlineStr"/>
     </row>
@@ -3801,25 +3801,25 @@
         <v>32.6</v>
       </c>
       <c r="F32" t="n">
-        <v>0.6207177798737793</v>
+        <v>0.6207177798836309</v>
       </c>
       <c r="G32" t="n">
         <v>0.09738046547862497</v>
       </c>
       <c r="H32" t="n">
-        <v>0.1026556514757471</v>
+        <v>0.102655651448909</v>
       </c>
       <c r="I32" t="n">
-        <v>0.1515085776379964</v>
+        <v>0.1515085776593587</v>
       </c>
       <c r="J32" t="n">
-        <v>0.02773752553385222</v>
+        <v>0.0277375255294765</v>
       </c>
       <c r="K32" t="n">
-        <v>0.5003204670714311</v>
+        <v>0.4784259818721357</v>
       </c>
       <c r="L32" t="n">
-        <v>0.4277157292674033</v>
+        <v>0.4396002722871774</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
@@ -3828,16 +3828,16 @@
         <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>4.53028971271256</v>
+        <v>4.54395154441503</v>
       </c>
       <c r="P32" t="n">
-        <v>4.425992246404511</v>
+        <v>4.423053759280506</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.9797092855898777</v>
+        <v>0.9796796490207097</v>
       </c>
       <c r="R32" t="n">
-        <v>0.01371647812577785</v>
+        <v>0.01372649159866854</v>
       </c>
       <c r="S32" t="inlineStr"/>
       <c r="T32" t="inlineStr"/>
@@ -3849,38 +3849,38 @@
       </c>
       <c r="Y32" t="inlineStr"/>
       <c r="Z32" t="n">
-        <v>0.9019187053601531</v>
+        <v>0.8824526577231863</v>
       </c>
       <c r="AA32" t="n">
-        <v>0.008931998180194519</v>
+        <v>0.00977826804544208</v>
       </c>
       <c r="AB32" t="inlineStr"/>
       <c r="AC32" t="n">
-        <v>0.227125782583355</v>
+        <v>0.224021570840371</v>
       </c>
       <c r="AD32" t="n">
-        <v>0.01745066310661357</v>
+        <v>0.01748567290604329</v>
       </c>
       <c r="AE32" t="inlineStr"/>
       <c r="AF32" t="n">
-        <v>-0.5421892580542693</v>
+        <v>-0.5501752516722134</v>
       </c>
       <c r="AG32" t="n">
-        <v>0.0157928614398565</v>
+        <v>0.01583369914951323</v>
       </c>
       <c r="AH32" t="inlineStr"/>
       <c r="AI32" t="n">
-        <v>0.2311239848234773</v>
+        <v>0.2701411407221971</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0.01816850662788654</v>
+        <v>0.01770151823585247</v>
       </c>
       <c r="AK32" t="inlineStr"/>
       <c r="AL32" t="n">
-        <v>0.07382372874138743</v>
+        <v>0.07982392336394573</v>
       </c>
       <c r="AM32" t="n">
-        <v>0.004891724033596115</v>
+        <v>0.004875852888111583</v>
       </c>
       <c r="AN32" t="inlineStr"/>
     </row>
@@ -3905,25 +3905,25 @@
       </c>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="n">
-        <v>0.6421516036650835</v>
+        <v>0.642151603719554</v>
       </c>
       <c r="G33" t="n">
-        <v>0.002523163010079717</v>
+        <v>0.002523163255140709</v>
       </c>
       <c r="H33" t="n">
-        <v>0.2245698007084695</v>
+        <v>0.2245698005775707</v>
       </c>
       <c r="I33" t="n">
-        <v>0.1058026140953321</v>
+        <v>0.1058026139657058</v>
       </c>
       <c r="J33" t="n">
-        <v>0.02495281852103528</v>
+        <v>0.0249528184820288</v>
       </c>
       <c r="K33" t="n">
-        <v>0.2851358817564152</v>
+        <v>0.2262549868912993</v>
       </c>
       <c r="L33" t="n">
-        <v>0.318877189205591</v>
+        <v>0.2964580981939559</v>
       </c>
       <c r="M33" t="n">
         <v>0</v>
@@ -3932,16 +3932,16 @@
         <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>4.308512879316226</v>
+        <v>4.301098115789768</v>
       </c>
       <c r="P33" t="n">
-        <v>4.271057230087922</v>
+        <v>4.263093428599172</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.9655580660003291</v>
+        <v>0.9639693762745506</v>
       </c>
       <c r="R33" t="n">
-        <v>0.005887686362091251</v>
+        <v>0.006021945102291516</v>
       </c>
       <c r="S33" t="inlineStr"/>
       <c r="T33" t="inlineStr"/>
@@ -3951,38 +3951,38 @@
       <c r="X33" t="inlineStr"/>
       <c r="Y33" t="inlineStr"/>
       <c r="Z33" t="n">
-        <v>0.9329657134926262</v>
+        <v>0.930968249733922</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.01046228497280141</v>
+        <v>0.01061701649445812</v>
       </c>
       <c r="AB33" t="inlineStr"/>
       <c r="AC33" t="n">
-        <v>0.1136216779889698</v>
+        <v>-0.004604854245426004</v>
       </c>
       <c r="AD33" t="n">
-        <v>0.006041859472656011</v>
+        <v>0.006432187423387583</v>
       </c>
       <c r="AE33" t="inlineStr"/>
       <c r="AF33" t="n">
-        <v>0.8419596117641139</v>
+        <v>0.8367644164105619</v>
       </c>
       <c r="AG33" t="n">
-        <v>0.004741891982336572</v>
+        <v>0.004819200890245548</v>
       </c>
       <c r="AH33" t="inlineStr"/>
       <c r="AI33" t="n">
-        <v>0.8087275627461875</v>
+        <v>0.8452926361595079</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0.00207519263564663</v>
+        <v>0.001866326887070679</v>
       </c>
       <c r="AK33" t="inlineStr"/>
       <c r="AL33" t="n">
-        <v>0.41811019654445</v>
+        <v>0.4709474565375992</v>
       </c>
       <c r="AM33" t="n">
-        <v>0.0007541993802418439</v>
+        <v>0.0007191429009148535</v>
       </c>
       <c r="AN33" t="inlineStr"/>
     </row>
@@ -4009,25 +4009,25 @@
         <v>26</v>
       </c>
       <c r="F34" t="n">
-        <v>0.7519633395058384</v>
+        <v>0.7519633396250179</v>
       </c>
       <c r="G34" t="n">
         <v>0.1221001221001221</v>
       </c>
       <c r="H34" t="n">
-        <v>0.01478397129559729</v>
+        <v>0.0147839710365304</v>
       </c>
       <c r="I34" t="n">
-        <v>0.1023682012617217</v>
+        <v>0.1023682013871307</v>
       </c>
       <c r="J34" t="n">
-        <v>0.008784365836720525</v>
+        <v>0.008784365851198749</v>
       </c>
       <c r="K34" t="n">
-        <v>0.5350531219152354</v>
+        <v>0.5348911130605229</v>
       </c>
       <c r="L34" t="n">
-        <v>0.4496288558276344</v>
+        <v>0.5384228813419599</v>
       </c>
       <c r="M34" t="n">
         <v>0</v>
@@ -4036,16 +4036,16 @@
         <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>4.263995602912937</v>
+        <v>4.266762406485488</v>
       </c>
       <c r="P34" t="n">
-        <v>4.285493285403806</v>
+        <v>4.312154834736841</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.8874123644329036</v>
+        <v>0.9361790115277747</v>
       </c>
       <c r="R34" t="n">
-        <v>0.02339900894059084</v>
+        <v>0.01761707800354978</v>
       </c>
       <c r="S34" t="inlineStr"/>
       <c r="T34" t="inlineStr"/>
@@ -4057,38 +4057,38 @@
       </c>
       <c r="Y34" t="inlineStr"/>
       <c r="Z34" t="n">
-        <v>0.8163313485894672</v>
+        <v>0.8974143595677306</v>
       </c>
       <c r="AA34" t="n">
-        <v>0.05130374898203999</v>
+        <v>0.0383420095060048</v>
       </c>
       <c r="AB34" t="inlineStr"/>
       <c r="AC34" t="n">
-        <v>0.9926351345987787</v>
+        <v>0.9955449680120769</v>
       </c>
       <c r="AD34" t="n">
-        <v>0.002030051118949896</v>
+        <v>0.001578883117276267</v>
       </c>
       <c r="AE34" t="inlineStr"/>
       <c r="AF34" t="n">
-        <v>0.6403832964109917</v>
+        <v>0.7013335067637991</v>
       </c>
       <c r="AG34" t="n">
-        <v>0.004616607184114195</v>
+        <v>0.004207229944072429</v>
       </c>
       <c r="AH34" t="inlineStr"/>
       <c r="AI34" t="n">
-        <v>0.3490818289130715</v>
+        <v>0.5013692040841152</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0.008955763179533109</v>
+        <v>0.007838427613536604</v>
       </c>
       <c r="AK34" t="inlineStr"/>
       <c r="AL34" t="n">
-        <v>0.06473814985066573</v>
+        <v>0.2739821713457488</v>
       </c>
       <c r="AM34" t="n">
-        <v>0.0009401333509796495</v>
+        <v>0.0008283168347656708</v>
       </c>
       <c r="AN34" t="inlineStr"/>
     </row>
@@ -4115,25 +4115,25 @@
         <v>74.09999999999999</v>
       </c>
       <c r="F35" t="n">
-        <v>0.687523750659823</v>
+        <v>0.6875237506860816</v>
       </c>
       <c r="G35" t="n">
         <v>0.042842148105306</v>
       </c>
       <c r="H35" t="n">
-        <v>0.2018749037744333</v>
+        <v>0.201874903841659</v>
       </c>
       <c r="I35" t="n">
-        <v>0.03464191229956181</v>
+        <v>0.03464191218332047</v>
       </c>
       <c r="J35" t="n">
-        <v>0.033117285160876</v>
+        <v>0.03311728518363292</v>
       </c>
       <c r="K35" t="n">
-        <v>0.3019491379002337</v>
+        <v>0.2505782405517368</v>
       </c>
       <c r="L35" t="n">
-        <v>0.2475197568595714</v>
+        <v>0.2476705459602902</v>
       </c>
       <c r="M35" t="n">
         <v>0</v>
@@ -4142,16 +4142,16 @@
         <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>4.049560543950747</v>
+        <v>4.045560608437414</v>
       </c>
       <c r="P35" t="n">
-        <v>4.155419298433618</v>
+        <v>4.150294987742657</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.9968026665346971</v>
+        <v>0.9960764293395998</v>
       </c>
       <c r="R35" t="n">
-        <v>0.005633106328177837</v>
+        <v>0.006240145575659438</v>
       </c>
       <c r="S35" t="inlineStr"/>
       <c r="T35" t="inlineStr"/>
@@ -4161,10 +4161,10 @@
       <c r="X35" t="inlineStr"/>
       <c r="Y35" t="inlineStr"/>
       <c r="Z35" t="n">
-        <v>0.986026611126027</v>
+        <v>0.9768827518398776</v>
       </c>
       <c r="AA35" t="n">
-        <v>0.006450528757181458</v>
+        <v>0.008296836093610347</v>
       </c>
       <c r="AB35" t="inlineStr"/>
       <c r="AC35" t="inlineStr"/>
@@ -4173,24 +4173,24 @@
       </c>
       <c r="AE35" t="inlineStr"/>
       <c r="AF35" t="n">
-        <v>0.6263631436893655</v>
+        <v>0.6126497126435606</v>
       </c>
       <c r="AG35" t="n">
-        <v>0.009128694080652602</v>
+        <v>0.009294707774008508</v>
       </c>
       <c r="AH35" t="inlineStr"/>
       <c r="AI35" t="n">
-        <v>0.725976549783718</v>
+        <v>0.7232976404329658</v>
       </c>
       <c r="AJ35" t="n">
-        <v>0.002115415272365411</v>
+        <v>0.002125730482752263</v>
       </c>
       <c r="AK35" t="inlineStr"/>
       <c r="AL35" t="n">
-        <v>0.5278622431736911</v>
+        <v>0.5017060060061725</v>
       </c>
       <c r="AM35" t="n">
-        <v>0.002333058229972926</v>
+        <v>0.00239681237673957</v>
       </c>
       <c r="AN35" t="inlineStr"/>
     </row>
@@ -4217,25 +4217,25 @@
         <v>46.2</v>
       </c>
       <c r="F36" t="n">
-        <v>0.6184344404805445</v>
+        <v>0.6184344404849657</v>
       </c>
       <c r="G36" t="n">
         <v>0.06871435442864013</v>
       </c>
       <c r="H36" t="n">
-        <v>0.1345326977341799</v>
+        <v>0.1345326978111002</v>
       </c>
       <c r="I36" t="n">
-        <v>0.1554100927459354</v>
+        <v>0.1554100926475006</v>
       </c>
       <c r="J36" t="n">
-        <v>0.02290841461070009</v>
+        <v>0.0229084146277933</v>
       </c>
       <c r="K36" t="n">
-        <v>0.4306133506575378</v>
+        <v>0.3956792038623254</v>
       </c>
       <c r="L36" t="n">
-        <v>0.3952277307226713</v>
+        <v>0.3772180634049475</v>
       </c>
       <c r="M36" t="n">
         <v>0</v>
@@ -4244,16 +4244,16 @@
         <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>4.307865273041947</v>
+        <v>4.298761590070962</v>
       </c>
       <c r="P36" t="n">
-        <v>4.321519067505179</v>
+        <v>4.314472797017256</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.9835354887150053</v>
+        <v>0.9833034591816343</v>
       </c>
       <c r="R36" t="n">
-        <v>0.01162717237780395</v>
+        <v>0.01170881490655285</v>
       </c>
       <c r="S36" t="inlineStr"/>
       <c r="T36" t="inlineStr"/>
@@ -4265,38 +4265,38 @@
       </c>
       <c r="Y36" t="inlineStr"/>
       <c r="Z36" t="n">
-        <v>0.8084317089137957</v>
+        <v>0.8030129752953671</v>
       </c>
       <c r="AA36" t="n">
-        <v>0.01902625059212809</v>
+        <v>0.01929346405109096</v>
       </c>
       <c r="AB36" t="inlineStr"/>
       <c r="AC36" t="n">
-        <v>0.3717595996132993</v>
+        <v>0.3937567515993992</v>
       </c>
       <c r="AD36" t="n">
-        <v>0.008130839074664459</v>
+        <v>0.00798722462225003</v>
       </c>
       <c r="AE36" t="inlineStr"/>
       <c r="AF36" t="n">
-        <v>0.06964126973225437</v>
+        <v>0.06392330402484447</v>
       </c>
       <c r="AG36" t="n">
-        <v>0.01345734462455408</v>
+        <v>0.01349863561353459</v>
       </c>
       <c r="AH36" t="inlineStr"/>
       <c r="AI36" t="n">
-        <v>0.728509641823178</v>
+        <v>0.7343155153926439</v>
       </c>
       <c r="AJ36" t="n">
-        <v>0.006104128876372306</v>
+        <v>0.006038507174148961</v>
       </c>
       <c r="AK36" t="inlineStr"/>
       <c r="AL36" t="n">
-        <v>0.1670701935279308</v>
+        <v>0.151383502696266</v>
       </c>
       <c r="AM36" t="n">
-        <v>0.004035884011984705</v>
+        <v>0.004073710948003456</v>
       </c>
       <c r="AN36" t="inlineStr"/>
     </row>
@@ -4323,25 +4323,25 @@
         <v>55</v>
       </c>
       <c r="F37" t="n">
-        <v>0.4310490712245829</v>
+        <v>0.4310490710111513</v>
       </c>
       <c r="G37" t="n">
         <v>0.05772005772005771</v>
       </c>
       <c r="H37" t="n">
-        <v>0.3585099706610048</v>
+        <v>0.3585099709374001</v>
       </c>
       <c r="I37" t="n">
-        <v>0.1452580722152676</v>
+        <v>0.1452580721451264</v>
       </c>
       <c r="J37" t="n">
-        <v>0.007462828179086988</v>
+        <v>0.007462828186264588</v>
       </c>
       <c r="K37" t="n">
-        <v>0.1032759135620988</v>
+        <v>0.05738019622196385</v>
       </c>
       <c r="L37" t="n">
-        <v>0.1052974555473489</v>
+        <v>0.07187183413434833</v>
       </c>
       <c r="M37" t="n">
         <v>0</v>
@@ -4350,61 +4350,61 @@
         <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>4.230764125716685</v>
+        <v>4.219329310499894</v>
       </c>
       <c r="P37" t="n">
-        <v>4.263232513024087</v>
+        <v>4.254728410727956</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.9931562102604981</v>
+        <v>0.9930173872572994</v>
       </c>
       <c r="R37" t="n">
-        <v>0.005512353980038237</v>
+        <v>0.005567981035393577</v>
       </c>
       <c r="S37" t="inlineStr"/>
       <c r="T37" t="inlineStr"/>
       <c r="U37" t="inlineStr"/>
       <c r="V37" t="inlineStr"/>
       <c r="W37" t="n">
-        <v>0.02232969103987603</v>
+        <v>0.0932675702980631</v>
       </c>
       <c r="X37" t="n">
-        <v>0.0004230041163021422</v>
+        <v>0.0004073689792571523</v>
       </c>
       <c r="Y37" t="inlineStr"/>
       <c r="Z37" t="n">
-        <v>0.9984068109743827</v>
+        <v>0.9986927389984463</v>
       </c>
       <c r="AA37" t="n">
-        <v>0.00189506155895734</v>
+        <v>0.001716606771902392</v>
       </c>
       <c r="AB37" t="inlineStr"/>
       <c r="AC37" t="n">
-        <v>-0.5007957506550722</v>
+        <v>-0.5161524176848171</v>
       </c>
       <c r="AD37" t="n">
-        <v>0.007756653822795167</v>
+        <v>0.007796237114690461</v>
       </c>
       <c r="AE37" t="inlineStr"/>
       <c r="AF37" t="n">
-        <v>0.9118017575571626</v>
+        <v>0.909420461135821</v>
       </c>
       <c r="AG37" t="n">
-        <v>0.009664547763306183</v>
+        <v>0.009794147150674554</v>
       </c>
       <c r="AH37" t="inlineStr"/>
       <c r="AI37" t="n">
-        <v>0.940625407252214</v>
+        <v>0.9306494066752465</v>
       </c>
       <c r="AJ37" t="n">
-        <v>0.002186139360582258</v>
+        <v>0.002362667520562983</v>
       </c>
       <c r="AK37" t="inlineStr"/>
       <c r="AL37" t="n">
-        <v>0.9999996806026822</v>
+        <v>0.9999992472983318</v>
       </c>
       <c r="AM37" t="n">
-        <v>5.563157774895456e-07</v>
+        <v>8.540183106247728e-07</v>
       </c>
       <c r="AN37" t="inlineStr"/>
     </row>
@@ -4431,25 +4431,25 @@
         <v>23</v>
       </c>
       <c r="F38" t="n">
-        <v>0.4115513533477569</v>
+        <v>0.4115513534924096</v>
       </c>
       <c r="G38" t="n">
         <v>0.1380262249827467</v>
       </c>
       <c r="H38" t="n">
-        <v>0.3184506857669814</v>
+        <v>0.318450685478181</v>
       </c>
       <c r="I38" t="n">
-        <v>0.1287866383384099</v>
+        <v>0.1287866384976123</v>
       </c>
       <c r="J38" t="n">
-        <v>0.003185097564105027</v>
+        <v>0.003185097549050355</v>
       </c>
       <c r="K38" t="n">
-        <v>0.1416438943560188</v>
+        <v>0.08867237739422326</v>
       </c>
       <c r="L38" t="n">
-        <v>0.1094955221332978</v>
+        <v>0.07327446990607386</v>
       </c>
       <c r="M38" t="n">
         <v>0</v>
@@ -4458,61 +4458,61 @@
         <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>4.113546643685265</v>
+        <v>4.086901387408154</v>
       </c>
       <c r="P38" t="n">
-        <v>4.195575058726416</v>
+        <v>4.186586613491636</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.9538747494938609</v>
+        <v>0.9589512985719434</v>
       </c>
       <c r="R38" t="n">
-        <v>0.01205090202935683</v>
+        <v>0.0113684144483331</v>
       </c>
       <c r="S38" t="inlineStr"/>
       <c r="T38" t="inlineStr"/>
       <c r="U38" t="inlineStr"/>
       <c r="V38" t="inlineStr"/>
       <c r="W38" t="n">
-        <v>0.1856746702867531</v>
+        <v>0.02144122315033237</v>
       </c>
       <c r="X38" t="n">
-        <v>0.001182812986735585</v>
+        <v>0.001296613594212609</v>
       </c>
       <c r="Y38" t="inlineStr"/>
       <c r="Z38" t="n">
-        <v>0.8117400695136249</v>
+        <v>0.847912062457137</v>
       </c>
       <c r="AA38" t="n">
-        <v>0.02092714413211252</v>
+        <v>0.01880954994763496</v>
       </c>
       <c r="AB38" t="inlineStr"/>
       <c r="AC38" t="n">
-        <v>-0.3889791861968517</v>
+        <v>-0.3387514716347118</v>
       </c>
       <c r="AD38" t="n">
-        <v>0.01710582175510812</v>
+        <v>0.01679368659617104</v>
       </c>
       <c r="AE38" t="inlineStr"/>
       <c r="AF38" t="n">
-        <v>0.9638846440510584</v>
+        <v>0.941950636522371</v>
       </c>
       <c r="AG38" t="n">
-        <v>0.004411335700999675</v>
+        <v>0.005592717556323321</v>
       </c>
       <c r="AH38" t="inlineStr"/>
       <c r="AI38" t="n">
-        <v>-1.16109724143762</v>
+        <v>-0.9297900459974751</v>
       </c>
       <c r="AJ38" t="n">
-        <v>0.004856150575323175</v>
+        <v>0.004588915366316424</v>
       </c>
       <c r="AK38" t="inlineStr"/>
       <c r="AL38" t="n">
-        <v>0.9999973457512438</v>
+        <v>0.9999950238400729</v>
       </c>
       <c r="AM38" t="n">
-        <v>6.529628274818922e-07</v>
+        <v>8.940562082327667e-07</v>
       </c>
       <c r="AN38" t="inlineStr"/>
     </row>
@@ -4539,25 +4539,25 @@
         <v>48</v>
       </c>
       <c r="F39" t="n">
-        <v>0.464866072408512</v>
+        <v>0.4648660724078407</v>
       </c>
       <c r="G39" t="n">
         <v>0.06613756613756613</v>
       </c>
       <c r="H39" t="n">
-        <v>0.3147165341115007</v>
+        <v>0.3147165341147267</v>
       </c>
       <c r="I39" t="n">
-        <v>0.1215057334841287</v>
+        <v>0.1215057334732506</v>
       </c>
       <c r="J39" t="n">
-        <v>0.03277409385829239</v>
+        <v>0.03277409386661587</v>
       </c>
       <c r="K39" t="n">
-        <v>0.1514776863482813</v>
+        <v>0.09605755582229301</v>
       </c>
       <c r="L39" t="n">
-        <v>0.1340732886312007</v>
+        <v>0.09760678814077213</v>
       </c>
       <c r="M39" t="n">
         <v>0</v>
@@ -4566,16 +4566,16 @@
         <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>4.258531293425802</v>
+        <v>4.239319110069875</v>
       </c>
       <c r="P39" t="n">
-        <v>4.266000771504852</v>
+        <v>4.257342768848647</v>
       </c>
       <c r="Q39" t="n">
-        <v>0.9829587365995249</v>
+        <v>0.9837605775358461</v>
       </c>
       <c r="R39" t="n">
-        <v>0.008737874047912922</v>
+        <v>0.008529826070278492</v>
       </c>
       <c r="S39" t="inlineStr"/>
       <c r="T39" t="inlineStr"/>
@@ -4585,38 +4585,38 @@
       <c r="X39" t="inlineStr"/>
       <c r="Y39" t="inlineStr"/>
       <c r="Z39" t="n">
-        <v>0.8831627197684985</v>
+        <v>0.8980761680671179</v>
       </c>
       <c r="AA39" t="n">
-        <v>0.01144041772745747</v>
+        <v>0.01068535694470511</v>
       </c>
       <c r="AB39" t="inlineStr"/>
       <c r="AC39" t="n">
-        <v>0.1261866791231349</v>
+        <v>0.108801178015107</v>
       </c>
       <c r="AD39" t="n">
-        <v>0.001390727162238847</v>
+        <v>0.001404494064848107</v>
       </c>
       <c r="AE39" t="inlineStr"/>
       <c r="AF39" t="n">
-        <v>-0.04784161916678453</v>
+        <v>-0.04529134157407189</v>
       </c>
       <c r="AG39" t="n">
-        <v>0.0146620188601067</v>
+        <v>0.01464416549569893</v>
       </c>
       <c r="AH39" t="inlineStr"/>
       <c r="AI39" t="n">
-        <v>0.7521066762451492</v>
+        <v>0.7583287512379153</v>
       </c>
       <c r="AJ39" t="n">
-        <v>0.005402853671293663</v>
+        <v>0.005334617473796769</v>
       </c>
       <c r="AK39" t="inlineStr"/>
       <c r="AL39" t="n">
-        <v>-0.1202639646824426</v>
+        <v>-0.111143401374113</v>
       </c>
       <c r="AM39" t="n">
-        <v>0.002183874932294108</v>
+        <v>0.002174966821564137</v>
       </c>
       <c r="AN39" t="inlineStr"/>
     </row>
@@ -4643,43 +4643,43 @@
         <v>70.70000000000002</v>
       </c>
       <c r="F40" t="n">
-        <v>0.4301189564620539</v>
+        <v>0.4301189564542686</v>
       </c>
       <c r="G40" t="n">
         <v>0.04490244942861631</v>
       </c>
       <c r="H40" t="n">
-        <v>0.1726240369116226</v>
+        <v>0.1726240368983525</v>
       </c>
       <c r="I40" t="n">
-        <v>0.3491894964880415</v>
+        <v>0.3491894964967999</v>
       </c>
       <c r="J40" t="n">
-        <v>0.003165060709665684</v>
+        <v>0.00316506072196271</v>
       </c>
       <c r="K40" t="n">
-        <v>0.369449111753018</v>
+        <v>0.3245675201964789</v>
       </c>
       <c r="L40" t="n">
-        <v>0.415290884536345</v>
+        <v>0.4116624100045712</v>
       </c>
       <c r="M40" t="n">
-        <v>0.3648046244607287</v>
+        <v>0.3548032515534763</v>
       </c>
       <c r="N40" t="n">
-        <v>0.04937948541704858</v>
+        <v>0.04427533566646177</v>
       </c>
       <c r="O40" t="n">
-        <v>4.291879477204492</v>
+        <v>4.31638491374612</v>
       </c>
       <c r="P40" t="n">
-        <v>4.517574852075538</v>
+        <v>4.513454101979352</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.9911917152218972</v>
+        <v>0.990826723413644</v>
       </c>
       <c r="R40" t="n">
-        <v>0.005637489397757618</v>
+        <v>0.005753105108540139</v>
       </c>
       <c r="S40" t="inlineStr"/>
       <c r="T40" t="inlineStr"/>
@@ -4689,38 +4689,38 @@
       <c r="X40" t="inlineStr"/>
       <c r="Y40" t="inlineStr"/>
       <c r="Z40" t="n">
-        <v>0.9653269449780828</v>
+        <v>0.9656559209455698</v>
       </c>
       <c r="AA40" t="n">
-        <v>0.01123719084758885</v>
+        <v>0.01118375488534484</v>
       </c>
       <c r="AB40" t="inlineStr"/>
       <c r="AC40" t="n">
-        <v>0.9342934874359159</v>
+        <v>0.9552475979151238</v>
       </c>
       <c r="AD40" t="n">
-        <v>0.0005831585441500598</v>
+        <v>0.0004812720160272493</v>
       </c>
       <c r="AE40" t="inlineStr"/>
       <c r="AF40" t="n">
-        <v>0.9817570138481977</v>
+        <v>0.980250840873868</v>
       </c>
       <c r="AG40" t="n">
-        <v>0.003392589128107481</v>
+        <v>0.00352986101698668</v>
       </c>
       <c r="AH40" t="inlineStr"/>
       <c r="AI40" t="n">
-        <v>0.9975745222153841</v>
+        <v>0.9944593856651955</v>
       </c>
       <c r="AJ40" t="n">
-        <v>0.002211695539662375</v>
+        <v>0.003342763505998418</v>
       </c>
       <c r="AK40" t="inlineStr"/>
       <c r="AL40" t="n">
-        <v>0.9999999504038204</v>
+        <v>0.9999999489563733</v>
       </c>
       <c r="AM40" t="n">
-        <v>1.354084727160346e-07</v>
+        <v>1.37370185497802e-07</v>
       </c>
       <c r="AN40" t="inlineStr"/>
     </row>
@@ -4747,25 +4747,25 @@
         <v>84.84</v>
       </c>
       <c r="F41" t="n">
-        <v>0.3369254806988865</v>
+        <v>0.3369254807409055</v>
       </c>
       <c r="G41" t="n">
         <v>0.03741870785718027</v>
       </c>
       <c r="H41" t="n">
-        <v>0.2464337952095151</v>
+        <v>0.2464337951089697</v>
       </c>
       <c r="I41" t="n">
-        <v>0.3649923484168429</v>
+        <v>0.3649923484758453</v>
       </c>
       <c r="J41" t="n">
-        <v>0.01422966781757511</v>
+        <v>0.0142296678170992</v>
       </c>
       <c r="K41" t="n">
-        <v>0.2579668639842531</v>
+        <v>0.1960310268779012</v>
       </c>
       <c r="L41" t="n">
-        <v>0.2827780651877471</v>
+        <v>0.2439921895004572</v>
       </c>
       <c r="M41" t="n">
         <v>0</v>
@@ -4774,16 +4774,16 @@
         <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>4.436658070637798</v>
+        <v>4.444024655632611</v>
       </c>
       <c r="P41" t="n">
-        <v>4.506800334756738</v>
+        <v>4.503905143528606</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.993566285594778</v>
+        <v>0.9935283772236047</v>
       </c>
       <c r="R41" t="n">
-        <v>0.006216499390980136</v>
+        <v>0.006234786748266476</v>
       </c>
       <c r="S41" t="inlineStr"/>
       <c r="T41" t="inlineStr"/>
@@ -4793,38 +4793,38 @@
       <c r="X41" t="inlineStr"/>
       <c r="Y41" t="inlineStr"/>
       <c r="Z41" t="n">
-        <v>0.8657218270983299</v>
+        <v>0.8663115329053979</v>
       </c>
       <c r="AA41" t="n">
-        <v>0.01067111827864404</v>
+        <v>0.01064766046448132</v>
       </c>
       <c r="AB41" t="inlineStr"/>
       <c r="AC41" t="n">
-        <v>0.6406308080845335</v>
+        <v>0.675295812595353</v>
       </c>
       <c r="AD41" t="n">
-        <v>0.001495005495576569</v>
+        <v>0.001421072751975918</v>
       </c>
       <c r="AE41" t="inlineStr"/>
       <c r="AF41" t="n">
-        <v>0.9709982371512711</v>
+        <v>0.9703863626860626</v>
       </c>
       <c r="AG41" t="n">
-        <v>0.004566180336330381</v>
+        <v>0.004614097184664481</v>
       </c>
       <c r="AH41" t="inlineStr"/>
       <c r="AI41" t="n">
-        <v>0.9468872634985886</v>
+        <v>0.945512014683437</v>
       </c>
       <c r="AJ41" t="n">
-        <v>0.007430020300221683</v>
+        <v>0.007525598363178988</v>
       </c>
       <c r="AK41" t="inlineStr"/>
       <c r="AL41" t="n">
-        <v>0.9002450500253879</v>
+        <v>0.9016669456593964</v>
       </c>
       <c r="AM41" t="n">
-        <v>0.001030200036920166</v>
+        <v>0.001022831508655481</v>
       </c>
       <c r="AN41" t="inlineStr"/>
     </row>
@@ -4851,25 +4851,25 @@
         <v>124.31</v>
       </c>
       <c r="F42" t="n">
-        <v>0.4255446328458828</v>
+        <v>0.4255446328415167</v>
       </c>
       <c r="G42" t="n">
         <v>0.02553779401981477</v>
       </c>
       <c r="H42" t="n">
-        <v>0.2146647956812922</v>
+        <v>0.214664795708344</v>
       </c>
       <c r="I42" t="n">
-        <v>0.3235805049574504</v>
+        <v>0.3235805049438804</v>
       </c>
       <c r="J42" t="n">
-        <v>0.01067227249555984</v>
+        <v>0.01067227248644411</v>
       </c>
       <c r="K42" t="n">
-        <v>0.3170323710220794</v>
+        <v>0.2509391170687325</v>
       </c>
       <c r="L42" t="n">
-        <v>0.3993080830134812</v>
+        <v>0.3540760181826904</v>
       </c>
       <c r="M42" t="n">
         <v>0</v>
@@ -4878,16 +4878,16 @@
         <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>4.517983722179811</v>
+        <v>4.41672374136586</v>
       </c>
       <c r="P42" t="n">
-        <v>4.483687791166234</v>
+        <v>4.454828376642536</v>
       </c>
       <c r="Q42" t="n">
-        <v>0.9576255058915635</v>
+        <v>0.9562274707647596</v>
       </c>
       <c r="R42" t="n">
-        <v>0.01363174979733731</v>
+        <v>0.01385479690299464</v>
       </c>
       <c r="S42" t="inlineStr"/>
       <c r="T42" t="inlineStr"/>
@@ -4897,31 +4897,31 @@
       <c r="X42" t="inlineStr"/>
       <c r="Y42" t="inlineStr"/>
       <c r="Z42" t="n">
-        <v>0.8251301097521397</v>
+        <v>0.8171857883461777</v>
       </c>
       <c r="AA42" t="n">
-        <v>0.02294825850524475</v>
+        <v>0.02346373751795033</v>
       </c>
       <c r="AB42" t="inlineStr"/>
       <c r="AC42" t="n">
-        <v>0.9707053533915105</v>
+        <v>0.9242271168961089</v>
       </c>
       <c r="AD42" t="n">
-        <v>0.0009147965762054967</v>
+        <v>0.001471252808635844</v>
       </c>
       <c r="AE42" t="inlineStr"/>
       <c r="AF42" t="n">
-        <v>0.6837167814146191</v>
+        <v>0.6825680577083362</v>
       </c>
       <c r="AG42" t="n">
-        <v>0.01641364939248493</v>
+        <v>0.01644342913674678</v>
       </c>
       <c r="AH42" t="inlineStr"/>
       <c r="AI42" t="n">
-        <v>0.9912451388612975</v>
+        <v>0.9908936329892041</v>
       </c>
       <c r="AJ42" t="n">
-        <v>0.002893550889321847</v>
+        <v>0.002951066991320317</v>
       </c>
       <c r="AK42" t="inlineStr"/>
       <c r="AL42" t="inlineStr"/>
@@ -4953,43 +4953,43 @@
         <v>40.1</v>
       </c>
       <c r="F43" t="n">
-        <v>0.5997176448026437</v>
+        <v>0.5997176446896944</v>
       </c>
       <c r="G43" t="n">
         <v>0.0791671614614258</v>
       </c>
       <c r="H43" t="n">
-        <v>0.2378772798847145</v>
+        <v>0.2378772801295146</v>
       </c>
       <c r="I43" t="n">
-        <v>0.05923193023736853</v>
+        <v>0.05923193014095748</v>
       </c>
       <c r="J43" t="n">
-        <v>0.0240059836138475</v>
+        <v>0.02400598357840774</v>
       </c>
       <c r="K43" t="n">
-        <v>0.2387871798140294</v>
+        <v>0.184253646780577</v>
       </c>
       <c r="L43" t="n">
-        <v>0.3353014420366665</v>
+        <v>0.2869418250228646</v>
       </c>
       <c r="M43" t="n">
-        <v>0.3126694229390591</v>
+        <v>0.3532149045753625</v>
       </c>
       <c r="N43" t="n">
-        <v>0.03893489566485876</v>
+        <v>0.03100133965093598</v>
       </c>
       <c r="O43" t="n">
-        <v>3.927442132088704</v>
+        <v>3.92087543992489</v>
       </c>
       <c r="P43" t="n">
-        <v>4.243780671119279</v>
+        <v>4.228635345665029</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.9475162360891128</v>
+        <v>0.9552468486375951</v>
       </c>
       <c r="R43" t="n">
-        <v>0.0139979237253551</v>
+        <v>0.01292596415418981</v>
       </c>
       <c r="S43" t="inlineStr"/>
       <c r="T43" t="inlineStr"/>
@@ -4999,38 +4999,38 @@
       <c r="X43" t="inlineStr"/>
       <c r="Y43" t="inlineStr"/>
       <c r="Z43" t="n">
-        <v>0.9038189645539311</v>
+        <v>0.9257637682881944</v>
       </c>
       <c r="AA43" t="n">
-        <v>0.02667158626857022</v>
+        <v>0.02343214687050422</v>
       </c>
       <c r="AB43" t="inlineStr"/>
       <c r="AC43" t="n">
-        <v>0.7161858144185551</v>
+        <v>0.8161771423810793</v>
       </c>
       <c r="AD43" t="n">
-        <v>0.002515940630695684</v>
+        <v>0.002024804493910288</v>
       </c>
       <c r="AE43" t="inlineStr"/>
       <c r="AF43" t="n">
-        <v>0.7417346933952286</v>
+        <v>0.7204522607259407</v>
       </c>
       <c r="AG43" t="n">
-        <v>0.01610507436084752</v>
+        <v>0.01675551157897956</v>
       </c>
       <c r="AH43" t="inlineStr"/>
       <c r="AI43" t="n">
-        <v>0.9267067145085874</v>
+        <v>0.9663900832833219</v>
       </c>
       <c r="AJ43" t="n">
-        <v>0.001517631198841486</v>
+        <v>0.001027703578826013</v>
       </c>
       <c r="AK43" t="inlineStr"/>
       <c r="AL43" t="n">
-        <v>0.9791523323083495</v>
+        <v>0.9725154461952552</v>
       </c>
       <c r="AM43" t="n">
-        <v>0.0005738006110159018</v>
+        <v>0.0006588349249318123</v>
       </c>
       <c r="AN43" t="inlineStr"/>
     </row>
@@ -5057,25 +5057,25 @@
         <v>25.2</v>
       </c>
       <c r="F44" t="n">
-        <v>0.3587984910438237</v>
+        <v>0.3587984911488203</v>
       </c>
       <c r="G44" t="n">
         <v>0.1259763164525069</v>
       </c>
       <c r="H44" t="n">
-        <v>0.2964643700107539</v>
+        <v>0.2964643700757857</v>
       </c>
       <c r="I44" t="n">
-        <v>0.1968371786437586</v>
+        <v>0.1968371786061268</v>
       </c>
       <c r="J44" t="n">
-        <v>0.02192364384915694</v>
+        <v>0.02192364371676016</v>
       </c>
       <c r="K44" t="n">
-        <v>0.1743546614482898</v>
+        <v>0.1161247165757327</v>
       </c>
       <c r="L44" t="n">
-        <v>0.3607161911403574</v>
+        <v>0.2747297028918776</v>
       </c>
       <c r="M44" t="n">
         <v>0</v>
@@ -5084,16 +5084,16 @@
         <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>4.252007996567885</v>
+        <v>4.226110669456893</v>
       </c>
       <c r="P44" t="n">
-        <v>4.379876703707501</v>
+        <v>4.359820668211799</v>
       </c>
       <c r="Q44" t="n">
-        <v>0.9322289901765384</v>
+        <v>0.9311393328987272</v>
       </c>
       <c r="R44" t="n">
-        <v>0.00886693672513535</v>
+        <v>0.008937936067054061</v>
       </c>
       <c r="S44" t="inlineStr"/>
       <c r="T44" t="inlineStr"/>
@@ -5103,38 +5103,38 @@
       <c r="X44" t="inlineStr"/>
       <c r="Y44" t="inlineStr"/>
       <c r="Z44" t="n">
-        <v>0.9118343741510551</v>
+        <v>0.9172164971207226</v>
       </c>
       <c r="AA44" t="n">
-        <v>0.01331514308618879</v>
+        <v>0.0129023283540272</v>
       </c>
       <c r="AB44" t="inlineStr"/>
       <c r="AC44" t="n">
-        <v>0.7629989410251768</v>
+        <v>0.7922042521305956</v>
       </c>
       <c r="AD44" t="n">
-        <v>0.005399165764861191</v>
+        <v>0.005055566719559172</v>
       </c>
       <c r="AE44" t="inlineStr"/>
       <c r="AF44" t="n">
-        <v>0.9073004518172708</v>
+        <v>0.8919406831134686</v>
       </c>
       <c r="AG44" t="n">
-        <v>0.01064883496157211</v>
+        <v>0.0114972611626813</v>
       </c>
       <c r="AH44" t="inlineStr"/>
       <c r="AI44" t="n">
-        <v>0.8476536494680851</v>
+        <v>0.8437722109036985</v>
       </c>
       <c r="AJ44" t="n">
-        <v>0.008479320456552345</v>
+        <v>0.008586657968263406</v>
       </c>
       <c r="AK44" t="inlineStr"/>
       <c r="AL44" t="n">
-        <v>0.6941211503297948</v>
+        <v>0.6685500910030241</v>
       </c>
       <c r="AM44" t="n">
-        <v>0.001171429311538728</v>
+        <v>0.001219411569503721</v>
       </c>
       <c r="AN44" t="inlineStr"/>
     </row>
@@ -5161,25 +5161,25 @@
         <v>20</v>
       </c>
       <c r="F45" t="n">
-        <v>0.4805050132618147</v>
+        <v>0.4805050130472089</v>
       </c>
       <c r="G45" t="n">
         <v>0.1587301587301587</v>
       </c>
       <c r="H45" t="n">
-        <v>0.1510431451475349</v>
+        <v>0.1510431452397918</v>
       </c>
       <c r="I45" t="n">
-        <v>0.1848438942219129</v>
+        <v>0.1848438943574318</v>
       </c>
       <c r="J45" t="n">
-        <v>0.02487778863857871</v>
+        <v>0.02487778862540869</v>
       </c>
       <c r="K45" t="n">
-        <v>0.3961005288343256</v>
+        <v>0.3561715337841546</v>
       </c>
       <c r="L45" t="n">
-        <v>0.2489886367685431</v>
+        <v>0.4596161945265416</v>
       </c>
       <c r="M45" t="n">
         <v>0</v>
@@ -5188,16 +5188,16 @@
         <v>0</v>
       </c>
       <c r="O45" t="n">
-        <v>4.214350986480778</v>
+        <v>4.204683775347685</v>
       </c>
       <c r="P45" t="n">
-        <v>4.320122892021073</v>
+        <v>4.422751219522892</v>
       </c>
       <c r="Q45" t="n">
-        <v>0.9702313440706339</v>
+        <v>0.9710823779105939</v>
       </c>
       <c r="R45" t="n">
-        <v>0.008426354157252566</v>
+        <v>0.008305033412205348</v>
       </c>
       <c r="S45" t="inlineStr"/>
       <c r="T45" t="inlineStr"/>
@@ -5207,38 +5207,38 @@
       <c r="X45" t="inlineStr"/>
       <c r="Y45" t="inlineStr"/>
       <c r="Z45" t="n">
-        <v>0.9784347599200411</v>
+        <v>0.978201337151219</v>
       </c>
       <c r="AA45" t="n">
-        <v>0.01256046048187576</v>
+        <v>0.01262825490661887</v>
       </c>
       <c r="AB45" t="inlineStr"/>
       <c r="AC45" t="n">
-        <v>0.9263908096369194</v>
+        <v>0.9264574993529273</v>
       </c>
       <c r="AD45" t="n">
-        <v>0.007115518876935951</v>
+        <v>0.007112294826646373</v>
       </c>
       <c r="AE45" t="inlineStr"/>
       <c r="AF45" t="n">
-        <v>0.8721738592106956</v>
+        <v>0.8787454696958589</v>
       </c>
       <c r="AG45" t="n">
-        <v>0.008496248798279732</v>
+        <v>0.008274968897209712</v>
       </c>
       <c r="AH45" t="inlineStr"/>
       <c r="AI45" t="n">
-        <v>0.9200557691923775</v>
+        <v>0.9287358778670444</v>
       </c>
       <c r="AJ45" t="n">
-        <v>0.008604497120791905</v>
+        <v>0.008123952952602731</v>
       </c>
       <c r="AK45" t="inlineStr"/>
       <c r="AL45" t="n">
-        <v>0.9793660680563808</v>
+        <v>0.9825409339116216</v>
       </c>
       <c r="AM45" t="n">
-        <v>0.0006307385896372336</v>
+        <v>0.0005801882243384206</v>
       </c>
       <c r="AN45" t="inlineStr"/>
     </row>
@@ -5265,25 +5265,25 @@
         <v>13.8</v>
       </c>
       <c r="F46" t="n">
-        <v>0.4123104193140011</v>
+        <v>0.4123104194730447</v>
       </c>
       <c r="G46" t="n">
         <v>0.2300437083045778</v>
       </c>
       <c r="H46" t="n">
-        <v>0.09500900007204896</v>
+        <v>0.09500899989902098</v>
       </c>
       <c r="I46" t="n">
-        <v>0.2190898484594311</v>
+        <v>0.2190898485295714</v>
       </c>
       <c r="J46" t="n">
-        <v>0.04354702384994095</v>
+        <v>0.04354702379378513</v>
       </c>
       <c r="K46" t="n">
-        <v>0.4197523519087317</v>
+        <v>0.4073750266228692</v>
       </c>
       <c r="L46" t="n">
-        <v>0.3538478146508492</v>
+        <v>0.4877311501843291</v>
       </c>
       <c r="M46" t="n">
         <v>0</v>
@@ -5292,16 +5292,16 @@
         <v>0</v>
       </c>
       <c r="O46" t="n">
-        <v>3.774562388265622</v>
+        <v>3.814004562068153</v>
       </c>
       <c r="P46" t="n">
-        <v>4.469631474021861</v>
+        <v>4.464592034099284</v>
       </c>
       <c r="Q46" t="n">
-        <v>0.9691700565078264</v>
+        <v>0.9751493750985125</v>
       </c>
       <c r="R46" t="n">
-        <v>0.008371678975015451</v>
+        <v>0.007516139969041939</v>
       </c>
       <c r="S46" t="inlineStr"/>
       <c r="T46" t="inlineStr"/>
@@ -5311,38 +5311,38 @@
       <c r="X46" t="inlineStr"/>
       <c r="Y46" t="inlineStr"/>
       <c r="Z46" t="n">
-        <v>0.9852529476931888</v>
+        <v>0.9876828141809345</v>
       </c>
       <c r="AA46" t="n">
-        <v>0.009364100463556499</v>
+        <v>0.008557939283508819</v>
       </c>
       <c r="AB46" t="inlineStr"/>
       <c r="AC46" t="n">
-        <v>0.9337676750333243</v>
+        <v>0.9377054773714882</v>
       </c>
       <c r="AD46" t="n">
-        <v>0.009552512080250805</v>
+        <v>0.009264191556377126</v>
       </c>
       <c r="AE46" t="inlineStr"/>
       <c r="AF46" t="n">
-        <v>0.9846233103721167</v>
+        <v>0.9877265388188802</v>
       </c>
       <c r="AG46" t="n">
-        <v>0.00202983142116043</v>
+        <v>0.001813477087712048</v>
       </c>
       <c r="AH46" t="inlineStr"/>
       <c r="AI46" t="n">
-        <v>0.8483107869021425</v>
+        <v>0.8912778190528515</v>
       </c>
       <c r="AJ46" t="n">
-        <v>0.01289745800054248</v>
+        <v>0.01091907505098744</v>
       </c>
       <c r="AK46" t="inlineStr"/>
       <c r="AL46" t="n">
-        <v>0.9862790930877983</v>
+        <v>0.9881586569867821</v>
       </c>
       <c r="AM46" t="n">
-        <v>0.001011702176816321</v>
+        <v>0.0009398569470527479</v>
       </c>
       <c r="AN46" t="inlineStr"/>
     </row>
@@ -5369,25 +5369,25 @@
         <v>19</v>
       </c>
       <c r="F47" t="n">
-        <v>0.4235443992070436</v>
+        <v>0.4235443991299785</v>
       </c>
       <c r="G47" t="n">
         <v>0.1670843776106934</v>
       </c>
       <c r="H47" t="n">
-        <v>0.2433419961172016</v>
+        <v>0.2433419961113411</v>
       </c>
       <c r="I47" t="n">
-        <v>0.1505472905220324</v>
+        <v>0.1505472906218897</v>
       </c>
       <c r="J47" t="n">
-        <v>0.01548193654302897</v>
+        <v>0.01548193652609739</v>
       </c>
       <c r="K47" t="n">
-        <v>0.2493695583752376</v>
+        <v>0.1887746212355711</v>
       </c>
       <c r="L47" t="n">
-        <v>0.334323690586066</v>
+        <v>0.2874926525482054</v>
       </c>
       <c r="M47" t="n">
         <v>0</v>
@@ -5396,16 +5396,16 @@
         <v>0</v>
       </c>
       <c r="O47" t="n">
-        <v>4.220558446554917</v>
+        <v>4.185310192182019</v>
       </c>
       <c r="P47" t="n">
-        <v>4.34135409092813</v>
+        <v>4.328274446329779</v>
       </c>
       <c r="Q47" t="n">
-        <v>0.9415799702410498</v>
+        <v>0.9420537386193443</v>
       </c>
       <c r="R47" t="n">
-        <v>0.009083243677576116</v>
+        <v>0.009046337550908161</v>
       </c>
       <c r="S47" t="inlineStr"/>
       <c r="T47" t="inlineStr"/>
@@ -5415,38 +5415,38 @@
       <c r="X47" t="inlineStr"/>
       <c r="Y47" t="inlineStr"/>
       <c r="Z47" t="n">
-        <v>0.9337982099239828</v>
+        <v>0.9396134589639014</v>
       </c>
       <c r="AA47" t="n">
-        <v>0.01417674747859337</v>
+        <v>0.01353978643124449</v>
       </c>
       <c r="AB47" t="inlineStr"/>
       <c r="AC47" t="n">
-        <v>0.812072719846809</v>
+        <v>0.8635723001645395</v>
       </c>
       <c r="AD47" t="n">
-        <v>0.006773450144281096</v>
+        <v>0.005771202364270337</v>
       </c>
       <c r="AE47" t="inlineStr"/>
       <c r="AF47" t="n">
-        <v>0.8225035807354626</v>
+        <v>0.7897414159202871</v>
       </c>
       <c r="AG47" t="n">
-        <v>0.01256175254053157</v>
+        <v>0.01367200798482611</v>
       </c>
       <c r="AH47" t="inlineStr"/>
       <c r="AI47" t="n">
-        <v>0.9685788529767632</v>
+        <v>0.9777742557730912</v>
       </c>
       <c r="AJ47" t="n">
-        <v>0.002748987619929098</v>
+        <v>0.002312011144988303</v>
       </c>
       <c r="AK47" t="inlineStr"/>
       <c r="AL47" t="n">
-        <v>0.9144623201650787</v>
+        <v>0.923475328011221</v>
       </c>
       <c r="AM47" t="n">
-        <v>0.0005587689846373318</v>
+        <v>0.0005285113244619222</v>
       </c>
       <c r="AN47" t="inlineStr"/>
     </row>
@@ -5473,25 +5473,25 @@
         <v>26.5</v>
       </c>
       <c r="F48" t="n">
-        <v>0.4466462867107708</v>
+        <v>0.4466462865765082</v>
       </c>
       <c r="G48" t="n">
         <v>0.1197963462114405</v>
       </c>
       <c r="H48" t="n">
-        <v>0.3318502634836513</v>
+        <v>0.3318502636697235</v>
       </c>
       <c r="I48" t="n">
-        <v>0.06116662707319055</v>
+        <v>0.06116662702741293</v>
       </c>
       <c r="J48" t="n">
-        <v>0.04054047652094685</v>
+        <v>0.04054047651491494</v>
       </c>
       <c r="K48" t="n">
-        <v>0.109062118721277</v>
+        <v>0.06767257822732965</v>
       </c>
       <c r="L48" t="n">
-        <v>0.4819694991065029</v>
+        <v>0.3438967560587061</v>
       </c>
       <c r="M48" t="n">
         <v>0</v>
@@ -5500,16 +5500,16 @@
         <v>0</v>
       </c>
       <c r="O48" t="n">
-        <v>3.575232101365941</v>
+        <v>3.655465587484483</v>
       </c>
       <c r="P48" t="n">
-        <v>4.350282899258956</v>
+        <v>4.37384633338082</v>
       </c>
       <c r="Q48" t="n">
-        <v>0.9799807072945712</v>
+        <v>0.9681890667047797</v>
       </c>
       <c r="R48" t="n">
-        <v>0.007295458123566167</v>
+        <v>0.009196369441592829</v>
       </c>
       <c r="S48" t="inlineStr"/>
       <c r="T48" t="inlineStr"/>
@@ -5519,38 +5519,38 @@
       <c r="X48" t="inlineStr"/>
       <c r="Y48" t="inlineStr"/>
       <c r="Z48" t="n">
-        <v>0.9670514601319901</v>
+        <v>0.9617958914675412</v>
       </c>
       <c r="AA48" t="n">
-        <v>0.01327282333452833</v>
+        <v>0.01429223874010929</v>
       </c>
       <c r="AB48" t="inlineStr"/>
       <c r="AC48" t="n">
-        <v>0.8511299313845332</v>
+        <v>0.8111865587639752</v>
       </c>
       <c r="AD48" t="n">
-        <v>0.006517710128062508</v>
+        <v>0.007340198439256735</v>
       </c>
       <c r="AE48" t="inlineStr"/>
       <c r="AF48" t="n">
-        <v>0.9879783933259402</v>
+        <v>0.9520929030577686</v>
       </c>
       <c r="AG48" t="n">
-        <v>0.006358306232025789</v>
+        <v>0.01269287815253036</v>
       </c>
       <c r="AH48" t="inlineStr"/>
       <c r="AI48" t="n">
-        <v>0.8971030179730674</v>
+        <v>0.9475153302757008</v>
       </c>
       <c r="AJ48" t="n">
-        <v>0.002650808591286444</v>
+        <v>0.001893186003532806</v>
       </c>
       <c r="AK48" t="inlineStr"/>
       <c r="AL48" t="n">
-        <v>0.9997445041281109</v>
+        <v>0.9995639084097956</v>
       </c>
       <c r="AM48" t="n">
-        <v>0.0001237628887575433</v>
+        <v>0.0001616915594861161</v>
       </c>
       <c r="AN48" t="inlineStr"/>
     </row>
@@ -5577,43 +5577,43 @@
         <v>27.2</v>
       </c>
       <c r="F49" t="n">
-        <v>0.4784766675558373</v>
+        <v>0.4784766676196412</v>
       </c>
       <c r="G49" t="n">
         <v>0.1167133520074696</v>
       </c>
       <c r="H49" t="n">
-        <v>0.1617722833471003</v>
+        <v>0.1617722832354314</v>
       </c>
       <c r="I49" t="n">
-        <v>0.2200624129180908</v>
+        <v>0.2200624129775048</v>
       </c>
       <c r="J49" t="n">
-        <v>0.02297528417150188</v>
+        <v>0.0229752841599529</v>
       </c>
       <c r="K49" t="n">
-        <v>0.3626999688036405</v>
+        <v>0.3236571036150679</v>
       </c>
       <c r="L49" t="n">
-        <v>0.4627744792868939</v>
+        <v>0.4680219017957259</v>
       </c>
       <c r="M49" t="n">
-        <v>0.005612064057232025</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>0.0001122412811446405</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
-        <v>4.039369874984286</v>
+        <v>4.059016345835413</v>
       </c>
       <c r="P49" t="n">
-        <v>4.387228406735362</v>
+        <v>4.380739583085585</v>
       </c>
       <c r="Q49" t="n">
-        <v>0.9269361823572662</v>
+        <v>0.9306133851363765</v>
       </c>
       <c r="R49" t="n">
-        <v>0.01281228109283159</v>
+        <v>0.01248570667776224</v>
       </c>
       <c r="S49" t="inlineStr"/>
       <c r="T49" t="inlineStr"/>
@@ -5623,38 +5623,38 @@
       <c r="X49" t="inlineStr"/>
       <c r="Y49" t="inlineStr"/>
       <c r="Z49" t="n">
-        <v>0.9261847630939968</v>
+        <v>0.924569180178753</v>
       </c>
       <c r="AA49" t="n">
-        <v>0.0183263436531129</v>
+        <v>0.0185258110871032</v>
       </c>
       <c r="AB49" t="inlineStr"/>
       <c r="AC49" t="n">
-        <v>0.939138751826249</v>
+        <v>0.9409052969664844</v>
       </c>
       <c r="AD49" t="n">
-        <v>0.002365812383843992</v>
+        <v>0.002331224778908566</v>
       </c>
       <c r="AE49" t="inlineStr"/>
       <c r="AF49" t="n">
-        <v>0.446330723848371</v>
+        <v>0.469391443993011</v>
       </c>
       <c r="AG49" t="n">
-        <v>0.01373726590074302</v>
+        <v>0.01344813982868332</v>
       </c>
       <c r="AH49" t="inlineStr"/>
       <c r="AI49" t="n">
-        <v>0.4015159472934428</v>
+        <v>0.4854913243846498</v>
       </c>
       <c r="AJ49" t="n">
-        <v>0.01699755332717078</v>
+        <v>0.01576000940614472</v>
       </c>
       <c r="AK49" t="inlineStr"/>
       <c r="AL49" t="n">
-        <v>0.8732485910420119</v>
+        <v>0.8805764955958068</v>
       </c>
       <c r="AM49" t="n">
-        <v>0.001300577004016838</v>
+        <v>0.001262422067757764</v>
       </c>
       <c r="AN49" t="inlineStr"/>
     </row>
@@ -5681,25 +5681,25 @@
         <v>22.6</v>
       </c>
       <c r="F50" t="n">
-        <v>0.4707222729765161</v>
+        <v>0.4707222730832482</v>
       </c>
       <c r="G50" t="n">
         <v>0.1404691670178395</v>
       </c>
       <c r="H50" t="n">
-        <v>0.06718571998428063</v>
+        <v>0.06718571980350242</v>
       </c>
       <c r="I50" t="n">
-        <v>0.2979720652205344</v>
+        <v>0.2979720652617544</v>
       </c>
       <c r="J50" t="n">
-        <v>0.02365077480082941</v>
+        <v>0.02365077483365554</v>
       </c>
       <c r="K50" t="n">
-        <v>0.509975097271933</v>
+        <v>0.5001414823415646</v>
       </c>
       <c r="L50" t="n">
-        <v>0.5505848201746671</v>
+        <v>0.5571628184286667</v>
       </c>
       <c r="M50" t="n">
         <v>0</v>
@@ -5708,16 +5708,16 @@
         <v>0</v>
       </c>
       <c r="O50" t="n">
-        <v>4.291212719785222</v>
+        <v>4.295513413439029</v>
       </c>
       <c r="P50" t="n">
-        <v>4.500481878863585</v>
+        <v>4.454303535379676</v>
       </c>
       <c r="Q50" t="n">
-        <v>0.9643131386676767</v>
+        <v>0.9648334216972402</v>
       </c>
       <c r="R50" t="n">
-        <v>0.01009684583614506</v>
+        <v>0.01002297404035096</v>
       </c>
       <c r="S50" t="inlineStr"/>
       <c r="T50" t="inlineStr"/>
@@ -5727,31 +5727,31 @@
       <c r="X50" t="inlineStr"/>
       <c r="Y50" t="inlineStr"/>
       <c r="Z50" t="n">
-        <v>0.9847225923342044</v>
+        <v>0.984532493118873</v>
       </c>
       <c r="AA50" t="n">
-        <v>0.01039843948697537</v>
+        <v>0.01046293419893906</v>
       </c>
       <c r="AB50" t="inlineStr"/>
       <c r="AC50" t="n">
-        <v>0.9360197628461002</v>
+        <v>0.9377681166232442</v>
       </c>
       <c r="AD50" t="n">
-        <v>0.005389682398801431</v>
+        <v>0.005315531835310413</v>
       </c>
       <c r="AE50" t="inlineStr"/>
       <c r="AF50" t="n">
-        <v>0.9495182886766423</v>
+        <v>0.9502984722141891</v>
       </c>
       <c r="AG50" t="n">
-        <v>0.002295511352826723</v>
+        <v>0.002277703968291541</v>
       </c>
       <c r="AH50" t="inlineStr"/>
       <c r="AI50" t="n">
-        <v>0.8194325120806389</v>
+        <v>0.8236463685043796</v>
       </c>
       <c r="AJ50" t="n">
-        <v>0.01705362614871232</v>
+        <v>0.01685346345701342</v>
       </c>
       <c r="AK50" t="inlineStr"/>
       <c r="AL50" t="inlineStr"/>
@@ -5783,25 +5783,25 @@
         <v>12.2</v>
       </c>
       <c r="F51" t="n">
-        <v>0.4132915616414226</v>
+        <v>0.4132915619983448</v>
       </c>
       <c r="G51" t="n">
         <v>0.2602133749674733</v>
       </c>
       <c r="H51" t="n">
-        <v>0.02750138666645612</v>
+        <v>0.02750138682641973</v>
       </c>
       <c r="I51" t="n">
-        <v>0.2472592619614906</v>
+        <v>0.247259261508163</v>
       </c>
       <c r="J51" t="n">
-        <v>0.05173441476315732</v>
+        <v>0.05173441469959904</v>
       </c>
       <c r="K51" t="n">
-        <v>0.4767246818589526</v>
+        <v>0.4746629412539786</v>
       </c>
       <c r="L51" t="n">
-        <v>0.5516625159727202</v>
+        <v>0.5579799924711972</v>
       </c>
       <c r="M51" t="n">
         <v>0</v>
@@ -5810,16 +5810,16 @@
         <v>0</v>
       </c>
       <c r="O51" t="n">
-        <v>3.852084868275818</v>
+        <v>3.848875145161648</v>
       </c>
       <c r="P51" t="n">
-        <v>4.425021504494057</v>
+        <v>4.425729460286711</v>
       </c>
       <c r="Q51" t="n">
-        <v>0.928518635689824</v>
+        <v>0.9284225402021243</v>
       </c>
       <c r="R51" t="n">
-        <v>0.01073767156444199</v>
+        <v>0.01074488669937242</v>
       </c>
       <c r="S51" t="inlineStr"/>
       <c r="T51" t="inlineStr"/>
@@ -5829,38 +5829,38 @@
       <c r="X51" t="inlineStr"/>
       <c r="Y51" t="inlineStr"/>
       <c r="Z51" t="n">
-        <v>0.9298020078864232</v>
+        <v>0.9294129968826711</v>
       </c>
       <c r="AA51" t="n">
-        <v>0.01566393252059432</v>
+        <v>0.01570727440097024</v>
       </c>
       <c r="AB51" t="inlineStr"/>
       <c r="AC51" t="n">
-        <v>0.7959709183259848</v>
+        <v>0.7965577171290564</v>
       </c>
       <c r="AD51" t="n">
-        <v>0.01442274227687904</v>
+        <v>0.01440198704484779</v>
       </c>
       <c r="AE51" t="inlineStr"/>
       <c r="AF51" t="n">
-        <v>-0.8079856495807261</v>
+        <v>-0.8051505386899462</v>
       </c>
       <c r="AG51" t="n">
-        <v>0.003373134653022638</v>
+        <v>0.003370488914467463</v>
       </c>
       <c r="AH51" t="inlineStr"/>
       <c r="AI51" t="n">
-        <v>0.8918970998225999</v>
+        <v>0.8918658259067099</v>
       </c>
       <c r="AJ51" t="n">
-        <v>0.01055632191053338</v>
+        <v>0.01055784873589891</v>
       </c>
       <c r="AK51" t="inlineStr"/>
       <c r="AL51" t="n">
-        <v>0.9956288507792258</v>
+        <v>0.9956408271332348</v>
       </c>
       <c r="AM51" t="n">
-        <v>0.0005474547176660709</v>
+        <v>0.0005467042269295646</v>
       </c>
       <c r="AN51" t="inlineStr"/>
     </row>
@@ -5887,25 +5887,25 @@
         <v>28.5</v>
       </c>
       <c r="F52" t="n">
-        <v>0.4153806106757402</v>
+        <v>0.4153806106021484</v>
       </c>
       <c r="G52" t="n">
         <v>0.1113895850737956</v>
       </c>
       <c r="H52" t="n">
-        <v>0.3106906626687218</v>
+        <v>0.3106906628036006</v>
       </c>
       <c r="I52" t="n">
-        <v>0.1579071580203451</v>
+        <v>0.1579071579734052</v>
       </c>
       <c r="J52" t="n">
-        <v>0.004631983561397277</v>
+        <v>0.004631983547050241</v>
       </c>
       <c r="K52" t="n">
-        <v>0.1577619308753721</v>
+        <v>0.101465410040746</v>
       </c>
       <c r="L52" t="n">
-        <v>0.2332576237530504</v>
+        <v>0.1831499130629796</v>
       </c>
       <c r="M52" t="n">
         <v>0</v>
@@ -5914,16 +5914,16 @@
         <v>0</v>
       </c>
       <c r="O52" t="n">
-        <v>4.292754697312242</v>
+        <v>4.284078512333842</v>
       </c>
       <c r="P52" t="n">
-        <v>4.285138203429157</v>
+        <v>4.269826538405476</v>
       </c>
       <c r="Q52" t="n">
-        <v>0.9438578508547878</v>
+        <v>0.9409099603363811</v>
       </c>
       <c r="R52" t="n">
-        <v>0.01144189036378144</v>
+        <v>0.01173844058261254</v>
       </c>
       <c r="S52" t="inlineStr"/>
       <c r="T52" t="inlineStr"/>
@@ -5933,38 +5933,38 @@
       <c r="X52" t="inlineStr"/>
       <c r="Y52" t="inlineStr"/>
       <c r="Z52" t="n">
-        <v>0.9213683409175074</v>
+        <v>0.9170010657064158</v>
       </c>
       <c r="AA52" t="n">
-        <v>0.01284086482256702</v>
+        <v>0.01319264306379424</v>
       </c>
       <c r="AB52" t="inlineStr"/>
       <c r="AC52" t="n">
-        <v>0.8528322432347442</v>
+        <v>0.8521207495766849</v>
       </c>
       <c r="AD52" t="n">
-        <v>0.002713810080924104</v>
+        <v>0.002720362231367404</v>
       </c>
       <c r="AE52" t="inlineStr"/>
       <c r="AF52" t="n">
-        <v>0.7649466021748099</v>
+        <v>0.7508068405966803</v>
       </c>
       <c r="AG52" t="n">
-        <v>0.01740939618453367</v>
+        <v>0.01792538532876083</v>
       </c>
       <c r="AH52" t="inlineStr"/>
       <c r="AI52" t="n">
-        <v>0.3437539527154617</v>
+        <v>0.3183274020097735</v>
       </c>
       <c r="AJ52" t="n">
-        <v>0.01335547456094254</v>
+        <v>0.01361174778928569</v>
       </c>
       <c r="AK52" t="inlineStr"/>
       <c r="AL52" t="n">
-        <v>0.05764133052217757</v>
+        <v>0.02139274129615065</v>
       </c>
       <c r="AM52" t="n">
-        <v>0.0009359084779877782</v>
+        <v>0.0009537388612291783</v>
       </c>
       <c r="AN52" t="inlineStr"/>
     </row>
@@ -5991,25 +5991,25 @@
         <v>26.8</v>
       </c>
       <c r="F53" t="n">
-        <v>0.4510893860666219</v>
+        <v>0.4510893861537268</v>
       </c>
       <c r="G53" t="n">
         <v>0.1184553423359393</v>
       </c>
       <c r="H53" t="n">
-        <v>0.200863297038614</v>
+        <v>0.2008632968133135</v>
       </c>
       <c r="I53" t="n">
-        <v>0.2264019040843809</v>
+        <v>0.2264019042000988</v>
       </c>
       <c r="J53" t="n">
-        <v>0.00319007047444387</v>
+        <v>0.003190070496921492</v>
       </c>
       <c r="K53" t="n">
-        <v>0.3306984100273074</v>
+        <v>0.2727378027638814</v>
       </c>
       <c r="L53" t="n">
-        <v>0.2222187220843617</v>
+        <v>0.2726287635947208</v>
       </c>
       <c r="M53" t="n">
         <v>0</v>
@@ -6018,16 +6018,16 @@
         <v>0</v>
       </c>
       <c r="O53" t="n">
-        <v>4.388506524434447</v>
+        <v>4.35109846563273</v>
       </c>
       <c r="P53" t="n">
-        <v>4.433029285114089</v>
+        <v>4.434421493170414</v>
       </c>
       <c r="Q53" t="n">
-        <v>0.987816836719875</v>
+        <v>0.9863442294331061</v>
       </c>
       <c r="R53" t="n">
-        <v>0.004745620692211202</v>
+        <v>0.005024248325364421</v>
       </c>
       <c r="S53" t="inlineStr"/>
       <c r="T53" t="inlineStr"/>
@@ -6037,38 +6037,38 @@
       <c r="X53" t="inlineStr"/>
       <c r="Y53" t="inlineStr"/>
       <c r="Z53" t="n">
-        <v>0.9846901797282983</v>
+        <v>0.9775572457437087</v>
       </c>
       <c r="AA53" t="n">
-        <v>0.007170994494039955</v>
+        <v>0.008682252661680974</v>
       </c>
       <c r="AB53" t="inlineStr"/>
       <c r="AC53" t="n">
-        <v>0.9248878354650139</v>
+        <v>0.9371056469774383</v>
       </c>
       <c r="AD53" t="n">
-        <v>0.002813421705909762</v>
+        <v>0.002574456286801667</v>
       </c>
       <c r="AE53" t="inlineStr"/>
       <c r="AF53" t="n">
-        <v>0.9762568144864854</v>
+        <v>0.9718954043873925</v>
       </c>
       <c r="AG53" t="n">
-        <v>0.003804235567470246</v>
+        <v>0.004138915678627068</v>
       </c>
       <c r="AH53" t="inlineStr"/>
       <c r="AI53" t="n">
-        <v>0.9608967543252724</v>
+        <v>0.9755266950079378</v>
       </c>
       <c r="AJ53" t="n">
-        <v>0.005758634183792521</v>
+        <v>0.004555744914180935</v>
       </c>
       <c r="AK53" t="inlineStr"/>
       <c r="AL53" t="n">
-        <v>0.987966082527848</v>
+        <v>0.9332617466523701</v>
       </c>
       <c r="AM53" t="n">
-        <v>4.858242130553261e-05</v>
+        <v>0.0001144097554973275</v>
       </c>
       <c r="AN53" t="inlineStr"/>
     </row>
@@ -6095,43 +6095,43 @@
         <v>25</v>
       </c>
       <c r="F54" t="n">
-        <v>0.4286683890706328</v>
+        <v>0.4286683889482371</v>
       </c>
       <c r="G54" t="n">
         <v>0.1269841269841269</v>
       </c>
       <c r="H54" t="n">
-        <v>0.2576179527120835</v>
+        <v>0.2576179529315623</v>
       </c>
       <c r="I54" t="n">
-        <v>0.1597790966902238</v>
+        <v>0.15977909662141</v>
       </c>
       <c r="J54" t="n">
-        <v>0.02695043454293275</v>
+        <v>0.02695043451466368</v>
       </c>
       <c r="K54" t="n">
-        <v>0.2248167586008439</v>
+        <v>0.1659250005802807</v>
       </c>
       <c r="L54" t="n">
-        <v>0.430984506537004</v>
+        <v>0.3927801870465932</v>
       </c>
       <c r="M54" t="n">
-        <v>0.2193819190100099</v>
+        <v>0.1270870073275063</v>
       </c>
       <c r="N54" t="n">
-        <v>0.02193961981936665</v>
+        <v>0.009093869230698236</v>
       </c>
       <c r="O54" t="n">
-        <v>4.171678408154621</v>
+        <v>4.164746083868372</v>
       </c>
       <c r="P54" t="n">
-        <v>4.31119189240106</v>
+        <v>4.287056348317851</v>
       </c>
       <c r="Q54" t="n">
-        <v>0.9063984135132683</v>
+        <v>0.8976010392334589</v>
       </c>
       <c r="R54" t="n">
-        <v>0.01110945921302189</v>
+        <v>0.01161981165156341</v>
       </c>
       <c r="S54" t="inlineStr"/>
       <c r="T54" t="inlineStr"/>
@@ -6141,38 +6141,38 @@
       <c r="X54" t="inlineStr"/>
       <c r="Y54" t="inlineStr"/>
       <c r="Z54" t="n">
-        <v>0.8563096775048245</v>
+        <v>0.8400327947124722</v>
       </c>
       <c r="AA54" t="n">
-        <v>0.01953010729127638</v>
+        <v>0.0206066003255388</v>
       </c>
       <c r="AB54" t="inlineStr"/>
       <c r="AC54" t="n">
-        <v>0.3948439112216421</v>
+        <v>0.4157050810753069</v>
       </c>
       <c r="AD54" t="n">
-        <v>0.004486168770392495</v>
+        <v>0.004408166186969813</v>
       </c>
       <c r="AE54" t="inlineStr"/>
       <c r="AF54" t="n">
-        <v>0.8090572030202201</v>
+        <v>0.8090418116832817</v>
       </c>
       <c r="AG54" t="n">
-        <v>0.01295890327429462</v>
+        <v>0.0129594255762038</v>
       </c>
       <c r="AH54" t="inlineStr"/>
       <c r="AI54" t="n">
-        <v>0.7164313503698311</v>
+        <v>0.6222150047288706</v>
       </c>
       <c r="AJ54" t="n">
-        <v>0.006823488247889323</v>
+        <v>0.007875890952024515</v>
       </c>
       <c r="AK54" t="inlineStr"/>
       <c r="AL54" t="n">
-        <v>0.878289257520015</v>
+        <v>0.8778992372439215</v>
       </c>
       <c r="AM54" t="n">
-        <v>0.001027839015685435</v>
+        <v>0.001029484544447829</v>
       </c>
       <c r="AN54" t="inlineStr"/>
     </row>
@@ -6199,43 +6199,43 @@
         <v>29</v>
       </c>
       <c r="F55" t="n">
-        <v>0.4347068963260962</v>
+        <v>0.4347068963151978</v>
       </c>
       <c r="G55" t="n">
         <v>0.1094690749863163</v>
       </c>
       <c r="H55" t="n">
-        <v>0.2837256736143648</v>
+        <v>0.2837256736186445</v>
       </c>
       <c r="I55" t="n">
-        <v>0.1694315236798098</v>
+        <v>0.1694315237196296</v>
       </c>
       <c r="J55" t="n">
-        <v>0.00266683139341308</v>
+        <v>0.002666831360211718</v>
       </c>
       <c r="K55" t="n">
-        <v>0.2017005542879495</v>
+        <v>0.1407164034552979</v>
       </c>
       <c r="L55" t="n">
-        <v>0.4728720831123575</v>
+        <v>0.4834916116363329</v>
       </c>
       <c r="M55" t="n">
-        <v>0.3569864257382174</v>
+        <v>0.3920313773681194</v>
       </c>
       <c r="N55" t="n">
-        <v>0.05480160995698746</v>
+        <v>0.06221590103233047</v>
       </c>
       <c r="O55" t="n">
-        <v>4.462283023203961</v>
+        <v>4.488546076885461</v>
       </c>
       <c r="P55" t="n">
-        <v>4.394418543764465</v>
+        <v>4.395236478214958</v>
       </c>
       <c r="Q55" t="n">
-        <v>0.8348241177272965</v>
+        <v>0.8156290030162563</v>
       </c>
       <c r="R55" t="n">
-        <v>0.01638892861442154</v>
+        <v>0.01731504195003764</v>
       </c>
       <c r="S55" t="inlineStr"/>
       <c r="T55" t="inlineStr"/>
@@ -6245,38 +6245,38 @@
       <c r="X55" t="inlineStr"/>
       <c r="Y55" t="inlineStr"/>
       <c r="Z55" t="n">
-        <v>0.6578275067183574</v>
+        <v>0.6149021116815609</v>
       </c>
       <c r="AA55" t="n">
-        <v>0.02823632311576517</v>
+        <v>0.02995512693999486</v>
       </c>
       <c r="AB55" t="inlineStr"/>
       <c r="AC55" t="n">
-        <v>0.1185532815212251</v>
+        <v>0.1012501978226779</v>
       </c>
       <c r="AD55" t="n">
-        <v>0.004110738570071028</v>
+        <v>0.004150890043851633</v>
       </c>
       <c r="AE55" t="inlineStr"/>
       <c r="AF55" t="n">
-        <v>0.5124703405610749</v>
+        <v>0.4516447166185901</v>
       </c>
       <c r="AG55" t="n">
-        <v>0.02236596832072579</v>
+        <v>0.02372019204231349</v>
       </c>
       <c r="AH55" t="inlineStr"/>
       <c r="AI55" t="n">
-        <v>0.8609315862355822</v>
+        <v>0.8935977635348507</v>
       </c>
       <c r="AJ55" t="n">
-        <v>0.005326340136285111</v>
+        <v>0.004658971190932141</v>
       </c>
       <c r="AK55" t="inlineStr"/>
       <c r="AL55" t="n">
-        <v>0.9008326717535063</v>
+        <v>0.9164644411793527</v>
       </c>
       <c r="AM55" t="n">
-        <v>0.0004362943760247326</v>
+        <v>0.000400434049870008</v>
       </c>
       <c r="AN55" t="inlineStr"/>
     </row>
@@ -6303,25 +6303,25 @@
         <v>19.9</v>
       </c>
       <c r="F56" t="n">
-        <v>0.3573142119608926</v>
+        <v>0.3573142119374196</v>
       </c>
       <c r="G56" t="n">
         <v>0.1595277977187525</v>
       </c>
       <c r="H56" t="n">
-        <v>0.2647607177751945</v>
+        <v>0.2647607177672366</v>
       </c>
       <c r="I56" t="n">
-        <v>0.1794591218770647</v>
+        <v>0.179459121882217</v>
       </c>
       <c r="J56" t="n">
-        <v>0.03893815066809572</v>
+        <v>0.03893815069437438</v>
       </c>
       <c r="K56" t="n">
-        <v>0.2039298221414741</v>
+        <v>0.1460704737966806</v>
       </c>
       <c r="L56" t="n">
-        <v>0.3222654196083304</v>
+        <v>0.2351498245325966</v>
       </c>
       <c r="M56" t="n">
         <v>0</v>
@@ -6330,16 +6330,16 @@
         <v>0</v>
       </c>
       <c r="O56" t="n">
-        <v>3.981252851815452</v>
+        <v>3.92679468727763</v>
       </c>
       <c r="P56" t="n">
-        <v>4.305313728523216</v>
+        <v>4.295903185919488</v>
       </c>
       <c r="Q56" t="n">
-        <v>0.8140026743624541</v>
+        <v>0.8244306602963709</v>
       </c>
       <c r="R56" t="n">
-        <v>0.01265400181587147</v>
+        <v>0.0122941605546842</v>
       </c>
       <c r="S56" t="inlineStr"/>
       <c r="T56" t="inlineStr"/>
@@ -6349,38 +6349,38 @@
       <c r="X56" t="inlineStr"/>
       <c r="Y56" t="inlineStr"/>
       <c r="Z56" t="n">
-        <v>0.6320085494266621</v>
+        <v>0.696273836658334</v>
       </c>
       <c r="AA56" t="n">
-        <v>0.02117953657030387</v>
+        <v>0.01924148960139036</v>
       </c>
       <c r="AB56" t="inlineStr"/>
       <c r="AC56" t="n">
-        <v>-0.02810911562099561</v>
+        <v>0.14570932502376</v>
       </c>
       <c r="AD56" t="n">
-        <v>0.00888682273930924</v>
+        <v>0.008100834239050229</v>
       </c>
       <c r="AE56" t="inlineStr"/>
       <c r="AF56" t="n">
-        <v>0.6507137560021403</v>
+        <v>0.5882595173686509</v>
       </c>
       <c r="AG56" t="n">
-        <v>0.0156253701047111</v>
+        <v>0.0169649020658686</v>
       </c>
       <c r="AH56" t="inlineStr"/>
       <c r="AI56" t="n">
-        <v>0.8767529975207164</v>
+        <v>0.8641818561177234</v>
       </c>
       <c r="AJ56" t="n">
-        <v>0.005104112906601275</v>
+        <v>0.005358102107242078</v>
       </c>
       <c r="AK56" t="inlineStr"/>
       <c r="AL56" t="n">
-        <v>0.8724483612498279</v>
+        <v>0.8506402572303703</v>
       </c>
       <c r="AM56" t="n">
-        <v>0.001693004009184952</v>
+        <v>0.00183202646723182</v>
       </c>
       <c r="AN56" t="inlineStr"/>
     </row>
@@ -6407,25 +6407,25 @@
         <v>13.4</v>
       </c>
       <c r="F57" t="n">
-        <v>0.3569988198360919</v>
+        <v>0.3569988198034146</v>
       </c>
       <c r="G57" t="n">
         <v>0.2369106846718786</v>
       </c>
       <c r="H57" t="n">
-        <v>0.1636235303975117</v>
+        <v>0.1636235302919157</v>
       </c>
       <c r="I57" t="n">
-        <v>0.2180246773556286</v>
+        <v>0.2180246774233276</v>
       </c>
       <c r="J57" t="n">
-        <v>0.02444228773888892</v>
+        <v>0.02444228780946331</v>
       </c>
       <c r="K57" t="n">
-        <v>0.3806411666965068</v>
+        <v>0.3372330102865788</v>
       </c>
       <c r="L57" t="n">
-        <v>0.446908871038932</v>
+        <v>0.4422700652767724</v>
       </c>
       <c r="M57" t="n">
         <v>0</v>
@@ -6434,16 +6434,16 @@
         <v>0</v>
       </c>
       <c r="O57" t="n">
-        <v>4.256768970266466</v>
+        <v>4.259702116978529</v>
       </c>
       <c r="P57" t="n">
-        <v>4.367295926384822</v>
+        <v>4.360264441256886</v>
       </c>
       <c r="Q57" t="n">
-        <v>0.9003983522957966</v>
+        <v>0.8987579024912619</v>
       </c>
       <c r="R57" t="n">
-        <v>0.009596819889347217</v>
+        <v>0.009675527455599754</v>
       </c>
       <c r="S57" t="inlineStr"/>
       <c r="T57" t="inlineStr"/>
@@ -6453,38 +6453,38 @@
       <c r="X57" t="inlineStr"/>
       <c r="Y57" t="inlineStr"/>
       <c r="Z57" t="n">
-        <v>0.7858990746237033</v>
+        <v>0.7772525994953501</v>
       </c>
       <c r="AA57" t="n">
-        <v>0.01751351879881869</v>
+        <v>0.01786366076274804</v>
       </c>
       <c r="AB57" t="inlineStr"/>
       <c r="AC57" t="n">
-        <v>0.6377957646282724</v>
+        <v>0.6410965661821657</v>
       </c>
       <c r="AD57" t="n">
-        <v>0.008676343508065438</v>
+        <v>0.008636718854951706</v>
       </c>
       <c r="AE57" t="inlineStr"/>
       <c r="AF57" t="n">
-        <v>0.7497121235996479</v>
+        <v>0.7575282678596247</v>
       </c>
       <c r="AG57" t="n">
-        <v>0.007680300061801535</v>
+        <v>0.007559426307468216</v>
       </c>
       <c r="AH57" t="inlineStr"/>
       <c r="AI57" t="n">
-        <v>0.9469764606982166</v>
+        <v>0.9532260355223445</v>
       </c>
       <c r="AJ57" t="n">
-        <v>0.004237528805731705</v>
+        <v>0.003979975496935578</v>
       </c>
       <c r="AK57" t="inlineStr"/>
       <c r="AL57" t="n">
-        <v>0.6899976100324631</v>
+        <v>0.7216388582182561</v>
       </c>
       <c r="AM57" t="n">
-        <v>0.001244517230741319</v>
+        <v>0.001179295654215196</v>
       </c>
       <c r="AN57" t="inlineStr"/>
     </row>
@@ -6511,43 +6511,43 @@
         <v>26</v>
       </c>
       <c r="F58" t="n">
-        <v>0.3897461385626112</v>
+        <v>0.3897461386008995</v>
       </c>
       <c r="G58" t="n">
         <v>0.1221001221001221</v>
       </c>
       <c r="H58" t="n">
-        <v>0.2557628102080468</v>
+        <v>0.2557628103268892</v>
       </c>
       <c r="I58" t="n">
-        <v>0.2061345128303654</v>
+        <v>0.2061345125957501</v>
       </c>
       <c r="J58" t="n">
-        <v>0.02625641629885448</v>
+        <v>0.02625641637633904</v>
       </c>
       <c r="K58" t="n">
-        <v>0.2253496777622122</v>
+        <v>0.1681963868140562</v>
       </c>
       <c r="L58" t="n">
-        <v>0.5201446820919224</v>
+        <v>0.518229450854724</v>
       </c>
       <c r="M58" t="n">
-        <v>0.5808150276325121</v>
+        <v>0.5655192006357713</v>
       </c>
       <c r="N58" t="n">
-        <v>0.08217763978476436</v>
+        <v>0.08763669139459054</v>
       </c>
       <c r="O58" t="n">
-        <v>4.133633433248462</v>
+        <v>4.153505266863479</v>
       </c>
       <c r="P58" t="n">
-        <v>4.449633703818832</v>
+        <v>4.446887573416661</v>
       </c>
       <c r="Q58" t="n">
-        <v>0.9701268943931739</v>
+        <v>0.9651122503968868</v>
       </c>
       <c r="R58" t="n">
-        <v>0.007267925063510743</v>
+        <v>0.007854286374820137</v>
       </c>
       <c r="S58" t="inlineStr"/>
       <c r="T58" t="inlineStr"/>
@@ -6557,38 +6557,38 @@
       <c r="X58" t="inlineStr"/>
       <c r="Y58" t="inlineStr"/>
       <c r="Z58" t="n">
-        <v>0.9771800191796252</v>
+        <v>0.9747048530845148</v>
       </c>
       <c r="AA58" t="n">
-        <v>0.00876507826600265</v>
+        <v>0.009228195023468911</v>
       </c>
       <c r="AB58" t="inlineStr"/>
       <c r="AC58" t="n">
-        <v>0.9882162910998799</v>
+        <v>0.9889988089024538</v>
       </c>
       <c r="AD58" t="n">
-        <v>0.0009990725629719082</v>
+        <v>0.0009653301796980699</v>
       </c>
       <c r="AE58" t="inlineStr"/>
       <c r="AF58" t="n">
-        <v>0.9653976550517741</v>
+        <v>0.9583312507074835</v>
       </c>
       <c r="AG58" t="n">
-        <v>0.007147378546939418</v>
+        <v>0.007843307665337647</v>
       </c>
       <c r="AH58" t="inlineStr"/>
       <c r="AI58" t="n">
-        <v>0.7956008072432688</v>
+        <v>0.7566341859360296</v>
       </c>
       <c r="AJ58" t="n">
-        <v>0.01159865998899373</v>
+        <v>0.01265604513951534</v>
       </c>
       <c r="AK58" t="inlineStr"/>
       <c r="AL58" t="n">
-        <v>0.9461867952425701</v>
+        <v>0.9470098767182217</v>
       </c>
       <c r="AM58" t="n">
-        <v>0.0008215820198064019</v>
+        <v>0.0008152746989939734</v>
       </c>
       <c r="AN58" t="inlineStr"/>
     </row>
@@ -6615,25 +6615,25 @@
         <v>10.6506024096385</v>
       </c>
       <c r="F59" t="n">
-        <v>0.4031657915982697</v>
+        <v>0.4031657917179133</v>
       </c>
       <c r="G59" t="n">
         <v>0.2980679451267702</v>
       </c>
       <c r="H59" t="n">
-        <v>0.09858303468278869</v>
+        <v>0.098583034577217</v>
       </c>
       <c r="I59" t="n">
-        <v>0.1793800069532604</v>
+        <v>0.1793800069472718</v>
       </c>
       <c r="J59" t="n">
-        <v>0.02080322163891103</v>
+        <v>0.02080322163082778</v>
       </c>
       <c r="K59" t="n">
-        <v>0.4654669130886756</v>
+        <v>0.4454560940571964</v>
       </c>
       <c r="L59" t="n">
-        <v>0.5135266407365338</v>
+        <v>0.5298941681217869</v>
       </c>
       <c r="M59" t="n">
         <v>0</v>
@@ -6642,16 +6642,16 @@
         <v>0</v>
       </c>
       <c r="O59" t="n">
-        <v>4.192052202289072</v>
+        <v>4.193144733448825</v>
       </c>
       <c r="P59" t="n">
-        <v>4.383827840564227</v>
+        <v>4.384068460531969</v>
       </c>
       <c r="Q59" t="n">
-        <v>0.8047445056530412</v>
+        <v>0.8126010847893519</v>
       </c>
       <c r="R59" t="n">
-        <v>0.01891378881081737</v>
+        <v>0.01852936089226071</v>
       </c>
       <c r="S59" t="inlineStr"/>
       <c r="T59" t="inlineStr"/>
@@ -6661,38 +6661,38 @@
       <c r="X59" t="inlineStr"/>
       <c r="Y59" t="inlineStr"/>
       <c r="Z59" t="n">
-        <v>0.781230944941273</v>
+        <v>0.7917578857052692</v>
       </c>
       <c r="AA59" t="n">
-        <v>0.02932140296772496</v>
+        <v>0.02860724816865818</v>
       </c>
       <c r="AB59" t="inlineStr"/>
       <c r="AC59" t="n">
-        <v>0.4412019164161227</v>
+        <v>0.4438808761107462</v>
       </c>
       <c r="AD59" t="n">
-        <v>0.02310131047756706</v>
+        <v>0.02304586841877636</v>
       </c>
       <c r="AE59" t="inlineStr"/>
       <c r="AF59" t="n">
-        <v>0.1387715782668283</v>
+        <v>0.1377844534069149</v>
       </c>
       <c r="AG59" t="n">
-        <v>0.01076620816955282</v>
+        <v>0.01077237639240744</v>
       </c>
       <c r="AH59" t="inlineStr"/>
       <c r="AI59" t="n">
-        <v>-0.7744006991037902</v>
+        <v>-0.5932706166532085</v>
       </c>
       <c r="AJ59" t="n">
-        <v>0.01652317940717141</v>
+        <v>0.0156571438570961</v>
       </c>
       <c r="AK59" t="inlineStr"/>
       <c r="AL59" t="n">
-        <v>-0.5584973427889075</v>
+        <v>-0.4829820038351713</v>
       </c>
       <c r="AM59" t="n">
-        <v>0.002512990659079899</v>
+        <v>0.00245135258948054</v>
       </c>
       <c r="AN59" t="inlineStr"/>
     </row>
@@ -6719,25 +6719,25 @@
         <v>45.2784503631961</v>
       </c>
       <c r="F60" t="n">
-        <v>0.6185024514073951</v>
+        <v>0.6185024514128479</v>
       </c>
       <c r="G60" t="n">
         <v>0.07011289364230544</v>
       </c>
       <c r="H60" t="n">
-        <v>0.1901432799511997</v>
+        <v>0.1901432797896153</v>
       </c>
       <c r="I60" t="n">
-        <v>0.1060804578008114</v>
+        <v>0.1060804579527164</v>
       </c>
       <c r="J60" t="n">
-        <v>0.0151609171982884</v>
+        <v>0.015160917202515</v>
       </c>
       <c r="K60" t="n">
-        <v>0.3195516907355711</v>
+        <v>0.2701213903358244</v>
       </c>
       <c r="L60" t="n">
-        <v>0.2337909910577463</v>
+        <v>0.2197642545761248</v>
       </c>
       <c r="M60" t="n">
         <v>0</v>
@@ -6746,16 +6746,16 @@
         <v>0</v>
       </c>
       <c r="O60" t="n">
-        <v>4.041987989944264</v>
+        <v>4.028615073796866</v>
       </c>
       <c r="P60" t="n">
-        <v>4.211312034823191</v>
+        <v>4.210097226686176</v>
       </c>
       <c r="Q60" t="n">
-        <v>0.8938767987070141</v>
+        <v>0.9374859094892489</v>
       </c>
       <c r="R60" t="n">
-        <v>0.02026178555644128</v>
+        <v>0.01555111389188623</v>
       </c>
       <c r="S60" t="inlineStr"/>
       <c r="T60" t="inlineStr"/>
@@ -6765,38 +6765,38 @@
       <c r="X60" t="inlineStr"/>
       <c r="Y60" t="inlineStr"/>
       <c r="Z60" t="n">
-        <v>0.6153863286901591</v>
+        <v>0.7864208390366414</v>
       </c>
       <c r="AA60" t="n">
-        <v>0.04344884916800898</v>
+        <v>0.03237765246310964</v>
       </c>
       <c r="AB60" t="inlineStr"/>
       <c r="AC60" t="n">
-        <v>-1.405634905383364</v>
+        <v>-1.493919976812546</v>
       </c>
       <c r="AD60" t="n">
-        <v>0.008220313021881646</v>
+        <v>0.0083697937094382</v>
       </c>
       <c r="AE60" t="inlineStr"/>
       <c r="AF60" t="n">
-        <v>0.618216638052747</v>
+        <v>0.602707475221207</v>
       </c>
       <c r="AG60" t="n">
-        <v>0.006814296643099133</v>
+        <v>0.006951327221777</v>
       </c>
       <c r="AH60" t="inlineStr"/>
       <c r="AI60" t="n">
-        <v>-9.226993784798434</v>
+        <v>-7.532698183515887</v>
       </c>
       <c r="AJ60" t="n">
-        <v>0.007115568369428657</v>
+        <v>0.006499482743844156</v>
       </c>
       <c r="AK60" t="inlineStr"/>
       <c r="AL60" t="n">
-        <v>0.9316574957294248</v>
+        <v>0.9322176893133124</v>
       </c>
       <c r="AM60" t="n">
-        <v>0.0005077179470773505</v>
+        <v>0.0005056328212029454</v>
       </c>
       <c r="AN60" t="inlineStr"/>
     </row>
@@ -6823,43 +6823,43 @@
         <v>53.51961950059453</v>
       </c>
       <c r="F61" t="n">
-        <v>0.7472990942554644</v>
+        <v>0.7472990942424869</v>
       </c>
       <c r="G61" t="n">
         <v>0.05931662452435613</v>
       </c>
       <c r="H61" t="n">
-        <v>0.1189424488256474</v>
+        <v>0.1189424488653025</v>
       </c>
       <c r="I61" t="n">
-        <v>0.05728789975449577</v>
+        <v>0.05728789972030301</v>
       </c>
       <c r="J61" t="n">
-        <v>0.01715393264003622</v>
+        <v>0.01715393264755156</v>
       </c>
       <c r="K61" t="n">
-        <v>0.3994271141921055</v>
+        <v>0.3824305879025255</v>
       </c>
       <c r="L61" t="n">
-        <v>0.2758743685540509</v>
+        <v>0.3784570990409153</v>
       </c>
       <c r="M61" t="n">
-        <v>0.2241048170806427</v>
+        <v>0.3199534926509083</v>
       </c>
       <c r="N61" t="n">
-        <v>0.0100484440660553</v>
+        <v>0.01742458552727234</v>
       </c>
       <c r="O61" t="n">
-        <v>3.830195138216759</v>
+        <v>3.905635756552347</v>
       </c>
       <c r="P61" t="n">
-        <v>4.249491999162036</v>
+        <v>4.265994286634675</v>
       </c>
       <c r="Q61" t="n">
-        <v>0.9833546433779143</v>
+        <v>0.9843592239890212</v>
       </c>
       <c r="R61" t="n">
-        <v>0.00919838327800061</v>
+        <v>0.008916493513709921</v>
       </c>
       <c r="S61" t="inlineStr"/>
       <c r="T61" t="inlineStr"/>
@@ -6871,38 +6871,38 @@
       </c>
       <c r="Y61" t="inlineStr"/>
       <c r="Z61" t="n">
-        <v>0.9711176223695276</v>
+        <v>0.972788486781638</v>
       </c>
       <c r="AA61" t="n">
-        <v>0.01894056224051919</v>
+        <v>0.01838453891998659</v>
       </c>
       <c r="AB61" t="inlineStr"/>
       <c r="AC61" t="n">
-        <v>0.4257842539181919</v>
+        <v>0.2875351849855194</v>
       </c>
       <c r="AD61" t="n">
-        <v>0.004107727087694948</v>
+        <v>0.004575575635632688</v>
       </c>
       <c r="AE61" t="inlineStr"/>
       <c r="AF61" t="n">
-        <v>0.6582824405837779</v>
+        <v>0.7090333266126018</v>
       </c>
       <c r="AG61" t="n">
-        <v>0.005922834159065873</v>
+        <v>0.005465344593510365</v>
       </c>
       <c r="AH61" t="inlineStr"/>
       <c r="AI61" t="n">
-        <v>0.879444629051122</v>
+        <v>0.9314997235909249</v>
       </c>
       <c r="AJ61" t="n">
-        <v>0.002775423796375348</v>
+        <v>0.002092098790850485</v>
       </c>
       <c r="AK61" t="inlineStr"/>
       <c r="AL61" t="n">
-        <v>0.2167420090563152</v>
+        <v>0.2680768817927681</v>
       </c>
       <c r="AM61" t="n">
-        <v>0.002410916087755386</v>
+        <v>0.00233057136925888</v>
       </c>
       <c r="AN61" t="inlineStr"/>
     </row>
@@ -6929,43 +6929,43 @@
         <v>54.48315911730546</v>
       </c>
       <c r="F62" t="n">
-        <v>0.6806747812354861</v>
+        <v>0.6806747812675474</v>
       </c>
       <c r="G62" t="n">
         <v>0.05826760463298514</v>
       </c>
       <c r="H62" t="n">
-        <v>0.1324809677416384</v>
+        <v>0.1324809676982178</v>
       </c>
       <c r="I62" t="n">
-        <v>0.09760455450858101</v>
+        <v>0.09760455450536588</v>
       </c>
       <c r="J62" t="n">
-        <v>0.03097209188130944</v>
+        <v>0.0309720918958838</v>
       </c>
       <c r="K62" t="n">
-        <v>0.4202651317069659</v>
+        <v>0.3890643238636384</v>
       </c>
       <c r="L62" t="n">
-        <v>0.2430607655564238</v>
+        <v>0.3567084555181538</v>
       </c>
       <c r="M62" t="n">
-        <v>0.6584053066600373</v>
+        <v>0.702109196059558</v>
       </c>
       <c r="N62" t="n">
-        <v>0.09948379243991619</v>
+        <v>0.1303090350658246</v>
       </c>
       <c r="O62" t="n">
-        <v>4.183223779089313</v>
+        <v>4.193892861560939</v>
       </c>
       <c r="P62" t="n">
-        <v>4.199946415830034</v>
+        <v>4.237873262463898</v>
       </c>
       <c r="Q62" t="n">
-        <v>0.988628183542563</v>
+        <v>0.9889854002833713</v>
       </c>
       <c r="R62" t="n">
-        <v>0.007032871583785351</v>
+        <v>0.00692153032962381</v>
       </c>
       <c r="S62" t="inlineStr"/>
       <c r="T62" t="inlineStr"/>
@@ -6977,38 +6977,38 @@
       </c>
       <c r="Y62" t="inlineStr"/>
       <c r="Z62" t="n">
-        <v>0.9847418735900173</v>
+        <v>0.9848435015358243</v>
       </c>
       <c r="AA62" t="n">
-        <v>0.01288403613543487</v>
+        <v>0.01284105688402221</v>
       </c>
       <c r="AB62" t="inlineStr"/>
       <c r="AC62" t="n">
-        <v>0.1329803532834265</v>
+        <v>-0.09599492265233933</v>
       </c>
       <c r="AD62" t="n">
-        <v>0.003099789505766278</v>
+        <v>0.003485154252570684</v>
       </c>
       <c r="AE62" t="inlineStr"/>
       <c r="AF62" t="n">
-        <v>0.6472639082518614</v>
+        <v>0.6836035595538739</v>
       </c>
       <c r="AG62" t="n">
-        <v>0.007951847064461887</v>
+        <v>0.007531107794222383</v>
       </c>
       <c r="AH62" t="inlineStr"/>
       <c r="AI62" t="n">
-        <v>0.9755347963306147</v>
+        <v>0.9863210401294785</v>
       </c>
       <c r="AJ62" t="n">
-        <v>0.002322095867356102</v>
+        <v>0.001736329986178572</v>
       </c>
       <c r="AK62" t="inlineStr"/>
       <c r="AL62" t="n">
-        <v>0.8468315138627321</v>
+        <v>0.8622158700704873</v>
       </c>
       <c r="AM62" t="n">
-        <v>0.001960653748448378</v>
+        <v>0.001859583968091311</v>
       </c>
       <c r="AN62" t="inlineStr"/>
     </row>
@@ -7035,43 +7035,43 @@
         <v>53.51961950059453</v>
       </c>
       <c r="F63" t="n">
-        <v>0.7472990942554644</v>
+        <v>0.7472990942424869</v>
       </c>
       <c r="G63" t="n">
         <v>0.05931662452435613</v>
       </c>
       <c r="H63" t="n">
-        <v>0.1189424488256474</v>
+        <v>0.1189424488653025</v>
       </c>
       <c r="I63" t="n">
-        <v>0.05728789975449577</v>
+        <v>0.05728789972030301</v>
       </c>
       <c r="J63" t="n">
-        <v>0.01715393264003622</v>
+        <v>0.01715393264755156</v>
       </c>
       <c r="K63" t="n">
-        <v>0.4162364024212756</v>
+        <v>0.3916462498773384</v>
       </c>
       <c r="L63" t="n">
-        <v>0.2950028200308563</v>
+        <v>0.3810933315304789</v>
       </c>
       <c r="M63" t="n">
-        <v>0.3706319695558645</v>
+        <v>0.4757398446706067</v>
       </c>
       <c r="N63" t="n">
-        <v>0.03725342766212937</v>
+        <v>0.05438725368197824</v>
       </c>
       <c r="O63" t="n">
-        <v>3.980573946132115</v>
+        <v>3.99353652419105</v>
       </c>
       <c r="P63" t="n">
-        <v>4.250735467782023</v>
+        <v>4.26170841377675</v>
       </c>
       <c r="Q63" t="n">
-        <v>0.9891906288030091</v>
+        <v>0.9888445652152906</v>
       </c>
       <c r="R63" t="n">
-        <v>0.007604216904528887</v>
+        <v>0.007724982987310988</v>
       </c>
       <c r="S63" t="inlineStr"/>
       <c r="T63" t="inlineStr"/>
@@ -7083,38 +7083,38 @@
       </c>
       <c r="Y63" t="inlineStr"/>
       <c r="Z63" t="n">
-        <v>0.9776089665062692</v>
+        <v>0.9766937971592882</v>
       </c>
       <c r="AA63" t="n">
-        <v>0.01647694979409975</v>
+        <v>0.01681030176244808</v>
       </c>
       <c r="AB63" t="inlineStr"/>
       <c r="AC63" t="n">
-        <v>0.9160632499711816</v>
+        <v>0.8631763388160307</v>
       </c>
       <c r="AD63" t="n">
-        <v>0.00126508767221641</v>
+        <v>0.001615195702015312</v>
       </c>
       <c r="AE63" t="inlineStr"/>
       <c r="AF63" t="n">
-        <v>0.9910776423350016</v>
+        <v>0.9910566103327207</v>
       </c>
       <c r="AG63" t="n">
-        <v>0.001050519846673862</v>
+        <v>0.001051757274750608</v>
       </c>
       <c r="AH63" t="inlineStr"/>
       <c r="AI63" t="n">
-        <v>0.8551898488181919</v>
+        <v>0.8867793420648816</v>
       </c>
       <c r="AJ63" t="n">
-        <v>0.003393759942068076</v>
+        <v>0.003000851148004779</v>
       </c>
       <c r="AK63" t="inlineStr"/>
       <c r="AL63" t="n">
-        <v>0.2009758563970437</v>
+        <v>0.2803488306545605</v>
       </c>
       <c r="AM63" t="n">
-        <v>0.002064295832510188</v>
+        <v>0.00195908374418207</v>
       </c>
       <c r="AN63" t="inlineStr"/>
     </row>
@@ -7141,43 +7141,43 @@
         <v>54.48315911730546</v>
       </c>
       <c r="F64" t="n">
-        <v>0.6806747812354861</v>
+        <v>0.6806747812675474</v>
       </c>
       <c r="G64" t="n">
         <v>0.05826760463298514</v>
       </c>
       <c r="H64" t="n">
-        <v>0.1324809677416384</v>
+        <v>0.1324809676982178</v>
       </c>
       <c r="I64" t="n">
-        <v>0.09760455450858101</v>
+        <v>0.09760455450536588</v>
       </c>
       <c r="J64" t="n">
-        <v>0.03097209188130944</v>
+        <v>0.0309720918958838</v>
       </c>
       <c r="K64" t="n">
-        <v>0.3674688031115195</v>
+        <v>0.3549664602965995</v>
       </c>
       <c r="L64" t="n">
-        <v>0.283775465909908</v>
+        <v>0.3886192185632856</v>
       </c>
       <c r="M64" t="n">
-        <v>0.4249259745682613</v>
+        <v>0.4498046689235923</v>
       </c>
       <c r="N64" t="n">
-        <v>0.02787018075536547</v>
+        <v>0.03122227898020125</v>
       </c>
       <c r="O64" t="n">
-        <v>3.69002349828743</v>
+        <v>3.849078802939207</v>
       </c>
       <c r="P64" t="n">
-        <v>4.235841271884143</v>
+        <v>4.264031993074069</v>
       </c>
       <c r="Q64" t="n">
-        <v>0.982818436213785</v>
+        <v>0.9823049148305536</v>
       </c>
       <c r="R64" t="n">
-        <v>0.00878237494817892</v>
+        <v>0.008912652191803788</v>
       </c>
       <c r="S64" t="inlineStr"/>
       <c r="T64" t="inlineStr"/>
@@ -7189,38 +7189,38 @@
       </c>
       <c r="Y64" t="inlineStr"/>
       <c r="Z64" t="n">
-        <v>0.9758883437391677</v>
+        <v>0.9736775891317687</v>
       </c>
       <c r="AA64" t="n">
-        <v>0.01639916906370878</v>
+        <v>0.01713448885009333</v>
       </c>
       <c r="AB64" t="inlineStr"/>
       <c r="AC64" t="n">
-        <v>0.604926596602269</v>
+        <v>0.4875722177989248</v>
       </c>
       <c r="AD64" t="n">
-        <v>0.003394456242877987</v>
+        <v>0.003865873633206719</v>
       </c>
       <c r="AE64" t="inlineStr"/>
       <c r="AF64" t="n">
-        <v>0.3687177045870821</v>
+        <v>0.458567332563243</v>
       </c>
       <c r="AG64" t="n">
-        <v>0.009668286344281799</v>
+        <v>0.008953852318820043</v>
       </c>
       <c r="AH64" t="inlineStr"/>
       <c r="AI64" t="n">
-        <v>0.9645042467835913</v>
+        <v>0.9792512715050721</v>
       </c>
       <c r="AJ64" t="n">
-        <v>0.00271907558201289</v>
+        <v>0.002078877149164134</v>
       </c>
       <c r="AK64" t="inlineStr"/>
       <c r="AL64" t="n">
-        <v>0.8307446980928745</v>
+        <v>0.8377232887035387</v>
       </c>
       <c r="AM64" t="n">
-        <v>0.002325493665698345</v>
+        <v>0.002277047652628583</v>
       </c>
       <c r="AN64" t="inlineStr"/>
     </row>
@@ -7247,43 +7247,43 @@
         <v>53.51961950059453</v>
       </c>
       <c r="F65" t="n">
-        <v>0.7472990942554644</v>
+        <v>0.7472990942424869</v>
       </c>
       <c r="G65" t="n">
         <v>0.05931662452435613</v>
       </c>
       <c r="H65" t="n">
-        <v>0.1189424488256474</v>
+        <v>0.1189424488653025</v>
       </c>
       <c r="I65" t="n">
-        <v>0.05728789975449577</v>
+        <v>0.05728789972030301</v>
       </c>
       <c r="J65" t="n">
-        <v>0.01715393264003622</v>
+        <v>0.01715393264755156</v>
       </c>
       <c r="K65" t="n">
-        <v>0.4085515562507576</v>
+        <v>0.3852925812491872</v>
       </c>
       <c r="L65" t="n">
-        <v>0.3571931464515894</v>
+        <v>0.4274074157095529</v>
       </c>
       <c r="M65" t="n">
-        <v>0.2952640069260904</v>
+        <v>0.3821759721992075</v>
       </c>
       <c r="N65" t="n">
-        <v>0.02279375794611013</v>
+        <v>0.0322243045516141</v>
       </c>
       <c r="O65" t="n">
-        <v>3.911842650195023</v>
+        <v>3.9329393834399</v>
       </c>
       <c r="P65" t="n">
-        <v>4.269299797239945</v>
+        <v>4.282533099756243</v>
       </c>
       <c r="Q65" t="n">
-        <v>0.9786330214974474</v>
+        <v>0.9793181103872355</v>
       </c>
       <c r="R65" t="n">
-        <v>0.01052893253618677</v>
+        <v>0.01035876293910804</v>
       </c>
       <c r="S65" t="inlineStr"/>
       <c r="T65" t="inlineStr"/>
@@ -7295,38 +7295,38 @@
       </c>
       <c r="Y65" t="inlineStr"/>
       <c r="Z65" t="n">
-        <v>0.9643330021219167</v>
+        <v>0.96527054313649</v>
       </c>
       <c r="AA65" t="n">
-        <v>0.02159079734616568</v>
+        <v>0.02130514031589186</v>
       </c>
       <c r="AB65" t="inlineStr"/>
       <c r="AC65" t="n">
-        <v>0.708418474992106</v>
+        <v>0.6989580806037383</v>
       </c>
       <c r="AD65" t="n">
-        <v>0.003656480012851004</v>
+        <v>0.003715323958169617</v>
       </c>
       <c r="AE65" t="inlineStr"/>
       <c r="AF65" t="n">
-        <v>0.6645594641749599</v>
+        <v>0.6882673501750656</v>
       </c>
       <c r="AG65" t="n">
-        <v>0.008151976170232061</v>
+        <v>0.007858619754532963</v>
       </c>
       <c r="AH65" t="inlineStr"/>
       <c r="AI65" t="n">
-        <v>0.9275836698363027</v>
+        <v>0.9423949705550441</v>
       </c>
       <c r="AJ65" t="n">
-        <v>0.002321779133958501</v>
+        <v>0.002070774697803601</v>
       </c>
       <c r="AK65" t="inlineStr"/>
       <c r="AL65" t="n">
-        <v>0.553878522517901</v>
+        <v>0.5773226291067055</v>
       </c>
       <c r="AM65" t="n">
-        <v>0.001908648672284967</v>
+        <v>0.001857821255463732</v>
       </c>
       <c r="AN65" t="inlineStr"/>
     </row>
@@ -7353,43 +7353,43 @@
         <v>54.48315911730546</v>
       </c>
       <c r="F66" t="n">
-        <v>0.6806747812354861</v>
+        <v>0.6806747812675474</v>
       </c>
       <c r="G66" t="n">
         <v>0.05826760463298514</v>
       </c>
       <c r="H66" t="n">
-        <v>0.1324809677416384</v>
+        <v>0.1324809676982178</v>
       </c>
       <c r="I66" t="n">
-        <v>0.09760455450858101</v>
+        <v>0.09760455450536588</v>
       </c>
       <c r="J66" t="n">
-        <v>0.03097209188130944</v>
+        <v>0.0309720918958838</v>
       </c>
       <c r="K66" t="n">
-        <v>0.396032261454521</v>
+        <v>0.3683063526754361</v>
       </c>
       <c r="L66" t="n">
-        <v>0.2888494714669217</v>
+        <v>0.3888539371120725</v>
       </c>
       <c r="M66" t="n">
-        <v>0.3555530335959829</v>
+        <v>0.3992556602164993</v>
       </c>
       <c r="N66" t="n">
-        <v>0.02161924171252751</v>
+        <v>0.0251736716013569</v>
       </c>
       <c r="O66" t="n">
-        <v>3.957047851229053</v>
+        <v>3.984066840056817</v>
       </c>
       <c r="P66" t="n">
-        <v>4.239953806950777</v>
+        <v>4.265866456034582</v>
       </c>
       <c r="Q66" t="n">
-        <v>0.9815684785941791</v>
+        <v>0.9813331664445752</v>
       </c>
       <c r="R66" t="n">
-        <v>0.009182779079204487</v>
+        <v>0.00924121067627188</v>
       </c>
       <c r="S66" t="inlineStr"/>
       <c r="T66" t="inlineStr"/>
@@ -7401,38 +7401,38 @@
       </c>
       <c r="Y66" t="inlineStr"/>
       <c r="Z66" t="n">
-        <v>0.9711260071913864</v>
+        <v>0.9698880581135585</v>
       </c>
       <c r="AA66" t="n">
-        <v>0.0178868657588605</v>
+        <v>0.01826628407463927</v>
       </c>
       <c r="AB66" t="inlineStr"/>
       <c r="AC66" t="n">
-        <v>0.711939438793706</v>
+        <v>0.652491925249314</v>
       </c>
       <c r="AD66" t="n">
-        <v>0.003308541204600216</v>
+        <v>0.003633934519348367</v>
       </c>
       <c r="AE66" t="inlineStr"/>
       <c r="AF66" t="n">
-        <v>0.678138720744636</v>
+        <v>0.7053972737811338</v>
       </c>
       <c r="AG66" t="n">
-        <v>0.008667843768580171</v>
+        <v>0.008292683472537728</v>
       </c>
       <c r="AH66" t="inlineStr"/>
       <c r="AI66" t="n">
-        <v>0.9391441282304176</v>
+        <v>0.9598671361775124</v>
       </c>
       <c r="AJ66" t="n">
-        <v>0.003430953185534736</v>
+        <v>0.00278620857103289</v>
       </c>
       <c r="AK66" t="inlineStr"/>
       <c r="AL66" t="n">
-        <v>0.843851155595404</v>
+        <v>0.8529109222667859</v>
       </c>
       <c r="AM66" t="n">
-        <v>0.002187404612634378</v>
+        <v>0.002122999780051077</v>
       </c>
       <c r="AN66" t="inlineStr"/>
     </row>
@@ -7459,25 +7459,25 @@
         <v>54.52272727272727</v>
       </c>
       <c r="F67" t="n">
-        <v>0.6524665781462966</v>
+        <v>0.652466577913562</v>
       </c>
       <c r="G67" t="n">
         <v>0.0582253187505376</v>
       </c>
       <c r="H67" t="n">
-        <v>0.1475232058308549</v>
+        <v>0.147523206464546</v>
       </c>
       <c r="I67" t="n">
-        <v>0.1417848972723109</v>
+        <v>0.1417848968713543</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>0.4199481453543742</v>
+        <v>0.3806197097218254</v>
       </c>
       <c r="L67" t="n">
-        <v>0.394686558825489</v>
+        <v>0.4180148780866773</v>
       </c>
       <c r="M67" t="n">
         <v>0</v>
@@ -7486,61 +7486,61 @@
         <v>0</v>
       </c>
       <c r="O67" t="n">
-        <v>4.39633004726497</v>
+        <v>4.399192655214832</v>
       </c>
       <c r="P67" t="n">
-        <v>4.347009068166593</v>
+        <v>4.341457123451502</v>
       </c>
       <c r="Q67" t="n">
-        <v>0.8548504315926932</v>
+        <v>0.8898400902899847</v>
       </c>
       <c r="R67" t="n">
-        <v>0.02755622641967012</v>
+        <v>0.02400621303560715</v>
       </c>
       <c r="S67" t="inlineStr"/>
       <c r="T67" t="inlineStr"/>
       <c r="U67" t="inlineStr"/>
       <c r="V67" t="inlineStr"/>
       <c r="W67" t="n">
-        <v>0.8037811043712753</v>
+        <v>0.7180164367759334</v>
       </c>
       <c r="X67" t="n">
-        <v>0.000769985072862494</v>
+        <v>0.0009230469453608505</v>
       </c>
       <c r="Y67" t="inlineStr"/>
       <c r="Z67" t="n">
-        <v>0.5957043416201471</v>
+        <v>0.6994418720030776</v>
       </c>
       <c r="AA67" t="n">
-        <v>0.06551771600311547</v>
+        <v>0.05649024377444228</v>
       </c>
       <c r="AB67" t="inlineStr"/>
       <c r="AC67" t="n">
-        <v>0.7655115095172615</v>
+        <v>0.6660638543482552</v>
       </c>
       <c r="AD67" t="n">
-        <v>0.0026529094063066</v>
+        <v>0.003165872126853521</v>
       </c>
       <c r="AE67" t="inlineStr"/>
       <c r="AF67" t="n">
-        <v>0.6425546340731398</v>
+        <v>0.6218933267726424</v>
       </c>
       <c r="AG67" t="n">
-        <v>0.01311359820442935</v>
+        <v>0.01348727494101168</v>
       </c>
       <c r="AH67" t="inlineStr"/>
       <c r="AI67" t="n">
-        <v>0.8046678127678512</v>
+        <v>0.8282022189602807</v>
       </c>
       <c r="AJ67" t="n">
-        <v>0.009152943365267199</v>
+        <v>0.008583860316607735</v>
       </c>
       <c r="AK67" t="inlineStr"/>
       <c r="AL67" t="n">
-        <v>0.8180785874530363</v>
+        <v>0.867746396220394</v>
       </c>
       <c r="AM67" t="n">
-        <v>0.0001138301359081168</v>
+        <v>9.705527253318891e-05</v>
       </c>
       <c r="AN67" t="inlineStr"/>
     </row>
@@ -7567,25 +7567,25 @@
         <v>54.52272727272727</v>
       </c>
       <c r="F68" t="n">
-        <v>0.6524665781462966</v>
+        <v>0.652466577913562</v>
       </c>
       <c r="G68" t="n">
         <v>0.0582253187505376</v>
       </c>
       <c r="H68" t="n">
-        <v>0.1475232058308549</v>
+        <v>0.147523206464546</v>
       </c>
       <c r="I68" t="n">
-        <v>0.1417848972723109</v>
+        <v>0.1417848968713543</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>0.4285024175374733</v>
+        <v>0.3886320832993509</v>
       </c>
       <c r="L68" t="n">
-        <v>0.388941449636978</v>
+        <v>0.4210164914544958</v>
       </c>
       <c r="M68" t="n">
         <v>0</v>
@@ -7594,61 +7594,61 @@
         <v>0</v>
       </c>
       <c r="O68" t="n">
-        <v>4.480409000587638</v>
+        <v>4.486141097122832</v>
       </c>
       <c r="P68" t="n">
-        <v>4.346260088719825</v>
+        <v>4.344541144699984</v>
       </c>
       <c r="Q68" t="n">
-        <v>0.7773934706989506</v>
+        <v>0.8070699052717809</v>
       </c>
       <c r="R68" t="n">
-        <v>0.03147392775018776</v>
+        <v>0.02930096900212845</v>
       </c>
       <c r="S68" t="inlineStr"/>
       <c r="T68" t="inlineStr"/>
       <c r="U68" t="inlineStr"/>
       <c r="V68" t="inlineStr"/>
       <c r="W68" t="n">
-        <v>0.4874339541326738</v>
+        <v>0.3800315330833699</v>
       </c>
       <c r="X68" t="n">
-        <v>0.001170819288718882</v>
+        <v>0.001287655692732865</v>
       </c>
       <c r="Y68" t="inlineStr"/>
       <c r="Z68" t="n">
-        <v>0.3955674114516097</v>
+        <v>0.4786279819552859</v>
       </c>
       <c r="AA68" t="n">
-        <v>0.07562635783685882</v>
+        <v>0.07023815721287743</v>
       </c>
       <c r="AB68" t="inlineStr"/>
       <c r="AC68" t="n">
-        <v>0.4695557683823047</v>
+        <v>0.3639112413919049</v>
       </c>
       <c r="AD68" t="n">
-        <v>0.003886914158561062</v>
+        <v>0.0042564147961794</v>
       </c>
       <c r="AE68" t="inlineStr"/>
       <c r="AF68" t="n">
-        <v>0.7501049465974345</v>
+        <v>0.7727286426576955</v>
       </c>
       <c r="AG68" t="n">
-        <v>0.007351067887737261</v>
+        <v>0.007010418717430248</v>
       </c>
       <c r="AH68" t="inlineStr"/>
       <c r="AI68" t="n">
-        <v>0.6990500340897213</v>
+        <v>0.7084528709377704</v>
       </c>
       <c r="AJ68" t="n">
-        <v>0.01237078583991602</v>
+        <v>0.01217599673170401</v>
       </c>
       <c r="AK68" t="inlineStr"/>
       <c r="AL68" t="n">
-        <v>0.2480709441268785</v>
+        <v>0.4075399265614856</v>
       </c>
       <c r="AM68" t="n">
-        <v>0.0007706685767893581</v>
+        <v>0.0006840829448425192</v>
       </c>
       <c r="AN68" t="inlineStr"/>
     </row>
@@ -7675,25 +7675,25 @@
         <v>51.72972972972973</v>
       </c>
       <c r="F69" t="n">
-        <v>0.387003570840844</v>
+        <v>0.3870035708733858</v>
       </c>
       <c r="G69" t="n">
         <v>0.06136902688626825</v>
       </c>
       <c r="H69" t="n">
-        <v>0.3121616657195941</v>
+        <v>0.3121616658061397</v>
       </c>
       <c r="I69" t="n">
-        <v>0.1933504308693656</v>
+        <v>0.1933504307114432</v>
       </c>
       <c r="J69" t="n">
-        <v>0.04611530568392795</v>
+        <v>0.04611530572276303</v>
       </c>
       <c r="K69" t="n">
-        <v>0.1574541057329026</v>
+        <v>0.1010562527983535</v>
       </c>
       <c r="L69" t="n">
-        <v>0.2051976353952231</v>
+        <v>0.172739751808195</v>
       </c>
       <c r="M69" t="n">
         <v>0</v>
@@ -7702,16 +7702,16 @@
         <v>0</v>
       </c>
       <c r="O69" t="n">
-        <v>4.332138796392004</v>
+        <v>4.331832199947486</v>
       </c>
       <c r="P69" t="n">
-        <v>4.301408134638223</v>
+        <v>4.292703203954071</v>
       </c>
       <c r="Q69" t="n">
-        <v>0.971964674427934</v>
+        <v>0.9719051072258843</v>
       </c>
       <c r="R69" t="n">
-        <v>0.009813396774144721</v>
+        <v>0.009823816601049489</v>
       </c>
       <c r="S69" t="inlineStr"/>
       <c r="T69" t="inlineStr"/>
@@ -7721,38 +7721,38 @@
       <c r="X69" t="inlineStr"/>
       <c r="Y69" t="inlineStr"/>
       <c r="Z69" t="n">
-        <v>0.9659052190880125</v>
+        <v>0.9674888851315926</v>
       </c>
       <c r="AA69" t="n">
-        <v>0.0102295534510854</v>
+        <v>0.009989152775492493</v>
       </c>
       <c r="AB69" t="inlineStr"/>
       <c r="AC69" t="n">
-        <v>0.4411317996927842</v>
+        <v>0.421250872053186</v>
       </c>
       <c r="AD69" t="n">
-        <v>0.004747446593787831</v>
+        <v>0.004831150459858264</v>
       </c>
       <c r="AE69" t="inlineStr"/>
       <c r="AF69" t="n">
-        <v>0.8485263686173259</v>
+        <v>0.8495371887650479</v>
       </c>
       <c r="AG69" t="n">
-        <v>0.01576023512306844</v>
+        <v>0.01570756117380479</v>
       </c>
       <c r="AH69" t="inlineStr"/>
       <c r="AI69" t="n">
-        <v>0.9048103366427537</v>
+        <v>0.8973026549048775</v>
       </c>
       <c r="AJ69" t="n">
-        <v>0.009361233507072192</v>
+        <v>0.009723391915422036</v>
       </c>
       <c r="AK69" t="inlineStr"/>
       <c r="AL69" t="n">
-        <v>0.5187109619344599</v>
+        <v>0.5232367987441527</v>
       </c>
       <c r="AM69" t="n">
-        <v>0.004279493469577684</v>
+        <v>0.00425932468211163</v>
       </c>
       <c r="AN69" t="inlineStr"/>
     </row>
@@ -7779,25 +7779,25 @@
         <v>33.0828025477707</v>
       </c>
       <c r="F70" t="n">
-        <v>0.3260336956980185</v>
+        <v>0.3260336958414495</v>
       </c>
       <c r="G70" t="n">
         <v>0.09595931813875594</v>
       </c>
       <c r="H70" t="n">
-        <v>0.3161491466910983</v>
+        <v>0.31614914647049</v>
       </c>
       <c r="I70" t="n">
-        <v>0.2279586239396759</v>
+        <v>0.2279586239311767</v>
       </c>
       <c r="J70" t="n">
-        <v>0.03389921553245138</v>
+        <v>0.03389921561812766</v>
       </c>
       <c r="K70" t="n">
-        <v>0.1548184556465437</v>
+        <v>0.09856641470047335</v>
       </c>
       <c r="L70" t="n">
-        <v>0.2818792756835835</v>
+        <v>0.2502590843189873</v>
       </c>
       <c r="M70" t="n">
         <v>0</v>
@@ -7806,16 +7806,16 @@
         <v>0</v>
       </c>
       <c r="O70" t="n">
-        <v>4.393884558299479</v>
+        <v>4.407350183726711</v>
       </c>
       <c r="P70" t="n">
-        <v>4.357184331136191</v>
+        <v>4.347882044824999</v>
       </c>
       <c r="Q70" t="n">
-        <v>0.9634331301343807</v>
+        <v>0.9647039526405778</v>
       </c>
       <c r="R70" t="n">
-        <v>0.009384186172923768</v>
+        <v>0.009219678113608272</v>
       </c>
       <c r="S70" t="inlineStr"/>
       <c r="T70" t="inlineStr"/>
@@ -7825,38 +7825,38 @@
       <c r="X70" t="inlineStr"/>
       <c r="Y70" t="inlineStr"/>
       <c r="Z70" t="n">
-        <v>0.9218597383630527</v>
+        <v>0.930672366284089</v>
       </c>
       <c r="AA70" t="n">
-        <v>0.01248178308088512</v>
+        <v>0.01175688821623678</v>
       </c>
       <c r="AB70" t="inlineStr"/>
       <c r="AC70" t="n">
-        <v>0.9266093425400458</v>
+        <v>0.9240889124308331</v>
       </c>
       <c r="AD70" t="n">
-        <v>0.00314246754918454</v>
+        <v>0.003195972393453977</v>
       </c>
       <c r="AE70" t="inlineStr"/>
       <c r="AF70" t="n">
-        <v>0.9388867506727477</v>
+        <v>0.9394095586078465</v>
       </c>
       <c r="AG70" t="n">
-        <v>0.01122532965866805</v>
+        <v>0.01117721163068067</v>
       </c>
       <c r="AH70" t="inlineStr"/>
       <c r="AI70" t="n">
-        <v>0.8165577140446746</v>
+        <v>0.8126445252812737</v>
       </c>
       <c r="AJ70" t="n">
-        <v>0.0119960427732964</v>
+        <v>0.01212331732950899</v>
       </c>
       <c r="AK70" t="inlineStr"/>
       <c r="AL70" t="n">
-        <v>0.7678154532435362</v>
+        <v>0.7709015693836885</v>
       </c>
       <c r="AM70" t="n">
-        <v>0.002175240515435225</v>
+        <v>0.002160735896618032</v>
       </c>
       <c r="AN70" t="inlineStr"/>
     </row>
@@ -7883,25 +7883,25 @@
         <v>47.07964601769911</v>
       </c>
       <c r="F71" t="n">
-        <v>0.3936990724378037</v>
+        <v>0.3936990724969831</v>
       </c>
       <c r="G71" t="n">
         <v>0.06743048096431555</v>
       </c>
       <c r="H71" t="n">
-        <v>0.2058669949880412</v>
+        <v>0.2058669949713333</v>
       </c>
       <c r="I71" t="n">
-        <v>0.3043928180016056</v>
+        <v>0.3043928180135104</v>
       </c>
       <c r="J71" t="n">
-        <v>0.02861063360823382</v>
+        <v>0.02861063355385755</v>
       </c>
       <c r="K71" t="n">
-        <v>0.3259372934798359</v>
+        <v>0.269045723492097</v>
       </c>
       <c r="L71" t="n">
-        <v>0.3494710757904321</v>
+        <v>0.3368382398912689</v>
       </c>
       <c r="M71" t="n">
         <v>0</v>
@@ -7910,16 +7910,16 @@
         <v>0</v>
       </c>
       <c r="O71" t="n">
-        <v>4.435983780461879</v>
+        <v>4.440211158709118</v>
       </c>
       <c r="P71" t="n">
-        <v>4.438832256269587</v>
+        <v>4.43413306451066</v>
       </c>
       <c r="Q71" t="n">
-        <v>0.9612297385743878</v>
+        <v>0.9604536771790378</v>
       </c>
       <c r="R71" t="n">
-        <v>0.01075114110392152</v>
+        <v>0.01085821034975055</v>
       </c>
       <c r="S71" t="inlineStr"/>
       <c r="T71" t="inlineStr"/>
@@ -7929,38 +7929,38 @@
       <c r="X71" t="inlineStr"/>
       <c r="Y71" t="inlineStr"/>
       <c r="Z71" t="n">
-        <v>0.9443524956060733</v>
+        <v>0.9442451439407445</v>
       </c>
       <c r="AA71" t="n">
-        <v>0.01403952816563101</v>
+        <v>0.01405306373216931</v>
       </c>
       <c r="AB71" t="inlineStr"/>
       <c r="AC71" t="n">
-        <v>0.740770136758883</v>
+        <v>0.7392837202048927</v>
       </c>
       <c r="AD71" t="n">
-        <v>0.004510070808753229</v>
+        <v>0.004522982634125823</v>
       </c>
       <c r="AE71" t="inlineStr"/>
       <c r="AF71" t="n">
-        <v>0.9068221337088034</v>
+        <v>0.9040248606288319</v>
       </c>
       <c r="AG71" t="n">
-        <v>0.009735558640804524</v>
+        <v>0.009880612600300249</v>
       </c>
       <c r="AH71" t="inlineStr"/>
       <c r="AI71" t="n">
-        <v>0.8424493265837444</v>
+        <v>0.8377069941394923</v>
       </c>
       <c r="AJ71" t="n">
-        <v>0.01626851016622633</v>
+        <v>0.01651153894274363</v>
       </c>
       <c r="AK71" t="inlineStr"/>
       <c r="AL71" t="n">
-        <v>0.9318214553838008</v>
+        <v>0.9148053965285752</v>
       </c>
       <c r="AM71" t="n">
-        <v>0.001020078571232061</v>
+        <v>0.001140291284357528</v>
       </c>
       <c r="AN71" t="inlineStr"/>
     </row>
@@ -7987,25 +7987,25 @@
         <v>37.36805555555556</v>
       </c>
       <c r="F72" t="n">
-        <v>0.2796444532400447</v>
+        <v>0.279644453194911</v>
       </c>
       <c r="G72" t="n">
         <v>0.08495500039822655</v>
       </c>
       <c r="H72" t="n">
-        <v>0.2106458171229023</v>
+        <v>0.2106458171994461</v>
       </c>
       <c r="I72" t="n">
-        <v>0.3902452407206423</v>
+        <v>0.3902452407095023</v>
       </c>
       <c r="J72" t="n">
-        <v>0.03450948851818413</v>
+        <v>0.03450948849791399</v>
       </c>
       <c r="K72" t="n">
-        <v>0.3247916833722452</v>
+        <v>0.2663662166319356</v>
       </c>
       <c r="L72" t="n">
-        <v>0.4124836133381382</v>
+        <v>0.3913727454368565</v>
       </c>
       <c r="M72" t="n">
         <v>0</v>
@@ -8014,16 +8014,16 @@
         <v>0</v>
       </c>
       <c r="O72" t="n">
-        <v>4.528094939538367</v>
+        <v>4.543373877819946</v>
       </c>
       <c r="P72" t="n">
-        <v>4.500901129508024</v>
+        <v>4.497358585254873</v>
       </c>
       <c r="Q72" t="n">
-        <v>0.9568065162032868</v>
+        <v>0.9561162007394569</v>
       </c>
       <c r="R72" t="n">
-        <v>0.01186831162414009</v>
+        <v>0.01196277498651009</v>
       </c>
       <c r="S72" t="inlineStr"/>
       <c r="T72" t="inlineStr"/>
@@ -8033,38 +8033,38 @@
       <c r="X72" t="inlineStr"/>
       <c r="Y72" t="inlineStr"/>
       <c r="Z72" t="n">
-        <v>0.8752494535083658</v>
+        <v>0.8830911649878134</v>
       </c>
       <c r="AA72" t="n">
-        <v>0.01475156371906827</v>
+        <v>0.01428040411402661</v>
       </c>
       <c r="AB72" t="inlineStr"/>
       <c r="AC72" t="n">
-        <v>0.7983015200767887</v>
+        <v>0.7983088114153877</v>
       </c>
       <c r="AD72" t="n">
-        <v>0.004946910977776198</v>
+        <v>0.004946821562305755</v>
       </c>
       <c r="AE72" t="inlineStr"/>
       <c r="AF72" t="n">
-        <v>0.9507928490029101</v>
+        <v>0.9513887364444562</v>
       </c>
       <c r="AG72" t="n">
-        <v>0.006951589258913556</v>
+        <v>0.00690936997168195</v>
       </c>
       <c r="AH72" t="inlineStr"/>
       <c r="AI72" t="n">
-        <v>0.8448082008498964</v>
+        <v>0.8352209609270952</v>
       </c>
       <c r="AJ72" t="n">
-        <v>0.02029269727636362</v>
+        <v>0.02091011280270681</v>
       </c>
       <c r="AK72" t="inlineStr"/>
       <c r="AL72" t="n">
-        <v>0.8996920647228908</v>
+        <v>0.895779428219033</v>
       </c>
       <c r="AM72" t="n">
-        <v>0.001444087145549991</v>
+        <v>0.001471981940328361</v>
       </c>
       <c r="AN72" t="inlineStr"/>
     </row>
@@ -8091,25 +8091,25 @@
         <v>80.48333333333333</v>
       </c>
       <c r="F73" t="n">
-        <v>0.4426967929782777</v>
+        <v>0.4426967930157429</v>
       </c>
       <c r="G73" t="n">
         <v>0.03944423078819433</v>
       </c>
       <c r="H73" t="n">
-        <v>0.3881444762932012</v>
+        <v>0.388144476200794</v>
       </c>
       <c r="I73" t="n">
-        <v>0.1098624187784432</v>
+        <v>0.1098624188419678</v>
       </c>
       <c r="J73" t="n">
-        <v>0.01985208116188355</v>
+        <v>0.01985208115330091</v>
       </c>
       <c r="K73" t="n">
-        <v>0.08004889403840529</v>
+        <v>0.04025276581779436</v>
       </c>
       <c r="L73" t="n">
-        <v>0.08114029233833665</v>
+        <v>0.05531300081131266</v>
       </c>
       <c r="M73" t="n">
         <v>0</v>
@@ -8118,16 +8118,16 @@
         <v>0</v>
       </c>
       <c r="O73" t="n">
-        <v>4.341167164957967</v>
+        <v>4.33317781811658</v>
       </c>
       <c r="P73" t="n">
-        <v>4.328595964617172</v>
+        <v>4.324615292479916</v>
       </c>
       <c r="Q73" t="n">
-        <v>0.99396379112802</v>
+        <v>0.9936981635915378</v>
       </c>
       <c r="R73" t="n">
-        <v>0.005166950074523005</v>
+        <v>0.005279413735731034</v>
       </c>
       <c r="S73" t="inlineStr"/>
       <c r="T73" t="inlineStr"/>
@@ -8137,38 +8137,38 @@
       <c r="X73" t="inlineStr"/>
       <c r="Y73" t="inlineStr"/>
       <c r="Z73" t="n">
-        <v>0.9488331545213385</v>
+        <v>0.9483509134037805</v>
       </c>
       <c r="AA73" t="n">
-        <v>0.007766523935344358</v>
+        <v>0.007803037364015429</v>
       </c>
       <c r="AB73" t="inlineStr"/>
       <c r="AC73" t="n">
-        <v>0.6127159826583171</v>
+        <v>0.6032814013844053</v>
       </c>
       <c r="AD73" t="n">
-        <v>0.001244029882727097</v>
+        <v>0.001259091540086999</v>
       </c>
       <c r="AE73" t="inlineStr"/>
       <c r="AF73" t="n">
-        <v>0.9644744443477057</v>
+        <v>0.9605307910978553</v>
       </c>
       <c r="AG73" t="n">
-        <v>0.00632388875759245</v>
+        <v>0.006665657467192313</v>
       </c>
       <c r="AH73" t="inlineStr"/>
       <c r="AI73" t="n">
-        <v>0.8257202694666327</v>
+        <v>0.8208989497700422</v>
       </c>
       <c r="AJ73" t="n">
-        <v>0.005104321817953664</v>
+        <v>0.005174443809277187</v>
       </c>
       <c r="AK73" t="inlineStr"/>
       <c r="AL73" t="n">
-        <v>-0.07098117044569197</v>
+        <v>-0.09169008203468731</v>
       </c>
       <c r="AM73" t="n">
-        <v>0.002361078299427955</v>
+        <v>0.002383796373284529</v>
       </c>
       <c r="AN73" t="inlineStr"/>
     </row>
@@ -8195,25 +8195,25 @@
         <v>59.11538461538462</v>
       </c>
       <c r="F74" t="n">
-        <v>0.2579745442485045</v>
+        <v>0.2579745444344787</v>
       </c>
       <c r="G74" t="n">
         <v>0.05370181037064575</v>
       </c>
       <c r="H74" t="n">
-        <v>0.3841123147856094</v>
+        <v>0.384112314707</v>
       </c>
       <c r="I74" t="n">
-        <v>0.2682526027331976</v>
+        <v>0.2682526026085332</v>
       </c>
       <c r="J74" t="n">
-        <v>0.03595872786204279</v>
+        <v>0.0359587278793424</v>
       </c>
       <c r="K74" t="n">
-        <v>0.08447253447494207</v>
+        <v>0.04324396783538792</v>
       </c>
       <c r="L74" t="n">
-        <v>0.1625861978258027</v>
+        <v>0.1245895699304262</v>
       </c>
       <c r="M74" t="n">
         <v>0</v>
@@ -8222,16 +8222,16 @@
         <v>0</v>
       </c>
       <c r="O74" t="n">
-        <v>4.398896285344729</v>
+        <v>4.406169716270606</v>
       </c>
       <c r="P74" t="n">
-        <v>4.385988673786605</v>
+        <v>4.378776684910091</v>
       </c>
       <c r="Q74" t="n">
-        <v>0.9699037090616688</v>
+        <v>0.9709576560640177</v>
       </c>
       <c r="R74" t="n">
-        <v>0.008218108408320513</v>
+        <v>0.00807293042776207</v>
       </c>
       <c r="S74" t="inlineStr"/>
       <c r="T74" t="inlineStr"/>
@@ -8241,38 +8241,38 @@
       <c r="X74" t="inlineStr"/>
       <c r="Y74" t="inlineStr"/>
       <c r="Z74" t="n">
-        <v>0.8562060823726922</v>
+        <v>0.8783227389583087</v>
       </c>
       <c r="AA74" t="n">
-        <v>0.009059686722696567</v>
+        <v>0.008333887532642139</v>
       </c>
       <c r="AB74" t="inlineStr"/>
       <c r="AC74" t="n">
-        <v>0.8695764770133199</v>
+        <v>0.8632656636179096</v>
       </c>
       <c r="AD74" t="n">
-        <v>0.00120012202260546</v>
+        <v>0.001228814239389254</v>
       </c>
       <c r="AE74" t="inlineStr"/>
       <c r="AF74" t="n">
-        <v>0.8768505607842143</v>
+        <v>0.8767150766759556</v>
       </c>
       <c r="AG74" t="n">
-        <v>0.01381821252077201</v>
+        <v>0.01382581154989434</v>
       </c>
       <c r="AH74" t="inlineStr"/>
       <c r="AI74" t="n">
-        <v>0.8554129903949861</v>
+        <v>0.8542083262504001</v>
       </c>
       <c r="AJ74" t="n">
-        <v>0.007688291306134383</v>
+        <v>0.007720253359617955</v>
       </c>
       <c r="AK74" t="inlineStr"/>
       <c r="AL74" t="n">
-        <v>0.7046206439018037</v>
+        <v>0.7027191400404189</v>
       </c>
       <c r="AM74" t="n">
-        <v>0.002028667591004688</v>
+        <v>0.002035186887215867</v>
       </c>
       <c r="AN74" t="inlineStr"/>
     </row>
@@ -8299,25 +8299,25 @@
         <v>38.49019607843137</v>
       </c>
       <c r="F75" t="n">
-        <v>0.3797999037751007</v>
+        <v>0.379799903884584</v>
       </c>
       <c r="G75" t="n">
         <v>0.0824782281735924</v>
       </c>
       <c r="H75" t="n">
-        <v>0.2705342292388105</v>
+        <v>0.2705342288932795</v>
       </c>
       <c r="I75" t="n">
-        <v>0.2132258416518971</v>
+        <v>0.2132258419102607</v>
       </c>
       <c r="J75" t="n">
-        <v>0.05396179716059933</v>
+        <v>0.05396179713828334</v>
       </c>
       <c r="K75" t="n">
-        <v>0.2074205046880389</v>
+        <v>0.148541542472987</v>
       </c>
       <c r="L75" t="n">
-        <v>0.2623019147692786</v>
+        <v>0.2363112797801991</v>
       </c>
       <c r="M75" t="n">
         <v>0</v>
@@ -8326,16 +8326,16 @@
         <v>0</v>
       </c>
       <c r="O75" t="n">
-        <v>4.197065933067138</v>
+        <v>4.193647807726889</v>
       </c>
       <c r="P75" t="n">
-        <v>4.282679100501563</v>
+        <v>4.27147382243856</v>
       </c>
       <c r="Q75" t="n">
-        <v>0.9696018005531949</v>
+        <v>0.9698381187427204</v>
       </c>
       <c r="R75" t="n">
-        <v>0.006885544761191853</v>
+        <v>0.006858728134933284</v>
       </c>
       <c r="S75" t="inlineStr"/>
       <c r="T75" t="inlineStr"/>
@@ -8345,38 +8345,38 @@
       <c r="X75" t="inlineStr"/>
       <c r="Y75" t="inlineStr"/>
       <c r="Z75" t="n">
-        <v>0.897979515517643</v>
+        <v>0.898979055058998</v>
       </c>
       <c r="AA75" t="n">
-        <v>0.0114134118736275</v>
+        <v>0.011357363150794</v>
       </c>
       <c r="AB75" t="inlineStr"/>
       <c r="AC75" t="n">
-        <v>0.8477274891773257</v>
+        <v>0.8250969026943455</v>
       </c>
       <c r="AD75" t="n">
-        <v>0.002354569719791642</v>
+        <v>0.002523478159703676</v>
       </c>
       <c r="AE75" t="inlineStr"/>
       <c r="AF75" t="n">
-        <v>0.9214214556774813</v>
+        <v>0.9224145021196758</v>
       </c>
       <c r="AG75" t="n">
-        <v>0.007357059870722868</v>
+        <v>0.007310424151293011</v>
       </c>
       <c r="AH75" t="inlineStr"/>
       <c r="AI75" t="n">
-        <v>0.8717190818218886</v>
+        <v>0.873575375278968</v>
       </c>
       <c r="AJ75" t="n">
-        <v>0.006793859121008478</v>
+        <v>0.006744524623290516</v>
       </c>
       <c r="AK75" t="inlineStr"/>
       <c r="AL75" t="n">
-        <v>0.9745856468645073</v>
+        <v>0.9756068556912962</v>
       </c>
       <c r="AM75" t="n">
-        <v>0.0009802104018786931</v>
+        <v>0.000960314905190899</v>
       </c>
       <c r="AN75" t="inlineStr"/>
     </row>
@@ -8403,25 +8403,25 @@
         <v>67.76923076923077</v>
       </c>
       <c r="F76" t="n">
-        <v>0.3107335005383793</v>
+        <v>0.3107335004737291</v>
       </c>
       <c r="G76" t="n">
         <v>0.04684431472172675</v>
       </c>
       <c r="H76" t="n">
-        <v>0.5076173756922413</v>
+        <v>0.5076173757282579</v>
       </c>
       <c r="I76" t="n">
-        <v>0.1034441405229936</v>
+        <v>0.1034441405920671</v>
       </c>
       <c r="J76" t="n">
-        <v>0.03136066852465918</v>
+        <v>0.03136066848421915</v>
       </c>
       <c r="K76" t="n">
-        <v>0.02053193249929068</v>
+        <v>0.006369374384653942</v>
       </c>
       <c r="L76" t="n">
-        <v>0.02513714530450089</v>
+        <v>0.01260697175336782</v>
       </c>
       <c r="M76" t="n">
         <v>0</v>
@@ -8430,16 +8430,16 @@
         <v>0</v>
       </c>
       <c r="O76" t="n">
-        <v>4.359073637778749</v>
+        <v>4.367107331905855</v>
       </c>
       <c r="P76" t="n">
-        <v>4.318198996410679</v>
+        <v>4.315908345918082</v>
       </c>
       <c r="Q76" t="n">
-        <v>0.9931707673983977</v>
+        <v>0.9932149930396004</v>
       </c>
       <c r="R76" t="n">
-        <v>0.005185566361732481</v>
+        <v>0.005168748403702921</v>
       </c>
       <c r="S76" t="inlineStr"/>
       <c r="T76" t="inlineStr"/>
@@ -8449,38 +8449,38 @@
       <c r="X76" t="inlineStr"/>
       <c r="Y76" t="inlineStr"/>
       <c r="Z76" t="n">
-        <v>0.9367592566914024</v>
+        <v>0.9425552698477182</v>
       </c>
       <c r="AA76" t="n">
-        <v>0.007154829300932363</v>
+        <v>0.006819081649310469</v>
       </c>
       <c r="AB76" t="inlineStr"/>
       <c r="AC76" t="n">
-        <v>0.8857275813456496</v>
+        <v>0.8906621525927797</v>
       </c>
       <c r="AD76" t="n">
-        <v>0.0009320008600393794</v>
+        <v>0.000911655723827234</v>
       </c>
       <c r="AE76" t="inlineStr"/>
       <c r="AF76" t="n">
-        <v>0.9550001365592991</v>
+        <v>0.9528410443630289</v>
       </c>
       <c r="AG76" t="n">
-        <v>0.008955011398001417</v>
+        <v>0.009167325134350398</v>
       </c>
       <c r="AH76" t="inlineStr"/>
       <c r="AI76" t="n">
-        <v>0.9887224243519334</v>
+        <v>0.9886453354469567</v>
       </c>
       <c r="AJ76" t="n">
-        <v>0.0008925362862222803</v>
+        <v>0.0008955815985079947</v>
       </c>
       <c r="AK76" t="inlineStr"/>
       <c r="AL76" t="n">
-        <v>0.5683726223519512</v>
+        <v>0.566691390918177</v>
       </c>
       <c r="AM76" t="n">
-        <v>0.001183821933613324</v>
+        <v>0.001186125240722502</v>
       </c>
       <c r="AN76" t="inlineStr"/>
     </row>
@@ -8507,25 +8507,25 @@
         <v>84.83333333333333</v>
       </c>
       <c r="F77" t="n">
-        <v>0.2190992506065154</v>
+        <v>0.2190992505888929</v>
       </c>
       <c r="G77" t="n">
         <v>0.03742164842361306</v>
       </c>
       <c r="H77" t="n">
-        <v>0.4560940070375605</v>
+        <v>0.4560940072232207</v>
       </c>
       <c r="I77" t="n">
-        <v>0.2593330805653106</v>
+        <v>0.2593330804892675</v>
       </c>
       <c r="J77" t="n">
-        <v>0.02805201336700053</v>
+        <v>0.02805201327500588</v>
       </c>
       <c r="K77" t="n">
-        <v>0.03782537579660925</v>
+        <v>0.014699157934358</v>
       </c>
       <c r="L77" t="n">
-        <v>0.0810297545649466</v>
+        <v>0.04739321233627111</v>
       </c>
       <c r="M77" t="n">
         <v>0</v>
@@ -8534,16 +8534,16 @@
         <v>0</v>
       </c>
       <c r="O77" t="n">
-        <v>4.268656568147811</v>
+        <v>4.273959898801073</v>
       </c>
       <c r="P77" t="n">
-        <v>4.245264030884003</v>
+        <v>4.239814421759615</v>
       </c>
       <c r="Q77" t="n">
-        <v>0.9704404554184087</v>
+        <v>0.9676120471436305</v>
       </c>
       <c r="R77" t="n">
-        <v>0.010309958460805</v>
+        <v>0.01079194679217427</v>
       </c>
       <c r="S77" t="inlineStr"/>
       <c r="T77" t="inlineStr"/>
@@ -8553,38 +8553,38 @@
       <c r="X77" t="inlineStr"/>
       <c r="Y77" t="inlineStr"/>
       <c r="Z77" t="n">
-        <v>0.5341118493949091</v>
+        <v>0.4533149481641617</v>
       </c>
       <c r="AA77" t="n">
-        <v>0.01243572554487824</v>
+        <v>0.01347097083709219</v>
       </c>
       <c r="AB77" t="inlineStr"/>
       <c r="AC77" t="n">
-        <v>-0.582295642587052</v>
+        <v>-0.5704224762109016</v>
       </c>
       <c r="AD77" t="n">
-        <v>0.00123012437861722</v>
+        <v>0.001225500409086378</v>
       </c>
       <c r="AE77" t="inlineStr"/>
       <c r="AF77" t="n">
-        <v>0.8994691169864605</v>
+        <v>0.8876250599523513</v>
       </c>
       <c r="AG77" t="n">
-        <v>0.01374480870856579</v>
+        <v>0.01453194307933653</v>
       </c>
       <c r="AH77" t="inlineStr"/>
       <c r="AI77" t="n">
-        <v>0.1670451556864152</v>
+        <v>0.1591295178557787</v>
       </c>
       <c r="AJ77" t="n">
-        <v>0.01362937384140957</v>
+        <v>0.0136939812661015</v>
       </c>
       <c r="AK77" t="inlineStr"/>
       <c r="AL77" t="n">
-        <v>0.8761432611718952</v>
+        <v>0.8716583729562278</v>
       </c>
       <c r="AM77" t="n">
-        <v>0.0007975862080373175</v>
+        <v>0.0008118982089698126</v>
       </c>
       <c r="AN77" t="inlineStr"/>
     </row>
@@ -8611,25 +8611,25 @@
         <v>194.7286349979082</v>
       </c>
       <c r="F78" t="n">
-        <v>0.1878797147510616</v>
+        <v>0.1878797146293589</v>
       </c>
       <c r="G78" t="n">
         <v>0.01630270337301587</v>
       </c>
       <c r="H78" t="n">
-        <v>0.486383629371598</v>
+        <v>0.48638362926571</v>
       </c>
       <c r="I78" t="n">
-        <v>0.2989072313345766</v>
+        <v>0.2989072315377535</v>
       </c>
       <c r="J78" t="n">
-        <v>0.01052672116974796</v>
+        <v>0.01052672119416169</v>
       </c>
       <c r="K78" t="n">
-        <v>0.02723295651487582</v>
+        <v>0.009272849175076056</v>
       </c>
       <c r="L78" t="n">
-        <v>0.07672500489828572</v>
+        <v>0.04508385870996436</v>
       </c>
       <c r="M78" t="n">
         <v>0</v>
@@ -8638,16 +8638,16 @@
         <v>0</v>
       </c>
       <c r="O78" t="n">
-        <v>4.413573948301897</v>
+        <v>4.409715680264562</v>
       </c>
       <c r="P78" t="n">
-        <v>4.378228133504346</v>
+        <v>4.363262961524207</v>
       </c>
       <c r="Q78" t="n">
-        <v>0.9788302541138123</v>
+        <v>0.9766505938335436</v>
       </c>
       <c r="R78" t="n">
-        <v>0.0105654922158259</v>
+        <v>0.01109608645566583</v>
       </c>
       <c r="S78" t="inlineStr"/>
       <c r="T78" t="inlineStr"/>
@@ -8657,38 +8657,38 @@
       <c r="X78" t="inlineStr"/>
       <c r="Y78" t="inlineStr"/>
       <c r="Z78" t="n">
-        <v>0.113949239312316</v>
+        <v>0.008862025101789239</v>
       </c>
       <c r="AA78" t="n">
-        <v>0.01141110164775913</v>
+        <v>0.01206883447620343</v>
       </c>
       <c r="AB78" t="inlineStr"/>
       <c r="AC78" t="n">
-        <v>0.7001184909678355</v>
+        <v>0.03827036897672387</v>
       </c>
       <c r="AD78" t="n">
-        <v>0.0006405333600049204</v>
+        <v>0.00114707920877698</v>
       </c>
       <c r="AE78" t="inlineStr"/>
       <c r="AF78" t="n">
-        <v>0.8316565248884472</v>
+        <v>0.8080364544675139</v>
       </c>
       <c r="AG78" t="n">
-        <v>0.01687303880176016</v>
+        <v>0.01801791538146744</v>
       </c>
       <c r="AH78" t="inlineStr"/>
       <c r="AI78" t="n">
-        <v>-0.2331874867252572</v>
+        <v>-0.2395043446452791</v>
       </c>
       <c r="AJ78" t="n">
-        <v>0.01169910140580508</v>
+        <v>0.01172902682715175</v>
       </c>
       <c r="AK78" t="inlineStr"/>
       <c r="AL78" t="n">
-        <v>-1.732284807928274</v>
+        <v>-1.948612323383598</v>
       </c>
       <c r="AM78" t="n">
-        <v>0.002440531274866863</v>
+        <v>0.002535305075741843</v>
       </c>
       <c r="AN78" t="inlineStr"/>
     </row>
@@ -8709,31 +8709,31 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>21</v>
+        <v>10.7</v>
       </c>
       <c r="E79" t="n">
         <v>46.1</v>
       </c>
       <c r="F79" t="n">
-        <v>0.5078749311749362</v>
+        <v>0.507874931382013</v>
       </c>
       <c r="G79" t="n">
         <v>0.06886340942740074</v>
       </c>
       <c r="H79" t="n">
-        <v>0.224536369038535</v>
+        <v>0.2245363687099741</v>
       </c>
       <c r="I79" t="n">
-        <v>0.198725290359128</v>
+        <v>0.1987252904806123</v>
       </c>
       <c r="J79" t="n">
-        <v>3.234988232153624e-17</v>
+        <v>0</v>
       </c>
       <c r="K79" t="n">
-        <v>0.2905655997701949</v>
+        <v>0.2305198222631793</v>
       </c>
       <c r="L79" t="n">
-        <v>0.3193146508064549</v>
+        <v>0.2944371202333186</v>
       </c>
       <c r="M79" t="n">
         <v>0</v>
@@ -8742,58 +8742,58 @@
         <v>0</v>
       </c>
       <c r="O79" t="n">
-        <v>4.384688376048642</v>
+        <v>4.376078257807563</v>
       </c>
       <c r="P79" t="n">
-        <v>4.414698453051978</v>
+        <v>4.375318599479638</v>
       </c>
       <c r="Q79" t="n">
-        <v>0.9815531322839578</v>
+        <v>0.9806003627502462</v>
       </c>
       <c r="R79" t="n">
-        <v>0.01997891499838656</v>
+        <v>0.02048836898984656</v>
       </c>
       <c r="S79" t="inlineStr"/>
       <c r="T79" t="n">
-        <v>0.9196623074491694</v>
+        <v>0.9150865299752611</v>
       </c>
       <c r="U79" t="n">
-        <v>0.04402501071364347</v>
+        <v>0.0452614109088064</v>
       </c>
       <c r="V79" t="inlineStr"/>
       <c r="W79" t="n">
-        <v>0.3516903794273151</v>
+        <v>0.3228512901398958</v>
       </c>
       <c r="X79" t="n">
-        <v>0.002266105277930717</v>
+        <v>0.002315959053874718</v>
       </c>
       <c r="Y79" t="inlineStr"/>
       <c r="Z79" t="n">
-        <v>0.9944839157949258</v>
+        <v>0.9970757539125313</v>
       </c>
       <c r="AA79" t="n">
-        <v>0.005804358405889685</v>
+        <v>0.004226158066282786</v>
       </c>
       <c r="AB79" t="inlineStr"/>
       <c r="AC79" t="n">
-        <v>0.5717723827826132</v>
+        <v>0.5385535671933877</v>
       </c>
       <c r="AD79" t="n">
-        <v>0.004945920136422913</v>
+        <v>0.005134171950720905</v>
       </c>
       <c r="AE79" t="inlineStr"/>
       <c r="AF79" t="n">
-        <v>0.9905129846447099</v>
+        <v>0.9910427757209966</v>
       </c>
       <c r="AG79" t="n">
-        <v>0.003125066478163995</v>
+        <v>0.003036555220087941</v>
       </c>
       <c r="AH79" t="inlineStr"/>
       <c r="AI79" t="n">
-        <v>0.8635593018077488</v>
+        <v>0.8492675055953676</v>
       </c>
       <c r="AJ79" t="n">
-        <v>0.009870716514327103</v>
+        <v>0.01037481007765759</v>
       </c>
       <c r="AK79" t="inlineStr"/>
       <c r="AL79" t="inlineStr"/>
@@ -8817,31 +8817,31 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>21</v>
+        <v>10.7</v>
       </c>
       <c r="E80" t="n">
         <v>45.1</v>
       </c>
       <c r="F80" t="n">
-        <v>0.3936300671811785</v>
+        <v>0.3936300668840204</v>
       </c>
       <c r="G80" t="n">
         <v>0.07039031429275332</v>
       </c>
       <c r="H80" t="n">
-        <v>0.3139495076888332</v>
+        <v>0.3139495080876725</v>
       </c>
       <c r="I80" t="n">
-        <v>0.2220301108372348</v>
+        <v>0.2220301107355537</v>
       </c>
       <c r="J80" t="n">
-        <v>7.592549229303372e-17</v>
+        <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>0.1624757209231998</v>
+        <v>0.1040560020796793</v>
       </c>
       <c r="L80" t="n">
-        <v>0.2461187518334399</v>
+        <v>0.2182783969412355</v>
       </c>
       <c r="M80" t="n">
         <v>0</v>
@@ -8850,58 +8850,58 @@
         <v>0</v>
       </c>
       <c r="O80" t="n">
-        <v>4.522041228329741</v>
+        <v>4.534282997629987</v>
       </c>
       <c r="P80" t="n">
-        <v>4.467278865581495</v>
+        <v>4.421241098153468</v>
       </c>
       <c r="Q80" t="n">
-        <v>0.9950344922844104</v>
+        <v>0.9952313022505453</v>
       </c>
       <c r="R80" t="n">
-        <v>0.009739621713846859</v>
+        <v>0.009544653286716316</v>
       </c>
       <c r="S80" t="inlineStr"/>
       <c r="T80" t="n">
-        <v>0.983543339462064</v>
+        <v>0.9844496798822913</v>
       </c>
       <c r="U80" t="n">
-        <v>0.02037113569480754</v>
+        <v>0.01980222784462607</v>
       </c>
       <c r="V80" t="inlineStr"/>
       <c r="W80" t="n">
-        <v>0.7897403724063593</v>
+        <v>0.7776461804996959</v>
       </c>
       <c r="X80" t="n">
-        <v>0.001226565936104548</v>
+        <v>0.001261348952731682</v>
       </c>
       <c r="Y80" t="inlineStr"/>
       <c r="Z80" t="n">
-        <v>0.998808074989621</v>
+        <v>0.9995980590174857</v>
       </c>
       <c r="AA80" t="n">
-        <v>0.002216587522656439</v>
+        <v>0.001287186754747993</v>
       </c>
       <c r="AB80" t="inlineStr"/>
       <c r="AC80" t="n">
-        <v>0.8188547743234074</v>
+        <v>0.8050772905177508</v>
       </c>
       <c r="AD80" t="n">
-        <v>0.00354124519466525</v>
+        <v>0.003673446946320415</v>
       </c>
       <c r="AE80" t="inlineStr"/>
       <c r="AF80" t="n">
-        <v>0.9865905088871375</v>
+        <v>0.9869243608870329</v>
       </c>
       <c r="AG80" t="n">
-        <v>0.006142155035295631</v>
+        <v>0.006065213454383066</v>
       </c>
       <c r="AH80" t="inlineStr"/>
       <c r="AI80" t="n">
-        <v>0.9619852004538377</v>
+        <v>0.9552178947138319</v>
       </c>
       <c r="AJ80" t="n">
-        <v>0.006387661091562089</v>
+        <v>0.006932945183578117</v>
       </c>
       <c r="AK80" t="inlineStr"/>
       <c r="AL80" t="inlineStr"/>
@@ -8925,87 +8925,87 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>21</v>
+        <v>13.7</v>
       </c>
       <c r="E81" t="n">
         <v>53.2</v>
       </c>
       <c r="F81" t="n">
-        <v>0.3868686426861032</v>
+        <v>0.386868642759827</v>
       </c>
       <c r="G81" t="n">
         <v>0.05967299200381906</v>
       </c>
       <c r="H81" t="n">
-        <v>0.2367160880230922</v>
+        <v>0.2367160880153139</v>
       </c>
       <c r="I81" t="n">
-        <v>0.3167422772869857</v>
+        <v>0.3167422772210401</v>
       </c>
       <c r="J81" t="n">
-        <v>9.901399624920571e-18</v>
+        <v>1.098340305577317e-17</v>
       </c>
       <c r="K81" t="n">
-        <v>0.2809117196549366</v>
+        <v>0.2167356659231921</v>
       </c>
       <c r="L81" t="n">
-        <v>0.2569309911902229</v>
+        <v>0.2375989149910943</v>
       </c>
       <c r="M81" t="n">
-        <v>0.01550715044127104</v>
+        <v>0.0152272853908928</v>
       </c>
       <c r="N81" t="n">
-        <v>0.0003101430088254209</v>
+        <v>0.000304545707817856</v>
       </c>
       <c r="O81" t="n">
-        <v>4.54352300571286</v>
+        <v>4.524759469348124</v>
       </c>
       <c r="P81" t="n">
-        <v>4.588441251671693</v>
+        <v>4.590078260861175</v>
       </c>
       <c r="Q81" t="n">
-        <v>0.9917981954435768</v>
+        <v>0.9929693226135287</v>
       </c>
       <c r="R81" t="n">
-        <v>0.01230753508043567</v>
+        <v>0.01139501652495114</v>
       </c>
       <c r="S81" t="inlineStr"/>
       <c r="T81" t="n">
-        <v>0.9763480632363547</v>
+        <v>0.9796790314112883</v>
       </c>
       <c r="U81" t="n">
-        <v>0.02304734062916472</v>
+        <v>0.02136287346975354</v>
       </c>
       <c r="V81" t="inlineStr"/>
       <c r="W81" t="inlineStr"/>
       <c r="X81" t="inlineStr"/>
       <c r="Y81" t="inlineStr"/>
       <c r="Z81" t="n">
-        <v>0.9798612306265722</v>
+        <v>0.9853406111387291</v>
       </c>
       <c r="AA81" t="n">
-        <v>0.009352819157074034</v>
+        <v>0.007979652987795105</v>
       </c>
       <c r="AB81" t="inlineStr"/>
       <c r="AC81" t="n">
-        <v>0.7584794322591948</v>
+        <v>0.7219759908504404</v>
       </c>
       <c r="AD81" t="n">
-        <v>0.002984228668381514</v>
+        <v>0.003201814658180689</v>
       </c>
       <c r="AE81" t="inlineStr"/>
       <c r="AF81" t="n">
-        <v>0.9655625310468964</v>
+        <v>0.9686594498017712</v>
       </c>
       <c r="AG81" t="n">
-        <v>0.005953583531188377</v>
+        <v>0.005679579035960567</v>
       </c>
       <c r="AH81" t="inlineStr"/>
       <c r="AI81" t="n">
-        <v>0.9598947322598147</v>
+        <v>0.963165175105502</v>
       </c>
       <c r="AJ81" t="n">
-        <v>0.009714483254968766</v>
+        <v>0.009309970365052576</v>
       </c>
       <c r="AK81" t="inlineStr"/>
       <c r="AL81" t="inlineStr"/>
@@ -9029,87 +9029,87 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>21</v>
+        <v>13.7</v>
       </c>
       <c r="E82" t="n">
         <v>57.4</v>
       </c>
       <c r="F82" t="n">
-        <v>0.3730456209331519</v>
+        <v>0.3730456210575596</v>
       </c>
       <c r="G82" t="n">
         <v>0.05530667551573475</v>
       </c>
       <c r="H82" t="n">
-        <v>0.261472183194441</v>
+        <v>0.2614721829646628</v>
       </c>
       <c r="I82" t="n">
-        <v>0.3101755203566725</v>
+        <v>0.3101755204620427</v>
       </c>
       <c r="J82" t="n">
-        <v>1.336850539002381e-17</v>
+        <v>8.893357462748227e-17</v>
       </c>
       <c r="K82" t="n">
-        <v>0.2356503211145312</v>
+        <v>0.1711357406879873</v>
       </c>
       <c r="L82" t="n">
-        <v>0.148057751150015</v>
+        <v>0.1581572607728012</v>
       </c>
       <c r="M82" t="n">
-        <v>0.1919334392279288</v>
+        <v>0.2751723992418059</v>
       </c>
       <c r="N82" t="n">
-        <v>0.01023216588646753</v>
+        <v>0.01475816020261699</v>
       </c>
       <c r="O82" t="n">
-        <v>4.465692697328193</v>
+        <v>4.428864509341516</v>
       </c>
       <c r="P82" t="n">
-        <v>4.595172440501289</v>
+        <v>4.607098130254322</v>
       </c>
       <c r="Q82" t="n">
-        <v>0.9711553463945806</v>
+        <v>0.9768949925243907</v>
       </c>
       <c r="R82" t="n">
-        <v>0.02291066667270036</v>
+        <v>0.02050492190440902</v>
       </c>
       <c r="S82" t="inlineStr"/>
       <c r="T82" t="n">
-        <v>0.9203277336269829</v>
+        <v>0.9369701166473373</v>
       </c>
       <c r="U82" t="n">
-        <v>0.04406862808979577</v>
+        <v>0.03919667216920426</v>
       </c>
       <c r="V82" t="inlineStr"/>
       <c r="W82" t="inlineStr"/>
       <c r="X82" t="inlineStr"/>
       <c r="Y82" t="inlineStr"/>
       <c r="Z82" t="n">
-        <v>0.9500201927113195</v>
+        <v>0.9668594510816959</v>
       </c>
       <c r="AA82" t="n">
-        <v>0.01496924644805508</v>
+        <v>0.01218940477175306</v>
       </c>
       <c r="AB82" t="inlineStr"/>
       <c r="AC82" t="n">
-        <v>0.3195872818241132</v>
+        <v>0.3819280960813224</v>
       </c>
       <c r="AD82" t="n">
-        <v>0.002420975949937057</v>
+        <v>0.002307404656842083</v>
       </c>
       <c r="AE82" t="inlineStr"/>
       <c r="AF82" t="n">
-        <v>0.7238868540660283</v>
+        <v>0.7377419672811794</v>
       </c>
       <c r="AG82" t="n">
-        <v>0.01890441831567093</v>
+        <v>0.01842401063415728</v>
       </c>
       <c r="AH82" t="inlineStr"/>
       <c r="AI82" t="n">
-        <v>0.9659246342608525</v>
+        <v>0.9740206139047682</v>
       </c>
       <c r="AJ82" t="n">
-        <v>0.009753602390630785</v>
+        <v>0.008516462270326678</v>
       </c>
       <c r="AK82" t="inlineStr"/>
       <c r="AL82" t="inlineStr"/>
@@ -9133,29 +9133,29 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>21</v>
+        <v>9.1</v>
       </c>
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="n">
-        <v>0.3465778704093958</v>
+        <v>0.3465778699121797</v>
       </c>
       <c r="G83" t="n">
-        <v>0.07437667461883628</v>
+        <v>0.07437667876585422</v>
       </c>
       <c r="H83" t="n">
-        <v>0.2955634795127128</v>
+        <v>0.2955634788718243</v>
       </c>
       <c r="I83" t="n">
-        <v>0.2811992414815186</v>
+        <v>0.2811992393986867</v>
       </c>
       <c r="J83" t="n">
-        <v>0.002282733977536599</v>
+        <v>0.002282733051455125</v>
       </c>
       <c r="K83" t="n">
-        <v>0.1900383461359677</v>
+        <v>0.1274211052633809</v>
       </c>
       <c r="L83" t="n">
-        <v>0.1856317839407446</v>
+        <v>0.159579580816888</v>
       </c>
       <c r="M83" t="n">
         <v>0</v>
@@ -9164,54 +9164,54 @@
         <v>0</v>
       </c>
       <c r="O83" t="n">
-        <v>4.580927191812872</v>
+        <v>4.571265893551568</v>
       </c>
       <c r="P83" t="n">
-        <v>4.571235328818583</v>
+        <v>4.569184206748631</v>
       </c>
       <c r="Q83" t="n">
-        <v>0.9757404407581288</v>
+        <v>0.9748948897595334</v>
       </c>
       <c r="R83" t="n">
-        <v>0.01864765519030246</v>
+        <v>0.01896984765791054</v>
       </c>
       <c r="S83" t="inlineStr"/>
       <c r="T83" t="n">
-        <v>0.9249197679761967</v>
+        <v>0.9217262055168085</v>
       </c>
       <c r="U83" t="n">
-        <v>0.03551167767854237</v>
+        <v>0.03625906333452</v>
       </c>
       <c r="V83" t="inlineStr"/>
       <c r="W83" t="inlineStr"/>
       <c r="X83" t="inlineStr"/>
       <c r="Y83" t="inlineStr"/>
       <c r="Z83" t="n">
-        <v>0.9595537246507585</v>
+        <v>0.9578638381404871</v>
       </c>
       <c r="AA83" t="n">
-        <v>0.009697847508947198</v>
+        <v>0.009898367399192004</v>
       </c>
       <c r="AB83" t="inlineStr"/>
       <c r="AC83" t="n">
-        <v>0.2748498321819083</v>
+        <v>0.2525032063413997</v>
       </c>
       <c r="AD83" t="n">
-        <v>0.009517551833251826</v>
+        <v>0.009663088427794949</v>
       </c>
       <c r="AE83" t="inlineStr"/>
       <c r="AF83" t="n">
-        <v>0.9182823089316973</v>
+        <v>0.9166668486835614</v>
       </c>
       <c r="AG83" t="n">
-        <v>0.0109736207374806</v>
+        <v>0.01108155748789063</v>
       </c>
       <c r="AH83" t="inlineStr"/>
       <c r="AI83" t="n">
-        <v>0.87585213908829</v>
+        <v>0.8773929954311899</v>
       </c>
       <c r="AJ83" t="n">
-        <v>0.0131355844042773</v>
+        <v>0.01305381382718253</v>
       </c>
       <c r="AK83" t="inlineStr"/>
       <c r="AL83" t="inlineStr"/>
@@ -9235,29 +9235,29 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>21</v>
+        <v>9.1</v>
       </c>
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="n">
-        <v>0.4410213099976569</v>
+        <v>0.4410213107040933</v>
       </c>
       <c r="G84" t="n">
-        <v>0.0196358885772423</v>
+        <v>0.01963588269307707</v>
       </c>
       <c r="H84" t="n">
-        <v>0.3091324863805823</v>
+        <v>0.3091324872855457</v>
       </c>
       <c r="I84" t="n">
-        <v>0.2286307167377633</v>
+        <v>0.2286307196912758</v>
       </c>
       <c r="J84" t="n">
-        <v>0.001579598306755124</v>
+        <v>0.001579599626008144</v>
       </c>
       <c r="K84" t="n">
-        <v>0.1700871734410854</v>
+        <v>0.1109470721818669</v>
       </c>
       <c r="L84" t="n">
-        <v>0.230632505156051</v>
+        <v>0.2280459734205627</v>
       </c>
       <c r="M84" t="n">
         <v>0</v>
@@ -9266,54 +9266,54 @@
         <v>0</v>
       </c>
       <c r="O84" t="n">
-        <v>4.554043371413063</v>
+        <v>4.586544133145753</v>
       </c>
       <c r="P84" t="n">
-        <v>4.502795030495846</v>
+        <v>4.494727715007937</v>
       </c>
       <c r="Q84" t="n">
-        <v>0.9948887639565135</v>
+        <v>0.989965360901395</v>
       </c>
       <c r="R84" t="n">
-        <v>0.008395638170334084</v>
+        <v>0.01176363724853049</v>
       </c>
       <c r="S84" t="inlineStr"/>
       <c r="T84" t="n">
-        <v>0.9920505547613314</v>
+        <v>0.9840583522801022</v>
       </c>
       <c r="U84" t="n">
-        <v>0.01192481307821156</v>
+        <v>0.01688689383730707</v>
       </c>
       <c r="V84" t="inlineStr"/>
       <c r="W84" t="inlineStr"/>
       <c r="X84" t="inlineStr"/>
       <c r="Y84" t="inlineStr"/>
       <c r="Z84" t="n">
-        <v>0.9949403542211152</v>
+        <v>0.9913303141936692</v>
       </c>
       <c r="AA84" t="n">
-        <v>0.00485279159118447</v>
+        <v>0.006352333109818426</v>
       </c>
       <c r="AB84" t="inlineStr"/>
       <c r="AC84" t="n">
-        <v>0.26012084473174</v>
+        <v>0.08148706545592155</v>
       </c>
       <c r="AD84" t="n">
-        <v>0.007787586637965768</v>
+        <v>0.008676911929500451</v>
       </c>
       <c r="AE84" t="inlineStr"/>
       <c r="AF84" t="n">
-        <v>0.9283595202945578</v>
+        <v>0.8296384584276383</v>
       </c>
       <c r="AG84" t="n">
-        <v>0.01103116421793434</v>
+        <v>0.01701092343445331</v>
       </c>
       <c r="AH84" t="inlineStr"/>
       <c r="AI84" t="n">
-        <v>0.9958075410492805</v>
+        <v>0.9983266529600704</v>
       </c>
       <c r="AJ84" t="n">
-        <v>0.002085631465824958</v>
+        <v>0.001317638205030274</v>
       </c>
       <c r="AK84" t="inlineStr"/>
       <c r="AL84" t="inlineStr"/>
@@ -9337,29 +9337,31 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>21</v>
-      </c>
-      <c r="E85" t="inlineStr"/>
+        <v>10.7</v>
+      </c>
+      <c r="E85" t="n">
+        <v>46.1</v>
+      </c>
       <c r="F85" t="n">
-        <v>0.5131512316840431</v>
+        <v>0.510053670891675</v>
       </c>
       <c r="G85" t="n">
-        <v>6.514458245503142e-16</v>
+        <v>0.06886340942740074</v>
       </c>
       <c r="H85" t="n">
-        <v>0.2632803536988662</v>
+        <v>0.2213241491814443</v>
       </c>
       <c r="I85" t="n">
-        <v>0.2235684146170903</v>
+        <v>0.19975877049948</v>
       </c>
       <c r="J85" t="n">
-        <v>0</v>
+        <v>2.168404344971009e-17</v>
       </c>
       <c r="K85" t="n">
-        <v>0.234087371719241</v>
+        <v>0.2332956893959356</v>
       </c>
       <c r="L85" t="n">
-        <v>0.2801892349008259</v>
+        <v>0.256747815056807</v>
       </c>
       <c r="M85" t="n">
         <v>0</v>
@@ -9368,54 +9370,54 @@
         <v>0</v>
       </c>
       <c r="O85" t="n">
-        <v>4.488615918273156</v>
+        <v>4.323756426548535</v>
       </c>
       <c r="P85" t="n">
-        <v>4.486831162584882</v>
+        <v>4.388006981668388</v>
       </c>
       <c r="Q85" t="n">
-        <v>0.9818367647150974</v>
+        <v>0.9914277545313992</v>
       </c>
       <c r="R85" t="n">
-        <v>0.01684313277916491</v>
+        <v>0.01171263100708735</v>
       </c>
       <c r="S85" t="inlineStr"/>
       <c r="T85" t="n">
-        <v>0.9556639838304075</v>
+        <v>0.972423715441383</v>
       </c>
       <c r="U85" t="n">
-        <v>0.02703215146365415</v>
+        <v>0.02343702495212267</v>
       </c>
       <c r="V85" t="inlineStr"/>
       <c r="W85" t="inlineStr"/>
       <c r="X85" t="inlineStr"/>
       <c r="Y85" t="inlineStr"/>
       <c r="Z85" t="n">
-        <v>0.9930839207702232</v>
+        <v>0.9946332173138098</v>
       </c>
       <c r="AA85" t="n">
-        <v>0.006408754386141705</v>
+        <v>0.005958471367620098</v>
       </c>
       <c r="AB85" t="inlineStr"/>
       <c r="AC85" t="n">
-        <v>-0.17773506303766</v>
+        <v>0.5054935831298185</v>
       </c>
       <c r="AD85" t="n">
-        <v>0.01695864834316122</v>
+        <v>0.005600797017149213</v>
       </c>
       <c r="AE85" t="inlineStr"/>
       <c r="AF85" t="n">
-        <v>0.6562344056870232</v>
+        <v>0.9503707123380436</v>
       </c>
       <c r="AG85" t="n">
-        <v>0.01893694208448688</v>
+        <v>0.006851009482500486</v>
       </c>
       <c r="AH85" t="inlineStr"/>
       <c r="AI85" t="n">
-        <v>0.9994565910971632</v>
+        <v>0.9650532100160338</v>
       </c>
       <c r="AJ85" t="n">
-        <v>0.0006653829039369449</v>
+        <v>0.00477764039449726</v>
       </c>
       <c r="AK85" t="inlineStr"/>
       <c r="AL85" t="inlineStr"/>
@@ -9439,29 +9441,31 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>21</v>
-      </c>
-      <c r="E86" t="inlineStr"/>
+        <v>10.7</v>
+      </c>
+      <c r="E86" t="n">
+        <v>45.1</v>
+      </c>
       <c r="F86" t="n">
-        <v>0.3947553823403973</v>
+        <v>0.3945200239537214</v>
       </c>
       <c r="G86" t="n">
-        <v>0.0245670665763035</v>
+        <v>0.07039031429275332</v>
       </c>
       <c r="H86" t="n">
-        <v>0.3466305638791009</v>
+        <v>0.3115441195160394</v>
       </c>
       <c r="I86" t="n">
-        <v>0.2327646937884924</v>
+        <v>0.2235455422374857</v>
       </c>
       <c r="J86" t="n">
-        <v>0.001282293415705915</v>
+        <v>4.155543639229597e-17</v>
       </c>
       <c r="K86" t="n">
-        <v>0.1246919775437176</v>
+        <v>0.1064698714707798</v>
       </c>
       <c r="L86" t="n">
-        <v>0.1551042893757214</v>
+        <v>0.1908591283697716</v>
       </c>
       <c r="M86" t="n">
         <v>0</v>
@@ -9470,54 +9474,54 @@
         <v>0</v>
       </c>
       <c r="O86" t="n">
-        <v>4.567691173450372</v>
+        <v>4.52106968442537</v>
       </c>
       <c r="P86" t="n">
-        <v>4.512783918100642</v>
+        <v>4.434878396731823</v>
       </c>
       <c r="Q86" t="n">
-        <v>0.9909039273174141</v>
+        <v>0.9930133210035428</v>
       </c>
       <c r="R86" t="n">
-        <v>0.01137490837087109</v>
+        <v>0.01039652552741771</v>
       </c>
       <c r="S86" t="inlineStr"/>
       <c r="T86" t="n">
-        <v>0.9863386789774761</v>
+        <v>0.9824451100680783</v>
       </c>
       <c r="U86" t="n">
-        <v>0.01624672726569851</v>
+        <v>0.0206057920671333</v>
       </c>
       <c r="V86" t="inlineStr"/>
       <c r="W86" t="inlineStr"/>
       <c r="X86" t="inlineStr"/>
       <c r="Y86" t="inlineStr"/>
       <c r="Z86" t="n">
-        <v>0.9964264413668207</v>
+        <v>0.9988764993655422</v>
       </c>
       <c r="AA86" t="n">
-        <v>0.003477268628531569</v>
+        <v>0.002131626476374783</v>
       </c>
       <c r="AB86" t="inlineStr"/>
       <c r="AC86" t="n">
-        <v>-0.3971742526560873</v>
+        <v>0.7269071225521778</v>
       </c>
       <c r="AD86" t="n">
-        <v>0.01769304384414355</v>
+        <v>0.00439255624001767</v>
       </c>
       <c r="AE86" t="inlineStr"/>
       <c r="AF86" t="n">
-        <v>0.9870512751829403</v>
+        <v>0.9721423745242257</v>
       </c>
       <c r="AG86" t="n">
-        <v>0.005817777186068403</v>
+        <v>0.008725374196155815</v>
       </c>
       <c r="AH86" t="inlineStr"/>
       <c r="AI86" t="n">
-        <v>0.977272647402363</v>
+        <v>0.9853925344698127</v>
       </c>
       <c r="AJ86" t="n">
-        <v>0.004899472054219723</v>
+        <v>0.003983655592275062</v>
       </c>
       <c r="AK86" t="inlineStr"/>
       <c r="AL86" t="inlineStr"/>
@@ -9541,85 +9545,87 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>21</v>
-      </c>
-      <c r="E87" t="inlineStr"/>
+        <v>13.7</v>
+      </c>
+      <c r="E87" t="n">
+        <v>57.4</v>
+      </c>
       <c r="F87" t="n">
-        <v>0.3717923415656336</v>
+        <v>0.3694757755244492</v>
       </c>
       <c r="G87" t="n">
-        <v>0</v>
+        <v>0.05530667551573475</v>
       </c>
       <c r="H87" t="n">
-        <v>0.3014084132402625</v>
+        <v>0.2674527900009642</v>
       </c>
       <c r="I87" t="n">
-        <v>0.3267992451941039</v>
+        <v>0.3077647589588519</v>
       </c>
       <c r="J87" t="n">
-        <v>1.327388309752159e-16</v>
+        <v>2.355429219724758e-17</v>
       </c>
       <c r="K87" t="n">
-        <v>0.1836947289226107</v>
+        <v>0.1614792491899684</v>
       </c>
       <c r="L87" t="n">
-        <v>0.2688491759473688</v>
+        <v>0.149644250995634</v>
       </c>
       <c r="M87" t="n">
-        <v>0</v>
+        <v>0.1410007172680899</v>
       </c>
       <c r="N87" t="n">
-        <v>0</v>
+        <v>0.003763217600936051</v>
       </c>
       <c r="O87" t="n">
-        <v>4.672696706020264</v>
+        <v>4.414995507077074</v>
       </c>
       <c r="P87" t="n">
-        <v>4.6165916632368</v>
+        <v>4.605453393790907</v>
       </c>
       <c r="Q87" t="n">
-        <v>0.9489770484239606</v>
+        <v>0.9753204293812853</v>
       </c>
       <c r="R87" t="n">
-        <v>0.02532277196970733</v>
+        <v>0.02100820451800525</v>
       </c>
       <c r="S87" t="inlineStr"/>
       <c r="T87" t="n">
-        <v>0.8878462413202373</v>
+        <v>0.9418515732983006</v>
       </c>
       <c r="U87" t="n">
-        <v>0.0434237275674613</v>
+        <v>0.03977594102664</v>
       </c>
       <c r="V87" t="inlineStr"/>
       <c r="W87" t="inlineStr"/>
       <c r="X87" t="inlineStr"/>
       <c r="Y87" t="inlineStr"/>
       <c r="Z87" t="n">
-        <v>0.8462727822444029</v>
+        <v>0.9707920803425326</v>
       </c>
       <c r="AA87" t="n">
-        <v>0.02191366823242608</v>
+        <v>0.01172282182781995</v>
       </c>
       <c r="AB87" t="inlineStr"/>
       <c r="AC87" t="n">
-        <v>0.6242750973345792</v>
+        <v>0.6243379596211738</v>
       </c>
       <c r="AD87" t="n">
-        <v>0.00718491791843408</v>
+        <v>0.002397766943216386</v>
       </c>
       <c r="AE87" t="inlineStr"/>
       <c r="AF87" t="n">
-        <v>0.4004281704486305</v>
+        <v>0.7520442077030332</v>
       </c>
       <c r="AG87" t="n">
-        <v>0.02735831935623596</v>
+        <v>0.01989859629295367</v>
       </c>
       <c r="AH87" t="inlineStr"/>
       <c r="AI87" t="n">
-        <v>0.9840846440822304</v>
+        <v>0.9713295325670214</v>
       </c>
       <c r="AJ87" t="n">
-        <v>0.006346987190991339</v>
+        <v>0.00924498936971779</v>
       </c>
       <c r="AK87" t="inlineStr"/>
       <c r="AL87" t="inlineStr"/>
@@ -9643,85 +9649,87 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>21</v>
-      </c>
-      <c r="E88" t="inlineStr"/>
+        <v>13.7</v>
+      </c>
+      <c r="E88" t="n">
+        <v>53.2</v>
+      </c>
       <c r="F88" t="n">
-        <v>0.3917057203335357</v>
+        <v>0.3890440313612025</v>
       </c>
       <c r="G88" t="n">
-        <v>0</v>
+        <v>0.05967299200381906</v>
       </c>
       <c r="H88" t="n">
-        <v>0.2685425476164555</v>
+        <v>0.2320759063377122</v>
       </c>
       <c r="I88" t="n">
-        <v>0.3397517320500086</v>
+        <v>0.3192070702972664</v>
       </c>
       <c r="J88" t="n">
-        <v>1.912261794240524e-16</v>
+        <v>2.419504177564497e-17</v>
       </c>
       <c r="K88" t="n">
-        <v>0.2272428571521708</v>
+        <v>0.2251944037531621</v>
       </c>
       <c r="L88" t="n">
-        <v>0.1651873530295883</v>
+        <v>0.2468144694350737</v>
       </c>
       <c r="M88" t="n">
-        <v>0</v>
+        <v>0.1593656024735453</v>
       </c>
       <c r="N88" t="n">
-        <v>0</v>
+        <v>0.007016910736438933</v>
       </c>
       <c r="O88" t="n">
-        <v>4.514091802725877</v>
+        <v>4.527491454904385</v>
       </c>
       <c r="P88" t="n">
-        <v>4.61723128323364</v>
+        <v>4.59359972816665</v>
       </c>
       <c r="Q88" t="n">
-        <v>0.9913494165910501</v>
+        <v>0.9907683664249969</v>
       </c>
       <c r="R88" t="n">
-        <v>0.0109046659038848</v>
+        <v>0.01292649346082227</v>
       </c>
       <c r="S88" t="inlineStr"/>
       <c r="T88" t="n">
-        <v>0.9752431053517345</v>
+        <v>0.9751975345126472</v>
       </c>
       <c r="U88" t="n">
-        <v>0.01983094465978683</v>
+        <v>0.02446996880651239</v>
       </c>
       <c r="V88" t="inlineStr"/>
       <c r="W88" t="inlineStr"/>
       <c r="X88" t="inlineStr"/>
       <c r="Y88" t="inlineStr"/>
       <c r="Z88" t="n">
-        <v>0.9852437620085113</v>
+        <v>0.9818240423284152</v>
       </c>
       <c r="AA88" t="n">
-        <v>0.006873079662333934</v>
+        <v>0.009170865543608769</v>
       </c>
       <c r="AB88" t="inlineStr"/>
       <c r="AC88" t="n">
-        <v>0.5498833804488671</v>
+        <v>0.8242119185591149</v>
       </c>
       <c r="AD88" t="n">
-        <v>0.004185006855959471</v>
+        <v>0.002569796569391669</v>
       </c>
       <c r="AE88" t="inlineStr"/>
       <c r="AF88" t="n">
-        <v>0.9655160293539473</v>
+        <v>0.9675023228934064</v>
       </c>
       <c r="AG88" t="n">
-        <v>0.005535002930686352</v>
+        <v>0.005897508517579566</v>
       </c>
       <c r="AH88" t="inlineStr"/>
       <c r="AI88" t="n">
-        <v>0.948953489190605</v>
+        <v>0.9567736311068908</v>
       </c>
       <c r="AJ88" t="n">
-        <v>0.01029089706513912</v>
+        <v>0.0105452622835937</v>
       </c>
       <c r="AK88" t="inlineStr"/>
       <c r="AL88" t="inlineStr"/>
@@ -9745,85 +9753,85 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>21</v>
+        <v>22.9</v>
       </c>
       <c r="E89" t="inlineStr"/>
       <c r="F89" t="n">
-        <v>0.468689526729295</v>
+        <v>0.4686895267262085</v>
       </c>
       <c r="G89" t="n">
-        <v>3.650881409255485e-16</v>
+        <v>2.428629807026475e-16</v>
       </c>
       <c r="H89" t="n">
-        <v>0.1956707823068736</v>
+        <v>0.1956707823126708</v>
       </c>
       <c r="I89" t="n">
-        <v>0.335639690963831</v>
+        <v>0.3356396909611205</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
       </c>
       <c r="K89" t="n">
-        <v>0.3475847711320364</v>
+        <v>0.2890984163093071</v>
       </c>
       <c r="L89" t="n">
-        <v>0.3219291007459254</v>
+        <v>0.2888790543618703</v>
       </c>
       <c r="M89" t="n">
-        <v>0.06172363439144923</v>
+        <v>0</v>
       </c>
       <c r="N89" t="n">
-        <v>0.001234472687828985</v>
+        <v>0</v>
       </c>
       <c r="O89" t="n">
-        <v>4.486632846602943</v>
+        <v>4.444533319955882</v>
       </c>
       <c r="P89" t="n">
-        <v>4.608423456168605</v>
+        <v>4.57504034731476</v>
       </c>
       <c r="Q89" t="n">
-        <v>0.9957171218059206</v>
+        <v>0.994066732885488</v>
       </c>
       <c r="R89" t="n">
-        <v>0.007744597041355554</v>
+        <v>0.009115445839784918</v>
       </c>
       <c r="S89" t="inlineStr"/>
       <c r="T89" t="n">
-        <v>0.9942343058906028</v>
+        <v>0.9878613236536845</v>
       </c>
       <c r="U89" t="n">
-        <v>0.01037691541133552</v>
+        <v>0.01505664266841187</v>
       </c>
       <c r="V89" t="inlineStr"/>
       <c r="W89" t="inlineStr"/>
       <c r="X89" t="inlineStr"/>
       <c r="Y89" t="inlineStr"/>
       <c r="Z89" t="n">
-        <v>0.995288873412944</v>
+        <v>0.9980386454176159</v>
       </c>
       <c r="AA89" t="n">
-        <v>0.005230713041086837</v>
+        <v>0.003375021669705757</v>
       </c>
       <c r="AB89" t="inlineStr"/>
       <c r="AC89" t="n">
-        <v>0.7649954660437221</v>
+        <v>0.6691736076116103</v>
       </c>
       <c r="AD89" t="n">
-        <v>0.004698001596208661</v>
+        <v>0.005574104075989573</v>
       </c>
       <c r="AE89" t="inlineStr"/>
       <c r="AF89" t="n">
-        <v>0.9803471441415109</v>
+        <v>0.9808667429012036</v>
       </c>
       <c r="AG89" t="n">
-        <v>0.0034059987940385</v>
+        <v>0.003360671869598569</v>
       </c>
       <c r="AH89" t="inlineStr"/>
       <c r="AI89" t="n">
-        <v>0.9366535539697193</v>
+        <v>0.9348100546518638</v>
       </c>
       <c r="AJ89" t="n">
-        <v>0.01145343343760667</v>
+        <v>0.01161889637228777</v>
       </c>
       <c r="AK89" t="inlineStr"/>
       <c r="AL89" t="inlineStr"/>
@@ -9849,83 +9857,87 @@
       <c r="D90" t="n">
         <v>12.8</v>
       </c>
-      <c r="E90" t="inlineStr"/>
+      <c r="E90" t="n">
+        <v>30.13605442176871</v>
+      </c>
       <c r="F90" t="n">
-        <v>0.6963378304438156</v>
+        <v>0.6739262842370797</v>
       </c>
       <c r="G90" t="n">
-        <v>0.06121827372612768</v>
+        <v>0.1053423626787058</v>
       </c>
       <c r="H90" t="n">
-        <v>0.04157121397092656</v>
+        <v>0.01105388716074765</v>
       </c>
       <c r="I90" t="n">
-        <v>0.1708251520974169</v>
+        <v>0.1819763294359777</v>
       </c>
       <c r="J90" t="n">
-        <v>0.03004752976171331</v>
+        <v>0.02770113648748916</v>
       </c>
       <c r="K90" t="n">
-        <v>0.559419327333303</v>
+        <v>0.5773718555675572</v>
       </c>
       <c r="L90" t="n">
-        <v>0.5228129052136478</v>
+        <v>0.5406742979289718</v>
       </c>
       <c r="M90" t="n">
-        <v>0.6569645775186483</v>
+        <v>0.2250110776348216</v>
       </c>
       <c r="N90" t="n">
-        <v>0.125351088660468</v>
+        <v>0.0107775695857306</v>
       </c>
       <c r="O90" t="n">
-        <v>4.527214580177771</v>
+        <v>4.57712737558739</v>
       </c>
       <c r="P90" t="n">
-        <v>4.271620727012309</v>
+        <v>4.295763458017572</v>
       </c>
       <c r="Q90" t="n">
-        <v>0.9896098720581251</v>
+        <v>0.9848104106211899</v>
       </c>
       <c r="R90" t="n">
-        <v>0.0134787691528249</v>
+        <v>0.01463296932642435</v>
       </c>
       <c r="S90" t="inlineStr"/>
       <c r="T90" t="n">
-        <v>0.9807444152220886</v>
+        <v>0.966665969169721</v>
       </c>
       <c r="U90" t="n">
-        <v>0.02247316513712744</v>
+        <v>0.02659039614368586</v>
       </c>
       <c r="V90" t="inlineStr"/>
       <c r="W90" t="inlineStr"/>
-      <c r="X90" t="inlineStr"/>
+      <c r="X90" t="n">
+        <v>5.204170427930421e-18</v>
+      </c>
       <c r="Y90" t="inlineStr"/>
       <c r="Z90" t="n">
-        <v>0.9878716595717181</v>
+        <v>0.9895636957671802</v>
       </c>
       <c r="AA90" t="n">
-        <v>0.01422675166769076</v>
+        <v>0.01110161350043567</v>
       </c>
       <c r="AB90" t="inlineStr"/>
       <c r="AC90" t="n">
-        <v>0.8296037825163912</v>
+        <v>0.8667998579748101</v>
       </c>
       <c r="AD90" t="n">
-        <v>0.004703019724144339</v>
+        <v>0.005674718824038234</v>
       </c>
       <c r="AE90" t="inlineStr"/>
       <c r="AF90" t="n">
-        <v>0.9948889173041052</v>
+        <v>0.954751585638985</v>
       </c>
       <c r="AG90" t="n">
-        <v>0.0005445359893933593</v>
+        <v>0.0007022578934415615</v>
       </c>
       <c r="AH90" t="inlineStr"/>
       <c r="AI90" t="n">
-        <v>0.9843216885672784</v>
+        <v>0.9844630719359052</v>
       </c>
       <c r="AJ90" t="n">
-        <v>0.004104216662021562</v>
+        <v>0.00383361803136025</v>
       </c>
       <c r="AK90" t="inlineStr"/>
       <c r="AL90" t="inlineStr"/>
